--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R56898c6699a74ccf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc43becb156d24643"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra5922813d5724096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R3d45c7c4a72c487a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbeae6323fe1f419a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R330a06df58b44f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Re53ffa40d3944d50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R9f64e45653664b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re2ea4b670cde4afc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rcb46d78ea223460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R8c150820fcc240f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1cb42a4d53ff435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re480ee3285d246c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rb268bd454de942a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R7ffa1907cf4c4a65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R9563ac501ea347b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0ce0dcf63d454d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R778185cb68184d13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3396715f5a0e428b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf820dfc847544dd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7fe1decee3c74044"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R582f602ce72043c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R049a2de5ff544b2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R2f2108adf5bf435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1496fb0c26b84e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R92f31c3cd0c742d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Redf8776483324dae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4205d0d97ff145b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Raa399de560fd4915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbc8329c095d945d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra25cadda5a4c44d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1b9d19fa04804f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R40459d660d5a4b5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R89d02afe67364022"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Raf3b5466b4264de1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R543c38dc47c043c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R9c8f8da0192c4d46"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2ea3a61ba2c44e6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2d2dd9e522544b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R973ecf3b4d294334"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -74,90 +74,28 @@
   <x:borders count="24">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -455,329 +393,329 @@
   <x:dxfs count="47">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFD9EAD3"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFF4CCCC"/>
         </x:patternFill>
       </x:fill>
@@ -844,9 +782,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="48672768"/>
-        <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="48672768"/>
@@ -915,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R975b47dee67047a3"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d379b08b806467d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1971,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R985eba3a13ef42a8"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2a0e671e0d4345"/>
 </x:worksheet>
 </file>
 
@@ -10099,7 +10035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c0ad1df17b04ede"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b758eba156f4ad7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11284,7 +11220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eaa742131a941e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ccc5076f2d5436b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24788,7 +24724,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0018ff9a82e48ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc698e6ebf750461a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24890,9 +24826,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M2" s="80" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M2" s="80" t="str">
+        <x:v>PROJECT_PLAN.md#task-gov-001</x:v>
+      </x:c>
       <x:c r="N2" s="82" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43475,7 +43413,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R37d7d187b7bc4445"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9896e03c63aa4e57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43747,7 +43685,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6e7796c3d9664593"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35511cbbeec74154"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45163,7 +45101,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9d0081dcb504352"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c935b3f0444242"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45559,7 +45497,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb28e684765d54cfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2301be3a04e4fdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48846,7 +48784,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eaaf03ed2e048dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f0a1cfc0f1d4a23"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7fe1decee3c74044"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R582f602ce72043c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R049a2de5ff544b2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R2f2108adf5bf435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1496fb0c26b84e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R92f31c3cd0c742d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Redf8776483324dae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4205d0d97ff145b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Raa399de560fd4915"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbc8329c095d945d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra25cadda5a4c44d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1b9d19fa04804f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R40459d660d5a4b5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R89d02afe67364022"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Raf3b5466b4264de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R543c38dc47c043c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R9c8f8da0192c4d46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2ea3a61ba2c44e6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2d2dd9e522544b6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R973ecf3b4d294334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R26efad16727c4485"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra1d490962cd947f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9e55318227c54d8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R22d4ebef970640de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd9293fe2a520447a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7a9e6bbad64e4753"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R20248324e71b43ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra6d91d3bcfca49f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rab082d8330ce46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4a89e679d39e4356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R782975c8f9374feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R20bfcaf9f80a4130"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re27761784738403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc20d934b23034621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd00d2c0d9ec44c07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6c891b97ed8a42ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1829e33eca6b4e04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra4549cd504be45e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rdb278d9cb262451d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf6f27a7f859840e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d379b08b806467d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f55c63c6d614b17"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1325,11 +1325,11 @@
       </x:c>
       <x:c r="E5" s="80" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A5,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="81" t="n">
         <x:f>IF(B5=0,0,E5/B5)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.1</x:v>
       </x:c>
       <x:c r="G5" s="80" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad2a0e671e0d4345"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bc363cf3c214d7a"/>
 </x:worksheet>
 </file>
 
@@ -10035,7 +10035,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b758eba156f4ad7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c180edd4419429a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10152,10 +10152,14 @@
         <x:v>GOV / SYS-001~002 / SEC</x:v>
       </x:c>
       <x:c r="G4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H4" s="84" t="str"/>
-      <x:c r="I4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H4" s="84" t="str">
+        <x:v>contracts/task-route.catalog.json</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="str">
+        <x:v>已形成 DEC-001 路由契约草案；尚无运行时路由实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -11220,7 +11224,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ccc5076f2d5436b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12ef55d1e1ab49dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11609,10 +11613,14 @@
       </x:c>
       <x:c r="M2" s="80" t="str"/>
       <x:c r="N2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O2" s="80" t="str"/>
-      <x:c r="P2" s="82" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O2" s="80" t="str">
+        <x:v>PROJECT_PLAN.md#task-gov-001</x:v>
+      </x:c>
+      <x:c r="P2" s="82" t="str">
+        <x:v>通过：308/308 需求 ID 在 DOCX 与 Excel 中均可定位；453/453 任务 ID 唯一，任务引用无孤立项。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -11651,10 +11659,14 @@
       </x:c>
       <x:c r="M3" s="84" t="str"/>
       <x:c r="N3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O3" s="84" t="str"/>
-      <x:c r="P3" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O3" s="84" t="str">
+        <x:v>contracts/task-route.catalog.json</x:v>
+      </x:c>
+      <x:c r="P3" s="86" t="str">
+        <x:v>未验证：八种模式契约与验收场景为草案；运行时路由尚未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -24724,7 +24736,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc698e6ebf750461a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra039e1b1b6f04cc9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24826,7 +24838,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L2" s="80" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M2" s="80" t="str">
         <x:v>PROJECT_PLAN.md#task-gov-001</x:v>
@@ -24868,9 +24880,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M3" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M3" s="84" t="str">
+        <x:v>contracts/task-route.catalog.json（契约草案；运行时路由尚未实现）</x:v>
+      </x:c>
       <x:c r="N3" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43413,7 +43427,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9896e03c63aa4e57"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R083b0e67fc1b4daa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43685,7 +43699,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35511cbbeec74154"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd584138f4e34587"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45101,7 +45115,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c935b3f0444242"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f8955478eaa4ff4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45497,7 +45511,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2301be3a04e4fdb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra190a294f3e14f38"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47129,7 +47143,7 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M2" s="80" t="str">
-        <x:v>未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="N2" s="82" t="str"/>
     </x:row>
@@ -48784,7 +48798,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f0a1cfc0f1d4a23"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232e90c341094359"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R26efad16727c4485"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra1d490962cd947f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9e55318227c54d8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R22d4ebef970640de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd9293fe2a520447a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7a9e6bbad64e4753"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R20248324e71b43ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra6d91d3bcfca49f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rab082d8330ce46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4a89e679d39e4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R782975c8f9374feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R20bfcaf9f80a4130"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re27761784738403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc20d934b23034621"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd00d2c0d9ec44c07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6c891b97ed8a42ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1829e33eca6b4e04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra4549cd504be45e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rdb278d9cb262451d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf6f27a7f859840e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R39349a766b674b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R235caefc03d9483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb16f16b6cd62461b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1054e5230977466b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb15e485b75e94e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc73a82640ab34d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R34282fbca7424159"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R9c0e9d50c0ab455f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R43825f0036414271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1792c5d9e0684be4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R7f43e546d0334ecc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1d526ec2f1c94bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9317773958554d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R55683e79a4cd4569"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rdf6f29631ebf4764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb9a0d0dff8674dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5afedaa70727403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra8d3ef73b6324f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R852cc80faf124203"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R25adcfb09c5c4f57"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9f55c63c6d614b17"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf93925d694f14705"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bc363cf3c214d7a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56fc1868133b461b"/>
 </x:worksheet>
 </file>
 
@@ -4958,7 +4958,7 @@
       </x:c>
       <x:c r="J4" s="86" t="str"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>ConstraintSet</x:v>
       </x:c>
@@ -4984,9 +4984,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J5" s="86" t="str">
+        <x:v>contracts/constraint-set.schema.json + fixtures（草案）；运行时校验器未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -10035,7 +10037,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c180edd4419429a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b9245e27734e5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11224,7 +11226,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12ef55d1e1ab49dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ef6d6b51604f2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11576,7 +11578,7 @@
         <x:v>验收结果</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="72" customHeight="1">
       <x:c r="A2" s="79" t="str">
         <x:v>GOV-001</x:v>
       </x:c>
@@ -11619,10 +11621,10 @@
         <x:v>PROJECT_PLAN.md#task-gov-001</x:v>
       </x:c>
       <x:c r="P2" s="82" t="str">
-        <x:v>通过：308/308 需求 ID 在 DOCX 与 Excel 中均可定位；453/453 任务 ID 唯一，任务引用无孤立项。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
+        <x:v>通过：需求ID 308/308；任务ID 453 唯一。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="72" customHeight="1">
       <x:c r="A3" s="83" t="str">
         <x:v>GOV-002</x:v>
       </x:c>
@@ -11665,10 +11667,10 @@
         <x:v>contracts/task-route.catalog.json</x:v>
       </x:c>
       <x:c r="P3" s="86" t="str">
-        <x:v>未验证：八种模式契约与验收场景为草案；运行时路由尚未实现。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
+        <x:v>未验证：八种模式契约为草案；运行时路由未实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="72" customHeight="1">
       <x:c r="A4" s="83" t="str">
         <x:v>GOV-003</x:v>
       </x:c>
@@ -11705,10 +11707,14 @@
       </x:c>
       <x:c r="M4" s="84" t="str"/>
       <x:c r="N4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O4" s="84" t="str"/>
-      <x:c r="P4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O4" s="84" t="str">
+        <x:v>contracts/constraint-set.catalog.json</x:v>
+      </x:c>
+      <x:c r="P4" s="86" t="str">
+        <x:v>未验证：约束分类/冲突示例为草案；运行时检测未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -24736,7 +24742,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra039e1b1b6f04cc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d9e069362494ea9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24805,7 +24811,7 @@
         <x:v>来源</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="79" t="str">
         <x:v>TASK-GOV-001</x:v>
       </x:c>
@@ -24847,7 +24853,7 @@
         <x:v>本规划</x:v>
       </x:c>
     </x:row>
-    <x:row r="3">
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="83" t="str">
         <x:v>TASK-GOV-002</x:v>
       </x:c>
@@ -24883,13 +24889,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M3" s="84" t="str">
-        <x:v>contracts/task-route.catalog.json（契约草案；运行时路由尚未实现）</x:v>
+        <x:v>contracts/task-route.catalog.json（草案；运行时路由未实现）</x:v>
       </x:c>
       <x:c r="N3" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
     </x:row>
-    <x:row r="4">
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="83" t="str">
         <x:v>TASK-GOV-003</x:v>
       </x:c>
@@ -24922,9 +24928,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M4" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M4" s="84" t="str">
+        <x:v>contracts/constraint-set.catalog.json（草案；运行时行为未实现）</x:v>
+      </x:c>
       <x:c r="N4" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43427,7 +43435,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R083b0e67fc1b4daa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red9a599b7b5646fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43699,7 +43707,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd584138f4e34587"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4e610f53dcc4615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45115,7 +45123,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f8955478eaa4ff4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a94ccfb0df42f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45511,7 +45519,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra190a294f3e14f38"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77d2b27da75a46c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48798,7 +48806,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R232e90c341094359"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6d1303a3074e89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R39349a766b674b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R235caefc03d9483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb16f16b6cd62461b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1054e5230977466b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb15e485b75e94e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc73a82640ab34d0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R34282fbca7424159"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R9c0e9d50c0ab455f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R43825f0036414271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1792c5d9e0684be4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R7f43e546d0334ecc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1d526ec2f1c94bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9317773958554d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R55683e79a4cd4569"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rdf6f29631ebf4764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb9a0d0dff8674dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5afedaa70727403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra8d3ef73b6324f8d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R852cc80faf124203"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R25adcfb09c5c4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0bd6a1a8a2be40c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9b4b4c9824ab49b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea58cea55fc4433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1974610ce43d4c71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3e3f69862a194884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfd6b40575a0464f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ref44475e51bf44ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Raa14d626af184afd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8b898a7d147b4273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4bf19755870c4317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0a1f709f41b245b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55a3aeeaa7324d9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf37206d613574d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R54e851f726334398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5868baec7842497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R25f747f19476486b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rfe556b50f2ba4dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb2edbd1c88bc434b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R32182337c60548cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb44a8c1df68042aa"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf93925d694f14705"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24e0e07782344063"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56fc1868133b461b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafec37e767b540fe"/>
 </x:worksheet>
 </file>
 
@@ -10037,7 +10037,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b9245e27734e5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc434d7e824a14f5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11226,7 +11226,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ef6d6b51604f2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96119fa7b19a4c92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11716,7 +11716,7 @@
         <x:v>未验证：约束分类/冲突示例为草案；运行时检测未实现。</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>GOV-004</x:v>
       </x:c>
@@ -11753,10 +11753,14 @@
       </x:c>
       <x:c r="M5" s="84" t="str"/>
       <x:c r="N5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O5" s="84" t="str"/>
-      <x:c r="P5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O5" s="84" t="str">
+        <x:v>contracts/fallback-record.catalog.json</x:v>
+      </x:c>
+      <x:c r="P5" s="86" t="str">
+        <x:v>未验证：契约草案；Trace/报告记录未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -24742,7 +24746,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d9e069362494ea9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5824a7686b6a4297"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24937,7 +24941,7 @@
         <x:v>本规划</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>TASK-GOV-004</x:v>
       </x:c>
@@ -24970,9 +24974,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M5" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M5" s="84" t="str">
+        <x:v>contracts/fallback-record.catalog.json（契约草案；运行时未实现）</x:v>
+      </x:c>
       <x:c r="N5" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43435,7 +43441,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red9a599b7b5646fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcf03d30fe7e4cb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43707,7 +43713,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4e610f53dcc4615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfef894081b94553"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45123,7 +45129,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5a94ccfb0df42f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7979cdc2cc214824"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45519,7 +45525,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77d2b27da75a46c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62c062a3a6934768"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48806,7 +48812,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb6d1303a3074e89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af1fe8e412d4be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -12051,9 +12051,11 @@
       </x:c>
       <x:c r="M12" s="84" t="str"/>
       <x:c r="N12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O12" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O12" s="84" t="str">
+        <x:v>research/P01/README.md</x:v>
+      </x:c>
       <x:c r="P12" s="86" t="str"/>
     </x:row>
     <x:row r="13">
@@ -25340,9 +25342,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M14" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M14" s="84" t="str">
+        <x:v>research/P01/README.md</x:v>
+      </x:c>
       <x:c r="N14" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43524,7 +43528,7 @@
         <x:v>MIT</x:v>
       </x:c>
       <x:c r="E2" s="80" t="str">
-        <x:v>main + 实施时 commit SHA</x:v>
+        <x:v>main；commit 2d72da616cf9fa40d4dcaf59fd4c980ecf534b7d；v6.6.0 tag 为另一提交 a50758ac29ec027e85966db33e2ae80031446756</x:v>
       </x:c>
       <x:c r="F2" s="80" t="str">
         <x:v>Generate PPTX / Create Template / Edit Native PPTX / Image-to-PPTX / Beautify / enhance</x:v>
@@ -43542,9 +43546,11 @@
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
-        <x:v>待复现</x:v>
-      </x:c>
-      <x:c r="L2" s="80" t="str"/>
+        <x:v>进行中：源码已固定；官方最小流程待复现（Docker API 无响应）</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>research/P01/README.md</x:v>
+      </x:c>
       <x:c r="M2" s="80" t="str"/>
       <x:c r="N2" s="82" t="str"/>
     </x:row>

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -23,6 +23,7 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R32182337c60548cc"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb44a8c1df68042aa"/>
   </x:sheets>
+  <x:calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </x:workbook>
 </file>
 
@@ -9638,6 +9639,26 @@
       <x:c r="E13" s="88" t="str"/>
       <x:c r="F13" s="90" t="str"/>
     </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="87" t="str">
+        <x:v>CH-013</x:v>
+      </x:c>
+      <x:c r="B14" s="88" t="str">
+        <x:v>产品范围声明</x:v>
+      </x:c>
+      <x:c r="C14" s="88" t="str">
+        <x:v>GOV-009：当前排除账号、计费、多租户、协同编辑、模板商城；CLI、API、MCP、调试入口属于系统核心要求。</x:v>
+      </x:c>
+      <x:c r="D14" s="88" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="E14" s="88" t="str">
+        <x:v>SCOPE.md；AGENTS.md</x:v>
+      </x:c>
+      <x:c r="F14" s="90" t="str">
+        <x:v>与 GOV-009 需求行、任务行保持一致。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D2:D13">
     <x:cfRule type="expression" dxfId="44" priority="1">
@@ -9645,7 +9666,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="D2:D13">
+    <x:dataValidation type="list" sqref="D2:D14">
       <x:formula1>"未开始,进行中,已完成,阻塞"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -11967,10 +11988,14 @@
       </x:c>
       <x:c r="M10" s="84" t="str"/>
       <x:c r="N10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O10" s="84" t="str"/>
-      <x:c r="P10" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O10" s="84" t="str">
+        <x:v>SCOPE.md</x:v>
+      </x:c>
+      <x:c r="P10" s="86" t="str">
+        <x:v>GOV-009 范围声明已与 AGENTS.md 和 Codex交接 CH-013 对齐。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -25262,9 +25287,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M12" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M12" s="84" t="str">
+        <x:v>SCOPE.md；AGENTS.md；Codex交接!A14:F14</x:v>
+      </x:c>
       <x:c r="N12" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -11862,10 +11862,14 @@
       </x:c>
       <x:c r="M7" s="84" t="str"/>
       <x:c r="N7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O7" s="84" t="str"/>
-      <x:c r="P7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O7" s="84" t="str">
+        <x:v>PROJECT_PLAN.md（TASK-GOV-006）；contracts/config-schema.schema.json；contracts/config-schema.catalog.json；contracts/config-schema.fixtures.json</x:v>
+      </x:c>
+      <x:c r="P7" s="86" t="str">
+        <x:v>Draft 2020-12 schema、catalog 与 pending fixture 标准校验通过；类型、默认值、范围及来源优先级待基线/DEC-004 决定；运行时有效配置 trace 未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -25167,9 +25171,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M9" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M9" s="84" t="str">
+        <x:v>PROJECT_PLAN.md（TASK-GOV-006）；contracts/config-schema.schema.json；contracts/config-schema.catalog.json；contracts/config-schema.fixtures.json</x:v>
+      </x:c>
       <x:c r="N9" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -11820,10 +11820,14 @@
       </x:c>
       <x:c r="M6" s="84" t="str"/>
       <x:c r="N6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O6" s="84" t="str"/>
-      <x:c r="P6" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O6" s="84" t="str">
+        <x:v>PROJECT_PLAN.md（TASK-GOV-005）；contracts/capability-status.schema.json；contracts/capability-status.catalog.json；contracts/capability-status.fixtures.json</x:v>
+      </x:c>
+      <x:c r="P6" s="86" t="str">
+        <x:v>PPT-001–030 × PP-01–09 共 270 状态无空白且均为 Untested；版本状态明确为未冻结；适配器实例和系统级原子能力清单及实际验证尚未完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -25089,9 +25093,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M7" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M7" s="84" t="str">
+        <x:v>PROJECT_PLAN.md（TASK-GOV-005）；contracts/capability-status.schema.json；contracts/capability-status.catalog.json；contracts/capability-status.fixtures.json</x:v>
+      </x:c>
       <x:c r="N7" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -45265,7 +45271,9 @@
       <x:c r="I2" s="80" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J2" s="80" t="str"/>
+      <x:c r="J2" s="80" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K2" s="80" t="str"/>
       <x:c r="L2" s="80" t="str"/>
       <x:c r="M2" s="80" t="str"/>
@@ -45299,7 +45307,9 @@
       <x:c r="I3" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J3" s="84" t="str"/>
+      <x:c r="J3" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K3" s="84" t="str"/>
       <x:c r="L3" s="84" t="str"/>
       <x:c r="M3" s="84" t="str"/>
@@ -45333,7 +45343,9 @@
       <x:c r="I4" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J4" s="84" t="str"/>
+      <x:c r="J4" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K4" s="84" t="str"/>
       <x:c r="L4" s="84" t="str"/>
       <x:c r="M4" s="84" t="str"/>
@@ -45367,7 +45379,9 @@
       <x:c r="I5" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J5" s="84" t="str"/>
+      <x:c r="J5" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K5" s="84" t="str"/>
       <x:c r="L5" s="84" t="str"/>
       <x:c r="M5" s="84" t="str"/>
@@ -45401,7 +45415,9 @@
       <x:c r="I6" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J6" s="84" t="str"/>
+      <x:c r="J6" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K6" s="84" t="str"/>
       <x:c r="L6" s="84" t="str"/>
       <x:c r="M6" s="84" t="str"/>
@@ -45435,7 +45451,9 @@
       <x:c r="I7" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J7" s="84" t="str"/>
+      <x:c r="J7" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K7" s="84" t="str"/>
       <x:c r="L7" s="84" t="str"/>
       <x:c r="M7" s="84" t="str"/>
@@ -45469,7 +45487,9 @@
       <x:c r="I8" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J8" s="84" t="str"/>
+      <x:c r="J8" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K8" s="84" t="str"/>
       <x:c r="L8" s="84" t="str"/>
       <x:c r="M8" s="84" t="str"/>
@@ -45503,7 +45523,9 @@
       <x:c r="I9" s="84" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J9" s="84" t="str"/>
+      <x:c r="J9" s="84" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K9" s="84" t="str"/>
       <x:c r="L9" s="84" t="str"/>
       <x:c r="M9" s="84" t="str"/>
@@ -45537,7 +45559,9 @@
       <x:c r="I10" s="88" t="str">
         <x:v>未执行</x:v>
       </x:c>
-      <x:c r="J10" s="88" t="str"/>
+      <x:c r="J10" s="88" t="str">
+        <x:v>未冻结（PoC未执行）</x:v>
+      </x:c>
       <x:c r="K10" s="88" t="str"/>
       <x:c r="L10" s="88" t="str"/>
       <x:c r="M10" s="88" t="str"/>
@@ -45683,7 +45707,9 @@
       </x:c>
       <x:c r="N2" s="80" t="str"/>
       <x:c r="O2" s="80" t="str"/>
-      <x:c r="P2" s="82" t="str"/>
+      <x:c r="P2" s="82" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -45727,7 +45753,9 @@
       </x:c>
       <x:c r="N3" s="84" t="str"/>
       <x:c r="O3" s="84" t="str"/>
-      <x:c r="P3" s="86" t="str"/>
+      <x:c r="P3" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -45771,7 +45799,9 @@
       </x:c>
       <x:c r="N4" s="84" t="str"/>
       <x:c r="O4" s="84" t="str"/>
-      <x:c r="P4" s="86" t="str"/>
+      <x:c r="P4" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -45815,7 +45845,9 @@
       </x:c>
       <x:c r="N5" s="84" t="str"/>
       <x:c r="O5" s="84" t="str"/>
-      <x:c r="P5" s="86" t="str"/>
+      <x:c r="P5" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -45859,7 +45891,9 @@
       </x:c>
       <x:c r="N6" s="84" t="str"/>
       <x:c r="O6" s="84" t="str"/>
-      <x:c r="P6" s="86" t="str"/>
+      <x:c r="P6" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -45903,7 +45937,9 @@
       </x:c>
       <x:c r="N7" s="84" t="str"/>
       <x:c r="O7" s="84" t="str"/>
-      <x:c r="P7" s="86" t="str"/>
+      <x:c r="P7" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -45947,7 +45983,9 @@
       </x:c>
       <x:c r="N8" s="84" t="str"/>
       <x:c r="O8" s="84" t="str"/>
-      <x:c r="P8" s="86" t="str"/>
+      <x:c r="P8" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -45991,7 +46029,9 @@
       </x:c>
       <x:c r="N9" s="84" t="str"/>
       <x:c r="O9" s="84" t="str"/>
-      <x:c r="P9" s="86" t="str"/>
+      <x:c r="P9" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -46035,7 +46075,9 @@
       </x:c>
       <x:c r="N10" s="84" t="str"/>
       <x:c r="O10" s="84" t="str"/>
-      <x:c r="P10" s="86" t="str"/>
+      <x:c r="P10" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -46079,7 +46121,9 @@
       </x:c>
       <x:c r="N11" s="84" t="str"/>
       <x:c r="O11" s="84" t="str"/>
-      <x:c r="P11" s="86" t="str"/>
+      <x:c r="P11" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -46123,7 +46167,9 @@
       </x:c>
       <x:c r="N12" s="84" t="str"/>
       <x:c r="O12" s="84" t="str"/>
-      <x:c r="P12" s="86" t="str"/>
+      <x:c r="P12" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -46167,7 +46213,9 @@
       </x:c>
       <x:c r="N13" s="84" t="str"/>
       <x:c r="O13" s="84" t="str"/>
-      <x:c r="P13" s="86" t="str"/>
+      <x:c r="P13" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -46211,7 +46259,9 @@
       </x:c>
       <x:c r="N14" s="84" t="str"/>
       <x:c r="O14" s="84" t="str"/>
-      <x:c r="P14" s="86" t="str"/>
+      <x:c r="P14" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -46255,7 +46305,9 @@
       </x:c>
       <x:c r="N15" s="84" t="str"/>
       <x:c r="O15" s="84" t="str"/>
-      <x:c r="P15" s="86" t="str"/>
+      <x:c r="P15" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -46299,7 +46351,9 @@
       </x:c>
       <x:c r="N16" s="84" t="str"/>
       <x:c r="O16" s="84" t="str"/>
-      <x:c r="P16" s="86" t="str"/>
+      <x:c r="P16" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -46343,7 +46397,9 @@
       </x:c>
       <x:c r="N17" s="84" t="str"/>
       <x:c r="O17" s="84" t="str"/>
-      <x:c r="P17" s="86" t="str"/>
+      <x:c r="P17" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -46387,7 +46443,9 @@
       </x:c>
       <x:c r="N18" s="84" t="str"/>
       <x:c r="O18" s="84" t="str"/>
-      <x:c r="P18" s="86" t="str"/>
+      <x:c r="P18" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="83" t="str">
@@ -46431,7 +46489,9 @@
       </x:c>
       <x:c r="N19" s="84" t="str"/>
       <x:c r="O19" s="84" t="str"/>
-      <x:c r="P19" s="86" t="str"/>
+      <x:c r="P19" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="83" t="str">
@@ -46475,7 +46535,9 @@
       </x:c>
       <x:c r="N20" s="84" t="str"/>
       <x:c r="O20" s="84" t="str"/>
-      <x:c r="P20" s="86" t="str"/>
+      <x:c r="P20" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="83" t="str">
@@ -46519,7 +46581,9 @@
       </x:c>
       <x:c r="N21" s="84" t="str"/>
       <x:c r="O21" s="84" t="str"/>
-      <x:c r="P21" s="86" t="str"/>
+      <x:c r="P21" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="83" t="str">
@@ -46563,7 +46627,9 @@
       </x:c>
       <x:c r="N22" s="84" t="str"/>
       <x:c r="O22" s="84" t="str"/>
-      <x:c r="P22" s="86" t="str"/>
+      <x:c r="P22" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -46607,7 +46673,9 @@
       </x:c>
       <x:c r="N23" s="84" t="str"/>
       <x:c r="O23" s="84" t="str"/>
-      <x:c r="P23" s="86" t="str"/>
+      <x:c r="P23" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -46651,7 +46719,9 @@
       </x:c>
       <x:c r="N24" s="84" t="str"/>
       <x:c r="O24" s="84" t="str"/>
-      <x:c r="P24" s="86" t="str"/>
+      <x:c r="P24" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="83" t="str">
@@ -46695,7 +46765,9 @@
       </x:c>
       <x:c r="N25" s="84" t="str"/>
       <x:c r="O25" s="84" t="str"/>
-      <x:c r="P25" s="86" t="str"/>
+      <x:c r="P25" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="83" t="str">
@@ -46739,7 +46811,9 @@
       </x:c>
       <x:c r="N26" s="84" t="str"/>
       <x:c r="O26" s="84" t="str"/>
-      <x:c r="P26" s="86" t="str"/>
+      <x:c r="P26" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="83" t="str">
@@ -46783,7 +46857,9 @@
       </x:c>
       <x:c r="N27" s="84" t="str"/>
       <x:c r="O27" s="84" t="str"/>
-      <x:c r="P27" s="86" t="str"/>
+      <x:c r="P27" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="83" t="str">
@@ -46827,7 +46903,9 @@
       </x:c>
       <x:c r="N28" s="84" t="str"/>
       <x:c r="O28" s="84" t="str"/>
-      <x:c r="P28" s="86" t="str"/>
+      <x:c r="P28" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="83" t="str">
@@ -46871,7 +46949,9 @@
       </x:c>
       <x:c r="N29" s="84" t="str"/>
       <x:c r="O29" s="84" t="str"/>
-      <x:c r="P29" s="86" t="str"/>
+      <x:c r="P29" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -46915,7 +46995,9 @@
       </x:c>
       <x:c r="N30" s="84" t="str"/>
       <x:c r="O30" s="84" t="str"/>
-      <x:c r="P30" s="86" t="str"/>
+      <x:c r="P30" s="86" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="87" t="str">
@@ -46959,7 +47041,9 @@
       </x:c>
       <x:c r="N31" s="88" t="str"/>
       <x:c r="O31" s="88" t="str"/>
-      <x:c r="P31" s="90" t="str"/>
+      <x:c r="P31" s="90" t="str">
+        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="E2:E31">

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,28 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0bd6a1a8a2be40c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9b4b4c9824ab49b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea58cea55fc4433e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1974610ce43d4c71"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3e3f69862a194884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfd6b40575a0464f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ref44475e51bf44ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Raa14d626af184afd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8b898a7d147b4273"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4bf19755870c4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0a1f709f41b245b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55a3aeeaa7324d9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf37206d613574d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R54e851f726334398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5868baec7842497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R25f747f19476486b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rfe556b50f2ba4dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb2edbd1c88bc434b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R32182337c60548cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb44a8c1df68042aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb87af9e087c54398"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2ecfb5c9ad384bf3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8e96575de88b46cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R917345222c954052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb46d052469a341bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R78f5d4acd2f64638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R70d95a13c0b541a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc1bdde3e0a784587"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R62722d17f53a4ef2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb7b67fdeb3e744e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rab4dc52a63274d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R50130fb9128f40cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R7a679304f82a4c53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R1f522ddeefb24ae4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R686a96ab58414559"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3198ea4afbc64579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3eb15411a1684560"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2a90618d31bf420f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd9c47823b56f4f60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R98e2f39c41f74f5e"/>
   </x:sheets>
-  <x:calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </x:workbook>
 </file>
 
@@ -852,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24e0e07782344063"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e204021b4094421"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1326,11 +1325,11 @@
       </x:c>
       <x:c r="E5" s="80" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A5,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="81" t="n">
         <x:f>IF(B5=0,0,E5/B5)</x:f>
-        <x:v>0.1</x:v>
+        <x:v>0.2</x:v>
       </x:c>
       <x:c r="G5" s="80" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1908,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafec37e767b540fe"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77f8299c7be432a"/>
 </x:worksheet>
 </file>
 
@@ -10058,7 +10057,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc434d7e824a14f5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d2dc4dd7e984816"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11247,7 +11246,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R96119fa7b19a4c92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffddebc77d9943d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12042,10 +12041,14 @@
       </x:c>
       <x:c r="M11" s="84" t="str"/>
       <x:c r="N11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O11" s="84" t="str"/>
-      <x:c r="P11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O11" s="84" t="str">
+        <x:v>contracts/version-manifest.catalog.json</x:v>
+      </x:c>
+      <x:c r="P11" s="86" t="str">
+        <x:v>TASK-GOV-010 已建立 VersionManifest 草案并冻结可核对源码/文件/容器基线；产品依赖与架构项仍待选型和锁定，PoC 未执行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -24781,7 +24784,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5824a7686b6a4297"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724a3629d9334992"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25341,9 +25344,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M13" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M13" s="84" t="str">
+        <x:v>contracts/version-manifest.schema.json；contracts/version-manifest.catalog.json；contracts/version-manifest.fixtures.json</x:v>
+      </x:c>
       <x:c r="N13" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43484,7 +43489,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcf03d30fe7e4cb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18527b236a364df8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43607,7 +43612,7 @@
         <x:v>MIT</x:v>
       </x:c>
       <x:c r="E3" s="84" t="str">
-        <x:v>v0.2.0 + v1.1.38 + main Skill</x:v>
+        <x:v>v0.2.0 commit d53296bc0ddd73e81d51c523d20dd711c7f233f3；v1.1.38 peeled commit 2419d30b134a71486523e95ded60b32489fd3c61（tag object 2e68c095a86bdbb91635dc4d91dad4662aba163c）；main / Skill commit 833cda553b343be0e486a93b0b57cac962cdd566</x:v>
       </x:c>
       <x:c r="F3" s="84" t="str">
         <x:v>Reference induction / outline / reference slide selection / editing actions / reflection/evaluation / current HTML-based Skill</x:v>
@@ -43627,7 +43632,9 @@
       <x:c r="K3" s="84" t="str">
         <x:v>待复现</x:v>
       </x:c>
-      <x:c r="L3" s="84" t="str"/>
+      <x:c r="L3" s="84" t="str">
+        <x:v>contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="M3" s="84" t="str"/>
       <x:c r="N3" s="86" t="str"/>
     </x:row>
@@ -43645,7 +43652,7 @@
         <x:v>Apache-2.0</x:v>
       </x:c>
       <x:c r="E4" s="84" t="str">
-        <x:v>main + package/app/export version + commit</x:v>
+        <x:v>main commit 35bf44290f821323e003da854f78ffcb0e918167</x:v>
       </x:c>
       <x:c r="F4" s="84" t="str">
         <x:v>Standard / Smart / Custom Template / API / MCP / Editor</x:v>
@@ -43665,7 +43672,9 @@
       <x:c r="K4" s="84" t="str">
         <x:v>待复现</x:v>
       </x:c>
-      <x:c r="L4" s="84" t="str"/>
+      <x:c r="L4" s="84" t="str">
+        <x:v>contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="M4" s="84" t="str"/>
       <x:c r="N4" s="86" t="str"/>
     </x:row>
@@ -43683,7 +43692,7 @@
         <x:v>MIT</x:v>
       </x:c>
       <x:c r="E5" s="84" t="str">
-        <x:v>main + commit</x:v>
+        <x:v>main commit c3605ebc487fc6c7d4f4139761e46d7021cd656c</x:v>
       </x:c>
       <x:c r="F5" s="84" t="str">
         <x:v>Topic/Document / HTML / Screenshot Reconstruction</x:v>
@@ -43703,7 +43712,9 @@
       <x:c r="K5" s="84" t="str">
         <x:v>待复现</x:v>
       </x:c>
-      <x:c r="L5" s="84" t="str"/>
+      <x:c r="L5" s="84" t="str">
+        <x:v>contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="M5" s="84" t="str"/>
       <x:c r="N5" s="86" t="str"/>
     </x:row>
@@ -43721,7 +43732,7 @@
         <x:v>AGPL-3.0</x:v>
       </x:c>
       <x:c r="E6" s="88" t="str">
-        <x:v>main + commit + deck schema version</x:v>
+        <x:v>main commit 5ae0670747885c464aa8063329a902d80a251877</x:v>
       </x:c>
       <x:c r="F6" s="88" t="str">
         <x:v>MCP / CLI / HTTP / JSON Skill / Revision / QA</x:v>
@@ -43741,7 +43752,9 @@
       <x:c r="K6" s="88" t="str">
         <x:v>待复现</x:v>
       </x:c>
-      <x:c r="L6" s="88" t="str"/>
+      <x:c r="L6" s="88" t="str">
+        <x:v>contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="M6" s="88" t="str"/>
       <x:c r="N6" s="90" t="str"/>
     </x:row>
@@ -43758,7 +43771,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfef894081b94553"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363cdd60455247b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45174,7 +45187,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7979cdc2cc214824"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f298e04d0804acd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45524,7 +45537,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="J9" s="84" t="str">
-        <x:v>未冻结（PoC未执行）</x:v>
+        <x:v>源码 commit 6b3939d72e5e867b90b269c603a6b8e79ca1c9f9（候选仓库版本；PoC 未执行，产品后端未选定）</x:v>
       </x:c>
       <x:c r="K9" s="84" t="str"/>
       <x:c r="L9" s="84" t="str"/>
@@ -45560,7 +45573,7 @@
         <x:v>未执行</x:v>
       </x:c>
       <x:c r="J10" s="88" t="str">
-        <x:v>未冻结（PoC未执行）</x:v>
+        <x:v>源码 commit 9f767046955e7469fa1a06f9abc89cc85442d98f（候选仓库版本；PoC 未执行，产品后端未选定）</x:v>
       </x:c>
       <x:c r="K10" s="88" t="str"/>
       <x:c r="L10" s="88" t="str"/>
@@ -45588,7 +45601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R62c062a3a6934768"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d2ba5c2a8de4f2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48935,7 +48948,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af1fe8e412d4be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b70f5a921d47d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb87af9e087c54398"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2ecfb5c9ad384bf3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8e96575de88b46cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R917345222c954052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb46d052469a341bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R78f5d4acd2f64638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R70d95a13c0b541a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc1bdde3e0a784587"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R62722d17f53a4ef2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb7b67fdeb3e744e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rab4dc52a63274d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R50130fb9128f40cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R7a679304f82a4c53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R1f522ddeefb24ae4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R686a96ab58414559"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3198ea4afbc64579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3eb15411a1684560"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2a90618d31bf420f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd9c47823b56f4f60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R98e2f39c41f74f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R314966fcb4884519"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R089a3bb9381a46e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra8db75022ca34082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R857df9f49c644055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R901d3042696f4456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R184a19f25e694624"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R18dc061125964089"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2496307574cd465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re80bc634d3924dc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf2a767c78a114055"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R814b0dcd50f144e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rfde918b9fe554332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf4570f048f1348fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2aed9517742848ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5ba102a9c44e4f21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1157f05aeebf4537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R37bf297432c04980"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rcfd06c02c6b64843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6627b0049d1d4867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rc3384a0649024d43"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2e204021b4094421"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca1d5983d58b44c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77f8299c7be432a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6a7e4ef8aee4fed"/>
 </x:worksheet>
 </file>
 
@@ -4924,9 +4924,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J3" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J3" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -5016,9 +5018,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J6" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J6" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -5046,9 +5050,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J7" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -5136,9 +5142,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J10" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J10" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -5346,9 +5354,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J17" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J17" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -5526,9 +5536,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J23" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J23" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -5706,9 +5718,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I29" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J29" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J29" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -5736,9 +5750,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I30" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J30" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J30" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="83" t="str">
@@ -5796,9 +5812,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I32" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J32" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J32" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="83" t="str">
@@ -5826,9 +5844,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I33" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J33" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J33" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="83" t="str">
@@ -5856,9 +5876,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I34" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J34" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J34" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="83" t="str">
@@ -5886,9 +5908,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J35" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J35" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="83" t="str">
@@ -5946,9 +5970,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J37" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J37" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="83" t="str">
@@ -5976,9 +6002,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J38" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J38" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="83" t="str">
@@ -6006,9 +6034,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J39" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J39" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -6036,9 +6066,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J40" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J40" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="83" t="str">
@@ -6066,9 +6098,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I41" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J41" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J41" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="83" t="str">
@@ -6096,9 +6130,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I42" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J42" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J42" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="83" t="str">
@@ -6126,9 +6162,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I43" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J43" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J43" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="83" t="str">
@@ -6156,9 +6194,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I44" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J44" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J44" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="83" t="str">
@@ -6186,9 +6226,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I45" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J45" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J45" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="83" t="str">
@@ -6216,9 +6258,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I46" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J46" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J46" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="83" t="str">
@@ -6246,9 +6290,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I47" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J47" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J47" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="83" t="str">
@@ -6276,9 +6322,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I48" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J48" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J48" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="83" t="str">
@@ -6288,7 +6336,7 @@
         <x:v>产物清单</x:v>
       </x:c>
       <x:c r="C49" s="84" t="str">
-        <x:v>artifact_id, type, path, hash, producer, source_ids, retention</x:v>
+        <x:v>artifact_id, deck_id, type, path, hash, producer, source_ids, retention</x:v>
       </x:c>
       <x:c r="D49" s="84" t="str">
         <x:v>待定义</x:v>
@@ -6306,9 +6354,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I49" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J49" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J49" s="86" t="str">
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="87" t="str">
@@ -10057,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d2dc4dd7e984816"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b35d9d0a6df46c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11246,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffddebc77d9943d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra31209f6fff34834"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11911,10 +11961,14 @@
       </x:c>
       <x:c r="M8" s="84" t="str"/>
       <x:c r="N8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O8" s="84" t="str"/>
-      <x:c r="P8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O8" s="84" t="str">
+        <x:v>contracts/object-id.catalog.json；PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P8" s="86" t="str">
+        <x:v>Fixture 追溯链检查通过；真实 PPT 端到端验收待运行时实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -24784,7 +24838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R724a3629d9334992"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7eb4fda7f6547ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25222,9 +25276,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M10" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M10" s="84" t="str">
+        <x:v>contracts/object-id.catalog.json；PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N10" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43489,7 +43545,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18527b236a364df8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R782a18d35e7d4a4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43771,7 +43827,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363cdd60455247b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3bd42a8e514f6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45187,7 +45243,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f298e04d0804acd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaccf96755d54851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45601,7 +45657,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d2ba5c2a8de4f2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb586d73b452f4737"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48948,7 +49004,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43b70f5a921d47d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c10af7201f463a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R314966fcb4884519"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R089a3bb9381a46e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra8db75022ca34082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R857df9f49c644055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R901d3042696f4456"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R184a19f25e694624"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R18dc061125964089"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2496307574cd465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re80bc634d3924dc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf2a767c78a114055"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R814b0dcd50f144e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rfde918b9fe554332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf4570f048f1348fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2aed9517742848ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5ba102a9c44e4f21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1157f05aeebf4537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R37bf297432c04980"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rcfd06c02c6b64843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6627b0049d1d4867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rc3384a0649024d43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd366c0c22cea4a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcbedc62de6404dbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Raa5dfecf9e5e4529"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc415ad3aa8c0450f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R5b94d32bca574c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R17e4c11ba61147b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rdbb40caa5ab143d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Reed9b6fa201b43d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R143102e6d02b4d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R9f25bcdfc4a1483f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra5a2faa6095d44e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R6b0f6a14255d4b74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R8a7ad36ee77d462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R284ab2fbb55449a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5b52a550d69e4259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1b95ff7f207341f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rbdb0a394e1664337"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R62800f85a03a4031"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3646b2aa9349484a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R5b60eade52dd4fd4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rca1d5983d58b44c7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd8fe6a092be34526"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6a7e4ef8aee4fed"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a914bac82724624"/>
 </x:worksheet>
 </file>
 
@@ -10107,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b35d9d0a6df46c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2819718f9cac4b5f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra31209f6fff34834"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd068422f85b141b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12007,10 +12007,14 @@
       </x:c>
       <x:c r="M9" s="84" t="str"/>
       <x:c r="N9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O9" s="84" t="str"/>
-      <x:c r="P9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O9" s="84" t="str">
+        <x:v>contracts/e2e-acceptance.catalog.json；PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P9" s="86" t="str">
+        <x:v>完成门槛已定义；AC-001–AC-030 均未执行，系统验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -24838,7 +24842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7eb4fda7f6547ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73eb790e3f5a438b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25318,9 +25322,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M11" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M11" s="84" t="str">
+        <x:v>contracts/e2e-acceptance.catalog.json；PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N11" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43545,7 +43551,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R782a18d35e7d4a4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1bb89dba3b4426c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43827,7 +43833,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c3bd42a8e514f6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9843a931f5044dd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45243,7 +45249,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaccf96755d54851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17928d326cb64a1f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45657,7 +45663,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb586d73b452f4737"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R066b8c13e1fe46d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49004,7 +49010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85c10af7201f463a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d8d712d30e4a10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd366c0c22cea4a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcbedc62de6404dbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Raa5dfecf9e5e4529"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc415ad3aa8c0450f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R5b94d32bca574c80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R17e4c11ba61147b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rdbb40caa5ab143d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Reed9b6fa201b43d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R143102e6d02b4d50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R9f25bcdfc4a1483f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra5a2faa6095d44e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R6b0f6a14255d4b74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R8a7ad36ee77d462a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R284ab2fbb55449a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5b52a550d69e4259"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1b95ff7f207341f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rbdb0a394e1664337"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R62800f85a03a4031"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3646b2aa9349484a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R5b60eade52dd4fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R4523b5db6c6847a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R46085ba8cd454fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6ad68f2040f34004"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R079b0d7c6d6e4531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6bb2510465ce48fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4c0e70c81a3f4332"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4d220f87ebb64889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R60b83f0f42fe4c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re4008c73958a4ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R0fc755a9ada1405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R4fd25bc6981e4389"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55a73299fd0742fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdd96a0093277411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0c69ff0976014d60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R649d163074c440fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rea2f5a846cda45c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R03b054b69ba741cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R7f81c8c2b7504eb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rea561adf422748e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R89becdf62a5b42f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd8fe6a092be34526"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ab3fed2f5c84988"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a914bac82724624"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc89e7347ff7048bd"/>
 </x:worksheet>
 </file>
 
@@ -10107,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2819718f9cac4b5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R859dce5a008d475f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd068422f85b141b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41b6ca8dc16f4314"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12365,10 +12365,14 @@
       </x:c>
       <x:c r="M17" s="84" t="str"/>
       <x:c r="N17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O17" s="84" t="str"/>
-      <x:c r="P17" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O17" s="84" t="str">
+        <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
+      <x:c r="P17" s="86" t="str">
+        <x:v>refs、依赖锁与 MIT 主许可证已静态核对；官方最小流程因 Docker Engine 不可用暂未复现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -24842,7 +24846,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73eb790e3f5a438b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re604062b0a944e92"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25868,9 +25872,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L24" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M24" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M24" s="84" t="str">
+        <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="N24" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -43551,7 +43557,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1bb89dba3b4426c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7d53aa720a64803"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43692,10 +43698,10 @@
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
       <x:c r="K3" s="84" t="str">
-        <x:v>待复现</x:v>
+        <x:v>源码已固定；待复现</x:v>
       </x:c>
       <x:c r="L3" s="84" t="str">
-        <x:v>contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M3" s="84" t="str"/>
       <x:c r="N3" s="86" t="str"/>
@@ -43833,7 +43839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9843a931f5044dd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67b1e67d90c4979"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45249,7 +45255,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17928d326cb64a1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra72f4ed287844c70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45663,7 +45669,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R066b8c13e1fe46d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R949c0ae5bbba4f00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49010,7 +49016,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58d8d712d30e4a10"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf118b0b3214ec3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R4523b5db6c6847a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R46085ba8cd454fac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6ad68f2040f34004"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R079b0d7c6d6e4531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6bb2510465ce48fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4c0e70c81a3f4332"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4d220f87ebb64889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R60b83f0f42fe4c7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re4008c73958a4ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R0fc755a9ada1405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R4fd25bc6981e4389"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55a73299fd0742fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdd96a0093277411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0c69ff0976014d60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R649d163074c440fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rea2f5a846cda45c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R03b054b69ba741cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R7f81c8c2b7504eb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rea561adf422748e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R89becdf62a5b42f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7e6f71a9501d47d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R5f06928ce00c4941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0f37c237f46f48df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6246b3f353394596"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R0bc926891fea4cc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R699f5a1b36e94670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbca743335a8646d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R82a7044cccbe4e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R033b47644714427d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb14c757a597f4b52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R80b681e2d0d542a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Recaeb49871d44334"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf9dd43865eef43bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R27a50ac8660b4906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf1d6ada7e2c6411d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R922c70b96a9c4568"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rad036de1ece24531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra766c14e8ae3464e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R057cca33c00548d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R61172aee83fc442a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5ab3fed2f5c84988"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68e25a8e4e344c14"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc89e7347ff7048bd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c46c3021c194908"/>
 </x:worksheet>
 </file>
 
@@ -10107,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R859dce5a008d475f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18cfca071a6046d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41b6ca8dc16f4314"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922629dcc325472f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12371,7 +12371,7 @@
         <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="P17" s="86" t="str">
-        <x:v>refs、依赖锁与 MIT 主许可证已静态核对；官方最小流程因 Docker Engine 不可用暂未复现。</x:v>
+        <x:v>待复现</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -12587,10 +12587,14 @@
       </x:c>
       <x:c r="M22" s="84" t="str"/>
       <x:c r="N22" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O22" s="84" t="str"/>
-      <x:c r="P22" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O22" s="84" t="str">
+        <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
+      <x:c r="P22" s="86" t="str">
+        <x:v>待复现</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -24846,7 +24850,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re604062b0a944e92"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b5ba006724c490a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26292,9 +26296,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L34" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M34" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M34" s="84" t="str">
+        <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="N34" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43557,7 +43563,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7d53aa720a64803"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R924082ebcb814030"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43738,10 +43744,10 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>待复现</x:v>
+        <x:v>源码已固定；待复现</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
-        <x:v>contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str"/>
       <x:c r="N4" s="86" t="str"/>
@@ -43839,7 +43845,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra67b1e67d90c4979"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cec511899e3480d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45255,7 +45261,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra72f4ed287844c70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5531939c8154fb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45669,7 +45675,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R949c0ae5bbba4f00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb7b22b9b664a9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49016,7 +49022,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf118b0b3214ec3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb95022f84042460f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R7e6f71a9501d47d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R5f06928ce00c4941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0f37c237f46f48df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6246b3f353394596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R0bc926891fea4cc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R699f5a1b36e94670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbca743335a8646d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R82a7044cccbe4e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R033b47644714427d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb14c757a597f4b52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R80b681e2d0d542a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Recaeb49871d44334"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rf9dd43865eef43bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R27a50ac8660b4906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf1d6ada7e2c6411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R922c70b96a9c4568"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rad036de1ece24531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra766c14e8ae3464e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R057cca33c00548d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R61172aee83fc442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re4e60dd560c34755"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9c0cb8b14a1e447f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8d8b8f4c9e9d431b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R47a487c35f6e42ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4093a89444d442a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5ff46b32d5c74456"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc9ff0746242f42f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R79c9d5909fb040c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R293f5704ce794328"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rfedeed443089412d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R54f5023b1c974ca7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rc5b224b4e09b4110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc35d0b1e76164ec3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R44711d4e7d19479b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R04e3863251434369"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rc1be278f845845c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1a87b5f7bc1745ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rda960a1314ad422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7135cd6524de4aa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra9282e2005474a8d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R68e25a8e4e344c14"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5dd34c286d994839"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c46c3021c194908"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b4f2656c264427d"/>
 </x:worksheet>
 </file>
 
@@ -10107,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18cfca071a6046d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85293ae3fbe34447"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R922629dcc325472f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc449a611c5f14428"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12809,10 +12809,14 @@
       </x:c>
       <x:c r="M27" s="84" t="str"/>
       <x:c r="N27" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O27" s="84" t="str"/>
-      <x:c r="P27" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O27" s="84" t="str">
+        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
+      <x:c r="P27" s="86" t="str">
+        <x:v>待复现</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="83" t="str">
@@ -24850,7 +24854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b5ba006724c490a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6316118bde5c4849"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26716,9 +26720,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L44" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M44" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M44" s="84" t="str">
+        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="N44" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -43563,7 +43569,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R924082ebcb814030"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra061b2f15cdd4db4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43784,10 +43790,10 @@
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
       <x:c r="K5" s="84" t="str">
-        <x:v>待复现</x:v>
+        <x:v>源码已固定；待复现</x:v>
       </x:c>
       <x:c r="L5" s="84" t="str">
-        <x:v>contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M5" s="84" t="str"/>
       <x:c r="N5" s="86" t="str"/>
@@ -43845,7 +43851,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cec511899e3480d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dfc309b2bc44fb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45261,7 +45267,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5531939c8154fb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46b779d0f4d64f73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45675,7 +45681,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb7b22b9b664a9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60a88197242040f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49022,7 +49028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb95022f84042460f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7055bb4367d048f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re4e60dd560c34755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9c0cb8b14a1e447f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8d8b8f4c9e9d431b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R47a487c35f6e42ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4093a89444d442a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5ff46b32d5c74456"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc9ff0746242f42f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R79c9d5909fb040c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R293f5704ce794328"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rfedeed443089412d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R54f5023b1c974ca7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rc5b224b4e09b4110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc35d0b1e76164ec3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R44711d4e7d19479b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R04e3863251434369"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rc1be278f845845c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1a87b5f7bc1745ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rda960a1314ad422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7135cd6524de4aa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra9282e2005474a8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R453439ea97be418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re36dddb937024ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc85da6ffee334737"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rfb02091d2937481d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rea62588d2aeb443e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R51bc934e3efc41a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R62a95e63b5b44dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra4a45f644e5f4721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3408584cae504fbe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf46f58aa895f4190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcaa51bba58754a14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb6306d32a4cf4e40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R47adb9e87d56479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2f378b31930f444d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf508cc8b09be4c13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Re4cf314e0418447b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rec71b7139cb94618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdae1d326b3d84615"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9ae4b3868b48486f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2ea53589ca134629"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5dd34c286d994839"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re97c280a6eb04d85"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b4f2656c264427d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb048e9fc71d4484c"/>
 </x:worksheet>
 </file>
 
@@ -10107,7 +10107,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85293ae3fbe34447"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06218b9396b14de3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11296,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc449a611c5f14428"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R433babf5006646de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13031,10 +13031,14 @@
       </x:c>
       <x:c r="M32" s="84" t="str"/>
       <x:c r="N32" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O32" s="84" t="str"/>
-      <x:c r="P32" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O32" s="84" t="str">
+        <x:v>research/P05/README.md；contracts/version-manifest.catalog.json；官方示例受Docker Engine阻塞</x:v>
+      </x:c>
+      <x:c r="P32" s="86" t="str">
+        <x:v>待复现</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="83" t="str">
@@ -24854,7 +24858,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6316118bde5c4849"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a8017e613c146c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27140,9 +27144,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L54" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M54" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M54" s="84" t="str">
+        <x:v>research/P05/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
       <x:c r="N54" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -43569,7 +43575,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra061b2f15cdd4db4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb558cb0303424565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43830,10 +43836,10 @@
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
       <x:c r="K6" s="88" t="str">
-        <x:v>待复现</x:v>
+        <x:v>源码已固定；待复现</x:v>
       </x:c>
       <x:c r="L6" s="88" t="str">
-        <x:v>contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P05/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M6" s="88" t="str"/>
       <x:c r="N6" s="90" t="str"/>
@@ -43851,7 +43857,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dfc309b2bc44fb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1bd30cdf4974160"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45267,7 +45273,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46b779d0f4d64f73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f09221452f54cb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45681,7 +45687,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60a88197242040f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1915b37f275b4ec9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49028,7 +49034,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7055bb4367d048f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39fa8e15f7dd43cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R453439ea97be418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re36dddb937024ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc85da6ffee334737"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rfb02091d2937481d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rea62588d2aeb443e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R51bc934e3efc41a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R62a95e63b5b44dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra4a45f644e5f4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3408584cae504fbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf46f58aa895f4190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcaa51bba58754a14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb6306d32a4cf4e40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R47adb9e87d56479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2f378b31930f444d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf508cc8b09be4c13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Re4cf314e0418447b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rec71b7139cb94618"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdae1d326b3d84615"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9ae4b3868b48486f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2ea53589ca134629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra9993cd8e8ef42c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R64496a0f55d74d27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re2acae9bf3744316"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Racbd228be0174e65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbda080e1a0c645a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R40d93824af39467b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R73c0c580754e440b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2cbe1f26429247bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9918338dd79c4e68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Refec2ef7dfaa466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra788e58b396147ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7a8c7dc0ec954ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rccc9a9695a694787"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd12ba9a299c54f4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R77cdc211cffd48c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8a7a4ce1b9bc4107"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R93050f6f35eb442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9a2dac148564469a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfcb7e6609ccf43cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R863db8e4351449c5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re97c280a6eb04d85"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f9101bf717447ba"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb048e9fc71d4484c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf91ef70e794a4021"/>
 </x:worksheet>
 </file>
 
@@ -4894,9 +4894,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J2" s="82" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J2" s="82" t="str">
+        <x:v>契约草案见 contracts/prompt-input.schema.json；解析与落盘待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -10107,7 +10109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06218b9396b14de3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67b441df7932465d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11296,7 +11298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R433babf5006646de"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1240b6d9ce714c0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13385,10 +13387,14 @@
       </x:c>
       <x:c r="M40" s="84" t="str"/>
       <x:c r="N40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O40" s="84" t="str"/>
-      <x:c r="P40" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O40" s="84" t="str">
+        <x:v>contracts/prompt-input.schema.json；contracts/prompt-input.catalog.json；contracts/prompt-input.fixtures.json；PROJECT_PLAN.md（TASK-IN-001）</x:v>
+      </x:c>
+      <x:c r="P40" s="86" t="str">
+        <x:v>样例跨度静态核对通过；运行时解析器未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="83" t="str">
@@ -24858,7 +24864,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a8017e613c146c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a7a78ad32c64dbd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27732,9 +27738,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L68" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M68" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M68" s="84" t="str">
+        <x:v>contracts/prompt-input.schema.json（草案）；contracts/prompt-input.catalog.json；contracts/prompt-input.fixtures.json；PROJECT_PLAN.md（TASK-IN-001）</x:v>
+      </x:c>
       <x:c r="N68" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43575,7 +43583,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb558cb0303424565"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6c6a6a879b941bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43857,7 +43865,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1bd30cdf4974160"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e8a9fc71616448d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45273,7 +45281,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f09221452f54cb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4286ca73c574c3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45687,7 +45695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1915b37f275b4ec9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434b663dee6e4e19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49034,7 +49042,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39fa8e15f7dd43cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red6d299168bf4255"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra9993cd8e8ef42c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R64496a0f55d74d27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re2acae9bf3744316"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Racbd228be0174e65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbda080e1a0c645a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R40d93824af39467b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R73c0c580754e440b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2cbe1f26429247bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9918338dd79c4e68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Refec2ef7dfaa466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra788e58b396147ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7a8c7dc0ec954ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rccc9a9695a694787"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd12ba9a299c54f4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R77cdc211cffd48c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8a7a4ce1b9bc4107"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R93050f6f35eb442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9a2dac148564469a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfcb7e6609ccf43cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R863db8e4351449c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1e65eb7cb09a4d23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R80acd4ad01c74a15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8c9b7feb4fa14367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9a9d4475fcc94dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R42eb896b2925452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R44c9ff02b1ae4c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd5da54b2442145f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb343eafdafcf4b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3e5754dab3814c73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R42a6d48d787b47bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5e0b9d33297c4abf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2f3a6b9ba8c445ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R07228e37504b4287"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re62a63ba127f4e5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R128aa3fb2c494ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0d6a04b3836a4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re880d9cdbb2346e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd342fbc6b3f043d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R427b3934eeac4f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R56fdd9af6db448e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3f9101bf717447ba"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R05c448ff70284cfb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf91ef70e794a4021"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38c7e64217a84b20"/>
 </x:worksheet>
 </file>
 
@@ -10109,7 +10109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67b441df7932465d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbbf3218a964c55"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11298,7 +11298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1240b6d9ce714c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9888fe013004f43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13433,10 +13433,14 @@
       </x:c>
       <x:c r="M41" s="84" t="str"/>
       <x:c r="N41" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O41" s="84" t="str"/>
-      <x:c r="P41" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O41" s="84" t="str">
+        <x:v>contracts/text-document.schema.json；contracts/text-document.catalog.json；contracts/text-document.fixtures.json；PROJECT_PLAN.md（TASK-IN-002）</x:v>
+      </x:c>
+      <x:c r="P41" s="86" t="str">
+        <x:v>结构/跨度静态核对通过；解析器未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="83" t="str">
@@ -24864,7 +24868,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a7a78ad32c64dbd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ddf511823f45da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27780,9 +27784,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L69" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M69" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M69" s="84" t="str">
+        <x:v>contracts/text-document.schema.json（草案）；contracts/text-document.catalog.json；contracts/text-document.fixtures.json；PROJECT_PLAN.md（TASK-IN-002）</x:v>
+      </x:c>
       <x:c r="N69" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43583,7 +43589,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6c6a6a879b941bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8ddf8db625d467c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43865,7 +43871,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e8a9fc71616448d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R689c8ff6839f44b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45281,7 +45287,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4286ca73c574c3f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R336af3c1e95c4e7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45695,7 +45701,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R434b663dee6e4e19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80786ae4c6774a32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49042,7 +49048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red6d299168bf4255"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d869dcd9d248e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1e65eb7cb09a4d23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R80acd4ad01c74a15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8c9b7feb4fa14367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9a9d4475fcc94dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R42eb896b2925452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R44c9ff02b1ae4c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd5da54b2442145f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb343eafdafcf4b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3e5754dab3814c73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R42a6d48d787b47bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5e0b9d33297c4abf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2f3a6b9ba8c445ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R07228e37504b4287"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re62a63ba127f4e5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R128aa3fb2c494ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0d6a04b3836a4a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re880d9cdbb2346e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd342fbc6b3f043d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R427b3934eeac4f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R56fdd9af6db448e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0eda4457db4d4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcd3834e09f204fb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2375c81430cd4ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8e311186b4ed4772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R06a1e5f98bf44c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rd3de40ade7aa40c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R994947ebebe24645"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7f726a64f1c449bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0aafc75ef55d4526"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R37facb38ffd248c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3bf5a56c17f54f40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R609b323260154d61"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R30c1dfe1523c4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rb69d7738d423469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R880dffdd9d354603"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1600187904a9405d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re1c82f0aa0cc477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R533d272eb0a14dc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R59756ab569814d4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8c4c3f363e824826"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R05c448ff70284cfb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd22bc6f2398f43d6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38c7e64217a84b20"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7604d341e7e4149"/>
 </x:worksheet>
 </file>
 
@@ -10109,7 +10109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Racbbf3218a964c55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ebb6680b294c30"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11298,7 +11298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9888fe013004f43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f0b471d9e3475a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13479,10 +13479,14 @@
       </x:c>
       <x:c r="M42" s="84" t="str"/>
       <x:c r="N42" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O42" s="84" t="str"/>
-      <x:c r="P42" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O42" s="84" t="str">
+        <x:v>contracts/docx-evidence.schema.json；contracts/docx-evidence.catalog.json；contracts/docx-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-003）</x:v>
+      </x:c>
+      <x:c r="P42" s="86" t="str">
+        <x:v>结构/资产静态核对通过；页码未实测，解析器未实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="83" t="str">
@@ -24868,7 +24872,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ddf511823f45da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3da365ece4ae4a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27826,9 +27830,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L70" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M70" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M70" s="84" t="str">
+        <x:v>contracts/docx-evidence.schema.json（草案）；contracts/docx-evidence.catalog.json；contracts/docx-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-003）</x:v>
+      </x:c>
       <x:c r="N70" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43589,7 +43595,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8ddf8db625d467c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R192f9889cae94b6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43871,7 +43877,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R689c8ff6839f44b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16889a86d224d79"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45287,7 +45293,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R336af3c1e95c4e7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f43473e04214b43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45701,7 +45707,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80786ae4c6774a32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5d1e55fc45486b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49048,7 +49054,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43d869dcd9d248e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59d5546430984d18"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R0eda4457db4d4f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcd3834e09f204fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2375c81430cd4ee1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8e311186b4ed4772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R06a1e5f98bf44c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rd3de40ade7aa40c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R994947ebebe24645"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7f726a64f1c449bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0aafc75ef55d4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R37facb38ffd248c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3bf5a56c17f54f40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R609b323260154d61"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R30c1dfe1523c4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rb69d7738d423469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R880dffdd9d354603"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1600187904a9405d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re1c82f0aa0cc477a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R533d272eb0a14dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R59756ab569814d4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8c4c3f363e824826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R96b94bdcfcd240ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re1fc44a731a04716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Recc708791765407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4bd05043de4e43bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R8b079ddaed6a4a6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6878f0c2d2634adb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rba90c6299b424521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd9dab9d10c114582"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re4e6c7a812454577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4ea7cffdaef4405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R45564ed35d684d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf6603ba2145b4418"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rec7b4ccd56264e93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R6a9cfff1ca8e4d2e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R91e21d167a954b01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R598a82d2507a4647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re56cd4dcaaaa44ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R44e4b73546c44448"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9e3ba133d85c41c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R6388c4cc977c4845"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd22bc6f2398f43d6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfabfffb06cbe4b66"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7604d341e7e4149"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2acb6dd0f9f4baf"/>
 </x:worksheet>
 </file>
 
@@ -10109,7 +10109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ebb6680b294c30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a77a9d33c4439e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11298,7 +11298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36f0b471d9e3475a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6238dc49f6fd42fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13525,10 +13525,14 @@
       </x:c>
       <x:c r="M43" s="84" t="str"/>
       <x:c r="N43" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O43" s="84" t="str"/>
-      <x:c r="P43" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O43" s="84" t="str">
+        <x:v>contracts/pdf-evidence.schema.json；contracts/pdf-evidence.catalog.json；contracts/pdf-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-004）</x:v>
+      </x:c>
+      <x:c r="P43" s="86" t="str">
+        <x:v>结构/坐标静态核对通过；解析器与真实坐标未验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="83" t="str">
@@ -24872,7 +24876,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3da365ece4ae4a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra808836d00d04fe8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27872,9 +27876,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L71" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M71" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M71" s="84" t="str">
+        <x:v>contracts/pdf-evidence.schema.json（草案）；contracts/pdf-evidence.catalog.json；contracts/pdf-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-004）</x:v>
+      </x:c>
       <x:c r="N71" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43595,7 +43601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R192f9889cae94b6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52f77f0793924fcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43877,7 +43883,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re16889a86d224d79"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2bcb3fd75724b19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45293,7 +45299,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f43473e04214b43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56aa9c20bd4c4d33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45707,7 +45713,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5d1e55fc45486b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f07ba82a7f545e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49054,7 +49060,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59d5546430984d18"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca9b5a774a14c0c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R96b94bdcfcd240ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re1fc44a731a04716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Recc708791765407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4bd05043de4e43bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R8b079ddaed6a4a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6878f0c2d2634adb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rba90c6299b424521"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd9dab9d10c114582"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re4e6c7a812454577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R4ea7cffdaef4405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R45564ed35d684d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf6603ba2145b4418"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rec7b4ccd56264e93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R6a9cfff1ca8e4d2e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R91e21d167a954b01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R598a82d2507a4647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re56cd4dcaaaa44ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R44e4b73546c44448"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9e3ba133d85c41c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R6388c4cc977c4845"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9345a0de946e4824"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R882362a364c0478d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2e061b34eb74437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R56457e0fa4b9456d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbf0f2eff6cf2432b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R984a63cc841c4f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R42d0fd358d1f47d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5826de10a93e4a40"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5ed1fed67e04404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R09659a5b9b0f4267"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb432bce09fc6414b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0f5be31d6a924064"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R31d119079d634051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5c9af6af910e4ad2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R0ffaa72c74a74f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R90a6290c9c0244cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2a99a06f0b834c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc6ab3b075ae341c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R77759d6ca2634474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf484dbef2d6c411b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfabfffb06cbe4b66"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redd36b9534c04424"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re2acb6dd0f9f4baf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798d3dcd954e4fa2"/>
 </x:worksheet>
 </file>
 
@@ -10109,7 +10109,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7a77a9d33c4439e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3bcf10136d4786"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11298,7 +11298,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6238dc49f6fd42fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2239a88c084d4cdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13613,10 +13613,14 @@
       </x:c>
       <x:c r="M45" s="84" t="str"/>
       <x:c r="N45" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O45" s="84" t="str"/>
-      <x:c r="P45" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O45" s="84" t="str">
+        <x:v>contracts/imported-deck.schema.json；contracts/imported-deck.catalog.json；contracts/imported-deck.fixtures.json；PROJECT_PLAN.md（TASK-IN-006）</x:v>
+      </x:c>
+      <x:c r="P45" s="86" t="str">
+        <x:v>静态核对通过；真实PPTX解析未验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="83" t="str">
@@ -24876,7 +24880,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra808836d00d04fe8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64ffd2d8666426b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27958,9 +27962,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L73" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M73" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M73" s="84" t="str">
+        <x:v>contracts/imported-deck.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-006）</x:v>
+      </x:c>
       <x:c r="N73" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43601,7 +43607,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52f77f0793924fcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89b87fb32380446a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43883,7 +43889,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2bcb3fd75724b19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdebb7a14a094f90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45299,7 +45305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56aa9c20bd4c4d33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34044b2fc1514c61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45713,7 +45719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f07ba82a7f545e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d36d9e0501a44e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49060,7 +49066,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca9b5a774a14c0c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c93ca9eff2340cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9345a0de946e4824"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R882362a364c0478d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2e061b34eb74437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R56457e0fa4b9456d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbf0f2eff6cf2432b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R984a63cc841c4f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R42d0fd358d1f47d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5826de10a93e4a40"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5ed1fed67e04404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R09659a5b9b0f4267"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb432bce09fc6414b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0f5be31d6a924064"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R31d119079d634051"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5c9af6af910e4ad2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R0ffaa72c74a74f51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R90a6290c9c0244cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2a99a06f0b834c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc6ab3b075ae341c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R77759d6ca2634474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf484dbef2d6c411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R94e5823a871946ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb6727a5c318848da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea7ccb5b370a4cbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rbcae1e1117f74843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb832771e043440fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rb641c239456c4c4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rf9e780c9a88c4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R6bee658f13704278"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R361599fd0f0d4ced"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R529fa8cf581e43f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3338bc49f6854f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8276f79a58604722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re14179b172ee408b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc41c45fe13874b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R81ea65b3dbda4850"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2620ee62e0e145e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf6aabdf7d8c44883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc940f86313324786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rccecf57bf1ae44c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R258996e60f39446f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Redd36b9534c04424"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7723d9571a948f1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798d3dcd954e4fa2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d1845148774c46"/>
 </x:worksheet>
 </file>
 
@@ -5672,10 +5672,10 @@
         <x:v>模板包</x:v>
       </x:c>
       <x:c r="C28" s="84" t="str">
-        <x:v>source, masters, layouts, tokens, assets, preview, license, version</x:v>
+        <x:v>source, masters, layouts, placeholders, tokens, brand, assets, preview, license, version</x:v>
       </x:c>
       <x:c r="D28" s="84" t="str">
-        <x:v>待定义</x:v>
+        <x:v>Draft 2020-12 草案</x:v>
       </x:c>
       <x:c r="E28" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5690,9 +5690,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J28" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J28" s="86" t="str">
+        <x:v>契约草案：contracts/template-pack.schema.json；模板解析验收待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="83" t="str">
@@ -10109,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d3bcf10136d4786"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6451baa3d1f0418a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11298,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2239a88c084d4cdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65343124c4c14d32"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13659,10 +13661,14 @@
       </x:c>
       <x:c r="M46" s="84" t="str"/>
       <x:c r="N46" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O46" s="84" t="str"/>
-      <x:c r="P46" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O46" s="84" t="str">
+        <x:v>contracts/template-pack.schema.json；contracts/template-pack.catalog.json；contracts/template-pack.fixtures.json；PROJECT_PLAN.md（TASK-IN-007）</x:v>
+      </x:c>
+      <x:c r="P46" s="86" t="str">
+        <x:v>静态核对通过；PPTX解析未验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="83" t="str">
@@ -24880,7 +24886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re64ffd2d8666426b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c5537e328d843ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28004,9 +28010,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L74" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M74" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M74" s="84" t="str">
+        <x:v>contracts/template-pack.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-007）</x:v>
+      </x:c>
       <x:c r="N74" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43607,7 +43615,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89b87fb32380446a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f19043f80e142a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43889,7 +43897,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdebb7a14a094f90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729d5c64319646a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45305,7 +45313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34044b2fc1514c61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd750ac36058149ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45719,7 +45727,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d36d9e0501a44e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad4555566e3a4407"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49066,7 +49074,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c93ca9eff2340cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86fad9550eb94476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R94e5823a871946ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb6727a5c318848da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea7ccb5b370a4cbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rbcae1e1117f74843"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rb832771e043440fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rb641c239456c4c4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rf9e780c9a88c4cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R6bee658f13704278"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R361599fd0f0d4ced"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R529fa8cf581e43f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3338bc49f6854f56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8276f79a58604722"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re14179b172ee408b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc41c45fe13874b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R81ea65b3dbda4850"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2620ee62e0e145e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf6aabdf7d8c44883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc940f86313324786"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rccecf57bf1ae44c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R258996e60f39446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd79737f79f7640e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc6ed90ab42f14185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7a75d515e9274faa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Ra8b35d3954c54e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1627c5fbc68c46db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R995f55f8da624bad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5c2f12248e934cd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R241b5c25eb7244d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2944199330ca4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R10217d7b47694a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf2b461d27b6445a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R33e2e534ca2c4d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R53bc86e0e3ec4ba3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9c0e46bc2e4c4a86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2c0fb14dfac84a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ref7510779f804b21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R150fc29e6cda4c56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3fee6bb959fd409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R367b8506f2ec49ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R5c7a62fb8f5949dd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7723d9571a948f1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f217628bd0f4122"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1d1845148774c46"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e0efe147e5455b"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6451baa3d1f0418a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4abfa03cd9f46ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65343124c4c14d32"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8df8013080af4615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13707,10 +13707,14 @@
       </x:c>
       <x:c r="M47" s="84" t="str"/>
       <x:c r="N47" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O47" s="84" t="str"/>
-      <x:c r="P47" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O47" s="84" t="str">
+        <x:v>contracts/tabular-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-008）</x:v>
+      </x:c>
+      <x:c r="P47" s="86" t="str">
+        <x:v>静态核对通过；真实解析器与验收待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="83" t="str">
@@ -24886,7 +24890,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c5537e328d843ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459ed586b3fb4379"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28052,9 +28056,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L75" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M75" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M75" s="84" t="str">
+        <x:v>contracts/tabular-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-008）</x:v>
+      </x:c>
       <x:c r="N75" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43615,7 +43621,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f19043f80e142a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra052ca944a944f0d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43897,7 +43903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R729d5c64319646a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99fba8a9f7a14586"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45313,7 +45319,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd750ac36058149ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7338c0fd2516435e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45727,7 +45733,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad4555566e3a4407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b816c9ecef4ceb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49074,7 +49080,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86fad9550eb94476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc43fbb61cef4a64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd79737f79f7640e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc6ed90ab42f14185"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7a75d515e9274faa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Ra8b35d3954c54e19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1627c5fbc68c46db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R995f55f8da624bad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5c2f12248e934cd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R241b5c25eb7244d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2944199330ca4381"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R10217d7b47694a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf2b461d27b6445a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R33e2e534ca2c4d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R53bc86e0e3ec4ba3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9c0e46bc2e4c4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2c0fb14dfac84a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ref7510779f804b21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R150fc29e6cda4c56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3fee6bb959fd409e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R367b8506f2ec49ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R5c7a62fb8f5949dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R177156bc484d4a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9f03948aee944dd8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re0a7109fc3904dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7e599b0e13334b11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7c853482224749ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra1783b7109d64d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8270bbd2af0446ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2d07986e552c44b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R48d8b62a70504d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R96d43f83f75d4247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0e299b135c2b40b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5b4f2c6374e74e1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R78df9498120e4813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0bac9473fd004e00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rcc598ec6b64e4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4f56ed3aba92477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2a10862878a3418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9e96ba2caaea4589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R09639769b4e640c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R52a11e5dd46b426c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6f217628bd0f4122"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R665d6813e7fc4dfc"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7e0efe147e5455b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddc63fccc0374213"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4abfa03cd9f46ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R978658803abb4d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8df8013080af4615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R573d563da6ae444d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13795,10 +13795,14 @@
       </x:c>
       <x:c r="M49" s="84" t="str"/>
       <x:c r="N49" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O49" s="84" t="str"/>
-      <x:c r="P49" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O49" s="84" t="str">
+        <x:v>contracts/structured-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-010）</x:v>
+      </x:c>
+      <x:c r="P49" s="86" t="str">
+        <x:v>JSON/引用/fixture静态核对通过；真实解析器与验收待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="83" t="str">
@@ -24890,7 +24894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R459ed586b3fb4379"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdee6a2a6a2e4287"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28138,9 +28142,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L77" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M77" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M77" s="84" t="str">
+        <x:v>contracts/structured-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-010）</x:v>
+      </x:c>
       <x:c r="N77" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43621,7 +43627,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra052ca944a944f0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a6a645afbc4493"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43903,7 +43909,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99fba8a9f7a14586"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8c437884a624a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45319,7 +45325,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7338c0fd2516435e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e9d112230234ea3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45733,7 +45739,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19b816c9ecef4ceb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a5d2e2baab246d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49080,7 +49086,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc43fbb61cef4a64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bb20acfe5f94a85"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R177156bc484d4a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9f03948aee944dd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re0a7109fc3904dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7e599b0e13334b11"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7c853482224749ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra1783b7109d64d8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8270bbd2af0446ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2d07986e552c44b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R48d8b62a70504d67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R96d43f83f75d4247"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0e299b135c2b40b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5b4f2c6374e74e1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R78df9498120e4813"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0bac9473fd004e00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rcc598ec6b64e4f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4f56ed3aba92477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2a10862878a3418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9e96ba2caaea4589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R09639769b4e640c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R52a11e5dd46b426c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6ca48f80dfec4275"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R5ea917f448e54b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rcc36f4b1e1844df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rf383ab1898c4415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Ra4af4195f3dd459e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1b7abb2ba317451b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R781202f09b894604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4a432716f72c47ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3b1e05c4e6ee4c0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6f821871970b4034"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Raaec8b3487864c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rab827182acf8498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re64faf0426e54890"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R101cda2bccac4081"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd8689eca28f54142"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6f76fb5b26ee495d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rae9cc00536884151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc8545542401642fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rb9384ede721e42eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R41c84531bca24b6e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R665d6813e7fc4dfc"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb1205fe50134488"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rddc63fccc0374213"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918d20d3e7834fa5"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R978658803abb4d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76e68329b79d4c6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R573d563da6ae444d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39f712b7b904cef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13841,10 +13841,14 @@
       </x:c>
       <x:c r="M50" s="84" t="str"/>
       <x:c r="N50" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O50" s="84" t="str"/>
-      <x:c r="P50" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O50" s="84" t="str">
+        <x:v>contracts/image-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-011）</x:v>
+      </x:c>
+      <x:c r="P50" s="86" t="str">
+        <x:v>静态结构/引用核对通过；真实图像分析与验收待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="83" t="str">
@@ -24894,7 +24898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdee6a2a6a2e4287"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34366652a75e46c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28184,9 +28188,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L78" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M78" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M78" s="84" t="str">
+        <x:v>contracts/image-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-011）</x:v>
+      </x:c>
       <x:c r="N78" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43627,7 +43633,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a6a645afbc4493"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3f7e64bb124de6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43909,7 +43915,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8c437884a624a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a6c52054dcd4183"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45325,7 +45331,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e9d112230234ea3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0f83f994f3472f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45739,7 +45745,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a5d2e2baab246d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95e6db68c83a4a20"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49086,7 +49092,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bb20acfe5f94a85"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0da0c6b6edf4425"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6ca48f80dfec4275"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R5ea917f448e54b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rcc36f4b1e1844df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rf383ab1898c4415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Ra4af4195f3dd459e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1b7abb2ba317451b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R781202f09b894604"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4a432716f72c47ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3b1e05c4e6ee4c0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6f821871970b4034"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Raaec8b3487864c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rab827182acf8498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re64faf0426e54890"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R101cda2bccac4081"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd8689eca28f54142"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6f76fb5b26ee495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rae9cc00536884151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc8545542401642fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rb9384ede721e42eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R41c84531bca24b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb379009c404d4290"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3c14351f3c0d41a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rec9c8aa7054d4223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R80747bef0c6244c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2f91b1975b5d4518"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R91ce8c22c65f4c96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3386a21db476415a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4e332b1d854c46a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0d8805159ebf4629"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Reca90c02c9ae4204"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0047c9c8236049c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd9267c6923a943ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rfaf25d954f984a5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R763f15c4b61046f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc31ed321b3c84b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4437e4b76e27442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8aaa149d7e484222"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R68a710e00f6f493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7b6a33452bdd4254"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R23a2aa70ecf946ff"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdb1205fe50134488"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5adc672a060b4415"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R918d20d3e7834fa5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb50f17b643324665"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76e68329b79d4c6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf1cc141e1ba4d06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re39f712b7b904cef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44f0333749004a41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13887,10 +13887,14 @@
       </x:c>
       <x:c r="M51" s="84" t="str"/>
       <x:c r="N51" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O51" s="84" t="str"/>
-      <x:c r="P51" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O51" s="84" t="str">
+        <x:v>contracts/asset-inventory.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-012）</x:v>
+      </x:c>
+      <x:c r="P51" s="86" t="str">
+        <x:v>路径/引用/fixture静态核对通过；真实目录扫描待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="83" t="str">
@@ -24898,7 +24902,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R34366652a75e46c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0193a94761d433c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28230,9 +28234,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L79" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M79" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M79" s="84" t="str">
+        <x:v>contracts/asset-inventory.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-012）</x:v>
+      </x:c>
       <x:c r="N79" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43633,7 +43639,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c3f7e64bb124de6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bcaca39000247f2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43915,7 +43921,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a6c52054dcd4183"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde728481473e4958"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45331,7 +45337,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0f83f994f3472f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cecfeae91524244"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45745,7 +45751,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95e6db68c83a4a20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0321a41afd284b36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49092,7 +49098,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0da0c6b6edf4425"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe647f227424cd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb379009c404d4290"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3c14351f3c0d41a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rec9c8aa7054d4223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R80747bef0c6244c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2f91b1975b5d4518"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R91ce8c22c65f4c96"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3386a21db476415a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R4e332b1d854c46a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0d8805159ebf4629"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Reca90c02c9ae4204"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0047c9c8236049c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd9267c6923a943ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rfaf25d954f984a5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R763f15c4b61046f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc31ed321b3c84b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4437e4b76e27442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8aaa149d7e484222"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R68a710e00f6f493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7b6a33452bdd4254"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R23a2aa70ecf946ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rbc2f1192482c4804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd46ac4ec87164b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R82774ab8409c47b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcdacc88337d74a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rdf2b657551b84bc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R18e80d466cb540c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R25850eadaa504c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R22b43d58e5e746c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8e37055d122041bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rfda7ebb3ef1c47cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R352b49bc5b8b4428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rbce52852e28e43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rb98e6df179094c90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra0c105ecf0bd4e23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc7d3e8c84e884677"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd0dff538366c4cf8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5464fea3f3cf4d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb6bfb5deb3254927"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Ra91c63bf16bc4853"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1e50f09ffd524e56"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5adc672a060b4415"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb38f377d7d8e4043"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb50f17b643324665"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76e634b6073844db"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf1cc141e1ba4d06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a37c5da01445bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R44f0333749004a41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ab9e43c87d34257"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13975,10 +13975,14 @@
       </x:c>
       <x:c r="M53" s="84" t="str"/>
       <x:c r="N53" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O53" s="84" t="str"/>
-      <x:c r="P53" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O53" s="84" t="str">
+        <x:v>contracts/source-bundle.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-014）</x:v>
+      </x:c>
+      <x:c r="P53" s="86" t="str">
+        <x:v>JSON/引用/冲突/去重静态核对通过；DEC-004 未决。</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="83" t="str">
@@ -24902,7 +24906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra0193a94761d433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8994144160c48f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28316,9 +28320,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L81" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M81" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M81" s="84" t="str">
+        <x:v>contracts/source-bundle.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-014）</x:v>
+      </x:c>
       <x:c r="N81" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43639,7 +43645,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9bcaca39000247f2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2db3cf992ae40c5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43921,7 +43927,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde728481473e4958"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4966b6f0c8b24a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45337,7 +45343,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9cecfeae91524244"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569f894597224849"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45751,7 +45757,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0321a41afd284b36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc187722ce54f481b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49098,7 +49104,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe647f227424cd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88c52519078e4698"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rbc2f1192482c4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd46ac4ec87164b59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R82774ab8409c47b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcdacc88337d74a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rdf2b657551b84bc9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R18e80d466cb540c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R25850eadaa504c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R22b43d58e5e746c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8e37055d122041bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rfda7ebb3ef1c47cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R352b49bc5b8b4428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rbce52852e28e43d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rb98e6df179094c90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra0c105ecf0bd4e23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc7d3e8c84e884677"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd0dff538366c4cf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5464fea3f3cf4d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb6bfb5deb3254927"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Ra91c63bf16bc4853"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1e50f09ffd524e56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3452e9ff770542cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc4a10027d1014010"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R40dc11184ac1439a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R241e58f34d9e4916"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R53d70fec40f04e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3650926a0c21459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0684bd3f9e1c4d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc00c090a81044ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf6f18dbdc3ba4b5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8a004b61228e400e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Raa962c7fb86c49db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R6c32e8bc29c545ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc1d1548ba6124e03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re4796dc58a4441ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R53ee57b362e64699"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8c7e0b1173a3437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra9b467caa7154905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6d5c3d2e4e54423b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28bc9db208184995"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rd9a9c695bc4e4da8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb38f377d7d8e4043"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8f56e2f31b554901"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76e634b6073844db"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3561f2e232214442"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2a37c5da01445bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57dc90127c714e60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ab9e43c87d34257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74254e1ac5bf4e2a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14021,10 +14021,14 @@
       </x:c>
       <x:c r="M54" s="84" t="str"/>
       <x:c r="N54" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O54" s="84" t="str"/>
-      <x:c r="P54" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O54" s="84" t="str">
+        <x:v>contracts/input-issue.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-IN-015）</x:v>
+      </x:c>
+      <x:c r="P54" s="86" t="str">
+        <x:v>JSON/引用/错误码关联静态核对通过；未运行解析器、实例校验器或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="83" t="str">
@@ -24906,7 +24910,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8994144160c48f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9067f3aa24054526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28362,9 +28366,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L82" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M82" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M82" s="84" t="str">
+        <x:v>contracts/input-issue.schema.json、catalog/fixtures；PROJECT_PLAN.md（TASK-IN-015）</x:v>
+      </x:c>
       <x:c r="N82" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43645,7 +43651,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2db3cf992ae40c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56af67cf42134fa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43927,7 +43933,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4966b6f0c8b24a05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c39642b6f4e4035"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45343,7 +45349,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R569f894597224849"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190d0862a36849e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45757,7 +45763,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc187722ce54f481b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R359c318ed8984a15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49104,7 +49110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88c52519078e4698"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc95685b8fe89488e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3452e9ff770542cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc4a10027d1014010"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R40dc11184ac1439a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R241e58f34d9e4916"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R53d70fec40f04e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3650926a0c21459b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0684bd3f9e1c4d1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc00c090a81044ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf6f18dbdc3ba4b5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8a004b61228e400e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Raa962c7fb86c49db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R6c32e8bc29c545ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc1d1548ba6124e03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re4796dc58a4441ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R53ee57b362e64699"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8c7e0b1173a3437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra9b467caa7154905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6d5c3d2e4e54423b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28bc9db208184995"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rd9a9c695bc4e4da8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re3459bb501d74791"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra106416c3ea84a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8ec6a0c6d04f4e8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9dd3b88988594cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4dbcbea22df04b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5c17227e6e7345a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd483d8ad5f174c09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ree457de582064581"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf4021456e0c94fbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab143d3ecfc64ff2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6212dac6d85249e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R71e8602a49844283"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ref998e4473b841e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re723a627b62a4355"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R29feca8a830845ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rdd882d0e7eab4246"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2bc989946c8d4197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4787379380684b9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rf9019325a33b4b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rbf8f8b801c6c41a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8f56e2f31b554901"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbee6a9a305d4821"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3561f2e232214442"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798d6b832c0244f6"/>
 </x:worksheet>
 </file>
 
@@ -10111,7 +10111,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57dc90127c714e60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4afac817f65a48e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74254e1ac5bf4e2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c31d9c209f4a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14067,10 +14067,14 @@
       </x:c>
       <x:c r="M55" s="84" t="str"/>
       <x:c r="N55" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O55" s="84" t="str"/>
-      <x:c r="P55" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O55" s="84" t="str">
+        <x:v>contracts/source-anchor.schema.json、catalog.json、fixtures.json；SourceBundle 已对齐；PROJECT_PLAN.md（TASK-IN-016）</x:v>
+      </x:c>
+      <x:c r="P55" s="86" t="str">
+        <x:v>JSON/引用/锚点身份静态核对通过；未运行解析器、网页抓取或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="83" t="str">
@@ -24910,7 +24914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9067f3aa24054526"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f66709130b46e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28408,9 +28412,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L83" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M83" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M83" s="84" t="str">
+        <x:v>contracts/source-anchor.schema.json、catalog/fixtures；source-bundle 锚点改为结构化对象</x:v>
+      </x:c>
       <x:c r="N83" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43651,7 +43657,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56af67cf42134fa4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ecfcb235746412b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43933,7 +43939,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c39642b6f4e4035"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a2eb4951594d7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45349,7 +45355,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190d0862a36849e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea1723d8b3b4202"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45763,7 +45769,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R359c318ed8984a15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eaed44682e74295"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49110,7 +49116,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc95685b8fe89488e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03d00a0e8ef0420d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re3459bb501d74791"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra106416c3ea84a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R8ec6a0c6d04f4e8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9dd3b88988594cea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4dbcbea22df04b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5c17227e6e7345a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd483d8ad5f174c09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ree457de582064581"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf4021456e0c94fbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab143d3ecfc64ff2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6212dac6d85249e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R71e8602a49844283"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ref998e4473b841e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re723a627b62a4355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R29feca8a830845ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rdd882d0e7eab4246"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2bc989946c8d4197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4787379380684b9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rf9019325a33b4b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rbf8f8b801c6c41a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdd08715b2f6f42f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R19151a988f0d4bdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb98d18af6e4e4f7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R0819315f5f614893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc7b212c6d2e74380"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re6c4075dac494287"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rcd25457e3a134ba1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7021267890c94f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R58572be646054c5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdb114ab9ec26400b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd5728105cc9041ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd51afe842b4c453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R896ec45790bd4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rebb69eba579c418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R589e798bd26a4f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R073cde68822944f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5a46ae017f034232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfcb51c7bf0634b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd5299e75103c4206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0cd8bb95f3184bfb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbee6a9a305d4821"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R407ca63e8208437b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R798d6b832c0244f6"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R578b65ceb7764848"/>
 </x:worksheet>
 </file>
 
@@ -5114,9 +5114,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J9" s="86" t="str">
+        <x:v>TASK-CNT-001 草案见 contracts/fact-constraint-set.schema.json、catalog.json、fixtures.json；事实抽取/改写校验器待实现。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -10111,7 +10113,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4afac817f65a48e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ac681e47cf749c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3c31d9c209f4a05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e98ff2c3094359"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14113,10 +14115,14 @@
       </x:c>
       <x:c r="M56" s="84" t="str"/>
       <x:c r="N56" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O56" s="84" t="str"/>
-      <x:c r="P56" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O56" s="84" t="str">
+        <x:v>contracts/fact-constraint-set.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-001）</x:v>
+      </x:c>
+      <x:c r="P56" s="86" t="str">
+        <x:v>JSON/refs/evidence 锚点关联静态核对通过；未运行引擎或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="83" t="str">
@@ -24914,7 +24920,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10f66709130b46e9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a7fd4844c5448b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28454,9 +28460,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L84" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M84" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M84" s="84" t="str">
+        <x:v>contracts/fact-constraint-set.schema.json、catalog/fixtures；PROJECT_PLAN.md（TASK-CNT-001）</x:v>
+      </x:c>
       <x:c r="N84" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43657,7 +43665,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ecfcb235746412b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf630671c3b4905"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43939,7 +43947,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a2eb4951594d7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52958fc0775d4efb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45355,7 +45363,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfea1723d8b3b4202"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f8357c8172c4d45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45769,7 +45777,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eaed44682e74295"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6532bbf93654133"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49116,7 +49124,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03d00a0e8ef0420d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c09867d35064322"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdd08715b2f6f42f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R19151a988f0d4bdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb98d18af6e4e4f7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R0819315f5f614893"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc7b212c6d2e74380"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re6c4075dac494287"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rcd25457e3a134ba1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7021267890c94f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R58572be646054c5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdb114ab9ec26400b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd5728105cc9041ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd51afe842b4c453b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R896ec45790bd4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rebb69eba579c418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R589e798bd26a4f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R073cde68822944f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5a46ae017f034232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfcb51c7bf0634b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd5299e75103c4206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0cd8bb95f3184bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6e6a17dd896541d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R780db8dee3454a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rfc6d3a2d79f949df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R852be8c0116a482a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R259df02396f1418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re5c97bf82a634feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9f7f58040ef14541"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R998e83a039c14151"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3ac38d0fafc0446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8a34a20e5630484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R8806bde5514e4bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8c1e901899354578"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6ae4168b589045cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R089433894c8e4ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rb5cd6fcb07be4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2c66184c391e497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0e9d2175011c4e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2e86debf63964330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R78218458923545f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf8d73bff36f847ef"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R407ca63e8208437b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R323f422d9a3b4109"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R578b65ceb7764848"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c14aac1232f43df"/>
 </x:worksheet>
 </file>
 
@@ -10113,7 +10113,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ac681e47cf749c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc53f4458f8e4cb1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11302,7 +11302,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e98ff2c3094359"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c61627aef3b4a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14161,10 +14161,14 @@
       </x:c>
       <x:c r="M57" s="84" t="str"/>
       <x:c r="N57" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O57" s="84" t="str"/>
-      <x:c r="P57" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O57" s="84" t="str">
+        <x:v>contracts/data-binding.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-002）</x:v>
+      </x:c>
+      <x:c r="P57" s="86" t="str">
+        <x:v>静态核对通过；引擎和AC未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="83" t="str">
@@ -24920,7 +24924,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4a7fd4844c5448b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8912086ca504a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28502,9 +28506,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L85" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M85" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M85" s="84" t="str">
+        <x:v>contracts/data-binding.*.json</x:v>
+      </x:c>
       <x:c r="N85" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43665,7 +43671,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cf630671c3b4905"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149332a5d70a4c75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43947,7 +43953,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52958fc0775d4efb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b2603719b64117"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45363,7 +45369,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f8357c8172c4d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1e96134c854072"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45777,7 +45783,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6532bbf93654133"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf668ea98265b483c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49124,7 +49130,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c09867d35064322"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec31a04ab5f42b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6e6a17dd896541d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R780db8dee3454a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rfc6d3a2d79f949df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R852be8c0116a482a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R259df02396f1418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re5c97bf82a634feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9f7f58040ef14541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R998e83a039c14151"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3ac38d0fafc0446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8a34a20e5630484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R8806bde5514e4bcc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8c1e901899354578"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6ae4168b589045cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R089433894c8e4ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rb5cd6fcb07be4530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2c66184c391e497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0e9d2175011c4e77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2e86debf63964330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R78218458923545f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf8d73bff36f847ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rff1c0f055c0e46f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Raee1f80bba4d4356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4619cee21a644338"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R542ab09760b440d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9f8bdc2198e0482b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R31bcb456c6994726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0f2ef2338ca34ddd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d40df389fa04fe9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra1d8111e52a34ed5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ra72d23bd1c504f64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcda320ac21514180"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7362643f45954936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2cc564a5fdda41e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Raeeea85fcecc42ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9315f88dfff94858"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2a86886790334a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R73e2942af14744d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R08142583286a4005"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0b7a8fce80da43a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R40a16e0e9e7a44c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R323f422d9a3b4109"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6bd5f72fa503460e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c14aac1232f43df"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad3c782bcde4780"/>
 </x:worksheet>
 </file>
 
@@ -5084,9 +5084,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J8" s="86" t="str">
+        <x:v>contracts/evidence-conflict.*.json；DEC-004/检测运行时未完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -10113,7 +10115,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc53f4458f8e4cb1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5af59599554567"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11302,7 +11304,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c61627aef3b4a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b3a4b427574673"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14207,10 +14209,14 @@
       </x:c>
       <x:c r="M58" s="84" t="str"/>
       <x:c r="N58" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O58" s="84" t="str"/>
-      <x:c r="P58" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O58" s="84" t="str">
+        <x:v>contracts/evidence-conflict.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-003）</x:v>
+      </x:c>
+      <x:c r="P58" s="86" t="str">
+        <x:v>静态核对通过；运行时与AC未执行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="83" t="str">
@@ -24924,7 +24930,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8912086ca504a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda00f335a89c4fe7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28548,9 +28554,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L86" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M86" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M86" s="84" t="str">
+        <x:v>contracts/evidence-conflict.*.json</x:v>
+      </x:c>
       <x:c r="N86" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43671,7 +43679,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149332a5d70a4c75"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1e3894526e94f5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43953,7 +43961,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18b2603719b64117"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca17e703e05e477a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45369,7 +45377,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce1e96134c854072"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cebd2050603419d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45783,7 +45791,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf668ea98265b483c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0a86eba47f4960"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49130,7 +49138,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reec31a04ab5f42b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63361f5ddae948cb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rff1c0f055c0e46f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Raee1f80bba4d4356"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4619cee21a644338"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R542ab09760b440d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9f8bdc2198e0482b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R31bcb456c6994726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0f2ef2338ca34ddd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d40df389fa04fe9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra1d8111e52a34ed5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ra72d23bd1c504f64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcda320ac21514180"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7362643f45954936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2cc564a5fdda41e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Raeeea85fcecc42ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9315f88dfff94858"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2a86886790334a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R73e2942af14744d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R08142583286a4005"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0b7a8fce80da43a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R40a16e0e9e7a44c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re0530f1972ec458a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R93f25e7982214b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2a08da65094e4c64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7e97b2be697740d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R75c930bb4cdd4775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rfda185657e2b47b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1bca74e502424195"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R03b6bf7f885b4b55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5cb7d236ec554c9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb84d624799f449f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3ce6b325bb01425e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R061eaa6d23954c30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra1505a25091d4caa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R1da86260dcf04b4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R94379f46c7ad47e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R685fb50c88154f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5359740313a14ac2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9e9ea483fc854627"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9a7cbfcd558e42dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R79803f47f85e4449"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6bd5f72fa503460e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28a5b316bc18426f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raad3c782bcde4780"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0289eb76024359"/>
 </x:worksheet>
 </file>
 
@@ -5151,7 +5151,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J10" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TASK-CNT-004 草案与六个 fixture 见 contracts/assumption.*.json；运行时集成/DEC-005 待后续任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -10115,7 +10115,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf5af59599554567"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd09c5f85dacf410f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11304,7 +11304,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b3a4b427574673"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R206223427d3742e8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14255,10 +14255,14 @@
       </x:c>
       <x:c r="M59" s="84" t="str"/>
       <x:c r="N59" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O59" s="84" t="str"/>
-      <x:c r="P59" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O59" s="84" t="str">
+        <x:v>contracts/assumption.schema.json、catalog.json、fixtures.json；contracts/evidence-conflict.fixtures.json；PROJECT_PLAN.md（TASK-CNT-004）</x:v>
+      </x:c>
+      <x:c r="P59" s="86" t="str">
+        <x:v>静态核对通过（6 个 fixture）；未运行 JSON Schema 实例验证器、运行时或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="83" t="str">
@@ -24930,7 +24934,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda00f335a89c4fe7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0305539fb5c40e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28596,9 +28600,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L87" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M87" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M87" s="84" t="str">
+        <x:v>contracts/assumption.*.json；contracts/evidence-conflict.fixtures.json；PROJECT_PLAN.md（TASK-CNT-004）</x:v>
+      </x:c>
       <x:c r="N87" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43679,7 +43685,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1e3894526e94f5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd685113f57b24dde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43961,7 +43967,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca17e703e05e477a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb239e0364cb44d3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45377,7 +45383,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7cebd2050603419d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R927be342e2524358"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45791,7 +45797,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f0a86eba47f4960"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1cfa60994a04baf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49138,7 +49144,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63361f5ddae948cb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c317325afbb4aaf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re0530f1972ec458a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R93f25e7982214b59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R2a08da65094e4c64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7e97b2be697740d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R75c930bb4cdd4775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rfda185657e2b47b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1bca74e502424195"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R03b6bf7f885b4b55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5cb7d236ec554c9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb84d624799f449f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3ce6b325bb01425e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R061eaa6d23954c30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra1505a25091d4caa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R1da86260dcf04b4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R94379f46c7ad47e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R685fb50c88154f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5359740313a14ac2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R9e9ea483fc854627"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9a7cbfcd558e42dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R79803f47f85e4449"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc5565c6d4f2e468b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rbcfce2a9402b415b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc6e8defaf7cc4a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R964accfe7ba54c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R31c9b6121234483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc6a0281207004909"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rea75f9cd8a1a402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8bb28a9129a3496a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R7414cdb9e07d4119"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6516bd2d597a49e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd7512067c60c441f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R573d2faeb6044775"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R907f983638c44ed2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R201bad9d18f24077"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9b0eda7c465044ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rcae9d464270b433b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0fda9b531d3f484e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3781beeac98f4b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R627619c0c8df4bf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rfae6d98f482f4177"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R28a5b316bc18426f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6bcf448349a4b55"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0289eb76024359"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73de8af459014d3e"/>
 </x:worksheet>
 </file>
 
@@ -10115,7 +10115,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd09c5f85dacf410f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e51858d67f42a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11304,7 +11304,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R206223427d3742e8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R586bf4c566164573"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14301,10 +14301,14 @@
       </x:c>
       <x:c r="M60" s="84" t="str"/>
       <x:c r="N60" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O60" s="84" t="str"/>
-      <x:c r="P60" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O60" s="84" t="str">
+        <x:v>contracts/audience-profile.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-005）</x:v>
+      </x:c>
+      <x:c r="P60" s="86" t="str">
+        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="83" t="str">
@@ -24934,7 +24938,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb0305539fb5c40e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd1ea68fb0114604"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28642,9 +28646,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L88" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M88" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M88" s="84" t="str">
+        <x:v>contracts/audience-profile.*.json；PROJECT_PLAN.md（TASK-CNT-005）</x:v>
+      </x:c>
       <x:c r="N88" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43685,7 +43691,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd685113f57b24dde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65375955c074140"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43967,7 +43973,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb239e0364cb44d3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf06f444fd1654e56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45383,7 +45389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R927be342e2524358"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2afcac7c4e4c4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45797,7 +45803,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1cfa60994a04baf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba70216397414853"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49144,7 +49150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c317325afbb4aaf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5561874ed9ae497e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc5565c6d4f2e468b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rbcfce2a9402b415b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc6e8defaf7cc4a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R964accfe7ba54c21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R31c9b6121234483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc6a0281207004909"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rea75f9cd8a1a402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8bb28a9129a3496a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R7414cdb9e07d4119"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6516bd2d597a49e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd7512067c60c441f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R573d2faeb6044775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R907f983638c44ed2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R201bad9d18f24077"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9b0eda7c465044ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rcae9d464270b433b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0fda9b531d3f484e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3781beeac98f4b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R627619c0c8df4bf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rfae6d98f482f4177"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd23dabb2af834179"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd6635abccafe4d55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4fd35f5795ff490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcce0a4f2870047f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6f43807d490c4e30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4312d61533f94b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbdbe0a0da53a4f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1576a72f3aa346f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb73026654f1b48d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ra80547abf43b4fd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R07c99713663a4ee4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rde569f559d2946a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6371326109554a99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd352ec0578ed45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R4725e30b601d45e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6ff2675b040245b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R68878f3026374a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8bb6903b7a2a47f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6ee104be5a184e21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0ac1816d12134e78"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra6bcf448349a4b55"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd8f60f8673a54304"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73de8af459014d3e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fdbfe6cf93a489d"/>
 </x:worksheet>
 </file>
 
@@ -10115,7 +10115,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R86e51858d67f42a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa1c560b2e3a4b49"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11304,7 +11304,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R586bf4c566164573"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64a7baf760341f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14347,10 +14347,14 @@
       </x:c>
       <x:c r="M61" s="84" t="str"/>
       <x:c r="N61" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O61" s="84" t="str"/>
-      <x:c r="P61" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O61" s="84" t="str">
+        <x:v>contracts/presentation-scenario.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-006）</x:v>
+      </x:c>
+      <x:c r="P61" s="86" t="str">
+        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="83" t="str">
@@ -24938,7 +24942,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd1ea68fb0114604"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b4615c301f47fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28688,9 +28692,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L89" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M89" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M89" s="84" t="str">
+        <x:v>contracts/presentation-scenario.*.json；PROJECT_PLAN.md（TASK-CNT-006）</x:v>
+      </x:c>
       <x:c r="N89" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43691,7 +43697,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd65375955c074140"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf60bfbf8e074a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43973,7 +43979,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf06f444fd1654e56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d78328097cf48b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45389,7 +45395,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2afcac7c4e4c4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e572202e5334919"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45803,7 +45809,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba70216397414853"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07782288916b4c5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49150,7 +49156,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5561874ed9ae497e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad00195a0584893"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd23dabb2af834179"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd6635abccafe4d55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4fd35f5795ff490f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcce0a4f2870047f6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6f43807d490c4e30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4312d61533f94b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbdbe0a0da53a4f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1576a72f3aa346f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb73026654f1b48d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ra80547abf43b4fd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R07c99713663a4ee4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rde569f559d2946a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6371326109554a99"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd352ec0578ed45e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R4725e30b601d45e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6ff2675b040245b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R68878f3026374a7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8bb6903b7a2a47f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6ee104be5a184e21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0ac1816d12134e78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2da2cfdb14c3443c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3bfbdd47cb9f4840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R769f347f045f4948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7235a391b1954794"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rda18b68a75304cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1aff558e345c427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra26ebf4a48b74be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rfc9308c12d32491f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rbea375aefb7e445a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R56a7dcc063584b82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rac43336bf16140e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R489335fea93f44f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra7106fb55bd5488c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rfc451b9781834fe8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R85ee5e8d3af641df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ra80666dc2c824918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra8e12f1190b8416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6bf4306511eb40af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc507f24d710e4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rba5d723664374e12"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd8f60f8673a54304"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra369dd30ddae4052"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fdbfe6cf93a489d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9076f3cbd04f18"/>
 </x:worksheet>
 </file>
 
@@ -10115,7 +10115,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa1c560b2e3a4b49"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b6671411154f83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11304,7 +11304,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64a7baf760341f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4b5b06c03614851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14393,10 +14393,14 @@
       </x:c>
       <x:c r="M62" s="84" t="str"/>
       <x:c r="N62" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O62" s="84" t="str"/>
-      <x:c r="P62" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O62" s="84" t="str">
+        <x:v>contracts/language-style-spec.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-007）</x:v>
+      </x:c>
+      <x:c r="P62" s="86" t="str">
+        <x:v>静态核对通过（4 个 fixture，覆盖中文/英文/混合）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="83" t="str">
@@ -24942,7 +24946,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7b4615c301f47fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R963891566e894801"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28734,9 +28738,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L90" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M90" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M90" s="84" t="str">
+        <x:v>contracts/language-style-spec.*.json；PROJECT_PLAN.md（TASK-CNT-007）</x:v>
+      </x:c>
       <x:c r="N90" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43697,7 +43703,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf60bfbf8e074a06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b449b96792343f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43979,7 +43985,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d78328097cf48b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687b53067e2246b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45395,7 +45401,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e572202e5334919"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9758a6eecdb45ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45809,7 +45815,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07782288916b4c5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff12cd4365494066"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49156,7 +49162,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3ad00195a0584893"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752dc5a2dbc448db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2da2cfdb14c3443c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3bfbdd47cb9f4840"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R769f347f045f4948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7235a391b1954794"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rda18b68a75304cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1aff558e345c427b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra26ebf4a48b74be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rfc9308c12d32491f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rbea375aefb7e445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R56a7dcc063584b82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rac43336bf16140e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R489335fea93f44f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra7106fb55bd5488c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rfc451b9781834fe8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R85ee5e8d3af641df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ra80666dc2c824918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra8e12f1190b8416b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6bf4306511eb40af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc507f24d710e4530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rba5d723664374e12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf70be67d00804102"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra58dd6d4773b43d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R142efb2d4b8a4969"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R51742b644c534c10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R30153ac9e0054577"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7102b238cd594391"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R613970173a4946ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8f84dc02eed749e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd147f3245f834b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb0091aafe2a44d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc364695e0a7248cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0dbcf076ec0d4fff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R35e3000e051c4271"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5585856f76454153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rffa6b8b3fcac40d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0510a9aa972c4fd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R36082d7e507b424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2f89d31a3c6543e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8edcb7c0d97740ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R78f4411a7ba64345"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra369dd30ddae4052"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R377b02decf6043fb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d9076f3cbd04f18"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0d3a41a07b14f3b"/>
 </x:worksheet>
 </file>
 
@@ -5210,9 +5210,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J12" s="86" t="str">
+        <x:v>TASK-CNT-008 契约见 contracts/deck-thesis.*.json；DEC-009 选择/生成机制与运行时待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -10115,7 +10117,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b6671411154f83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec1535c85574294"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11304,7 +11306,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4b5b06c03614851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7cf190ce23c45b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14439,10 +14441,14 @@
       </x:c>
       <x:c r="M63" s="84" t="str"/>
       <x:c r="N63" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O63" s="84" t="str"/>
-      <x:c r="P63" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O63" s="84" t="str">
+        <x:v>contracts/deck-thesis.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-008）</x:v>
+      </x:c>
+      <x:c r="P63" s="86" t="str">
+        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、DEC-009、运行时和 AC 未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="83" t="str">
@@ -24946,7 +24952,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R963891566e894801"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re627175cb3924aa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28780,9 +28786,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L91" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M91" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M91" s="84" t="str">
+        <x:v>contracts/deck-thesis.*.json；PROJECT_PLAN.md（TASK-CNT-008）</x:v>
+      </x:c>
       <x:c r="N91" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43703,7 +43711,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b449b96792343f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d19a56bf904526"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43985,7 +43993,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R687b53067e2246b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fb8c8d5fa148d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45401,7 +45409,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9758a6eecdb45ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fc4ce4b24234159"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45815,7 +45823,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff12cd4365494066"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70f2a5c1ed124def"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49162,7 +49170,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752dc5a2dbc448db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R991799bd584e44f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf70be67d00804102"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Ra58dd6d4773b43d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R142efb2d4b8a4969"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R51742b644c534c10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R30153ac9e0054577"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7102b238cd594391"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R613970173a4946ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8f84dc02eed749e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd147f3245f834b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb0091aafe2a44d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc364695e0a7248cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0dbcf076ec0d4fff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R35e3000e051c4271"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5585856f76454153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rffa6b8b3fcac40d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0510a9aa972c4fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R36082d7e507b424f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2f89d31a3c6543e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8edcb7c0d97740ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R78f4411a7ba64345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R315c86e159034633"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R1f89c786c56d4bb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rcbb936bfa10f4f67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcfe6b49702024086"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R30ad3028f38c49b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R36f306d0a0ab4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R148818b0adb642ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rbe14b38d177f457d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R4c195fdebbba45ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1487f0768f0248cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0ce7f03f6f184ac5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R38bdd5dbf79344e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re5f42e9728144340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7e4aa4c3b9ea4ad4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R889c80cfd68b4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4440411de82f4255"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rfe5657cc02e348ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R5a450e52096a4221"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rf764eea2483b4006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rbb8827bfee5448b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R377b02decf6043fb"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69786295978a496a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0d3a41a07b14f3b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a9477fd256e4471"/>
 </x:worksheet>
 </file>
 
@@ -5242,9 +5242,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J13" s="86" t="str">
+        <x:v>TASK-CNT-009 契约见 contracts/content-graph.*.json；关系抽取与图语义校验待后续任务。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -10117,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raec1535c85574294"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30da878c860043ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11306,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc7cf190ce23c45b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01f60576e06d43d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14487,10 +14489,14 @@
       </x:c>
       <x:c r="M64" s="84" t="str"/>
       <x:c r="N64" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O64" s="84" t="str"/>
-      <x:c r="P64" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O64" s="84" t="str">
+        <x:v>contracts/content-graph.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-009）</x:v>
+      </x:c>
+      <x:c r="P64" s="86" t="str">
+        <x:v>静态核对通过（3 个 fixture）；关系抽取、图语义校验、运行时与 AC 未运行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="83" t="str">
@@ -24952,7 +24958,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re627175cb3924aa4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d6128e24f1743f0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28828,9 +28834,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L92" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M92" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M92" s="84" t="str">
+        <x:v>contracts/content-graph.*.json；PROJECT_PLAN.md（TASK-CNT-009）</x:v>
+      </x:c>
       <x:c r="N92" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43711,7 +43719,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb7d19a56bf904526"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77f25ee64794deb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43993,7 +44001,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2fb8c8d5fa148d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aa61059b1de417d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45409,7 +45417,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fc4ce4b24234159"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab31e5a1bb6c40ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45823,7 +45831,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70f2a5c1ed124def"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5353e94801204ca2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49170,7 +49178,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R991799bd584e44f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3414a53fa5449e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R315c86e159034633"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R1f89c786c56d4bb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rcbb936bfa10f4f67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcfe6b49702024086"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R30ad3028f38c49b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R36f306d0a0ab4e86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R148818b0adb642ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rbe14b38d177f457d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R4c195fdebbba45ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1487f0768f0248cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0ce7f03f6f184ac5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R38bdd5dbf79344e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re5f42e9728144340"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7e4aa4c3b9ea4ad4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R889c80cfd68b4887"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4440411de82f4255"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rfe5657cc02e348ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R5a450e52096a4221"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rf764eea2483b4006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rbb8827bfee5448b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc7f982e6886b4a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rda4a2c850fc8453f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4922516cc5cc4ff4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rdcf5376f8e374bc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R911abeb858ae4a84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rd6c42b82b2ed40e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9177c725c1f34f23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb8024bf28c184129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rc0b530228e9f484b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R56befc6a73a2412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3b76b3c932ef4f7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R13d12fc734f24722"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rde32f9bb8f284e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R4994e37204ba4def"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6e6baa266c6c4d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R36aae23a1e0a4988"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1eaa6fc8b63a4a03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R995078ef5b374cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R05c495d1a69847a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf7e25e28e8644099"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69786295978a496a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaebe8d660bb4296"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a9477fd256e4471"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07813ffc1fc042c5"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30da878c860043ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53f8da498d624c2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01f60576e06d43d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R958f6753865b4113"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14535,10 +14535,14 @@
       </x:c>
       <x:c r="M65" s="84" t="str"/>
       <x:c r="N65" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O65" s="84" t="str"/>
-      <x:c r="P65" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O65" s="84" t="str">
+        <x:v>contracts/citation-policy.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-010）</x:v>
+      </x:c>
+      <x:c r="P65" s="86" t="str">
+        <x:v>静态核对通过（8 个 fixture）；未运行 JSON Schema 实例验证器、DEC-021、引用展示运行时和 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="83" t="str">
@@ -24958,7 +24962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d6128e24f1743f0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9c38425f204e70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28876,9 +28880,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L93" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M93" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M93" s="84" t="str">
+        <x:v>contracts/citation-policy.*.json；PROJECT_PLAN.md（TASK-CNT-010）</x:v>
+      </x:c>
       <x:c r="N93" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43719,7 +43725,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd77f25ee64794deb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54310b97531543aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44001,7 +44007,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0aa61059b1de417d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R577698e142914774"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45417,7 +45423,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab31e5a1bb6c40ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24d1ebfe514c4993"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45831,7 +45837,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5353e94801204ca2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca43d5944b774dc5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49178,7 +49184,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3414a53fa5449e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raebd276ebdff4f97"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc7f982e6886b4a4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rda4a2c850fc8453f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4922516cc5cc4ff4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rdcf5376f8e374bc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R911abeb858ae4a84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rd6c42b82b2ed40e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9177c725c1f34f23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb8024bf28c184129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rc0b530228e9f484b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R56befc6a73a2412b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R3b76b3c932ef4f7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R13d12fc734f24722"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rde32f9bb8f284e3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R4994e37204ba4def"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6e6baa266c6c4d20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R36aae23a1e0a4988"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1eaa6fc8b63a4a03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R995078ef5b374cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R05c495d1a69847a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf7e25e28e8644099"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd0af5d21d83141df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rade12772d8d64f44"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re20263b95008437a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rebd7a63dba874e41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3a5ed1f68c5146cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf945ab8f0e514cfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5ef0aefeda284a4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R59596c4c5a054343"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rea1c268015024b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbbe127362f4648f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rbc3e200f7f504a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra94944e030774e5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0c408beda8a24373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9c1e7627965a4a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9acce2c316a84e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rac8fc219affe455a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rdf583db99d154c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8acd4007bca14abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R337e27aa7a8343dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rc9dfd99854684feb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Raaebe8d660bb4296"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R529077b12bc947e6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07813ffc1fc042c5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b6dc5e23ae49ac"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53f8da498d624c2f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R767f5cd2a6254ee8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R958f6753865b4113"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fcbb3a07b5541b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14581,10 +14581,14 @@
       </x:c>
       <x:c r="M66" s="84" t="str"/>
       <x:c r="N66" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O66" s="84" t="str"/>
-      <x:c r="P66" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O66" s="84" t="str">
+        <x:v>contracts/content-rewrite-trace.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-011）</x:v>
+      </x:c>
+      <x:c r="P66" s="86" t="str">
+        <x:v>静态核对通过（4 个 fixture）；未运行 JSON Schema 实例验证器、摘要运行时/语义检查和 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="83" t="str">
@@ -24962,7 +24966,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb9c38425f204e70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R842b3bf214f84435"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28922,9 +28926,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L94" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M94" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M94" s="84" t="str">
+        <x:v>contracts/content-rewrite-trace.*.json；PROJECT_PLAN.md（TASK-CNT-011）</x:v>
+      </x:c>
       <x:c r="N94" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43725,7 +43731,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54310b97531543aa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R828d9ab89b5c4381"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44007,7 +44013,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R577698e142914774"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899c166829f94cbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45423,7 +45429,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24d1ebfe514c4993"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1174e7a21f4a7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45837,7 +45843,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca43d5944b774dc5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ab5acdc872148e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49184,7 +49190,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raebd276ebdff4f97"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab4069bec3b542d3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd0af5d21d83141df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rade12772d8d64f44"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Re20263b95008437a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rebd7a63dba874e41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3a5ed1f68c5146cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf945ab8f0e514cfe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5ef0aefeda284a4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R59596c4c5a054343"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rea1c268015024b2f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbbe127362f4648f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rbc3e200f7f504a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra94944e030774e5b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0c408beda8a24373"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9c1e7627965a4a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9acce2c316a84e1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rac8fc219affe455a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rdf583db99d154c69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8acd4007bca14abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R337e27aa7a8343dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rc9dfd99854684feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb647bdabc30e48ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R388a2cfadcea405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R28fded8d66b34b72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rfcce5c14e9964184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R541a87c92ac64b90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R27bd8d9531224e7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7f39908eda2646f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Re3410a395a604cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R96e450ad692f4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R0e1b991537834e7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf9611b8902d449b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rad02a72eb0c04cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rbd85e3101d69411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7640b3a7d97948d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2c0132feeae0418f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R32ee3de554e14019"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ref30adafbb794067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R199d2d2c367e4305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5b39fb5c35044999"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R661351b5d2d04165"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R529077b12bc947e6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d869251386c491e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22b6dc5e23ae49ac"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R947ab2864c104cdc"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R767f5cd2a6254ee8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410ac8b4c0054a45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fcbb3a07b5541b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbea3265b364955"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14627,10 +14627,14 @@
       </x:c>
       <x:c r="M67" s="84" t="str"/>
       <x:c r="N67" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O67" s="84" t="str"/>
-      <x:c r="P67" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O67" s="84" t="str">
+        <x:v>contracts/hallucination-guard.schema.json；catalog.json；fixtures.json</x:v>
+      </x:c>
+      <x:c r="P67" s="86" t="str">
+        <x:v>静态核对通过（6 个 fixture）；未运行 JSON Schema 实例验证器、语义/运行时检测器或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="83" t="str">
@@ -24966,7 +24970,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R842b3bf214f84435"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R925bc5712b72436f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28968,9 +28972,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L95" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M95" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M95" s="84" t="str">
+        <x:v>contracts/hallucination-guard.*.json；PROJECT_PLAN.md（TASK-CNT-012）</x:v>
+      </x:c>
       <x:c r="N95" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43731,7 +43737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R828d9ab89b5c4381"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a6ddda652be4fb4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44013,7 +44019,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R899c166829f94cbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea64348ff3d24070"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45429,7 +45435,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1174e7a21f4a7e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f1d5c5a32f6424d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45843,7 +45849,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ab5acdc872148e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b51942215a4be9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49190,7 +49196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab4069bec3b542d3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa64328379864f14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb647bdabc30e48ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R388a2cfadcea405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R28fded8d66b34b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rfcce5c14e9964184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R541a87c92ac64b90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R27bd8d9531224e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7f39908eda2646f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Re3410a395a604cd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R96e450ad692f4819"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R0e1b991537834e7e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf9611b8902d449b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rad02a72eb0c04cc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rbd85e3101d69411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7640b3a7d97948d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2c0132feeae0418f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R32ee3de554e14019"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ref30adafbb794067"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R199d2d2c367e4305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5b39fb5c35044999"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R661351b5d2d04165"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc9d48fe23b1c40b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb6b2f8a546704096"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra327547e6fea44f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R06ac388dab2944b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1883028611d546c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra207949adf2c4155"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Re3bb0854593e4c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc84db463527e44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R108c9ab2333b4317"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3a8c437ddada4f56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0c0e094411f84c2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2213d93d3ccc4219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9787ceb8fa8848e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra39122148587493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rff733880757a407b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5e29aa8f7b1447d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R224a26bf85bc40fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdd1504420cd74df1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R40a475050efa4ca6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R473e93c82a114406"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2d869251386c491e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3448c2eb325243c2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R947ab2864c104cdc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9aedd6d7a3478c"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R410ac8b4c0054a45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8da82b39e9c4dd2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cbea3265b364955"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2455ba3e91448b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14673,10 +14673,14 @@
       </x:c>
       <x:c r="M68" s="84" t="str"/>
       <x:c r="N68" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O68" s="84" t="str"/>
-      <x:c r="P68" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O68" s="84" t="str">
+        <x:v>contracts/notes-spec.schema.json；catalog.json；fixtures.json</x:v>
+      </x:c>
+      <x:c r="P68" s="86" t="str">
+        <x:v>静态核对通过（3 个 fixture）；未运行 JSON Schema 实例验证器、PPT notes writer、PPT-023 或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="83" t="str">
@@ -24970,7 +24974,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R925bc5712b72436f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc06de211601d46d8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29014,9 +29018,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L96" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M96" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M96" s="84" t="str">
+        <x:v>contracts/notes-spec.*.json；PROJECT_PLAN.md（TASK-CNT-013）</x:v>
+      </x:c>
       <x:c r="N96" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43737,7 +43743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a6ddda652be4fb4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f9310e918e4e14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44019,7 +44025,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea64348ff3d24070"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f1f83bcc2d4f2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45435,7 +45441,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f1d5c5a32f6424d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1064b6d204b24a70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45849,7 +45855,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80b51942215a4be9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b1181bc243e4688"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49196,7 +49202,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa64328379864f14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e4885c207141c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc9d48fe23b1c40b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb6b2f8a546704096"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra327547e6fea44f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R06ac388dab2944b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1883028611d546c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra207949adf2c4155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Re3bb0854593e4c48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc84db463527e44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R108c9ab2333b4317"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3a8c437ddada4f56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R0c0e094411f84c2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2213d93d3ccc4219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9787ceb8fa8848e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra39122148587493e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rff733880757a407b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5e29aa8f7b1447d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R224a26bf85bc40fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdd1504420cd74df1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R40a475050efa4ca6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R473e93c82a114406"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R933f8cfb63d5416f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R7f2b23bd964d4869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R3c9cebda6617450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rf2ef8cd34c754e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rda17931ab926469c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R0110233bd8744091"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9bbe8c671a8b4f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5f0433eca4304fdb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra4d0640f2a2b4558"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf7d734b196f94dd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ebe2cb106494124"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re726ed2f2899441a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0f24356846394112"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rb720f3ff71874a72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc3dbbf27734c4e1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R21f6839f5c864bfa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra9d649c40b95497e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R750cf3d16a294024"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6e68abeaaa4a483d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R79e614aa6c5e4786"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3448c2eb325243c2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1effbd6496e94ec0"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b9aedd6d7a3478c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6835100e11404ebf"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re8da82b39e9c4dd2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b9d08455ccc4580"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2455ba3e91448b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e1f09b7e4a4eb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14719,10 +14719,14 @@
       </x:c>
       <x:c r="M69" s="84" t="str"/>
       <x:c r="N69" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O69" s="84" t="str"/>
-      <x:c r="P69" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O69" s="84" t="str">
+        <x:v>contracts/appendix-plan.schema.json；catalog.json；fixtures.json</x:v>
+      </x:c>
+      <x:c r="P69" s="86" t="str">
+        <x:v>静态核对通过（4 个 fixture）；未运行 JSON Schema 实例验证器、附录 runtime 或 AC。</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="83" t="str">
@@ -24974,7 +24978,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc06de211601d46d8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60bc721cd574502"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29060,9 +29064,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L97" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M97" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M97" s="84" t="str">
+        <x:v>contracts/appendix-plan.*.json；PROJECT_PLAN.md（TASK-CNT-014）</x:v>
+      </x:c>
       <x:c r="N97" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43743,7 +43749,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6f9310e918e4e14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R256a7b9084a54795"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44025,7 +44031,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25f1f83bcc2d4f2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a5d088eed740be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45441,7 +45447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1064b6d204b24a70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ee56e6abd2343ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45855,7 +45861,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b1181bc243e4688"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb52337a4c104205"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49202,7 +49208,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60e4885c207141c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9dbee23551f4079"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R933f8cfb63d5416f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R7f2b23bd964d4869"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R3c9cebda6617450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rf2ef8cd34c754e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rda17931ab926469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R0110233bd8744091"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R9bbe8c671a8b4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5f0433eca4304fdb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra4d0640f2a2b4558"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf7d734b196f94dd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ebe2cb106494124"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re726ed2f2899441a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0f24356846394112"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rb720f3ff71874a72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc3dbbf27734c4e1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R21f6839f5c864bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ra9d649c40b95497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R750cf3d16a294024"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6e68abeaaa4a483d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R79e614aa6c5e4786"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra58cfcd9d82341f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R06684e65afe74b43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0565ff93b68f435c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R79492122309d4f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd2c9f564a2d944b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Refaba520a92f47ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R10e1f293b27a4a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R849a94f618e54209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R033d14f771424e82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R918d43355cb445c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R114d2cf395844206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2e0668f6a91348d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R5eba4ec57f954555"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R8d727648843745a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R251140647cd0465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R9643097a8faf45ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R90786a00a9554468"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdee5504630c84f72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc8c7c4ea7e2c4f15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R172bcf21478449ec"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1effbd6496e94ec0"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fa09730dc944aa4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6835100e11404ebf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra214e7550dff4ef0"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b9d08455ccc4580"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f34671eef7d4caa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3e1f09b7e4a4eb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96f0e0217cf402f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16525,10 +16525,14 @@
       </x:c>
       <x:c r="M110" s="84" t="str"/>
       <x:c r="N110" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O110" s="84" t="str"/>
-      <x:c r="P110" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O110" s="84" t="str">
+        <x:v>contracts/template-source-record.*.json；PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P110" s="86" t="str">
+        <x:v>静态对照 3 个上游项目及真实 PPTX；运行时、渲染与 AC 未验证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="83" t="str">
@@ -24978,7 +24982,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf60bc721cd574502"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5b3cf4b45c446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32466,9 +32470,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L178" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M178" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M178" s="84" t="str">
+        <x:v>contracts/template-source-record.*.json；PROJECT_PLAN.md（TASK-TPL-001）</x:v>
+      </x:c>
       <x:c r="N178" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43749,7 +43755,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R256a7b9084a54795"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R977b8331a2c74130"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44031,7 +44037,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38a5d088eed740be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f7827793daf40c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45447,7 +45453,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ee56e6abd2343ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb3efb21e21a4f9a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45861,7 +45867,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb52337a4c104205"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf7ec6df42e4f9d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49208,7 +49214,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9dbee23551f4079"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41bc75a5dfe40eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra58cfcd9d82341f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R06684e65afe74b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0565ff93b68f435c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R79492122309d4f24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd2c9f564a2d944b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Refaba520a92f47ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R10e1f293b27a4a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R849a94f618e54209"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R033d14f771424e82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R918d43355cb445c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R114d2cf395844206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2e0668f6a91348d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R5eba4ec57f954555"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R8d727648843745a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R251140647cd0465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R9643097a8faf45ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R90786a00a9554468"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rdee5504630c84f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc8c7c4ea7e2c4f15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R172bcf21478449ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf30dfb2a275044f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rea829b1c28034a88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R5cb4954dbfab4c79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8aa567fcee6b48c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd82fab7907464893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf3ed48dd792d43b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1b3bb2fe2aca41c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R62d03e5a8f8c4322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R6d15f81830cf49f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R5ec3565cfb124120"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc90c3ef08af04c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R22603af4be494c65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R446de2c07c344131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra7909fe5cce64724"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6cd2b237da014ee3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd6c815a252c44d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R66f5a9f57e5c4754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb0e5c63adeae4739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd45deadcb3484ff1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R72eace2644004e79"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fa09730dc944aa4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01eb00be78ef48f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra214e7550dff4ef0"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc533c23ee8d547a7"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f34671eef7d4caa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafd9c3c9b0ca41ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc96f0e0217cf402f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d36ff1183134e24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16571,10 +16571,14 @@
       </x:c>
       <x:c r="M111" s="84" t="str"/>
       <x:c r="N111" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O111" s="84" t="str"/>
-      <x:c r="P111" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O111" s="84" t="str">
+        <x:v>contracts/master-spec.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-TPL-002）</x:v>
+      </x:c>
+      <x:c r="P111" s="86" t="str">
+        <x:v>静态核对；继承未解析。</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="83" t="str">
@@ -24982,7 +24986,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf5b3cf4b45c446d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0016d73626464a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32512,9 +32516,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L179" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M179" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M179" s="84" t="str">
+        <x:v>contracts/master-spec.*.json；PROJECT_PLAN.md（TASK-TPL-002）</x:v>
+      </x:c>
       <x:c r="N179" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43755,7 +43761,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R977b8331a2c74130"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21accfee8a9d47ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44037,7 +44043,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f7827793daf40c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra11448f077824b4d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45453,7 +45459,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb3efb21e21a4f9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b6a72d883e44b09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45867,7 +45873,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbf7ec6df42e4f9d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0b273bb4e004787"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49214,7 +49220,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf41bc75a5dfe40eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3df95eae2e949ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf30dfb2a275044f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rea829b1c28034a88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R5cb4954dbfab4c79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8aa567fcee6b48c1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd82fab7907464893"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf3ed48dd792d43b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1b3bb2fe2aca41c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R62d03e5a8f8c4322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R6d15f81830cf49f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R5ec3565cfb124120"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc90c3ef08af04c14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R22603af4be494c65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R446de2c07c344131"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra7909fe5cce64724"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6cd2b237da014ee3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd6c815a252c44d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R66f5a9f57e5c4754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb0e5c63adeae4739"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd45deadcb3484ff1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R72eace2644004e79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1d13a3b31dfd4b2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R415204208be54060"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R32978bca3abd4f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcc07e6c672be456e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Re4755f58817d480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R0d913dd2d3e04482"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rb36b1d6ccb064aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R034855929f274a1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5253f73b766842b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb3dfe310fde94516"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc06fe2a589084ab6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1a0094ce3d834543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rad61755a6f6842fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9ae9f0ba1aa542fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re91686d1d7ac405e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rff01bf2336934ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rc8474cccb22242b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0bc196a895ed4c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R07d776f7cfb94ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rdf4fd22d4ab1474e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R01eb00be78ef48f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1707ef09c07452c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc533c23ee8d547a7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11fd808564b24c35"/>
 </x:worksheet>
 </file>
 
@@ -5715,7 +5715,7 @@
         <x:v>layout_id, page_types, slots, constraints, capacity, backend_support</x:v>
       </x:c>
       <x:c r="D29" s="84" t="str">
-        <x:v>待定义</x:v>
+        <x:v>Draft 2020-12 草案（TPL-003）</x:v>
       </x:c>
       <x:c r="E29" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5733,7 +5733,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J29" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TPL-003 已建立 layout-template Schema/catalog/fixtures 草案，尚无产品 parser/runtime。TPL-004 slots、TPL-006 page-type 映射、TPL-007 capacity 与后端实测待后续任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafd9c3c9b0ca41ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363fb78e272a4d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d36ff1183134e24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R268152a0725347e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16617,10 +16617,14 @@
       </x:c>
       <x:c r="M112" s="84" t="str"/>
       <x:c r="N112" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O112" s="84" t="str"/>
-      <x:c r="P112" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O112" s="84" t="str">
+        <x:v>contracts/layout-template.schema.json; contracts/layout-template.catalog.json; contracts/layout-template.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P112" s="86" t="str">
+        <x:v>已完成静态源码对照及真实 PPTX 结构盘点；产品解析器、继承结果和应用级验证待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="83" t="str">
@@ -24986,7 +24990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0016d73626464a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13fd3dab018a4fbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32558,9 +32562,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L180" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M180" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M180" s="84" t="str">
+        <x:v>contracts/layout-template.schema.json; contracts/layout-template.catalog.json; contracts/layout-template.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N180" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43761,7 +43767,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21accfee8a9d47ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d23c7f12f6e4eac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44043,7 +44049,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra11448f077824b4d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a4a96d7c9914b0f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45459,7 +45465,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b6a72d883e44b09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c9598e915d4629"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45873,7 +45879,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0b273bb4e004787"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78cbb1677c094c2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49220,7 +49226,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3df95eae2e949ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd1aac624ef74bfa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1d13a3b31dfd4b2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R415204208be54060"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R32978bca3abd4f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rcc07e6c672be456e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Re4755f58817d480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R0d913dd2d3e04482"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rb36b1d6ccb064aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R034855929f274a1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5253f73b766842b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rb3dfe310fde94516"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc06fe2a589084ab6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1a0094ce3d834543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rad61755a6f6842fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9ae9f0ba1aa542fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re91686d1d7ac405e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rff01bf2336934ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rc8474cccb22242b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0bc196a895ed4c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R07d776f7cfb94ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rdf4fd22d4ab1474e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6e6d7a9eeab84a08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R257b798db95b424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb4c73d58e700403d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8bd7ddf227904057"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7e6c69e8932a4da4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R2a73a258e5bc4cd5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R75df51e52ea94322"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Racb3d0b7cff34a78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2fb466044f1c40c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R373055f6f6b44716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5a4b685df6bd442a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7171d162110b4349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R48399cda14df4442"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5d672aaca34c44df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rea9829a2da1642da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4d89a9a8b47b4b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R7a99a4e0d3f24bb1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc48e2fdf853c4f1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcc66865287c74cff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R6dd0fa81959e43d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1707ef09c07452c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra738d2b82a974aca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11fd808564b24c35"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4569e8cdaaad4aae"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363fb78e272a4d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc13a755d6c9a45c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R268152a0725347e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20be71a907794d24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13581,10 +13581,14 @@
       </x:c>
       <x:c r="M44" s="84" t="str"/>
       <x:c r="N44" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O44" s="84" t="str"/>
-      <x:c r="P44" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O44" s="84" t="str">
+        <x:v>contracts/ocr-evidence.schema.json; contracts/ocr-evidence.catalog.json; contracts/ocr-evidence.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P44" s="86" t="str">
+        <x:v>静态结构样例及错误映射已核对；实际 OCR、PDF parser 和引擎许可/版本验证待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="83" t="str">
@@ -24990,7 +24994,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13fd3dab018a4fbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra855a5ade14a480c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28032,9 +28036,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L72" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M72" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M72" s="84" t="str">
+        <x:v>contracts/ocr-evidence.schema.json; contracts/ocr-evidence.catalog.json; contracts/ocr-evidence.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N72" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43767,7 +43773,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d23c7f12f6e4eac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a240ce21a3c47ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44049,7 +44055,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a4a96d7c9914b0f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd5c3083fe5d4d7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45465,7 +45471,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20c9598e915d4629"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc72b7eb9e44344f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45879,7 +45885,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R78cbb1677c094c2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc5798c61c1643ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49226,7 +49232,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd1aac624ef74bfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b5dc65c4094594"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R6e6d7a9eeab84a08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R257b798db95b424c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb4c73d58e700403d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R8bd7ddf227904057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7e6c69e8932a4da4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R2a73a258e5bc4cd5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R75df51e52ea94322"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Racb3d0b7cff34a78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2fb466044f1c40c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R373055f6f6b44716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5a4b685df6bd442a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7171d162110b4349"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R48399cda14df4442"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5d672aaca34c44df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rea9829a2da1642da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4d89a9a8b47b4b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R7a99a4e0d3f24bb1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc48e2fdf853c4f1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcc66865287c74cff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R6dd0fa81959e43d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1f7fa2b8c2b14405"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R7b6f526548de45b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R78f3e136d7b54366"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rb51f2acc841841d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6896d9d801dd47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Redb1a4c3bc544d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R759c49a9cb694690"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc1c033961d8b48be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R743d8326a3884d79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rc518d85575ac42cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rccc85d38f684431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5d55cc63e39e4a3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R3521d2f243a54a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R95c40ec748de40b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5b18170bf48f423e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd242f390a9284c3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1f8f3c2256094e9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd70e05a404dd4bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Redbdc7a280a74df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb2d35ca22db24e7f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra738d2b82a974aca"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf182ac186994538"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4569e8cdaaad4aae"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R423ea93330d949a5"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc13a755d6c9a45c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599a97a9374840ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20be71a907794d24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R773061b58fde4951"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13765,10 +13765,14 @@
       </x:c>
       <x:c r="M48" s="84" t="str"/>
       <x:c r="N48" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O48" s="84" t="str"/>
-      <x:c r="P48" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O48" s="84" t="str">
+        <x:v>contracts/web-evidence.schema.json; contracts/web-evidence.catalog.json; contracts/web-evidence.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P48" s="86" t="str">
+        <x:v>契约与 6 个合成场景已静态核验；实际解析及网络安全验证待运行时确定。</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="83" t="str">
@@ -24994,7 +24998,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra855a5ade14a480c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9e402dbb39f4953"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28204,9 +28208,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L76" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M76" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M76" s="84" t="str">
+        <x:v>contracts/web-evidence.schema.json; contracts/web-evidence.catalog.json; contracts/web-evidence.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N76" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43773,7 +43779,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a240ce21a3c47ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6510766705674b77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44055,7 +44061,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd5c3083fe5d4d7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae1540b658664047"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45471,7 +45477,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc72b7eb9e44344f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b77c13c9f03459d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45885,7 +45891,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc5798c61c1643ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b840afcc7074b40"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49232,7 +49238,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08b5dc65c4094594"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9c00a31a374fbb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1f7fa2b8c2b14405"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R7b6f526548de45b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R78f3e136d7b54366"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rb51f2acc841841d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6896d9d801dd47a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Redb1a4c3bc544d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R759c49a9cb694690"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc1c033961d8b48be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R743d8326a3884d79"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rc518d85575ac42cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rccc85d38f684431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5d55cc63e39e4a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R3521d2f243a54a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R95c40ec748de40b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5b18170bf48f423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd242f390a9284c3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1f8f3c2256094e9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd70e05a404dd4bb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Redbdc7a280a74df4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb2d35ca22db24e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rde03b421a2ef4866"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Red2b3935d3c04c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rd1f9aa415e56454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R707ef939aa4a42f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R15e693e99b87477a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Refc69778cda043e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R2d86525f8945413d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rfd60edeb4355452e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8747a95f7f6a46cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3aa4484c590d4ff0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rba5909a648324e94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb5e61871de3d4b5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rcc58ce20d6434a69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc4ff5b7e84a74a0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R062bbd42398c47f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8582e463097347e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rde2639371d924219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R50027329861d4113"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5e00b992d13649e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8b9371cc8e594fed"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rdf182ac186994538"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2cd43c8a94114ca8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R423ea93330d949a5"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb227eebd5e9e4f31"/>
 </x:worksheet>
 </file>
 
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R599a97a9374840ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c0b5a27b05943cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R773061b58fde4951"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R293340d1c7604375"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13949,10 +13949,14 @@
       </x:c>
       <x:c r="M52" s="84" t="str"/>
       <x:c r="N52" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O52" s="84" t="str"/>
-      <x:c r="P52" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O52" s="84" t="str">
+        <x:v>contracts/style-reference.schema.json; contracts/style-reference.catalog.json; contracts/style-reference.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P52" s="86" t="str">
+        <x:v>4 个合成场景与特征/权利边界已静态核验；图像分析与授权流程待运行时验证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="83" t="str">
@@ -24998,7 +25002,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9e402dbb39f4953"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f105ba3f2344f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28376,9 +28380,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L80" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M80" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M80" s="84" t="str">
+        <x:v>contracts/style-reference.schema.json; contracts/style-reference.catalog.json; contracts/style-reference.fixtures.json; PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N80" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43779,7 +43785,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6510766705674b77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9ba309640834137"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44061,7 +44067,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae1540b658664047"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97407952f5ea4d19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45477,7 +45483,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b77c13c9f03459d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca8976433544618"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45891,7 +45897,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b840afcc7074b40"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f6382882e8431e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49238,7 +49244,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdc9c00a31a374fbb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8608452fb9f44ec7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rde03b421a2ef4866"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Red2b3935d3c04c95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rd1f9aa415e56454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R707ef939aa4a42f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R15e693e99b87477a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Refc69778cda043e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R2d86525f8945413d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rfd60edeb4355452e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8747a95f7f6a46cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3aa4484c590d4ff0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rba5909a648324e94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb5e61871de3d4b5c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rcc58ce20d6434a69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc4ff5b7e84a74a0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R062bbd42398c47f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8582e463097347e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rde2639371d924219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R50027329861d4113"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5e00b992d13649e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8b9371cc8e594fed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd6171f4094c544e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3b3ecfbdced14f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R022e9425447a4c3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R36225ef42d084a29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R84e86e3fbf914a54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rfb687697e85c4183"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rfa23916dac5245ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R157d713fa9254f92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb3d15542262842a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Re18e524718364c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R178d9043edb045de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rcc90dd0b48764ab1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9758f2852fe94811"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R606ea83e21944561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6c451e5640a74948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ra7fe547c9cb84b83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5c41d44446a94436"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Re42ce76735414531"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R1e6c1da451304ef6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rca389c68657e41c2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2cd43c8a94114ca8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac196c37352d4f29"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb227eebd5e9e4f31"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d39bbb221074f52"/>
 </x:worksheet>
 </file>
 
@@ -5733,7 +5733,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J29" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TPL-003 已建立 layout-template Schema/catalog/fixtures 草案，尚无产品 parser/runtime。TPL-004 slots、TPL-006 page-type 映射、TPL-007 capacity 与后端实测待后续任务。</x:v>
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TPL-003 已建立 layout-template Schema/catalog/fixtures 草案；TPL-004 LayoutSlot Schema/catalog/fixtures 已定义并由 LayoutTemplate.slots 引用；仍无产品 parser/runtime。TPL-006 page-type 映射、TPL-007 capacity 与后端实测待后续任务。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -5747,7 +5747,7 @@
         <x:v>slot_id, role, bounds, content_types, required, repeatable, capacity, style, overflow_policy</x:v>
       </x:c>
       <x:c r="D30" s="84" t="str">
-        <x:v>待定义</x:v>
+        <x:v>Draft 2020-12 草案（TASK-TPL-004）</x:v>
       </x:c>
       <x:c r="E30" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5765,7 +5765,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J30" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；Draft 2020-12 Schema/catalog/fixtures：contracts/layout-slot.schema.json、layout-slot.catalog.json、layout-slot.fixtures.json；LayoutTemplate.slots 已使用该类型；未知来源值保留状态和原因；产品 parser/runtime 与 TPL-007 容量规则待后续。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10119,7 +10119,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c0b5a27b05943cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3d1a2122144e6b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11308,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R293340d1c7604375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd91097c944c94fde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16675,10 +16675,14 @@
       </x:c>
       <x:c r="M113" s="84" t="str"/>
       <x:c r="N113" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O113" s="84" t="str"/>
-      <x:c r="P113" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O113" s="84" t="str">
+        <x:v>contracts/layout-slot.*.json; contracts/layout-template.*.json; PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P113" s="86" t="str">
+        <x:v>产品运行时验证待完成</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="83" t="str">
@@ -25002,7 +25006,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5f105ba3f2344f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dea679c7a2a4b73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32622,9 +32626,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L181" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M181" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M181" s="84" t="str">
+        <x:v>contracts/layout-slot.*.json; contracts/layout-template.*.json; PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N181" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43785,7 +43791,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9ba309640834137"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2f1024cbd04822"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44067,7 +44073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97407952f5ea4d19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb6e179c75e42b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45483,7 +45489,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reca8976433544618"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra011cbc0c12747bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45897,7 +45903,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29f6382882e8431e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e8b199d70e4603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49244,7 +49250,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8608452fb9f44ec7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1266c5a8fc254530"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd6171f4094c544e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3b3ecfbdced14f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R022e9425447a4c3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R36225ef42d084a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R84e86e3fbf914a54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rfb687697e85c4183"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rfa23916dac5245ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R157d713fa9254f92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb3d15542262842a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Re18e524718364c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R178d9043edb045de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rcc90dd0b48764ab1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9758f2852fe94811"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R606ea83e21944561"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R6c451e5640a74948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ra7fe547c9cb84b83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5c41d44446a94436"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Re42ce76735414531"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R1e6c1da451304ef6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rca389c68657e41c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8152582be4cd49e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Readd87a74ca9463a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rfd2c27163a66497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R57963ea02a824235"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R958a29a963704bc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc773f90bca2743eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Raec3c7eddbf9497f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd420e956c4ac4212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R09bf18a6d9144fa2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ree5542b81bda47af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd95f1d7c5e5d4f93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R46150b53555a4a5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R7799f011be624cf4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rcf24a2ca71af4ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd190bf3e193e4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R630a7b6bbd2c4588"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R54bb8696cf2e494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8be9a791a94c454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R05d04ed0fdf140bf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf963718aab734c1c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rac196c37352d4f29"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3aa5b31ded214305"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d39bbb221074f52"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R705ea1ee9fe7418c"/>
 </x:worksheet>
 </file>
 
@@ -5776,10 +5776,10 @@
         <x:v>设计 token</x:v>
       </x:c>
       <x:c r="C31" s="84" t="str">
-        <x:v>fonts, type_scale, colors, spacing, radius, border, shadow, backgrounds, image_treatment</x:v>
+        <x:v>fonts, type_scale, colors, spacing, radius, border, shadow, backgrounds, image_treatment, chart_style, table_style</x:v>
       </x:c>
       <x:c r="D31" s="84" t="str">
-        <x:v>待定义</x:v>
+        <x:v>Draft 2020-12 草案（TASK-TPL-005）</x:v>
       </x:c>
       <x:c r="E31" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5794,9 +5794,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I31" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J31" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J31" s="86" t="str">
+        <x:v>语言/运行时无关 DesignTokens 契约与来源 crosswalk 已建立；真实 PPTX 仅有主题/母版/版式结构，未提供 slides/charts/media；未观察项保持 unknown/partial 且不补默认值。契约和样例不是产品 parser/runtime；标准 Draft 2020-12 validator 尚未安装。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="83" t="str">
@@ -10119,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e3d1a2122144e6b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree12aed5a6c7456c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11308,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd91097c944c94fde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R958b1de1a7f44d69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16721,10 +16723,14 @@
       </x:c>
       <x:c r="M114" s="84" t="str"/>
       <x:c r="N114" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O114" s="84" t="str"/>
-      <x:c r="P114" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O114" s="84" t="str">
+        <x:v>contracts/design-tokens.schema.json、design-tokens.catalog.json、design-tokens.fixtures.json、PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P114" s="86" t="str">
+        <x:v>上游源码与真实 PPTX 样例静态对照已建立；产品 parser/runtime、渲染和 AC 验证待完成</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="83" t="str">
@@ -25006,7 +25012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4dea679c7a2a4b73"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58cc5c7001ae43b2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32668,9 +32674,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L182" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M182" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M182" s="84" t="str">
+        <x:v>contracts/design-tokens.schema.json、design-tokens.catalog.json、design-tokens.fixtures.json、PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N182" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43791,7 +43799,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf2f1024cbd04822"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R643fd4fa1c274052"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44073,7 +44081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cb6e179c75e42b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4e92b8a7aef4232"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45489,7 +45497,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra011cbc0c12747bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65440f1fc29c4600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45903,7 +45911,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89e8b199d70e4603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ace7703c0e34ad8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49250,7 +49258,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1266c5a8fc254530"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd330dd1543ce4569"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8152582be4cd49e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Readd87a74ca9463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rfd2c27163a66497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R57963ea02a824235"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R958a29a963704bc8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc773f90bca2743eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Raec3c7eddbf9497f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd420e956c4ac4212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R09bf18a6d9144fa2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Ree5542b81bda47af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rd95f1d7c5e5d4f93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R46150b53555a4a5a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R7799f011be624cf4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rcf24a2ca71af4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd190bf3e193e4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R630a7b6bbd2c4588"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R54bb8696cf2e494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8be9a791a94c454e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R05d04ed0fdf140bf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf963718aab734c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra2393d7bfcd74153"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R8d176a3bcf4d417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R61b9f6f0dab84cf1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6d4e7d0a3dfb4ed1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Reedbaccdda404a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5f7ade81d04a4302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra953b42335d14c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc47b445d844347e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re28b1ec1aed74141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R14c256699f0d4497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R857bdf3b53e64429"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R42ceb9f7f7d44b56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R996b323d3455421d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R232430c4e02b4302"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3f7c12b0eda346ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3297f0941bc84855"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R977c70fb76ac49ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Re97e1f7d1a1e4383"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R981b87601fc64184"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R81ab33adf4b84ee1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3aa5b31ded214305"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbd5f1ac95d84eb7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R705ea1ee9fe7418c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68e66acd470941a9"/>
 </x:worksheet>
 </file>
 
@@ -5715,7 +5715,7 @@
         <x:v>layout_id, page_types, slots, constraints, capacity, backend_support</x:v>
       </x:c>
       <x:c r="D29" s="84" t="str">
-        <x:v>Draft 2020-12 草案（TPL-003）</x:v>
+        <x:v>Draft 2020-12 草案（TASK-TPL-003/006）</x:v>
       </x:c>
       <x:c r="E29" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5733,7 +5733,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J29" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TPL-003 已建立 layout-template Schema/catalog/fixtures 草案；TPL-004 LayoutSlot Schema/catalog/fixtures 已定义并由 LayoutTemplate.slots 引用；仍无产品 parser/runtime。TPL-006 page-type 映射、TPL-007 capacity 与后端实测待后续任务。</x:v>
+        <x:v>TPL-006 LayoutApplicability 契约已接入既有 LayoutTemplate.page_types；taxonomy 依据 DEC-017/S16，候选和 unknown 均保留证据；没有产品 parser/runtime。TPL-007 capacity、backend 和运行时映射验证待后续。未新增数据对象行。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree12aed5a6c7456c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b70dd0bec364603"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R958b1de1a7f44d69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R996e636efdcc42b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16769,10 +16769,14 @@
       </x:c>
       <x:c r="M115" s="84" t="str"/>
       <x:c r="N115" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O115" s="84" t="str"/>
-      <x:c r="P115" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O115" s="84" t="str">
+        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P115" s="86" t="str">
+        <x:v>已建立带证据的候选/未知关系；产品 parser/runtime、决策评分、渲染和 AC 验证待完成</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="83" t="str">
@@ -25012,7 +25016,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58cc5c7001ae43b2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R117ddd1456c24186"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32716,9 +32720,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L183" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M183" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M183" s="84" t="str">
+        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md</x:v>
+      </x:c>
       <x:c r="N183" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43799,7 +43805,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R643fd4fa1c274052"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6226bc60a6452d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44081,7 +44087,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4e92b8a7aef4232"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58785ae399e4950"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45497,7 +45503,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65440f1fc29c4600"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f92c472941442d7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45911,7 +45917,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ace7703c0e34ad8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea02a2616dc0480e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49258,7 +49264,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd330dd1543ce4569"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c4dc09cacf14f3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Ra2393d7bfcd74153"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R8d176a3bcf4d417c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R61b9f6f0dab84cf1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6d4e7d0a3dfb4ed1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Reedbaccdda404a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5f7ade81d04a4302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra953b42335d14c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rc47b445d844347e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re28b1ec1aed74141"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R14c256699f0d4497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R857bdf3b53e64429"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R42ceb9f7f7d44b56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R996b323d3455421d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R232430c4e02b4302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3f7c12b0eda346ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3297f0941bc84855"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R977c70fb76ac49ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Re97e1f7d1a1e4383"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R981b87601fc64184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R81ab33adf4b84ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R05e8d109053846fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R1b16cc7b35754070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R73a5a686c1bc4d64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R3350a9fb818a4d56"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Raefe4b770efa4be6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rde8752982665494d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rdeddbc4aadd04f6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8232c2dc9f644b3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8ddc3e8500c94959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R693deb14e2aa4c45"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R1315e81faa684566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re1546634a98c47b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2b30cac49d1f4098"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc692550b8cf04020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Ra11cace71cd14e13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R57da1bd10cda4bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8fe3bd720a264331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc64d90cb802141a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rb6bfe029172442e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf8b7ff02bd424717"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcbd5f1ac95d84eb7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R022df49d861f4a2d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68e66acd470941a9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2609fe1d83b34286"/>
 </x:worksheet>
 </file>
 
@@ -5715,7 +5715,7 @@
         <x:v>layout_id, page_types, slots, constraints, capacity, backend_support</x:v>
       </x:c>
       <x:c r="D29" s="84" t="str">
-        <x:v>Draft 2020-12 草案（TASK-TPL-003/006）</x:v>
+        <x:v>Draft 2020-12 草案（TASK-TPL-003/006/007）</x:v>
       </x:c>
       <x:c r="E29" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5733,7 +5733,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J29" s="86" t="str">
-        <x:v>TPL-006 LayoutApplicability 契约已接入既有 LayoutTemplate.page_types；taxonomy 依据 DEC-017/S16，候选和 unknown 均保留证据；没有产品 parser/runtime。TPL-007 capacity、backend 和运行时映射验证待后续。未新增数据对象行。</x:v>
+        <x:v>TPL-006 LayoutApplicability、TPL-007 CapacityRules 已接入 page_types/capacity；七项容量维度保持 unknown，真实阈值及产品 parser/runtime、后端能力待验证。不新增数据对象行。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -5747,7 +5747,7 @@
         <x:v>slot_id, role, bounds, content_types, required, repeatable, capacity, style, overflow_policy</x:v>
       </x:c>
       <x:c r="D30" s="84" t="str">
-        <x:v>Draft 2020-12 草案（TASK-TPL-004）</x:v>
+        <x:v>Draft 2020-12 草案（TASK-TPL-004/007）</x:v>
       </x:c>
       <x:c r="E30" s="84" t="str">
         <x:v>见 0-1 链路/DEC/SYS</x:v>
@@ -5765,7 +5765,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J30" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；Draft 2020-12 Schema/catalog/fixtures：contracts/layout-slot.schema.json、layout-slot.catalog.json、layout-slot.fixtures.json；LayoutTemplate.slots 已使用该类型；未知来源值保留状态和原因；产品 parser/runtime 与 TPL-007 容量规则待后续。</x:v>
+        <x:v>LayoutSlot.capacity 复用 TASK-TPL-007 CapacityRules；现有真实样例没有 slide 内容，容量与最小字号为 unknown；产品 parser/runtime 和渲染测量待验证。</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b70dd0bec364603"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b1cdaebf2e6416e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R996e636efdcc42b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ec04ee09714932"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16815,10 +16815,14 @@
       </x:c>
       <x:c r="M116" s="84" t="str"/>
       <x:c r="N116" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O116" s="84" t="str"/>
-      <x:c r="P116" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O116" s="84" t="str">
+        <x:v>contracts/capacity-rules.schema.json/catalog.json/fixtures.json；contracts/layout-template.*.json；contracts/layout-slot.*.json；PROJECT_PLAN.md</x:v>
+      </x:c>
+      <x:c r="P116" s="86" t="str">
+        <x:v>已建立容量规则并接入 LayoutTemplate/Slot。覆盖字符、行、列表、图片、表格、图表和最小字号；真实样例无 slide 部件，未测阈值保留 unknown。</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="83" t="str">
@@ -25016,7 +25020,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R117ddd1456c24186"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bea4110ed67433d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32762,9 +32766,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L184" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M184" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M184" s="84" t="str">
+        <x:v>contracts/capacity-rules.schema.json/catalog.json/fixtures.json；contracts/layout-template.*.json；contracts/layout-slot.*.json；PROJECT_PLAN.md；以 source_review_only fixture 记录无实测容量，产品阈值待验证。</x:v>
+      </x:c>
       <x:c r="N184" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43805,7 +43811,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce6226bc60a6452d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190b5b8d5560408f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44087,7 +44093,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58785ae399e4950"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R849109e491d94758"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45503,7 +45509,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f92c472941442d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R241640e6638448b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45917,7 +45923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea02a2616dc0480e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97c580d0cb684265"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49264,7 +49270,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c4dc09cacf14f3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1ce8e87c6d4b1e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R05e8d109053846fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R1b16cc7b35754070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R73a5a686c1bc4d64"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R3350a9fb818a4d56"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Raefe4b770efa4be6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rde8752982665494d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rdeddbc4aadd04f6c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R8232c2dc9f644b3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8ddc3e8500c94959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R693deb14e2aa4c45"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R1315e81faa684566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re1546634a98c47b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2b30cac49d1f4098"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc692550b8cf04020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Ra11cace71cd14e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R57da1bd10cda4bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8fe3bd720a264331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc64d90cb802141a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rb6bfe029172442e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf8b7ff02bd424717"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9e513ea1a25849f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R756fa9d49f7f4f5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rd3344fdf2e7a4691"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R482a8eefd3af4c6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rfd7fe36e8d434cce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re778ece4c8d048ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R31a4580c9e784eeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R456898799b6043a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R79b7318ecea34006"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd6c7ddb0bb184375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R26157de28cd64424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R82dee72c63684d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R44cb484033944ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R576080b355f84a7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R1183c627eed14129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb98bb51665014111"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R4bd5c808ed3a4407"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4216234e38ae4aeb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28633db2ebbe485c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R25a8d8753c5c478f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R022df49d861f4a2d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe0811741cba4256"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2609fe1d83b34286"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893fd5acee944b7c"/>
 </x:worksheet>
 </file>
 
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b1cdaebf2e6416e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f53d70167eb49b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77ec04ee09714932"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad9d7f060a894059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16861,10 +16861,14 @@
       </x:c>
       <x:c r="M117" s="84" t="str"/>
       <x:c r="N117" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O117" s="84" t="str"/>
-      <x:c r="P117" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O117" s="84" t="str">
+        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008</x:v>
+      </x:c>
+      <x:c r="P117" s="86" t="str">
+        <x:v>静态 crosswalk 覆盖 4 类来源；P03=unknown、subTitle=unmapped；runtime 待验。</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="83" t="str">
@@ -25020,7 +25024,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bea4110ed67433d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e32fdc3bb4d4bb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32808,9 +32812,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L185" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M185" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M185" s="84" t="str">
+        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008</x:v>
+      </x:c>
       <x:c r="N185" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43811,7 +43817,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R190b5b8d5560408f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R662cb3f14bd042fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44093,7 +44099,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R849109e491d94758"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dd0f6e188204a05"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45509,7 +45515,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R241640e6638448b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raafdfb3a11df4086"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45923,7 +45929,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97c580d0cb684265"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R148a4392d31644f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49270,7 +49276,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1ce8e87c6d4b1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R400d8fe303484783"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R9e513ea1a25849f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R756fa9d49f7f4f5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rd3344fdf2e7a4691"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R482a8eefd3af4c6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rfd7fe36e8d434cce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re778ece4c8d048ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R31a4580c9e784eeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R456898799b6043a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R79b7318ecea34006"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd6c7ddb0bb184375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R26157de28cd64424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R82dee72c63684d36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R44cb484033944ef7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R576080b355f84a7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R1183c627eed14129"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb98bb51665014111"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R4bd5c808ed3a4407"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4216234e38ae4aeb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28633db2ebbe485c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R25a8d8753c5c478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8df8b191ae6f440f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4b3a2ac847384942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc646ff7660df45c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R5566efea3daa4d83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2ed6a546a6464dd4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R479d1a8f379a495f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rcb05858ef86e4f75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2d9a2efe2bb243d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9b5d14fda99c4c92"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf8c81449c4ce45ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R94e852616de64c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R80bd51af0ca341a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0f0df509eed84648"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd157076423924680"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rbcb867520f4e4884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5f09d6a55e344dba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R6445f5d9e12646de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc897cce32d7b4327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7d981f766aa44296"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0b1d80c4af0d4c15"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfe0811741cba4256"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2565361e882d485f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R893fd5acee944b7c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2189cd9db7f94328"/>
 </x:worksheet>
 </file>
 
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f53d70167eb49b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5759edf866e64c15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rad9d7f060a894059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6239f746a44846dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16907,10 +16907,14 @@
       </x:c>
       <x:c r="M118" s="84" t="str"/>
       <x:c r="N118" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O118" s="84" t="str"/>
-      <x:c r="P118" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O118" s="84" t="str">
+        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+      </x:c>
+      <x:c r="P118" s="86" t="str">
+        <x:v>输入包静态盘点为 1 master/11 layouts/1 theme/0 slides；重建、master/layout/theme 输出比对、round-trip、页面渲染均未运行，任务保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="83" t="str">
@@ -25024,7 +25028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e32fdc3bb4d4bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R898502d9fd9b46fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32854,9 +32858,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L186" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M186" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M186" s="84" t="str">
+        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+      </x:c>
       <x:c r="N186" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43817,7 +43823,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R662cb3f14bd042fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra156cda504854f94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44099,7 +44105,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dd0f6e188204a05"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4445bca643ea49ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45515,7 +45521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raafdfb3a11df4086"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc9fc63d4bf44fe1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45929,7 +45935,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R148a4392d31644f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f29fd18883f45ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49276,7 +49282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R400d8fe303484783"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaa8373133b7485a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8df8b191ae6f440f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4b3a2ac847384942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc646ff7660df45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R5566efea3daa4d83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2ed6a546a6464dd4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R479d1a8f379a495f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rcb05858ef86e4f75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2d9a2efe2bb243d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9b5d14fda99c4c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf8c81449c4ce45ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R94e852616de64c1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R80bd51af0ca341a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0f0df509eed84648"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd157076423924680"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rbcb867520f4e4884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5f09d6a55e344dba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R6445f5d9e12646de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc897cce32d7b4327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7d981f766aa44296"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R0b1d80c4af0d4c15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rbfd1e54ab73a4082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9446f7ef1b994549"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7893a26b98bb41fa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R37db9701840f4eee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rfc29fb725c0f4da2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R80b43671b50d43be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rda90e129c4eb4d3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R91f259a2a3e44247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3d74f05e47ba40f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R46d1fd6c70cd48d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R83779e0455ee4ae7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8fb682f2c524367"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R5ba05913cde14b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R3dd586152e624c90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R748b25bedd424046"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3c5e874587e04426"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3c7ef0adee5e409d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd172338fb97a4cc5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Ref63253a9e374b6b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf2e056c18f7b4e19"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2565361e882d485f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c2642f76101430e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2189cd9db7f94328"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe32c947ca0f4590"/>
 </x:worksheet>
 </file>
 
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5759edf866e64c15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4ce1f3f8f0b4741"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6239f746a44846dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9105e4fa75e4a02"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16910,10 +16910,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O118" s="84" t="str">
-        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; scripts/project.ps1; compose.yaml; Dockerfile; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
       </x:c>
       <x:c r="P118" s="86" t="str">
-        <x:v>输入包静态盘点为 1 master/11 layouts/1 theme/0 slides；重建、master/layout/theme 输出比对、round-trip、页面渲染均未运行，任务保持进行中。</x:v>
+        <x:v>样例为 1 master/11 layouts/1 theme/0 slides；项目 Docker workspace 已运行（Engine 27.4.0 环境观测，通用容器不含产品 runtime）；模板导入/重建、输出 master/layout/theme 比对、round-trip/render 未运行，任务继续进行中。</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -25028,7 +25028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R898502d9fd9b46fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33b38b9ef0a84797"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32861,7 +32861,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M186" s="84" t="str">
-        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; scripts/project.ps1; compose.yaml; Dockerfile; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
       </x:c>
       <x:c r="N186" s="86" t="str">
         <x:v>本规划</x:v>
@@ -43823,7 +43823,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra156cda504854f94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8405bbaeb420424e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44105,7 +44105,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4445bca643ea49ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R897154da0ba144d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45521,7 +45521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcc9fc63d4bf44fe1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ced6cfff3441ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45935,7 +45935,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f29fd18883f45ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e73a6633e2241ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49282,7 +49282,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaa8373133b7485a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98996a3483ca4811"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rbfd1e54ab73a4082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9446f7ef1b994549"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7893a26b98bb41fa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R37db9701840f4eee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rfc29fb725c0f4da2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R80b43671b50d43be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rda90e129c4eb4d3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R91f259a2a3e44247"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R3d74f05e47ba40f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R46d1fd6c70cd48d5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R83779e0455ee4ae7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8fb682f2c524367"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R5ba05913cde14b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R3dd586152e624c90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R748b25bedd424046"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3c5e874587e04426"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3c7ef0adee5e409d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rd172338fb97a4cc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Ref63253a9e374b6b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rf2e056c18f7b4e19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc3c27739368544d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2f4b0bd716764377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf869bb31120e47c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Re28aa00fe3094a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbfa39d25fcfa4149"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfa30fbc2792473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R83a36ca283a943a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2df3694208b24409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rbefe77f10d51471f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6828cdfffd754cf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ree522582ca8d4884"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R67005f6fcce044aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9510fec50854400c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd88f9e10f13444f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3dcffc5ba92a4490"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4b81df9d91c44377"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re9aac1b298754191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb9b50c17131d4968"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8a3ff04991394563"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R47d44061fe7d4682"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -851,7 +851,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5c2642f76101430e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc87035df6a2c463d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1907,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe32c947ca0f4590"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f792e608b8d4bfa"/>
 </x:worksheet>
 </file>
 
@@ -10121,7 +10121,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4ce1f3f8f0b4741"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1f85f109c74cc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11310,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc9105e4fa75e4a02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra804c7936d19401d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25028,7 +25028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33b38b9ef0a84797"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76fa300e3a164c58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36586,7 +36586,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L276" s="84" t="str">
-        <x:v>未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="M276" s="84" t="str"/>
       <x:c r="N276" s="86" t="str">
@@ -36628,7 +36628,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L277" s="84" t="str">
-        <x:v>未开始</x:v>
+        <x:v>进行中</x:v>
       </x:c>
       <x:c r="M277" s="84" t="str"/>
       <x:c r="N277" s="86" t="str">
@@ -43823,7 +43823,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8405bbaeb420424e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbbf4eec7214930"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44105,7 +44105,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R897154da0ba144d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd09bc6b6898941d2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45521,7 +45521,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13ced6cfff3441ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc40234be48be4210"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45698,7 +45698,7 @@
       <x:c r="M4" s="84" t="str"/>
       <x:c r="N4" s="86" t="str"/>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="58.5" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>PP-04</x:v>
       </x:c>
@@ -45721,18 +45721,26 @@
         <x:v>package/parts/relationships；presentation/slides/master/layout/theme；shapes/text/images/tables/charts；notes/comments；transition/animation；media；unknown parts preserve；OpenXmlValidator；单位 EMU。</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>待搭建</x:v>
+        <x:v>PoC Docker 已运行（候选实验）</x:v>
       </x:c>
       <x:c r="I5" s="84" t="str">
-        <x:v>未执行</x:v>
+        <x:v>已执行（部分通过）</x:v>
       </x:c>
       <x:c r="J5" s="84" t="str">
-        <x:v>未冻结（PoC未执行）</x:v>
-      </x:c>
-      <x:c r="K5" s="84" t="str"/>
-      <x:c r="L5" s="84" t="str"/>
-      <x:c r="M5" s="84" t="str"/>
-      <x:c r="N5" s="86" t="str"/>
+        <x:v>DocumentFormat.OpenXml 3.5.1 (MIT)；SDK 10.0.401（仅实验环境）</x:v>
+      </x:c>
+      <x:c r="K5" s="84" t="str">
+        <x:v>artifacts/pp04-output.pptx + report.json：新增 1 张标题/正文页；Office2019 校验 0 错误。</x:v>
+      </x:c>
+      <x:c r="L5" s="84" t="str">
+        <x:v>母版/主题哈希一致；layout1/11 字节变化；未知部件哈希一致。</x:v>
+      </x:c>
+      <x:c r="M5" s="84" t="str">
+        <x:v>未测：图片/表格/图表、既有对象读改、notes/评论、动画/切换、EMU、Office 渲染。</x:v>
+      </x:c>
+      <x:c r="N5" s="84" t="str">
+        <x:v>本轮仅有阶段性证据；PP-04 非产品后端选型。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -45935,7 +45943,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e73a6633e2241ee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0325442effdd41d9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46035,7 +46043,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
         <x:v>Untested</x:v>
@@ -46081,7 +46089,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H3" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I3" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46173,7 +46181,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I5" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46219,7 +46227,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I6" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46265,7 +46273,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I7" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46311,7 +46319,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I8" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46357,7 +46365,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I9" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46403,7 +46411,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I10" s="84" t="str">
         <x:v>Untested</x:v>
@@ -49282,7 +49290,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98996a3483ca4811"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2065b022cb52427c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc3c27739368544d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2f4b0bd716764377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf869bb31120e47c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Re28aa00fe3094a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbfa39d25fcfa4149"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfa30fbc2792473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R83a36ca283a943a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R2df3694208b24409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rbefe77f10d51471f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R6828cdfffd754cf5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ree522582ca8d4884"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R67005f6fcce044aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9510fec50854400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd88f9e10f13444f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3dcffc5ba92a4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R4b81df9d91c44377"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re9aac1b298754191"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb9b50c17131d4968"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8a3ff04991394563"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R47d44061fe7d4682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rea59b07dae894de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R07ded8165bc24dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf30ba5c278974cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R82c7bdfb6a0846a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R81c36776bb334adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3fdb613814364c94"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R70b4aa55a50144e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3978b3b0785140ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R864655d3fbcd4a6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R31c6f6e96b7a4197"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R8cab6f03d0a74fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb451b7c23f6d4b13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6c5591d940fe48f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0f1cad3cfb284656"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5d905f8a21dd4ec5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R19fd419859674df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rc2bf68aa6b3e4301"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R58f17eb20a6e4afa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3244d4d458f94d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R11f251b46b204f20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -100,7 +100,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="125">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -385,6 +385,9 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -851,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc87035df6a2c463d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81bd4060781b4b59"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1907,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f792e608b8d4bfa"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d26ff4f235498c"/>
 </x:worksheet>
 </file>
 
@@ -10121,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea1f85f109c74cc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8acc47b67ce44071"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11310,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra804c7936d19401d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c9dac79c5bd4637"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18322,7 +18325,7 @@
       <x:c r="O151" s="84" t="str"/>
       <x:c r="P151" s="86" t="str"/>
     </x:row>
-    <x:row r="152">
+    <x:row r="152" ht="54" customHeight="1">
       <x:c r="A152" s="83" t="str">
         <x:v>PPT-011</x:v>
       </x:c>
@@ -18361,10 +18364,14 @@
       </x:c>
       <x:c r="M152" s="84" t="str"/>
       <x:c r="N152" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O152" s="84" t="str"/>
-      <x:c r="P152" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O152" s="84" t="str">
+        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+      </x:c>
+      <x:c r="P152" s="84" t="str">
+        <x:v>部分：PP-04 已验证矩形 AutoShape 与文本修改、fill/stroke、EMU；圆/箭头/callout/banner、adjustments、rotation、完整读改保留渲染仍未覆盖，暂无路线证明完整 P0。</x:v>
+      </x:c>
     </x:row>
     <x:row r="153">
       <x:c r="A153" s="83" t="str">
@@ -19328,7 +19335,7 @@
       <x:c r="O174" s="84" t="str"/>
       <x:c r="P174" s="86" t="str"/>
     </x:row>
-    <x:row r="175">
+    <x:row r="175" ht="54" customHeight="1">
       <x:c r="A175" s="83" t="str">
         <x:v>ADP-PP-04-01</x:v>
       </x:c>
@@ -19365,10 +19372,14 @@
       </x:c>
       <x:c r="M175" s="84" t="str"/>
       <x:c r="N175" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O175" s="84" t="str"/>
-      <x:c r="P175" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O175" s="84" t="str">
+        <x:v>research/poc/PP-04/README.md；research/poc/PP-04/artifacts/report.json；contracts/capability-status.catalog.json</x:v>
+      </x:c>
+      <x:c r="P175" s="84" t="str">
+        <x:v>部分：PoC 可运行且已有能力证据，但输入要求的 image/table/chart、notes/comments、transition/animation、media 创建/读改保存尚未覆盖；TASK/VERIFY 继续进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="176">
       <x:c r="A176" s="83" t="str">
@@ -25028,7 +25039,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76fa300e3a164c58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2332fd15d25411f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36553,7 +36564,7 @@
         <x:v>https://learn.microsoft.com/en-us/visualstudio/vsto/powerpoint-solutions?view=visualstudio</x:v>
       </x:c>
     </x:row>
-    <x:row r="276">
+    <x:row r="276" ht="52" customHeight="1">
       <x:c r="A276" s="83" t="str">
         <x:v>TASK-ADP-PP-04-01</x:v>
       </x:c>
@@ -36588,12 +36599,14 @@
       <x:c r="L276" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
-      <x:c r="M276" s="84" t="str"/>
+      <x:c r="M276" s="125" t="str">
+        <x:v>部分完成：锁定版本 PoC 已运行；新增 slide 与探针形状文本修改通过 Validator，未知部件和布局结构对照证据见 report.json。</x:v>
+      </x:c>
       <x:c r="N276" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
       </x:c>
     </x:row>
-    <x:row r="277">
+    <x:row r="277" ht="52" customHeight="1">
       <x:c r="A277" s="83" t="str">
         <x:v>VERIFY-ADP-PP-04-01</x:v>
       </x:c>
@@ -36630,7 +36643,9 @@
       <x:c r="L277" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
-      <x:c r="M277" s="84" t="str"/>
+      <x:c r="M277" s="125" t="str">
+        <x:v>部分：正常/边界/失败用例有结果；图片/表格/图表、media、notes/comments、transition/animation 与相应读改保存仍待实测。</x:v>
+      </x:c>
       <x:c r="N277" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
       </x:c>
@@ -43823,7 +43838,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3dbbf4eec7214930"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R656fe6cb705149e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44105,7 +44120,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd09bc6b6898941d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8e3e543d892424b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45521,7 +45536,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc40234be48be4210"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20cb288e0e254d7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45698,7 +45713,7 @@
       <x:c r="M4" s="84" t="str"/>
       <x:c r="N4" s="86" t="str"/>
     </x:row>
-    <x:row r="5" ht="58.5" customHeight="1">
+    <x:row r="5" ht="86" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>PP-04</x:v>
       </x:c>
@@ -45729,17 +45744,17 @@
       <x:c r="J5" s="84" t="str">
         <x:v>DocumentFormat.OpenXml 3.5.1 (MIT)；SDK 10.0.401（仅实验环境）</x:v>
       </x:c>
-      <x:c r="K5" s="84" t="str">
-        <x:v>artifacts/pp04-output.pptx + report.json：新增 1 张标题/正文页；Office2019 校验 0 错误。</x:v>
-      </x:c>
-      <x:c r="L5" s="84" t="str">
-        <x:v>母版/主题哈希一致；layout1/11 字节变化；未知部件哈希一致。</x:v>
-      </x:c>
-      <x:c r="M5" s="84" t="str">
-        <x:v>未测：图片/表格/图表、既有对象读改、notes/评论、动画/切换、EMU、Office 渲染。</x:v>
-      </x:c>
-      <x:c r="N5" s="84" t="str">
-        <x:v>本轮仅有阶段性证据；PP-04 非产品后端选型。</x:v>
+      <x:c r="K5" s="125" t="str">
+        <x:v>新建写入：新增1页标题/正文；Office 2019 Validator 0错误。见 report.json。</x:v>
+      </x:c>
+      <x:c r="L5" s="125" t="str">
+        <x:v>既有形状编辑：文本更新；shape ID/name、preset、fill/stroke 与 EMU 几何保持。母版/布局/主题 XML 规范化后相同；layout 原始字节有变化。未知部件 SHA-256 一致。</x:v>
+      </x:c>
+      <x:c r="M5" s="125" t="str">
+        <x:v>PPT-011 Partial：矩形 AutoShape 固定 fill/stroke/EMU；变更前后字段相同。未测其他 shape、图片/表格/图表、notes/动画和 Office 渲染。</x:v>
+      </x:c>
+      <x:c r="N5" s="125" t="str">
+        <x:v>ADP-PP-04-01 PoC 与验证任务已完成；此路线仍只有部分能力证据，非产品后端/运行时选型。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -45943,7 +45958,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0325442effdd41d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb5b7ccf6c7f49f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46503,7 +46518,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I12" s="84" t="str">
         <x:v>Untested</x:v>
@@ -49290,7 +49305,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2065b022cb52427c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24759105dee54b2e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rea59b07dae894de4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R07ded8165bc24dff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf30ba5c278974cb4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R82c7bdfb6a0846a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R81c36776bb334adf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3fdb613814364c94"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R70b4aa55a50144e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3978b3b0785140ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R864655d3fbcd4a6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R31c6f6e96b7a4197"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R8cab6f03d0a74fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb451b7c23f6d4b13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6c5591d940fe48f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0f1cad3cfb284656"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5d905f8a21dd4ec5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R19fd419859674df8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rc2bf68aa6b3e4301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R58f17eb20a6e4afa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3244d4d458f94d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R11f251b46b204f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdc25a67a970f4284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rce89a24f15aa4d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7bba15e441a74b23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R20a5cf21e6fc4766"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rae7f5a909a0e494a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R397e548dbcc5441e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8ae33da612a2463e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rf2be4b4793284f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0fe3aa30f9794258"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rc98e9f8c09724025"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R9a183c9e4c004e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0ed9ab491de64546"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R894badf7b1d34d53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R577bba8d09ec4b3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R8afcbb2bbd074419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R584778596bb04de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rdc82e0a459614543"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb67b2849f9ab4a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R78b6c3c2d1114da0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R198e9fdf8f1c48f0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R81bd4060781b4b59"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbb0e217aef224176"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45d26ff4f235498c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eaf684c391e4c63"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8acc47b67ce44071"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R694ec21f90134510"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c9dac79c5bd4637"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf890843341c64c63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18500,10 +18500,14 @@
       </x:c>
       <x:c r="M155" s="84" t="str"/>
       <x:c r="N155" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O155" s="84" t="str"/>
-      <x:c r="P155" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O155" s="84" t="str">
+        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+      </x:c>
+      <x:c r="P155" s="86" t="str">
+        <x:v>部分：PP-04 已验证本 PoC 嵌入 PNG 的 add/replace/read；关系、alt text、对象身份、EMU bounds 保持，SHA-256 改变，Validator 0 错误。裁切、布局、其他图片操作与渲染未覆盖。</x:v>
+      </x:c>
     </x:row>
     <x:row r="156">
       <x:c r="A156" s="83" t="str">
@@ -25039,7 +25043,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2332fd15d25411f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R142afff98a6b4f41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36600,7 +36604,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M276" s="125" t="str">
-        <x:v>部分完成：锁定版本 PoC 已运行；新增 slide 与探针形状文本修改通过 Validator，未知部件和布局结构对照证据见 report.json。</x:v>
+        <x:v>进行中：嵌入 PNG add/replace/read 通过；关系、alt text、身份/EMU 与 SHA-256 断言通过，Office 2019 校验 0 错误。</x:v>
       </x:c>
       <x:c r="N276" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -36644,7 +36648,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M277" s="125" t="str">
-        <x:v>部分：正常/边界/失败用例有结果；图片/表格/图表、media、notes/comments、transition/animation 与相应读改保存仍待实测。</x:v>
+        <x:v>进行中：正常/边界/失败与 PNG 替换可复现；图片裁切/布局/渲染、表格/图表、media/notes/comments/转场/动画及读改保存仍待测。</x:v>
       </x:c>
       <x:c r="N277" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -43838,7 +43842,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R656fe6cb705149e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c460716023249bf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44120,7 +44124,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8e3e543d892424b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38147a6b43034c26"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45536,7 +45540,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20cb288e0e254d7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b94e045496849b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45751,10 +45755,10 @@
         <x:v>既有形状编辑：文本更新；shape ID/name、preset、fill/stroke 与 EMU 几何保持。母版/布局/主题 XML 规范化后相同；layout 原始字节有变化。未知部件 SHA-256 一致。</x:v>
       </x:c>
       <x:c r="M5" s="125" t="str">
-        <x:v>PPT-011 Partial：矩形 AutoShape 固定 fill/stroke/EMU；变更前后字段相同。未测其他 shape、图片/表格/图表、notes/动画和 Office 渲染。</x:v>
+        <x:v>PPT-011 Partial：矩形文本修改后 fill/stroke/EMU 保持。PPT-014 Partial：嵌入 PNG 替换后关系、alt text、身份/EMU 保持，SHA-256 改变。其他图片操作、表格/图表和渲染未测。</x:v>
       </x:c>
       <x:c r="N5" s="125" t="str">
-        <x:v>ADP-PP-04-01 PoC 与验证任务已完成；此路线仍只有部分能力证据，非产品后端/运行时选型。</x:v>
+        <x:v>TASK/VERIFY 仍进行中：图片其他操作、表格/图表、media、notes/comments、转场/动画及读改保存尚未实测。实验版本不构成产品选型。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -45958,7 +45962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb5b7ccf6c7f49f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc52fafb825714220"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46656,7 +46660,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H15" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I15" s="84" t="str">
         <x:v>Untested</x:v>
@@ -49305,7 +49309,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24759105dee54b2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3753191edcc44fab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdc25a67a970f4284"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rce89a24f15aa4d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7bba15e441a74b23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R20a5cf21e6fc4766"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rae7f5a909a0e494a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R397e548dbcc5441e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8ae33da612a2463e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rf2be4b4793284f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0fe3aa30f9794258"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rc98e9f8c09724025"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R9a183c9e4c004e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R0ed9ab491de64546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R894badf7b1d34d53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R577bba8d09ec4b3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R8afcbb2bbd074419"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R584778596bb04de3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rdc82e0a459614543"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb67b2849f9ab4a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R78b6c3c2d1114da0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R198e9fdf8f1c48f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5feb378241d34df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3e470cf80b4441cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R809a1dd6bee14818"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Reb39a52995484327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rdafac246fe294b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R19d3986d6758485e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R012dc3c7c17f4b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R23a892beec614ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rceac029ec4094fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R08ee716fc0a54df2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R2d6502d5ff8249c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rac13b4afc4184cb6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc07fa5bb11b84b66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7f98218b3e874b48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R389784a51c094f88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R56e97da2de81451e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5c457ffddbcd486a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1717d48309ae435b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R99c60ce69f974fa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2000bd8a7e754a6c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rbb0e217aef224176"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R45947e6fd7874c6a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2eaf684c391e4c63"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56ba625e1d5e41ab"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R694ec21f90134510"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c5dd1e3f86847b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf890843341c64c63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e986f22e79247f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18592,10 +18592,14 @@
       </x:c>
       <x:c r="M157" s="84" t="str"/>
       <x:c r="N157" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O157" s="84" t="str"/>
-      <x:c r="P157" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O157" s="84" t="str">
+        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+      </x:c>
+      <x:c r="P157" s="86" t="str">
+        <x:v>Partial：表格文本往返通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="158">
       <x:c r="A158" s="83" t="str">
@@ -25043,7 +25047,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R142afff98a6b4f41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe981bc75f1b4c4c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36604,7 +36608,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M276" s="125" t="str">
-        <x:v>进行中：嵌入 PNG add/replace/read 通过；关系、alt text、身份/EMU 与 SHA-256 断言通过，Office 2019 校验 0 错误。</x:v>
+        <x:v>进行中：PPT-016 表格 PoC 新建 2×2 table，保存重开后更新并读回 1 个单元格；ID/name、行列数、EMU 坐标保持，Office 2019 校验 0 错误。样式、合并、分页和第三方既有表格未测。</x:v>
       </x:c>
       <x:c r="N276" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -36648,7 +36652,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M277" s="125" t="str">
-        <x:v>进行中：正常/边界/失败与 PNG 替换可复现；图片裁切/布局/渲染、表格/图表、media/notes/comments/转场/动画及读改保存仍待测。</x:v>
+        <x:v>进行中：新增 2×2 table 单元格文本往返证据；图片与表格仍有范围未测，图表/media/notes/comments/转场/动画、渲染及第三方 PPT 读改保存待验证。</x:v>
       </x:c>
       <x:c r="N277" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -43842,7 +43846,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c460716023249bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9cab1c896494b59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44124,7 +44128,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38147a6b43034c26"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22d8c5fcf8114bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45540,7 +45544,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b94e045496849b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0dd84108c81472e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45755,10 +45759,10 @@
         <x:v>既有形状编辑：文本更新；shape ID/name、preset、fill/stroke 与 EMU 几何保持。母版/布局/主题 XML 规范化后相同；layout 原始字节有变化。未知部件 SHA-256 一致。</x:v>
       </x:c>
       <x:c r="M5" s="125" t="str">
-        <x:v>PPT-011 Partial：矩形文本修改后 fill/stroke/EMU 保持。PPT-014 Partial：嵌入 PNG 替换后关系、alt text、身份/EMU 保持，SHA-256 改变。其他图片操作、表格/图表和渲染未测。</x:v>
+        <x:v>PPT-011 Partial：矩形文本修改后 fill/stroke/EMU 保持。PPT-014 Partial：嵌入 PNG 替换后关系、alt text、身份/EMU 保持，SHA-256 改变。PPT-016 Partial：2×2 表格保存重开后单元格文本更新并读回，ID/name、行列数、EMU 保持。Office 2019 Validator 均为 0 错误；样式、合并、分页和渲染未测。</x:v>
       </x:c>
       <x:c r="N5" s="125" t="str">
-        <x:v>TASK/VERIFY 仍进行中：图片其他操作、表格/图表、media、notes/comments、转场/动画及读改保存尚未实测。实验版本不构成产品选型。</x:v>
+        <x:v>TASK/VERIFY 仍进行中：图片裁切/布局/其他操作与表格合并、样式、行列编辑、分页/渲染、第三方对象读改保存，以及图表、media、notes/comments、转场/动画尚未实测。实验版本不构成产品选型。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -45962,7 +45966,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc52fafb825714220"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R212c4151e42f4c42"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46752,7 +46756,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H17" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I17" s="84" t="str">
         <x:v>Untested</x:v>
@@ -49309,7 +49313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3753191edcc44fab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70de127ce6b7437f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R5feb378241d34df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3e470cf80b4441cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R809a1dd6bee14818"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Reb39a52995484327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rdafac246fe294b86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R19d3986d6758485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R012dc3c7c17f4b49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R23a892beec614ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rceac029ec4094fea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R08ee716fc0a54df2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R2d6502d5ff8249c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rac13b4afc4184cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rc07fa5bb11b84b66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7f98218b3e874b48"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R389784a51c094f88"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R56e97da2de81451e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R5c457ffddbcd486a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1717d48309ae435b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R99c60ce69f974fa0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2000bd8a7e754a6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R745717578c54454a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R38707c327e1c4774"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R524c34b66ae9422a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1554413350ff42ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R75817ccc4dda4935"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R43c40d07d4f54375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7880e9737fc94905"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ref32937ae22c44cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re7a99578e2fa428a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Raddc372b284c4f8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ff54b8da5bb44b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rff31fec5cc1c42f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R3d886a6a859149ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7a666f4eef7d4ad7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf00c185b932d493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1835b943bf2448dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R30b40438d1304fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3ffa2738a9594b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfa93ae6e240f4cd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rdee561304e6d4065"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R45947e6fd7874c6a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73ba7dba0d2b45d6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56ba625e1d5e41ab"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00772f8dfb564600"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c5dd1e3f86847b1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926bcde02b6943a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e986f22e79247f6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb66725176cc478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18640,10 +18640,14 @@
       </x:c>
       <x:c r="M158" s="84" t="str"/>
       <x:c r="N158" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O158" s="84" t="str"/>
-      <x:c r="P158" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O158" s="84" t="str">
+        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+      </x:c>
+      <x:c r="P158" s="86" t="str">
+        <x:v>Partial：图表数据往返通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="159">
       <x:c r="A159" s="83" t="str">
@@ -25047,7 +25051,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe981bc75f1b4c4c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6db261d93024d61"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36608,7 +36612,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M276" s="125" t="str">
-        <x:v>进行中：PPT-016 表格 PoC 新建 2×2 table，保存重开后更新并读回 1 个单元格；ID/name、行列数、EMU 坐标保持，Office 2019 校验 0 错误。样式、合并、分页和第三方既有表格未测。</x:v>
+        <x:v>进行中：PPT-016 2×2表格文本往返通过；PPT-017 单系列图表同步更新缓存与内嵌 XLSX 数据通过。详细证据见 report.json；剩余未测项见项目计划。</x:v>
       </x:c>
       <x:c r="N276" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -36652,7 +36656,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M277" s="125" t="str">
-        <x:v>进行中：新增 2×2 table 单元格文本往返证据；图片与表格仍有范围未测，图表/media/notes/comments/转场/动画、渲染及第三方 PPT 读改保存待验证。</x:v>
+        <x:v>进行中：表格样式/合并/分页/第三方对象；图表组合图/误差线/日期轴/其他类型/渲染与第三方对象；media/notes/comments/转场/动画仍待验证。</x:v>
       </x:c>
       <x:c r="N277" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/open-xml/presentation/overview</x:v>
@@ -43846,7 +43850,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9cab1c896494b59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c1d7bc268f4ccf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44128,7 +44132,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22d8c5fcf8114bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R794ee80ddf564ff7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45544,7 +45548,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0dd84108c81472e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98e1c235f99b4064"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45759,10 +45763,10 @@
         <x:v>既有形状编辑：文本更新；shape ID/name、preset、fill/stroke 与 EMU 几何保持。母版/布局/主题 XML 规范化后相同；layout 原始字节有变化。未知部件 SHA-256 一致。</x:v>
       </x:c>
       <x:c r="M5" s="125" t="str">
-        <x:v>PPT-011 Partial：矩形文本修改后 fill/stroke/EMU 保持。PPT-014 Partial：嵌入 PNG 替换后关系、alt text、身份/EMU 保持，SHA-256 改变。PPT-016 Partial：2×2 表格保存重开后单元格文本更新并读回，ID/name、行列数、EMU 保持。Office 2019 Validator 均为 0 错误；样式、合并、分页和渲染未测。</x:v>
+        <x:v>PPT-011/014/016 Partial：矩形文本与嵌入 PNG、2×2 表格的指定读改保存断言通过。PPT-017 Partial：单系列三类别柱形图绑定内嵌 XLSX；Q2 从 18 改为 20 后缓存与工作簿一致，title/axis/legend/value labels/公式、身份/EMU 保持。PPTX 与 XLSX Office 2019 Validator 均为 0。</x:v>
       </x:c>
       <x:c r="N5" s="125" t="str">
-        <x:v>TASK/VERIFY 仍进行中：图片裁切/布局/其他操作与表格合并、样式、行列编辑、分页/渲染、第三方对象读改保存，以及图表、media、notes/comments、转场/动画尚未实测。实验版本不构成产品选型。</x:v>
+        <x:v>TASK/VERIFY 仍进行中：图片与表格仍有范围未测；图表组合图/误差线/日期轴/其他类型、image fallback、PowerPoint 编辑数据行为、渲染/第三方对象，以及 media、notes/comments、转场/动画尚未实测。实验版本不构成产品选型。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -45966,7 +45970,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R212c4151e42f4c42"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cae68c5a2e34e65"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46802,7 +46806,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="H18" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>Partial</x:v>
       </x:c>
       <x:c r="I18" s="84" t="str">
         <x:v>Untested</x:v>
@@ -49313,7 +49317,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70de127ce6b7437f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c5eb4eb911e40fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R745717578c54454a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R38707c327e1c4774"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R524c34b66ae9422a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R1554413350ff42ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R75817ccc4dda4935"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R43c40d07d4f54375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7880e9737fc94905"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ref32937ae22c44cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Re7a99578e2fa428a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Raddc372b284c4f8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ff54b8da5bb44b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rff31fec5cc1c42f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R3d886a6a859149ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7a666f4eef7d4ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf00c185b932d493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1835b943bf2448dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R30b40438d1304fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R3ffa2738a9594b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfa93ae6e240f4cd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rdee561304e6d4065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R14fe8b0d0ac545db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R22d9544c515f46a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6f2b98cb4bc74017"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7b31a564e34044f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2d2be158dbaf4dbd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6452969f4ed4402f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R79b9bfa0798d42af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra3ed7c3baf1643e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R00c9009e16f349cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd75d122e74e545c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc1e5f11eda844d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2b6a48e8c6524cfd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd10fb68879624ecf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rf3334978c06f445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf705eaa1c4224e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd395d4bf9be74e76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R9a5fa5ddc4584b47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0f025e4ad9e8466c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Re4ae32fd70dc4882"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8bea6993533847e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R73ba7dba0d2b45d6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd83021cdb5604bac"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00772f8dfb564600"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a8939b7ce54468b"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926bcde02b6943a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf34abce315a64dd4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb66725176cc478d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b118d52239e4bb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12165,9 +12165,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O12" s="84" t="str">
-        <x:v>research/P01/README.md</x:v>
-      </x:c>
-      <x:c r="P12" s="86" t="str"/>
+        <x:v>research/P01/README.md；research/P01/artifacts/quick-smoke/environment.json；research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json</x:v>
+      </x:c>
+      <x:c r="P12" s="86" t="str">
+        <x:v>Docker 中已复现三页可编辑 PPTX，结构检查通过；真实 PowerPoint/LibreOffice 打开与渲染待验证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -25051,7 +25053,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6db261d93024d61"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50a823f087874f62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25657,10 +25659,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L14" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M14" s="84" t="str">
-        <x:v>research/P01/README.md</x:v>
+        <x:v>research/P01/README.md；research/P01/artifacts/quick-smoke/environment.json；research/P01/projects/p01_hello_world_20261007/exports/p01-hello-world.pptx</x:v>
       </x:c>
       <x:c r="N14" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
@@ -25701,9 +25703,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M15" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M15" s="84" t="str">
+        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json；Office/LibreOffice 渲染待验证</x:v>
+      </x:c>
       <x:c r="N15" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43850,7 +43854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89c1d7bc268f4ccf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cb9ce6595b841cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44132,7 +44136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R794ee80ddf564ff7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d308a6b83d4a21"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45548,7 +45552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98e1c235f99b4064"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b553e9e20c4803"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45970,7 +45974,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cae68c5a2e34e65"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R008651dad77b42a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49317,7 +49321,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c5eb4eb911e40fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f0f89f0e0c434e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R14fe8b0d0ac545db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R22d9544c515f46a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6f2b98cb4bc74017"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R7b31a564e34044f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R2d2be158dbaf4dbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6452969f4ed4402f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R79b9bfa0798d42af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra3ed7c3baf1643e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R00c9009e16f349cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd75d122e74e545c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc1e5f11eda844d37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2b6a48e8c6524cfd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd10fb68879624ecf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rf3334978c06f445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf705eaa1c4224e17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd395d4bf9be74e76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R9a5fa5ddc4584b47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0f025e4ad9e8466c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Re4ae32fd70dc4882"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8bea6993533847e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc0b310f2ae174b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb4c4930d1db8442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra72ecc0a9d954a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc079d27fc2424de5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9d6eac00e12144a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1d7758ee46734ce9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra93548c030b04126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R69e4633ce2bf4d25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0ba16694eaf440b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Re1192b2463334a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re1301cc930d845f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8867565c7374aab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R02551f65637040d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R07cc39e3628c4d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf093a40684494d1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6899055196704b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3aea414010314379"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2fc1cca4d66a4e60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R81cf590a184b436d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R75daaf07d4f24e2a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd83021cdb5604bac"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6586bbfad77a48c5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.03571428571428571</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a8939b7ce54468b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263316093a8a4d10"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf34abce315a64dd4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb775624dca54bbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b118d52239e4bb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raea94fda64e244dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12162,13 +12162,13 @@
       </x:c>
       <x:c r="M12" s="84" t="str"/>
       <x:c r="N12" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="O12" s="84" t="str">
-        <x:v>research/P01/README.md；research/P01/artifacts/quick-smoke/environment.json；research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json</x:v>
+        <x:v>research/P01/README.md；research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json</x:v>
       </x:c>
       <x:c r="P12" s="86" t="str">
-        <x:v>Docker 中已复现三页可编辑 PPTX，结构检查通过；真实 PowerPoint/LibreOffice 打开与渲染待验证。</x:v>
+        <x:v>PPTX 结构检查及 PowerPoint 16.0 只读打开/3 页 1920×1080 原生渲染通过；无裁切、遮挡或缺字。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -25053,7 +25053,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50a823f087874f62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6921498085db4586"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25662,7 +25662,7 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="M14" s="84" t="str">
-        <x:v>research/P01/README.md；research/P01/artifacts/quick-smoke/environment.json；research/P01/projects/p01_hello_world_20261007/exports/p01-hello-world.pptx</x:v>
+        <x:v>research/P01/README.md；research/P01/projects/p01_hello_world_20261007/exports/p01-hello-world.pptx</x:v>
       </x:c>
       <x:c r="N14" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
@@ -25703,10 +25703,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L15" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M15" s="84" t="str">
-        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json；Office/LibreOffice 渲染待验证</x:v>
+        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json</x:v>
       </x:c>
       <x:c r="N15" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
@@ -43854,7 +43854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cb9ce6595b841cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R844cdf17544d4ee9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44136,7 +44136,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8d308a6b83d4a21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R852f96ce5e64436a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45552,7 +45552,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R01b553e9e20c4803"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5eced4dff74482f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45974,7 +45974,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R008651dad77b42a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d39b4640fe349b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49321,7 +49321,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06f0f89f0e0c434e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reac9ca85edc140a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc0b310f2ae174b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb4c4930d1db8442d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra72ecc0a9d954a18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc079d27fc2424de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9d6eac00e12144a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1d7758ee46734ce9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Ra93548c030b04126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R69e4633ce2bf4d25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R0ba16694eaf440b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Re1192b2463334a0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re1301cc930d845f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8867565c7374aab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R02551f65637040d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R07cc39e3628c4d47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf093a40684494d1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6899055196704b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3aea414010314379"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R2fc1cca4d66a4e60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R81cf590a184b436d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R75daaf07d4f24e2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3018aa1ce35144bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R57fbe98f69d046bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R39ee8c72e3674ec9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6a55c614cd0d4a00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Racf9125620e849cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra5fa842e0ea7454c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rb67516789c7b4ae2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5bc37db9b8974bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb5046e990afa4270"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab0bc4303f2c450b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R00304afec97e4707"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R76a3411629f74f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6ac4620e196a4b97"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rbc4e1393e14b4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rb49a743eb78f4411"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R574f11b980ec4375"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re1adf5f08210490d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R46752591a8df4dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd7d7787212134703"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1cf0da3111874465"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6586bbfad77a48c5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R07394874b0de4493"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.03571428571428571</x:v>
+        <x:v>0.07142857142857142</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R263316093a8a4d10"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fed5905224a4e95"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb775624dca54bbe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re33b93036f8947e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raea94fda64e244dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8559a53203e403a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12210,10 +12210,14 @@
       </x:c>
       <x:c r="M13" s="84" t="str"/>
       <x:c r="N13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O13" s="84" t="str"/>
-      <x:c r="P13" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O13" s="84" t="str">
+        <x:v>research/P01/call_graph.md；research/P01/source_index.json；research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-02.json</x:v>
+      </x:c>
+      <x:c r="P13" s="86" t="str">
+        <x:v>源码索引覆盖 Default/Quick 主链；Quick 正常流程与只读路径失败证据通过；Default 仅源码追踪。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -25053,7 +25057,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6921498085db4586"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9019044b06742a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25747,9 +25751,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M16" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M16" s="84" t="str">
+        <x:v>research/P01/call_graph.md；research/P01/source_index.json</x:v>
+      </x:c>
       <x:c r="N16" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -25789,9 +25795,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M17" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M17" s="84" t="str">
+        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-02.json</x:v>
+      </x:c>
       <x:c r="N17" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43854,7 +43862,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R844cdf17544d4ee9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf147f79de3bc4b14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44136,7 +44144,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R852f96ce5e64436a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92fe1dd1c8144149"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45552,7 +45560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5eced4dff74482f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d84a7cd3514201"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45974,7 +45982,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d39b4640fe349b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea7d8b20f59646dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49321,7 +49329,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reac9ca85edc140a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d1d5d9167be478b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3018aa1ce35144bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R57fbe98f69d046bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R39ee8c72e3674ec9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6a55c614cd0d4a00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Racf9125620e849cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Ra5fa842e0ea7454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rb67516789c7b4ae2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5bc37db9b8974bfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb5046e990afa4270"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab0bc4303f2c450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R00304afec97e4707"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R76a3411629f74f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R6ac4620e196a4b97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rbc4e1393e14b4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rb49a743eb78f4411"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R574f11b980ec4375"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re1adf5f08210490d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R46752591a8df4dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd7d7787212134703"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1cf0da3111874465"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R816fdda315e94428"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R266118c6db0b49df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc9951cdf546640fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R870a5c0a0f0e40e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc45e478c87564f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5f147eb36af14dec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd285595f032b4a81"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb75a9c08d008490a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd32f5bb0ad9149b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R11a371c62bb44b8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R9efd80c0049d4de3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1d4326b7f2d44f1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R77a87d66d7d2437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra7511017634f4ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R4cfbb3ca3fb74c89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R57dd1d1f984340f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R304c368e7d8845d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Raf4afce97e2840b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Re8f38ca584814f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rd03a0e2b558d4777"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R07394874b0de4493"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8e166cb0837d45aa"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.07142857142857142</x:v>
+        <x:v>0.10714285714285714</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fed5905224a4e95"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83facaa30ba64b1b"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re33b93036f8947e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f68d601ae84958"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8559a53203e403a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aa95484281f4622"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12258,10 +12258,14 @@
       </x:c>
       <x:c r="M14" s="84" t="str"/>
       <x:c r="N14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O14" s="84" t="str"/>
-      <x:c r="P14" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O14" s="84" t="str">
+        <x:v>research/P01/decision_map.md；research/P01/project_decision_map.json；research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-03.json</x:v>
+      </x:c>
+      <x:c r="P14" s="86" t="str">
+        <x:v>提取24个页面结构/视觉决策节点，覆盖DEC-001–040；Agent内部推理和未运行路线边界已注明。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -25057,7 +25061,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9019044b06742a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42669c3b0c31454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25839,9 +25843,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M18" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M18" s="84" t="str">
+        <x:v>research/P01/decision_map.md；research/P01/project_decision_map.json</x:v>
+      </x:c>
       <x:c r="N18" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -25881,9 +25887,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L19" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M19" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M19" s="84" t="str">
+        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-03.json</x:v>
+      </x:c>
       <x:c r="N19" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43862,7 +43870,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf147f79de3bc4b14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ebbbfe4214344b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44144,7 +44152,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92fe1dd1c8144149"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6ca878920043dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45560,7 +45568,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8d84a7cd3514201"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81f283cb3c7473f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45982,7 +45990,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea7d8b20f59646dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09acf08fd01d473a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49329,7 +49337,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d1d5d9167be478b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48903edf74e54ac9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R816fdda315e94428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R266118c6db0b49df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rc9951cdf546640fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R870a5c0a0f0e40e4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc45e478c87564f2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R5f147eb36af14dec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd285595f032b4a81"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rb75a9c08d008490a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd32f5bb0ad9149b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R11a371c62bb44b8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R9efd80c0049d4de3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1d4326b7f2d44f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R77a87d66d7d2437d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra7511017634f4ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R4cfbb3ca3fb74c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R57dd1d1f984340f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R304c368e7d8845d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Raf4afce97e2840b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Re8f38ca584814f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rd03a0e2b558d4777"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R442a64c6a2b946cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3e0dd2b7caa641c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R35c1fd7bba574605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6eac19ff312f460e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1fbb0a3bbe0f450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7f5b4aec7a3b466e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbc910a6c71014d1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Reaa7988940814af7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R48d099831a794320"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R47fb756358b14d59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R734dd9944fac44b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re5642a2a1d0243e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R08a19b3404294052"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R43d0030b146c4351"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R587d93f0ce124c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2ddd35c478424975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0cb342d680a74998"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc6504599ef864ac6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R079e806fb38c432c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R72564e11a3604961"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8e166cb0837d45aa"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfcb926f3d22a44b2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.10714285714285714</x:v>
+        <x:v>0.14285714285714285</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83facaa30ba64b1b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f8a39550a0444c"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97f68d601ae84958"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c9906bb82764a7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8aa95484281f4622"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bc862187234d29"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12306,10 +12306,14 @@
       </x:c>
       <x:c r="M15" s="84" t="str"/>
       <x:c r="N15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O15" s="84" t="str"/>
-      <x:c r="P15" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O15" s="84" t="str">
+        <x:v>research/P01/project_template_map.json；research/P01/tools/build_project_template_map.mjs；research/P01/validation/verify-res-p01-04.json</x:v>
+      </x:c>
+      <x:c r="P15" s="86" t="str">
+        <x:v>建立ProjectTemplateMap，覆盖7组Layout、86个SVG、53种页面类型、320个slot和287个Design Spec token；字符数上限及token-slot映射缺失如实标注。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -25061,7 +25065,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42669c3b0c31454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31f58cea61a74cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25931,9 +25935,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L20" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M20" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M20" s="84" t="str">
+        <x:v>research/P01/project_template_map.json；research/P01/tools/build_project_template_map.mjs</x:v>
+      </x:c>
       <x:c r="N20" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -25973,9 +25979,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L21" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M21" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M21" s="84" t="str">
+        <x:v>research/P01/validation/verify-res-p01-04.json</x:v>
+      </x:c>
       <x:c r="N21" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43870,7 +43878,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ebbbfe4214344b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1ce17353fda435a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44152,7 +44160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe6ca878920043dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e90773f06154009"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45568,7 +45576,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb81f283cb3c7473f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12b6c39501b4ea5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45990,7 +45998,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09acf08fd01d473a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3152eb97659245ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49337,7 +49345,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48903edf74e54ac9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0834128f110493b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R442a64c6a2b946cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3e0dd2b7caa641c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R35c1fd7bba574605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6eac19ff312f460e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1fbb0a3bbe0f450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7f5b4aec7a3b466e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rbc910a6c71014d1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Reaa7988940814af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R48d099831a794320"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R47fb756358b14d59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R734dd9944fac44b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re5642a2a1d0243e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R08a19b3404294052"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R43d0030b146c4351"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R587d93f0ce124c02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R2ddd35c478424975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R0cb342d680a74998"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc6504599ef864ac6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R079e806fb38c432c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R72564e11a3604961"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R099581dd04374f89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd9ec878f0f9646a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rca89eddf80ef4a52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4fceb1390a454826"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4cfcc3dfe14f4125"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rdca10f7ada884704"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R2ea59066b2874083"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra095f32979ab44f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rc8d5faa985464ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R55f53f237eba4230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6cf28dde92cf46ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf7bbbadad7814f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra9879d37469b481b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R421882d8877f4a19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5bf303b9eed94be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8ddf0a91aa414027"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R18b435cdb8974de9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc40d960e8ca947ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R333d3ffc579f4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R39f64eb2a6e14c4d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfcb926f3d22a44b2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c189815c9ac4353"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f8a39550a0444c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6394b6c9b94b74"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c9906bb82764a7f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37c703a91a04e56"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5bc862187234d29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7d95d534ec84a07"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12354,10 +12354,14 @@
       </x:c>
       <x:c r="M16" s="84" t="str"/>
       <x:c r="N16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O16" s="84" t="str"/>
-      <x:c r="P16" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O16" s="84" t="str">
+        <x:v>research/P01/project_capability_map.json；research/P01/validation/verify-res-p01-05.json</x:v>
+      </x:c>
+      <x:c r="P16" s="86" t="str">
+        <x:v>已登记30项PPT对象能力及QA/Revision/既有PPT编辑边界；复用P01-01正常证据；容器内边界/失败验证待执行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -25065,7 +25069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31f58cea61a74cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295cd6d122a145b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26023,9 +26027,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L22" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M22" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M22" s="84" t="str">
+        <x:v>research/P01/project_capability_map.json</x:v>
+      </x:c>
       <x:c r="N22" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -26065,9 +26071,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M23" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M23" s="84" t="str">
+        <x:v>research/P01/validation/verify-res-p01-05.json</x:v>
+      </x:c>
       <x:c r="N23" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
@@ -43878,7 +43886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb1ce17353fda435a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b47a431bd24c6c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43979,13 +43987,17 @@
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
       <x:c r="K2" s="80" t="str">
-        <x:v>进行中：源码已固定；官方最小流程待复现（Docker API 无响应）</x:v>
+        <x:v>进行中：源码固定；Quick最小流程已复现；P01-05能力图谱已建，Docker验证待执行</x:v>
       </x:c>
       <x:c r="L2" s="80" t="str">
         <x:v>research/P01/README.md</x:v>
       </x:c>
-      <x:c r="M2" s="80" t="str"/>
-      <x:c r="N2" s="82" t="str"/>
+      <x:c r="M2" s="80" t="str">
+        <x:v>research/P01/projects/p01_hello_world_20261007/validation/verify-res-p01-01.json</x:v>
+      </x:c>
+      <x:c r="N2" s="82" t="str">
+        <x:v>research/P01/project_capability_map.json；research/P01/validation/verify-res-p01-05.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -44160,7 +44172,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e90773f06154009"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26f8aeec4a541a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45576,7 +45588,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf12b6c39501b4ea5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf62f8bb9a9d447b9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45998,7 +46010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3152eb97659245ce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2ac643e3fd4627"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49345,7 +49357,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0834128f110493b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279470f375684a47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R099581dd04374f89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rd9ec878f0f9646a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rca89eddf80ef4a52"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4fceb1390a454826"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4cfcc3dfe14f4125"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rdca10f7ada884704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R2ea59066b2874083"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra095f32979ab44f5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rc8d5faa985464ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R55f53f237eba4230"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6cf28dde92cf46ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf7bbbadad7814f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Ra9879d37469b481b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R421882d8877f4a19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5bf303b9eed94be3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8ddf0a91aa414027"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R18b435cdb8974de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc40d960e8ca947ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R333d3ffc579f4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R39f64eb2a6e14c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R992856d40b444dcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R774ca3d8db354d1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R5ce952d4f34f42a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd4485467597b402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1b8bcac6deb44bc6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R630b4e8cb44445c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8bf7228ca5e847d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R20cb6abc4f884c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5141ef470d0b4c04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd13c4b835954471b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc6f5658475464c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2250c89aa0d1473c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re9aba1145d5f4a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R733499642bca43b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R08c244d35c064003"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rebd88138b8a0406f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re6608ca71f2e4e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rf0fe13cd263c409c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6efeee6ca9b14d0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra3e1d67587fd4942"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c189815c9ac4353"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74a5783c9657439e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b6394b6c9b94b74"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re972d2d95961402c"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc37c703a91a04e56"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5745f8ac27f94fa5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7d95d534ec84a07"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65d7013d5f0e43ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25069,7 +25069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R295cd6d122a145b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee6ccc852514bb8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25216,7 +25216,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M3" s="84" t="str">
-        <x:v>contracts/task-route.catalog.json（草案；运行时路由未实现）</x:v>
+        <x:v>contracts/task-route.schema.json；contracts/task-route.catalog.json；contracts/task-route.fixtures.json；PROJECT_PLAN.md（TASK-GOV-002；运行时路由未实现）</x:v>
       </x:c>
       <x:c r="N3" s="86" t="str">
         <x:v>本规划</x:v>
@@ -43886,7 +43886,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6b47a431bd24c6c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a232892b93a41d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44172,7 +44172,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb26f8aeec4a541a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb920f6b8a3be4a83"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45588,7 +45588,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf62f8bb9a9d447b9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b50ac2372c84380"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46010,7 +46010,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a2ac643e3fd4627"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b5df97c029e4c66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49357,7 +49357,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279470f375684a47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R026494d85325454c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R992856d40b444dcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R774ca3d8db354d1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R5ce952d4f34f42a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd4485467597b402e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R1b8bcac6deb44bc6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R630b4e8cb44445c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8bf7228ca5e847d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R20cb6abc4f884c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5141ef470d0b4c04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd13c4b835954471b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc6f5658475464c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2250c89aa0d1473c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Re9aba1145d5f4a76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R733499642bca43b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R08c244d35c064003"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rebd88138b8a0406f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re6608ca71f2e4e47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rf0fe13cd263c409c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6efeee6ca9b14d0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra3e1d67587fd4942"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3456e98f14834c36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Reac7fd0b7998418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6ae8ee16c2fc40b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R0dcc3e1f3b264672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6117a8f8f85b4fc2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1563b9b2a8454e80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R406e35ee77984ce3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R829cbca183414647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R7aa62cc4cddb42ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R27c8678b0e9b498d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R34bab506fc314827"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd1147ae9ac3441aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd49dd4bfb0734a42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R6a7596886b4d4390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R630a7189396345eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R16fba901b07640b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf9463761db7b4037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1b98768d404b4100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6a547900429d42fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R67064c4528224953"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R74a5783c9657439e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a08504c619a488f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re972d2d95961402c"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5941fe1bef84cef"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5745f8ac27f94fa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea254c031954092"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65d7013d5f0e43ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc88165ed8ad34217"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25069,7 +25069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ee6ccc852514bb8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ff0cedfe074955"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26157,9 +26157,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L25" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M25" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M25" s="84" t="str">
+        <x:v>research/P02/validation/verify-res-p02-01.json</x:v>
+      </x:c>
       <x:c r="N25" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -43886,7 +43888,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a232892b93a41d5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ca753e8a204d5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44172,7 +44174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb920f6b8a3be4a83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re196dc84ec5e4119"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45588,7 +45590,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1b50ac2372c84380"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d4cb99950541d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46010,7 +46012,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b5df97c029e4c66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50cae9847cbb4846"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49357,7 +49359,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R026494d85325454c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c0b5fdc81524184"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3456e98f14834c36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Reac7fd0b7998418c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6ae8ee16c2fc40b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R0dcc3e1f3b264672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6117a8f8f85b4fc2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1563b9b2a8454e80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R406e35ee77984ce3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R829cbca183414647"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R7aa62cc4cddb42ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R27c8678b0e9b498d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R34bab506fc314827"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd1147ae9ac3441aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd49dd4bfb0734a42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R6a7596886b4d4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R630a7189396345eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R16fba901b07640b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf9463761db7b4037"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1b98768d404b4100"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R6a547900429d42fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R67064c4528224953"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Red072d58f93c42b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc24dccda0ca14a36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R49c50b3e0b524883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd8f815c603784715"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc28e6e8c08c44ec4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R83542f8c9f82489d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rac6ba72573a8479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5cf34bc9f01841a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb36f9e61288a4a26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R569b999025894906"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6fd8532db3c241b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R14b754244eaa4251"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R43d63947c13348b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re7c9955caf714bfc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R8b5da6a8609d4784"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R51692d7ae99d4522"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rd128f20b915a4d09"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R63782eb68b24489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R44c1f6072b0541c2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1b80441cafd843cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2a08504c619a488f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R12560ab508644139"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.14285714285714285</x:v>
+        <x:v>0.17857142857142858</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5941fe1bef84cef"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d36609a91745fd"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcea254c031954092"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd542d18e93a4b6f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc88165ed8ad34217"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06e67ce3bd714548"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12622,13 +12622,13 @@
       </x:c>
       <x:c r="M22" s="84" t="str"/>
       <x:c r="N22" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="O22" s="84" t="str">
-        <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P03/README.md</x:v>
       </x:c>
       <x:c r="P22" s="86" t="str">
-        <x:v>待复现</x:v>
+        <x:v>已复现</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -25069,7 +25069,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41ff0cedfe074955"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf148b8aa13d42a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26535,10 +26535,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L34" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M34" s="84" t="str">
-        <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P03/validation/smoke.json</x:v>
       </x:c>
       <x:c r="N34" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
@@ -26579,9 +26579,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M35" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M35" s="84" t="str">
+        <x:v>research/P03/validation/smoke.json</x:v>
+      </x:c>
       <x:c r="N35" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43888,7 +43890,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95ca753e8a204d5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46e9059541d4122"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44073,13 +44075,17 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>源码已固定；待复现</x:v>
+        <x:v>官方 Docker 已复现</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
         <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
-      <x:c r="M4" s="84" t="str"/>
-      <x:c r="N4" s="86" t="str"/>
+      <x:c r="M4" s="84" t="str">
+        <x:v>research/P03/validation/smoke.json</x:v>
+      </x:c>
+      <x:c r="N4" s="86" t="str">
+        <x:v>research/P03/README.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -44174,7 +44180,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re196dc84ec5e4119"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8d3cd31d4454384"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45590,7 +45596,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d4cb99950541d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06cfbc2f01af4bf4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46012,7 +46018,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50cae9847cbb4846"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23c09c0eaef846f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49359,7 +49365,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c0b5fdc81524184"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdf5e25af3854e8c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Red072d58f93c42b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc24dccda0ca14a36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R49c50b3e0b524883"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd8f815c603784715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc28e6e8c08c44ec4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R83542f8c9f82489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rac6ba72573a8479d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R5cf34bc9f01841a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb36f9e61288a4a26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R569b999025894906"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6fd8532db3c241b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R14b754244eaa4251"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R43d63947c13348b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re7c9955caf714bfc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R8b5da6a8609d4784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R51692d7ae99d4522"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rd128f20b915a4d09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R63782eb68b24489e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R44c1f6072b0541c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1b80441cafd843cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R47088e7742484565"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9de7f07fa865408d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf55b3bcdf34e4f3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd44b606813d247e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd718120d9f244175"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re46a515a163f4d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc893ab4e68174ab7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R04cfda8f1e1a49ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd2e47072f2834e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf1c8ab3d50c54279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rbec04af2cd5f42dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1f4bc802e6c74126"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd1ef9904d35442b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0ac298f43ba34e7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rec385db21cc1477b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb4760bf0d8154e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re4932554ed904b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R361f1f36503b41b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7bc3d6d08b7e404f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R3407cb41bc6c4b88"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R12560ab508644139"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71511a80bda54365"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.17857142857142858</x:v>
+        <x:v>0.21428571428571427</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40d36609a91745fd"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re93ae2d7143f4960"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd542d18e93a4b6f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfee3c07029634efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06e67ce3bd714548"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6557842813874104"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12670,10 +12670,14 @@
       </x:c>
       <x:c r="M23" s="84" t="str"/>
       <x:c r="N23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O23" s="84" t="str"/>
-      <x:c r="P23" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O23" s="84" t="str">
+        <x:v>research/P03/call-graph.md; research/P03/source-index.json</x:v>
+      </x:c>
+      <x:c r="P23" s="86" t="str">
+        <x:v>静态源码追踪已完成</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -25069,7 +25073,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf148b8aa13d42a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89bce4f546e040cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26623,9 +26627,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L36" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M36" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M36" s="84" t="str">
+        <x:v>research/P03/call-graph.md; research/P03/source-index.json</x:v>
+      </x:c>
       <x:c r="N36" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -26665,9 +26671,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M37" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M37" s="84" t="str">
+        <x:v>research/P03/validation/verify-res-p03-02.json</x:v>
+      </x:c>
       <x:c r="N37" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43890,7 +43898,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc46e9059541d4122"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cb4ce466b3430d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44075,16 +44083,16 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>官方 Docker 已复现</x:v>
+        <x:v>Docker基线已复现；调用链已完成；生成验证待凭据</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
         <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>research/P03/validation/smoke.json</x:v>
+        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json</x:v>
       </x:c>
       <x:c r="N4" s="86" t="str">
-        <x:v>research/P03/README.md</x:v>
+        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -44180,7 +44188,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8d3cd31d4454384"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c32036ba880425b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45596,7 +45604,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06cfbc2f01af4bf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68cdad97034447a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46018,7 +46026,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23c09c0eaef846f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0756d4fc339453b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49365,7 +49373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcdf5e25af3854e8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94afaef013e43ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R47088e7742484565"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R9de7f07fa865408d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf55b3bcdf34e4f3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd44b606813d247e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd718120d9f244175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re46a515a163f4d41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc893ab4e68174ab7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R04cfda8f1e1a49ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd2e47072f2834e89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf1c8ab3d50c54279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rbec04af2cd5f42dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R1f4bc802e6c74126"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd1ef9904d35442b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R0ac298f43ba34e7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rec385db21cc1477b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb4760bf0d8154e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Re4932554ed904b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R361f1f36503b41b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R7bc3d6d08b7e404f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R3407cb41bc6c4b88"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R88e3ee0c6e7241af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4c629e0e492244be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4d276453a73e4471"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R46b4fb96df5c41f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd8f4c25b0bdc4217"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf4bdb506929f4b14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0ac66ec748cd4c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R12c0d800dca64a73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R29014079d550467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R2a51f3471c7245c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R70690679018e4f03"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2ff0891ea3394c43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rab2e2e7fe51f47b8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R3ed6fac89eca4b76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5c8872dd87694aa3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R145be019179c45c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ref8991d9baf74af1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R77e01b6caf7e4d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8f2cc12dd899431d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Re2f7a616f20d4761"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71511a80bda54365"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R75c12ce26e1746a6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.21428571428571427</x:v>
+        <x:v>0.25</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re93ae2d7143f4960"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41c9731c998d4ad3"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfee3c07029634efc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1a4956377346fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6557842813874104"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc38d4fb5b0d472d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12718,10 +12718,14 @@
       </x:c>
       <x:c r="M24" s="84" t="str"/>
       <x:c r="N24" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O24" s="84" t="str"/>
-      <x:c r="P24" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O24" s="84" t="str">
+        <x:v>research/P03/decision-map.md; research/P03/decision-map.json</x:v>
+      </x:c>
+      <x:c r="P24" s="86" t="str">
+        <x:v>源码决策映射已完成</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="83" t="str">
@@ -25073,7 +25077,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89bce4f546e040cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R867d89c1e03c4193"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26715,9 +26719,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M38" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M38" s="84" t="str">
+        <x:v>research/P03/decision-map.md; research/P03/decision-map.json</x:v>
+      </x:c>
       <x:c r="N38" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -26757,9 +26763,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M39" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M39" s="84" t="str">
+        <x:v>research/P03/validation/verify-res-p03-03.json</x:v>
+      </x:c>
       <x:c r="N39" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43898,7 +43906,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23cb4ce466b3430d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e94481cdb114716"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44083,16 +44091,16 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>Docker基线已复现；调用链已完成；生成验证待凭据</x:v>
+        <x:v>Docker基线已复现；调用链、决策图已完成；生成验证待凭据</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
         <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json</x:v>
+        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json; research/P03/validation/verify-res-p03-03.json</x:v>
       </x:c>
       <x:c r="N4" s="86" t="str">
-        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json</x:v>
+        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json; research/P03/decision-map.md; research/P03/decision-map.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -44188,7 +44196,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c32036ba880425b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fac471a8d074dee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45604,7 +45612,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R68cdad97034447a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb978d1c8aff94029"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46026,7 +46034,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0756d4fc339453b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9134581e3b75464d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49373,7 +49381,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd94afaef013e43ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf70c2213c4d4154"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R88e3ee0c6e7241af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4c629e0e492244be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R4d276453a73e4471"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R46b4fb96df5c41f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd8f4c25b0bdc4217"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rf4bdb506929f4b14"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0ac66ec748cd4c8e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R12c0d800dca64a73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R29014079d550467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R2a51f3471c7245c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R70690679018e4f03"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2ff0891ea3394c43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rab2e2e7fe51f47b8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R3ed6fac89eca4b76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R5c8872dd87694aa3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R145be019179c45c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Ref8991d9baf74af1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R77e01b6caf7e4d50"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R8f2cc12dd899431d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Re2f7a616f20d4761"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf90335321e4349bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcdad2f53d4b749cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9961cf57b41b49b6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R35077c4f52964888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R846f7b21a6424327"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re87649967b1840af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4823549e931b411c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra8eea6b112e14474"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9eb43349a2d44f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R87c9cee1763a419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rda8f6362fbd14f02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R82eda3b2e07f4f55"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R850ce2a8d5804ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R52560a15c4ee425b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf68773ac979540c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5f9f616b974e4dde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf7264a9d3da74b65"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R51102a5b31bd40dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0b7b960d7be847b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra0a1e9842b3f411b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R75c12ce26e1746a6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R322c85d02b2e4564"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.25</x:v>
+        <x:v>0.2857142857142857</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41c9731c998d4ad3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6545efaac2cc48a7"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1a4956377346fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R968f0d94448a4458"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc38d4fb5b0d472d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5bc133a21474ced"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12766,10 +12766,14 @@
       </x:c>
       <x:c r="M25" s="84" t="str"/>
       <x:c r="N25" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O25" s="84" t="str"/>
-      <x:c r="P25" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O25" s="84" t="str">
+        <x:v>research/P03/template-map.md; research/P03/template-map.json</x:v>
+      </x:c>
+      <x:c r="P25" s="86" t="str">
+        <x:v>静态完成；运行待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="83" t="str">
@@ -25077,7 +25081,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R867d89c1e03c4193"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fd7df54d7c40c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26807,9 +26811,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M40" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M40" s="84" t="str">
+        <x:v>research/P03/template-map.md; research/P03/template-map.json</x:v>
+      </x:c>
       <x:c r="N40" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -26849,9 +26855,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L41" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M41" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M41" s="84" t="str">
+        <x:v>research/P03/validation/verify-res-p03-04.json</x:v>
+      </x:c>
       <x:c r="N41" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43906,7 +43914,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4e94481cdb114716"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca33021d52041fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44091,16 +44099,16 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>Docker基线已复现；调用链、决策图已完成；生成验证待凭据</x:v>
+        <x:v>Docker基线已复现；调用链、决策图、模板结构图已完成；生成验证待认证</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
         <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json; research/P03/validation/verify-res-p03-03.json</x:v>
+        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json; research/P03/validation/verify-res-p03-03.json; research/P03/validation/verify-res-p03-04.json</x:v>
       </x:c>
       <x:c r="N4" s="86" t="str">
-        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json; research/P03/decision-map.md; research/P03/decision-map.json</x:v>
+        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json; research/P03/decision-map.json; research/P03/template-map.md; research/P03/template-map.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -44196,7 +44204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fac471a8d074dee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ebb2e11f254612"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45612,7 +45620,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb978d1c8aff94029"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3f4672f347c4945"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46034,7 +46042,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9134581e3b75464d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330638712013421d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49381,7 +49389,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf70c2213c4d4154"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb88cf04b4f4492c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf90335321e4349bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcdad2f53d4b749cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9961cf57b41b49b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R35077c4f52964888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R846f7b21a6424327"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re87649967b1840af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4823549e931b411c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra8eea6b112e14474"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R9eb43349a2d44f78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R87c9cee1763a419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rda8f6362fbd14f02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R82eda3b2e07f4f55"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R850ce2a8d5804ac9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R52560a15c4ee425b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf68773ac979540c3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R5f9f616b974e4dde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf7264a9d3da74b65"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R51102a5b31bd40dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0b7b960d7be847b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra0a1e9842b3f411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re3d74146920d4c8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rf14aac7f4fd0490f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R15e99593f0624f66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R451328a0eb1a4272"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rea02c38757414266"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4472cfa4a11644ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R54982497a7f74477"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd9ff20f492ec438a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rfb27fc4fe7d54f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rce398879c44740ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb853b733fc0040cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rc3de130689124749"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R463e0f9cf56c41f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd741cddbea9a43f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3d7a16df71e94b02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R93f3767022384b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb6b1d45aa9994310"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4b4e371abd1840c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfc0b003d569e4d0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R3e7d082b9c6f48d7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R322c85d02b2e4564"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re22eed4619004e7a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0.32142857142857145</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6545efaac2cc48a7"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5a26e4782483a"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R968f0d94448a4458"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5039538203dc4c7c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5bc133a21474ced"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd20dd7e149b94170"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12814,10 +12814,14 @@
       </x:c>
       <x:c r="M26" s="84" t="str"/>
       <x:c r="N26" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O26" s="84" t="str"/>
-      <x:c r="P26" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O26" s="84" t="str">
+        <x:v>research/P03/capability-map.md; research/P03/capability-map.json</x:v>
+      </x:c>
+      <x:c r="P26" s="86" t="str">
+        <x:v>静态能力映射完成；运行待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="83" t="str">
@@ -25081,7 +25085,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R29fd7df54d7c40c0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3713ef618ed447bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26899,9 +26903,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L42" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M42" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M42" s="84" t="str">
+        <x:v>research/P03/capability-map.md; research/P03/capability-map.json</x:v>
+      </x:c>
       <x:c r="N42" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -26941,9 +26947,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L43" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M43" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M43" s="84" t="str">
+        <x:v>research/P03/validation/verify-res-p03-05.json</x:v>
+      </x:c>
       <x:c r="N43" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
@@ -43914,7 +43922,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcca33021d52041fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5f52a01646a4875"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44099,16 +44107,16 @@
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
       <x:c r="K4" s="84" t="str">
-        <x:v>Docker基线已复现；调用链、决策图、模板结构图已完成；生成验证待认证</x:v>
+        <x:v>Docker基线已复现；调用链、决策图、模板结构图、能力图已完成；生成验证待认证</x:v>
       </x:c>
       <x:c r="L4" s="84" t="str">
         <x:v>research/P03/README.md；contracts/version-manifest.catalog.json</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json; research/P03/validation/verify-res-p03-03.json; research/P03/validation/verify-res-p03-04.json</x:v>
+        <x:v>research/P03/validation/smoke.json; research/P03/validation/verify-res-p03-02.json; research/P03/validation/verify-res-p03-03.json; research/P03/validation/verify-res-p03-04.json; research/P03/validation/verify-res-p03-05.json</x:v>
       </x:c>
       <x:c r="N4" s="86" t="str">
-        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json; research/P03/decision-map.json; research/P03/template-map.md; research/P03/template-map.json</x:v>
+        <x:v>research/P03/README.md; research/P03/call-graph.md; research/P03/source-index.json; research/P03/decision-map.json; research/P03/template-map.md; research/P03/template-map.json; research/P03/capability-map.md; research/P03/capability-map.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -44204,7 +44212,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43ebb2e11f254612"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra178e2cb3fe043c4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45620,7 +45628,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd3f4672f347c4945"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46643dd734394135"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46042,7 +46050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R330638712013421d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raacadb7afe78412b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49389,7 +49397,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb88cf04b4f4492c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R077cb4b4609f48fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.32142857142857145</x:v>
+        <x:v>0.35714285714285715</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -12859,14 +12859,20 @@
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
       <x:c r="M27" s="84" t="str"/>
-      <x:c r="N27" s="84" t="str">
-        <x:v>进行中</x:v>
-      </x:c>
-      <x:c r="O27" s="84" t="str">
-        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
-      </x:c>
-      <x:c r="P27" s="86" t="str">
-        <x:v>待复现</x:v>
+      <x:c r="N27" s="84" t="inlineStr">
+        <x:is>
+          <x:t>已完成</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="O27" s="84" t="inlineStr">
+        <x:is>
+          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="P27" s="86" t="inlineStr">
+        <x:is>
+          <x:t>官方 HTML 已在 Node 24 复现；Node 18 声明兼容偏差已记录</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -26988,11 +26994,15 @@
       <x:c r="K44" s="84" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="L44" s="84" t="str">
-        <x:v>进行中</x:v>
-      </x:c>
-      <x:c r="M44" s="84" t="str">
-        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
+      <x:c r="L44" s="84" t="inlineStr">
+        <x:is>
+          <x:t>已完成</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M44" s="84" t="inlineStr">
+        <x:is>
+          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；contracts/version-manifest.catalog.json</x:t>
+        </x:is>
       </x:c>
       <x:c r="N44" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
@@ -27032,10 +27042,16 @@
       <x:c r="K45" s="84" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="L45" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M45" s="84" t="str"/>
+      <x:c r="L45" s="84" t="inlineStr">
+        <x:is>
+          <x:t>已完成</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="M45" s="84" t="inlineStr">
+        <x:is>
+          <x:t>research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；research/P04/validation/edge-nested-html-poc.pptx</x:t>
+        </x:is>
+      </x:c>
       <x:c r="N45" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -44150,11 +44166,15 @@
       <x:c r="J5" s="84" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
-      <x:c r="K5" s="84" t="str">
-        <x:v>源码已固定；待复现</x:v>
-      </x:c>
-      <x:c r="L5" s="84" t="str">
-        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
+      <x:c r="K5" s="84" t="inlineStr">
+        <x:is>
+          <x:t>源码已固定；官方最小流程已复现（Node 24）；Node 18 偏差已记录</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L5" s="84" t="inlineStr">
+        <x:is>
+          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
+        </x:is>
       </x:c>
       <x:c r="M5" s="84" t="str"/>
       <x:c r="N5" s="86" t="str"/>

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.35714285714285715</x:v>
+        <x:v>0.42857142857142855</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -12913,11 +12913,21 @@
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
       <x:c r="M28" s="84" t="str"/>
-      <x:c r="N28" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O28" s="84" t="str"/>
-      <x:c r="P28" s="86" t="str"/>
+      <x:c r="N28" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>已完成</t>
+        </is>
+      </x:c>
+      <x:c r="O28" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>research/P04/call-graph.md；research/P04/source-index.json</t>
+        </is>
+      </x:c>
+      <x:c r="P28" s="86" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>通过：固定源码主链路节点均可定位；外部黑盒、页面输出未发现项及边界明确标注；离线正常/边界/失败证据见验证报告。</t>
+        </is>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="83" t="str">
@@ -27090,10 +27100,16 @@
       <x:c r="K46" s="84" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="L46" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M46" s="84" t="str"/>
+      <x:c r="L46" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>已完成</t>
+        </is>
+      </x:c>
+      <x:c r="M46" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>research/P04/call-graph.md；research/P04/source-index.json</t>
+        </is>
+      </x:c>
       <x:c r="N46" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -27132,10 +27148,16 @@
       <x:c r="K47" s="84" t="str">
         <x:v>P0</x:v>
       </x:c>
-      <x:c r="L47" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M47" s="84" t="str"/>
+      <x:c r="L47" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>已完成</t>
+        </is>
+      </x:c>
+      <x:c r="M47" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>research/P04/validation/verify-res-p04-02.json；research/P04/validation/verify-res-p04-02.mjs；research/P04/validation/topic-route-normal.pptx；research/P04/validation/topic-route-fill-fallback.pptx</t>
+        </is>
+      </x:c>
       <x:c r="N47" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -44167,17 +44189,25 @@
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
       <x:c r="K5" s="84" t="inlineStr">
-        <x:is>
-          <x:t>源码已固定；官方最小流程已复现（Node 24）；Node 18 偏差已记录</x:t>
-        </x:is>
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>源码已固定；官方最小流程已复现（Node 24）；Node 18 偏差已记录；P04-02 调用链与离线验证已完成；P04-03/04/05 待后续</t>
+        </is>
       </x:c>
       <x:c r="L5" s="84" t="inlineStr">
         <x:is>
           <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
         </x:is>
       </x:c>
-      <x:c r="M5" s="84" t="str"/>
-      <x:c r="N5" s="86" t="str"/>
+      <x:c r="M5" s="84" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>research/P04/validation/verify-res-p04-01.json；research/P04/validation/verify-res-p04-02.json</t>
+        </is>
+      </x:c>
+      <x:c r="N5" s="86" t="inlineStr">
+        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+          <t>research/P04/call-graph.md；research/P04/source-index.json；research/P04/README.md</t>
+        </is>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="87" t="str">

--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re3d74146920d4c8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rf14aac7f4fd0490f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R15e99593f0624f66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R451328a0eb1a4272"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rea02c38757414266"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R4472cfa4a11644ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R54982497a7f74477"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rd9ff20f492ec438a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rfb27fc4fe7d54f6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rce398879c44740ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb853b733fc0040cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rc3de130689124749"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R463e0f9cf56c41f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rd741cddbea9a43f2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3d7a16df71e94b02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R93f3767022384b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb6b1d45aa9994310"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4b4e371abd1840c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rfc0b003d569e4d0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R3e7d082b9c6f48d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdd624288f3694bef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re12281e97c8f4ee0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6494421d2858488b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc0dadb8bbfe64de7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Re598b40a47c84333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R69688561e5714f37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3428f33ae7414e16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d897cfb9fef4d74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R467287f5bae14db5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1415512e99ae4b3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf946d52f5ebe46ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra84750471c9e411b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R60394ea385d141db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9211699525f941bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R376d4265a4104e0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R445c5e1a7d394832"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R229f27279ad546c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R52898962ead64d5f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcda3362f8d2f43ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R48ae19f074a14792"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re22eed4619004e7a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38ed85fda23940e8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.42857142857142855</x:v>
+        <x:v>0.4642857142857143</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcef5a26e4782483a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6a6c271fdab48a4"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5039538203dc4c7c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16821ac06bd9451e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd20dd7e149b94170"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1663af06ceb482e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12861,17 +12861,17 @@
       <x:c r="M27" s="84" t="str"/>
       <x:c r="N27" s="84" t="inlineStr">
         <x:is>
-          <x:t>已完成</x:t>
+          <x:t xml:space="preserve">已完成</x:t>
         </x:is>
       </x:c>
       <x:c r="O27" s="84" t="inlineStr">
         <x:is>
-          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
+          <x:t xml:space="preserve">research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
         </x:is>
       </x:c>
       <x:c r="P27" s="86" t="inlineStr">
         <x:is>
-          <x:t>官方 HTML 已在 Node 24 复现；Node 18 声明兼容偏差已记录</x:t>
+          <x:t xml:space="preserve">官方 HTML 已在 Node 24 复现；Node 18 声明兼容偏差已记录</x:t>
         </x:is>
       </x:c>
     </x:row>
@@ -12914,19 +12914,19 @@
       </x:c>
       <x:c r="M28" s="84" t="str"/>
       <x:c r="N28" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>已完成</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="O28" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>research/P04/call-graph.md；research/P04/source-index.json</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">research/P04/call-graph.md；research/P04/source-index.json</x:t>
+        </x:is>
       </x:c>
       <x:c r="P28" s="86" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>通过：固定源码主链路节点均可定位；外部黑盒、页面输出未发现项及边界明确标注；离线正常/边界/失败证据见验证报告。</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">通过：固定源码主链路节点均可定位；外部黑盒、页面输出未发现项及边界明确标注；离线正常/边界/失败证据见验证报告。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -12968,10 +12968,14 @@
       </x:c>
       <x:c r="M29" s="84" t="str"/>
       <x:c r="N29" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O29" s="84" t="str"/>
-      <x:c r="P29" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O29" s="84" t="str">
+        <x:v>research/P04/decision-map.md；research/P04/decision-map.json；research/P04/validation/verify-res-p04-03.json</x:v>
+      </x:c>
+      <x:c r="P29" s="86" t="str">
+        <x:v>17节点；DEC-001–040全覆盖(3/27/10)；禁网Docker核对源码与4个PPTX哈希。真实LLM/Vision和产品未验证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -25101,7 +25105,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3713ef618ed447bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re336b607fba442ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27006,12 +27010,12 @@
       </x:c>
       <x:c r="L44" s="84" t="inlineStr">
         <x:is>
-          <x:t>已完成</x:t>
+          <x:t xml:space="preserve">已完成</x:t>
         </x:is>
       </x:c>
       <x:c r="M44" s="84" t="inlineStr">
         <x:is>
-          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；contracts/version-manifest.catalog.json</x:t>
+          <x:t xml:space="preserve">research/P04/README.md；research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；contracts/version-manifest.catalog.json</x:t>
         </x:is>
       </x:c>
       <x:c r="N44" s="86" t="str">
@@ -27054,12 +27058,12 @@
       </x:c>
       <x:c r="L45" s="84" t="inlineStr">
         <x:is>
-          <x:t>已完成</x:t>
+          <x:t xml:space="preserve">已完成</x:t>
         </x:is>
       </x:c>
       <x:c r="M45" s="84" t="inlineStr">
         <x:is>
-          <x:t>research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；research/P04/validation/edge-nested-html-poc.pptx</x:t>
+          <x:t xml:space="preserve">research/P04/validation/verify-res-p04-01.json；research/P04/validation/minimal-html-poc.pptx；research/P04/validation/edge-nested-html-poc.pptx</x:t>
         </x:is>
       </x:c>
       <x:c r="N45" s="86" t="str">
@@ -27101,14 +27105,14 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L46" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>已完成</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="M46" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>research/P04/call-graph.md；research/P04/source-index.json</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">research/P04/call-graph.md；research/P04/source-index.json</x:t>
+        </x:is>
       </x:c>
       <x:c r="N46" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
@@ -27149,14 +27153,14 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L47" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>已完成</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">已完成</x:t>
+        </x:is>
       </x:c>
       <x:c r="M47" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>research/P04/validation/verify-res-p04-02.json；research/P04/validation/verify-res-p04-02.mjs；research/P04/validation/topic-route-normal.pptx；research/P04/validation/topic-route-fill-fallback.pptx</t>
-        </is>
+        <x:is>
+          <x:t xml:space="preserve">research/P04/validation/verify-res-p04-02.json；research/P04/validation/verify-res-p04-02.mjs；research/P04/validation/topic-route-normal.pptx；research/P04/validation/topic-route-fill-fallback.pptx</x:t>
+        </x:is>
       </x:c>
       <x:c r="N47" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
@@ -27197,9 +27201,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L48" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M48" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M48" s="84" t="str">
+        <x:v>research/P04/decision-map.md；research/P04/decision-map.json</x:v>
+      </x:c>
       <x:c r="N48" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -27239,9 +27245,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L49" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M49" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M49" s="84" t="str">
+        <x:v>research/P04/validation/verify-res-p04-03.mjs；research/P04/validation/verify-res-p04-03.json；复核 P04-01/02 的正常、边界、失败报告及 PPTX 哈希</x:v>
+      </x:c>
       <x:c r="N49" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -43960,7 +43968,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5f52a01646a4875"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc910cbd37306410f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44188,25 +44196,17 @@
       <x:c r="J5" s="84" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
-      <x:c r="K5" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>源码已固定；官方最小流程已复现（Node 24）；Node 18 偏差已记录；P04-02 调用链与离线验证已完成；P04-03/04/05 待后续</t>
-        </is>
-      </x:c>
-      <x:c r="L5" s="84" t="inlineStr">
-        <x:is>
-          <x:t>research/P04/README.md；research/P04/validation/verify-res-p04-01.json；contracts/version-manifest.catalog.json</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="M5" s="84" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>research/P04/validation/verify-res-p04-01.json；research/P04/validation/verify-res-p04-02.json</t>
-        </is>
-      </x:c>
-      <x:c r="N5" s="86" t="inlineStr">
-        <is xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-          <t>research/P04/call-graph.md；research/P04/source-index.json；research/P04/README.md</t>
-        </is>
+      <x:c r="K5" s="84" t="str">
+        <x:v>P04-01–03 已完成；P04-04/05 未开始；P04-03 为17节点/DEC-001–040映射。</x:v>
+      </x:c>
+      <x:c r="L5" s="84" t="str">
+        <x:v>research/P04/README.md；contracts/version-manifest.catalog.json</x:v>
+      </x:c>
+      <x:c r="M5" s="84" t="str">
+        <x:v>research/P04/validation/verify-res-p04-01.json；research/P04/validation/verify-res-p04-02.json；research/P04/validation/verify-res-p04-03.json</x:v>
+      </x:c>
+      <x:c r="N5" s="86" t="str">
+        <x:v>research/P04/README.md；research/P04/call-graph.md；research/P04/source-index.json；research/P04/decision-map.md；research/P04/decision-map.json；research/P04/validation/verify-res-p04-03.json</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -44262,7 +44262,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra178e2cb3fe043c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289e4fbb181b4274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45678,7 +45678,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46643dd734394135"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re258aa08dcf14a77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46100,7 +46100,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raacadb7afe78412b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra755680c0e2441f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49447,7 +49447,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R077cb4b4609f48fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81614aa6adc40b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rdd624288f3694bef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Re12281e97c8f4ee0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R6494421d2858488b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rc0dadb8bbfe64de7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Re598b40a47c84333"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R69688561e5714f37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3428f33ae7414e16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d897cfb9fef4d74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R467287f5bae14db5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1415512e99ae4b3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf946d52f5ebe46ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra84750471c9e411b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R60394ea385d141db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9211699525f941bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R376d4265a4104e0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R445c5e1a7d394832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R229f27279ad546c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R52898962ead64d5f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcda3362f8d2f43ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R48ae19f074a14792"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R206403acc796447d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2e1c6edf341a4694"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7450623ad2d64b8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rae0a7017bba64736"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbdec20c3c6784e08"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R092214987b704f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3f50d55a9e9d45b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R35f7d5330d414148"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rdccc1f89154b4a12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rcb6ca46aa1d046ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R881a2cd954524f83"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R4c88a0e100134345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0a3414596459480b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7f4e9e9c4b6a4331"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3012fda9883e4896"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3cc0ccb2700c45f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8e475321a5b24530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6a7d3493d188460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5a16dd8946934fc3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2dd95e70cbfc455c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R38ed85fda23940e8"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re48dfa22132e42b5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.4642857142857143</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6a6c271fdab48a4"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84288c74a6534ddc"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R16821ac06bd9451e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89b4a97cb3264f71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1663af06ceb482e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5935998955734223"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12977,7 +12977,7 @@
         <x:v>17节点；DEC-001–040全覆盖(3/27/10)；禁网Docker核对源码与4个PPTX哈希。真实LLM/Vision和产品未验证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="30">
+    <x:row r="30" ht="120" customHeight="1">
       <x:c r="A30" s="83" t="str">
         <x:v>RES-P04-04</x:v>
       </x:c>
@@ -13016,12 +13016,16 @@
       </x:c>
       <x:c r="M30" s="84" t="str"/>
       <x:c r="N30" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O30" s="84" t="str"/>
-      <x:c r="P30" s="86" t="str"/>
-    </x:row>
-    <x:row r="31">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O30" s="84" t="str">
+        <x:v>research/P04/template-map.json；research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
+      <x:c r="P30" s="86" t="str">
+        <x:v>5模板/8版式，运行探针通过。仅候选研究。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="120" customHeight="1">
       <x:c r="A31" s="83" t="str">
         <x:v>RES-P04-05</x:v>
       </x:c>
@@ -13060,10 +13064,14 @@
       </x:c>
       <x:c r="M31" s="84" t="str"/>
       <x:c r="N31" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O31" s="84" t="str"/>
-      <x:c r="P31" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O31" s="84" t="str">
+        <x:v>research/P04/capability-map.json；research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
+      <x:c r="P31" s="86" t="str">
+        <x:v>30对象边界；图表/演讲稿未消费。仅候选研究。</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="83" t="str">
@@ -25105,7 +25113,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re336b607fba442ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1e06346912435c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27289,9 +27297,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L50" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M50" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M50" s="84" t="str">
+        <x:v>research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
       <x:c r="N50" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -27331,9 +27341,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L51" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M51" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M51" s="84" t="str">
+        <x:v>research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
       <x:c r="N51" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -27373,9 +27385,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L52" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M52" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M52" s="84" t="str">
+        <x:v>research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
       <x:c r="N52" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -27415,9 +27429,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L53" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M53" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M53" s="84" t="str">
+        <x:v>research/P04/template-capability-map.md；research/P04/validation/verify-res-p04-04-05.json</x:v>
+      </x:c>
       <x:c r="N53" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
@@ -43968,7 +43984,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc910cbd37306410f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8866cb5477c74b09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44262,7 +44278,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289e4fbb181b4274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14160391ca2d4b74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45678,7 +45694,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re258aa08dcf14a77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25078fbf8cb7442a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46100,7 +46116,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra755680c0e2441f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65858377aa644a09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49447,7 +49463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra81614aa6adc40b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49aa27620b42492f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R206403acc796447d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2e1c6edf341a4694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R7450623ad2d64b8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rae0a7017bba64736"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rbdec20c3c6784e08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R092214987b704f5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3f50d55a9e9d45b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R35f7d5330d414148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rdccc1f89154b4a12"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rcb6ca46aa1d046ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R881a2cd954524f83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R4c88a0e100134345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R0a3414596459480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R7f4e9e9c4b6a4331"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3012fda9883e4896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R3cc0ccb2700c45f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8e475321a5b24530"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R6a7d3493d188460d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R5a16dd8946934fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R2dd95e70cbfc455c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1558819408ca43a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R89d23a0779644e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9424acb1a0214ffc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R72e6e54458944413"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3eb6d3a25be64b38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R934f800981bc420a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7a064b8197e04515"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra658070c161a4424"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R327d6983ec704a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd16cb39f0fab442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re1fafb4181934ba8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R3e9ff8f747cc4c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9636d00bbacf4e0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc360210dcaf64b9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re511249d64bb4493"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R350d0cba8192450e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf2aa4359368c47d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0eaf2706460c478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rac0333d7be6c49c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R35e8c170b0e749eb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re48dfa22132e42b5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf022aa73c39f4d90"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.5</x:v>
+        <x:v>0.5357142857142857</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R84288c74a6534ddc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4555d732e24797"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89b4a97cb3264f71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dd005bae42b4e71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5935998955734223"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf97ddef10684a62"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12315,7 +12315,7 @@
         <x:v>建立ProjectTemplateMap，覆盖7组Layout、86个SVG、53种页面类型、320个slot和287个Design Spec token；字符数上限及token-slot映射缺失如实标注。</x:v>
       </x:c>
     </x:row>
-    <x:row r="16">
+    <x:row r="16" ht="120" customHeight="1">
       <x:c r="A16" s="83" t="str">
         <x:v>RES-P01-05</x:v>
       </x:c>
@@ -12354,13 +12354,13 @@
       </x:c>
       <x:c r="M16" s="84" t="str"/>
       <x:c r="N16" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="O16" s="84" t="str">
         <x:v>research/P01/project_capability_map.json；research/P01/validation/verify-res-p01-05.json</x:v>
       </x:c>
       <x:c r="P16" s="86" t="str">
-        <x:v>已登记30项PPT对象能力及QA/Revision/既有PPT编辑边界；复用P01-01正常证据；容器内边界/失败验证待执行。</x:v>
+        <x:v>30对象边界；选定26项测试通过。仅候选研究。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -25113,7 +25113,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b1e06346912435c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19f7f5abcf14390"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26071,7 +26071,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L22" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M22" s="84" t="str">
         <x:v>research/P01/project_capability_map.json</x:v>
@@ -26115,7 +26115,7 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L23" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M23" s="84" t="str">
         <x:v>research/P01/validation/verify-res-p01-05.json</x:v>
@@ -43984,7 +43984,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8866cb5477c74b09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a6650960984166"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44278,7 +44278,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14160391ca2d4b74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R399a3424f7e446cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45694,7 +45694,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25078fbf8cb7442a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea4c5572d1ce4491"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46116,7 +46116,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65858377aa644a09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88f50c08cc7b4b8e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49463,7 +49463,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49aa27620b42492f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf775528770034276"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R1558819408ca43a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R89d23a0779644e9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R9424acb1a0214ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R72e6e54458944413"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R3eb6d3a25be64b38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R934f800981bc420a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7a064b8197e04515"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Ra658070c161a4424"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R327d6983ec704a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rd16cb39f0fab442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re1fafb4181934ba8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R3e9ff8f747cc4c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R9636d00bbacf4e0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc360210dcaf64b9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re511249d64bb4493"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R350d0cba8192450e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rf2aa4359368c47d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R0eaf2706460c478c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rac0333d7be6c49c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R35e8c170b0e749eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf4ced04dea794131"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc6f7b4bb068e4f1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea9047af6ef6410b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R028d81f6a2724f62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rca57ae3c84204566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rae04771f66e84b54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd398a5d1ec894523"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1852e5b854844065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R44d39e035c7a4a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf4bebe469b264e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R1122b75ab6ae4390"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5ded36ef84a942d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd281d6c5be564a89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9562e010e918473f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R1cfa73d6c0294434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0431d157b6654bf0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R61d79801a9b54de2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4bb341bec5bb4c8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2b2a16cf0bd7453e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R4a1e73cf7ac84fd6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf022aa73c39f4d90"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3625da5f613644e6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.5357142857142857</x:v>
+        <x:v>0.6071428571428571</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4555d732e24797"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3551ab91ed24bcc"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8dd005bae42b4e71"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35797d1a3b7d4c94"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf97ddef10684a62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3210d8cbf051426d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13073,7 +13073,7 @@
         <x:v>30对象边界；图表/演讲稿未消费。仅候选研究。</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
+    <x:row r="32" ht="120" customHeight="1">
       <x:c r="A32" s="83" t="str">
         <x:v>RES-P05-01</x:v>
       </x:c>
@@ -13110,16 +13110,16 @@
       </x:c>
       <x:c r="M32" s="84" t="str"/>
       <x:c r="N32" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="O32" s="84" t="str">
-        <x:v>research/P05/README.md；contracts/version-manifest.catalog.json；官方示例受Docker Engine阻塞</x:v>
+        <x:v>research/P05/README.md；research/P05/validation/verify-res-p05-01-02.json</x:v>
       </x:c>
       <x:c r="P32" s="86" t="str">
-        <x:v>待复现</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
+        <x:v>8页mock生成；严格QA未通过。研究已复现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="120" customHeight="1">
       <x:c r="A33" s="83" t="str">
         <x:v>RES-P05-02</x:v>
       </x:c>
@@ -13158,10 +13158,14 @@
       </x:c>
       <x:c r="M33" s="84" t="str"/>
       <x:c r="N33" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O33" s="84" t="str"/>
-      <x:c r="P33" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O33" s="84" t="str">
+        <x:v>research/P05/source_index.json；research/P05/call_graph.md；research/P05/validation/verify-res-p05-01-02.json</x:v>
+      </x:c>
+      <x:c r="P33" s="86" t="str">
+        <x:v>41节点/40边；分支与外部边界可追溯。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="83" t="str">
@@ -25113,7 +25117,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19f7f5abcf14390"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61805767bf2348fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27471,10 +27475,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L54" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M54" s="84" t="str">
-        <x:v>research/P05/README.md；contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P05/README.md；research/P05/validation/verify-res-p05-01-02.json</x:v>
       </x:c>
       <x:c r="N54" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
@@ -27515,9 +27519,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L55" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M55" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M55" s="84" t="str">
+        <x:v>research/P05/validation/verify-res-p05-01-02.json</x:v>
+      </x:c>
       <x:c r="N55" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27557,9 +27563,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L56" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M56" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M56" s="84" t="str">
+        <x:v>research/P05/call_graph.md；research/P05/source_index.json</x:v>
+      </x:c>
       <x:c r="N56" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27599,9 +27607,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L57" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M57" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M57" s="84" t="str">
+        <x:v>research/P05/validation/verify-res-p05-01-02.json</x:v>
+      </x:c>
       <x:c r="N57" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -43984,7 +43994,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23a6650960984166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f18bbe833bd480b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44278,7 +44288,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R399a3424f7e446cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f095f29bf3455d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45694,7 +45704,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea4c5572d1ce4491"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2f43a2138fa43ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46116,7 +46126,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R88f50c08cc7b4b8e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae26d16055184b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49463,7 +49473,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf775528770034276"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5f7f8263b845b8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf4ced04dea794131"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc6f7b4bb068e4f1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rea9047af6ef6410b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R028d81f6a2724f62"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rca57ae3c84204566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rae04771f66e84b54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rd398a5d1ec894523"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1852e5b854844065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R44d39e035c7a4a87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rf4bebe469b264e18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R1122b75ab6ae4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R5ded36ef84a942d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rd281d6c5be564a89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9562e010e918473f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R1cfa73d6c0294434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R0431d157b6654bf0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R61d79801a9b54de2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4bb341bec5bb4c8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2b2a16cf0bd7453e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R4a1e73cf7ac84fd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rae94808c4b9b447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R6d7d2aadac364731"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf3917fc8cf9346b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R3421c892ec554219"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc1270c4b910f4d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re190a0b41e504fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R61129d1805204c9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R9438913fddc94c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rdb402c6f17ad4bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab41c8a7ddea4525"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re89e0c830d9848d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Reabfa9946c3f46ce"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rfad5af6865c04706"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re1778d79f1b2405c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc53d0d516fd94540"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Re625466c75ea4a1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R7244b824a11247b2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R395d5631acb845be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2f079a01400145eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rddbb7a3c5338458b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3625da5f613644e6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c31395566f94309"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.6071428571428571</x:v>
+        <x:v>0.7142857142857143</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3551ab91ed24bcc"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043c92d542164f50"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35797d1a3b7d4c94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a61c37095734c1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3210d8cbf051426d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4b33d296f6a442d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13167,7 +13167,7 @@
         <x:v>41节点/40边；分支与外部边界可追溯。</x:v>
       </x:c>
     </x:row>
-    <x:row r="34">
+    <x:row r="34" ht="120" customHeight="1">
       <x:c r="A34" s="83" t="str">
         <x:v>RES-P05-03</x:v>
       </x:c>
@@ -13206,12 +13206,16 @@
       </x:c>
       <x:c r="M34" s="84" t="str"/>
       <x:c r="N34" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O34" s="84" t="str"/>
-      <x:c r="P34" s="86" t="str"/>
-    </x:row>
-    <x:row r="35">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O34" s="84" t="str">
+        <x:v>research/P05/ProjectDecisionMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
+      <x:c r="P34" s="86" t="str">
+        <x:v>14决策组/40DEC对照；模型黑盒与缺失算法保留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="120" customHeight="1">
       <x:c r="A35" s="83" t="str">
         <x:v>RES-P05-04</x:v>
       </x:c>
@@ -13250,12 +13254,16 @@
       </x:c>
       <x:c r="M35" s="84" t="str"/>
       <x:c r="N35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O35" s="84" t="str"/>
-      <x:c r="P35" s="86" t="str"/>
-    </x:row>
-    <x:row r="36">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O35" s="84" t="str">
+        <x:v>research/P05/ProjectTemplateMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
+      <x:c r="P35" s="86" t="str">
+        <x:v>17JS布局/6主题；模板主题漏读，旧页删除报错。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="120" customHeight="1">
       <x:c r="A36" s="83" t="str">
         <x:v>RES-P05-05</x:v>
       </x:c>
@@ -13294,10 +13302,14 @@
       </x:c>
       <x:c r="M36" s="84" t="str"/>
       <x:c r="N36" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O36" s="84" t="str"/>
-      <x:c r="P36" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O36" s="84" t="str">
+        <x:v>research/P05/ProjectCapabilityMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
+      <x:c r="P36" s="86" t="str">
+        <x:v>30对象边界；原生对象实测，KPI丢失/补零留证。</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="83" t="str">
@@ -25117,7 +25129,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61805767bf2348fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d05401926314bd6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27651,9 +27663,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L58" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M58" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M58" s="84" t="str">
+        <x:v>research/P05/ProjectDecisionMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N58" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27693,9 +27707,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L59" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M59" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M59" s="84" t="str">
+        <x:v>research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N59" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27735,9 +27751,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L60" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M60" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M60" s="84" t="str">
+        <x:v>research/P05/ProjectTemplateMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N60" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27777,9 +27795,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L61" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M61" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M61" s="84" t="str">
+        <x:v>research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N61" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27819,9 +27839,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L62" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M62" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M62" s="84" t="str">
+        <x:v>research/P05/ProjectCapabilityMap.json；research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N62" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -27861,9 +27883,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L63" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M63" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M63" s="84" t="str">
+        <x:v>research/P05/validation/verify-res-p05-03-05.json</x:v>
+      </x:c>
       <x:c r="N63" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
@@ -43994,7 +44018,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f18bbe833bd480b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced1a14ba9484868"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44288,7 +44312,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f095f29bf3455d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752a1db005234871"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45704,7 +45728,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2f43a2138fa43ae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ec0eb1dc0454962"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46126,7 +46150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae26d16055184b80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64dd96fc6de4260"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49473,7 +49497,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f5f7f8263b845b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d99d0cb46d246a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rae94808c4b9b447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R6d7d2aadac364731"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rf3917fc8cf9346b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R3421c892ec554219"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rc1270c4b910f4d18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re190a0b41e504fee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R61129d1805204c9b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R9438913fddc94c8f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rdb402c6f17ad4bcd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rab41c8a7ddea4525"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re89e0c830d9848d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Reabfa9946c3f46ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rfad5af6865c04706"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Re1778d79f1b2405c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rc53d0d516fd94540"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Re625466c75ea4a1a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R7244b824a11247b2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R395d5631acb845be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R2f079a01400145eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rddbb7a3c5338458b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R68c561fdb7c14247"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R325d0d71bc1d4886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R3e0a7100e1204589"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd7f1cce00cd84c1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rf23ae0c930934593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3aedaa34179c492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8e87ec7cd14540f0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rf23c646c472a44a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Raf1c4c0533114e22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdb2fe4005ffb47e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc4abc27026fb452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7413ebb0cd6b47f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R475d4564135c4cd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9f7d2423ce1048e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Reac5694638ad49a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R600d3fe18a4b42ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R602ec21ea0814764"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra1b7875e71af4a05"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc5cd13e07191407d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8627dd98da0441e5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3c31395566f94309"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd10443791c7476d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.7142857142857143</x:v>
+        <x:v>0.75</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043c92d542164f50"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c6917005fc3449f"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a61c37095734c1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e467948bfd84eb5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4b33d296f6a442d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2da9c0706f24a76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12363,7 +12363,7 @@
         <x:v>30对象边界；选定26项测试通过。仅候选研究。</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="120" customHeight="1">
       <x:c r="A17" s="83" t="str">
         <x:v>RES-P02-01</x:v>
       </x:c>
@@ -12400,13 +12400,13 @@
       </x:c>
       <x:c r="M17" s="84" t="str"/>
       <x:c r="N17" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="O17" s="84" t="str">
-        <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P02/README.md；research/P02/validation/verify-official-six.json</x:v>
       </x:c>
       <x:c r="P17" s="86" t="str">
-        <x:v>待复现</x:v>
+        <x:v>真模型6页；主机审查complete=true，外部JSON失败留证。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -25129,7 +25129,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d05401926314bd6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb046d5b02e114675"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26173,10 +26173,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L24" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M24" s="84" t="str">
-        <x:v>research/P02/README.md；contracts/version-manifest.catalog.json</x:v>
+        <x:v>research/P02/README.md；research/P02/validation/verify-official-six.json</x:v>
       </x:c>
       <x:c r="N24" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
@@ -26217,10 +26217,10 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L25" s="84" t="str">
-        <x:v>进行中</x:v>
+        <x:v>已完成</x:v>
       </x:c>
       <x:c r="M25" s="84" t="str">
-        <x:v>research/P02/validation/verify-res-p02-01.json</x:v>
+        <x:v>research/P02/validation/verify-official-six.json</x:v>
       </x:c>
       <x:c r="N25" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
@@ -44018,7 +44018,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rced1a14ba9484868"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R443ff7a66f764c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44312,7 +44312,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R752a1db005234871"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccaee2ce69ed45e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45728,7 +45728,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7ec0eb1dc0454962"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda609e3dac864932"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46150,7 +46150,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd64dd96fc6de4260"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6caa0e6e80d947ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49497,7 +49497,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d99d0cb46d246a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66b94ee836e64f33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R68c561fdb7c14247"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R325d0d71bc1d4886"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R3e0a7100e1204589"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Rd7f1cce00cd84c1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rf23ae0c930934593"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3aedaa34179c492a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8e87ec7cd14540f0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rf23c646c472a44a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Raf1c4c0533114e22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdb2fe4005ffb47e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rc4abc27026fb452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R7413ebb0cd6b47f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R475d4564135c4cd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9f7d2423ce1048e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Reac5694638ad49a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R600d3fe18a4b42ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R602ec21ea0814764"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra1b7875e71af4a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc5cd13e07191407d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8627dd98da0441e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rfb0a916436eb4e4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcb8d0c220a334444"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R90effe63b3204975"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R74d977f7dc65439c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R09170e5405ae4f91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R44ae95c1d4714bc4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R33ba697b19a7458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R0c92472c112e4a53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf5fdbba5ec4146ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R09904bcc8b8f4959"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re873fec7ed7347ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rad068c1c0f284907"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdb3e53471743429c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R27f9544941e647e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2510eb5df73c46ab"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb32e54dc6fd24497"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2b5b433b6f1b43b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rf75ec0ca7ba9403c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc57bb6c9cf62467f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R97293071462c4674"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcd10443791c7476d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc6ff10654df8413c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>21</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.75</x:v>
+        <x:v>0.8928571428571429</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c6917005fc3449f"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93d525ab91bd43d2"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e467948bfd84eb5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R740ad60b9a864a63"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2da9c0706f24a76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf082c30a34f743da"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12409,7 +12409,7 @@
         <x:v>真模型6页；主机审查complete=true，外部JSON失败留证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="18">
+    <x:row r="18" ht="120" customHeight="1">
       <x:c r="A18" s="83" t="str">
         <x:v>RES-P02-02</x:v>
       </x:c>
@@ -12448,12 +12448,16 @@
       </x:c>
       <x:c r="M18" s="84" t="str"/>
       <x:c r="N18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O18" s="84" t="str"/>
-      <x:c r="P18" s="86" t="str"/>
-    </x:row>
-    <x:row r="19">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O18" s="84" t="str">
+        <x:v>research/P02/call-graph.json；research/P02/source-index.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
+      <x:c r="P18" s="86" t="str">
+        <x:v>主机规划黑盒；main/1.1.37分开索引。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="120" customHeight="1">
       <x:c r="A19" s="83" t="str">
         <x:v>RES-P02-03</x:v>
       </x:c>
@@ -12492,12 +12496,16 @@
       </x:c>
       <x:c r="M19" s="84" t="str"/>
       <x:c r="N19" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O19" s="84" t="str"/>
-      <x:c r="P19" s="86" t="str"/>
-    </x:row>
-    <x:row r="20">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O19" s="84" t="str">
+        <x:v>research/P02/decision-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
+      <x:c r="P19" s="86" t="str">
+        <x:v>40个DEC完整映射；不提升为产品决策实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="120" customHeight="1">
       <x:c r="A20" s="83" t="str">
         <x:v>RES-P02-04</x:v>
       </x:c>
@@ -12536,12 +12544,16 @@
       </x:c>
       <x:c r="M20" s="84" t="str"/>
       <x:c r="N20" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O20" s="84" t="str"/>
-      <x:c r="P20" s="86" t="str"/>
-    </x:row>
-    <x:row r="21">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O20" s="84" t="str">
+        <x:v>research/P02/template-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
+      <x:c r="P20" s="86" t="str">
+        <x:v>单模板/三画布/DOM-IR；容量与占位边界。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="120" customHeight="1">
       <x:c r="A21" s="83" t="str">
         <x:v>RES-P02-05</x:v>
       </x:c>
@@ -12580,10 +12592,14 @@
       </x:c>
       <x:c r="M21" s="84" t="str"/>
       <x:c r="N21" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O21" s="84" t="str"/>
-      <x:c r="P21" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O21" s="84" t="str">
+        <x:v>research/P02/capability-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
+      <x:c r="P21" s="86" t="str">
+        <x:v>30个对象及QA/修订边界；SVG实测失败保留。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="83" t="str">
@@ -25129,7 +25145,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb046d5b02e114675"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14842c0d0b5e4ef8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26261,9 +26277,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L26" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M26" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M26" s="84" t="str">
+        <x:v>research/P02/call-graph.json；research/P02/source-index.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
       <x:c r="N26" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26303,9 +26321,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L27" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M27" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M27" s="84" t="str">
+        <x:v>research/P02/validation/verify-maps.json；research/P02/validation/maps-probes.json</x:v>
+      </x:c>
       <x:c r="N27" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26345,9 +26365,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L28" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M28" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M28" s="84" t="str">
+        <x:v>research/P02/decision-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
       <x:c r="N28" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26387,9 +26409,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L29" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M29" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M29" s="84" t="str">
+        <x:v>research/P02/validation/verify-maps.json；research/P02/validation/maps-probes.json</x:v>
+      </x:c>
       <x:c r="N29" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26429,9 +26453,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L30" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M30" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M30" s="84" t="str">
+        <x:v>research/P02/template-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
       <x:c r="N30" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26471,9 +26497,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L31" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M31" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M31" s="84" t="str">
+        <x:v>research/P02/validation/verify-maps.json；research/P02/validation/maps-probes.json</x:v>
+      </x:c>
       <x:c r="N31" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26513,9 +26541,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L32" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M32" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M32" s="84" t="str">
+        <x:v>research/P02/capability-map.json；research/P02/validation/verify-maps.json</x:v>
+      </x:c>
       <x:c r="N32" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -26555,9 +26585,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L33" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M33" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M33" s="84" t="str">
+        <x:v>research/P02/validation/verify-maps.json；research/P02/validation/maps-probes.json</x:v>
+      </x:c>
       <x:c r="N33" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
@@ -44018,7 +44050,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R443ff7a66f764c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re74f25fdfc7f46e6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44312,7 +44344,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccaee2ce69ed45e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41e0b2a81e3941a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45728,7 +45760,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda609e3dac864932"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d965353d9184656"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46150,7 +46182,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6caa0e6e80d947ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R251526fee482408e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49497,7 +49529,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66b94ee836e64f33"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ab5526f849949ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rfb0a916436eb4e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rcb8d0c220a334444"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R90effe63b3204975"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R74d977f7dc65439c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R09170e5405ae4f91"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R44ae95c1d4714bc4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R33ba697b19a7458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R0c92472c112e4a53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf5fdbba5ec4146ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R09904bcc8b8f4959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re873fec7ed7347ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rad068c1c0f284907"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdb3e53471743429c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R27f9544941e647e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R2510eb5df73c46ab"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rb32e54dc6fd24497"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2b5b433b6f1b43b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rf75ec0ca7ba9403c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc57bb6c9cf62467f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R97293071462c4674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc568ee76d90f416d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc3b562e2adf04e5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb4df383442af414d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R408f304dc6d7402c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9e616e98fa5a41bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re2cf61d8cf0e4e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc4f4f67d04674e35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R95fea202852e496c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R92c0db4d103b4b7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbdd861b89af34941"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Red5da874076f4dac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8b26d1ffe8a45c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R1688881812e14f3f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R41d9ff3bd8804c07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3ced3bd04cc14b70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R69bf95a2ba914c7c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8cec275bd5b141cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfb3754056f064065"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R917aee43da224650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8a98bac91f744356"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc6ff10654df8413c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6bf32892a7a4764"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.8928571428571429</x:v>
+        <x:v>0.9285714285714286</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93d525ab91bd43d2"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R650f3471f2e54104"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R740ad60b9a864a63"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc4d9d07d9444c34"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf082c30a34f743da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1b18d8880804ff3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13327,7 +13327,7 @@
         <x:v>30对象边界；原生对象实测，KPI丢失/补零留证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="37">
+    <x:row r="37" ht="120" customHeight="1">
       <x:c r="A37" s="83" t="str">
         <x:v>RES-031</x:v>
       </x:c>
@@ -13366,10 +13366,14 @@
       </x:c>
       <x:c r="M37" s="84" t="str"/>
       <x:c r="N37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O37" s="84" t="str"/>
-      <x:c r="P37" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O37" s="84" t="str">
+        <x:v>research/cross-project/CrossProjectMatrix.json；research/cross-project/validation.json</x:v>
+      </x:c>
+      <x:c r="P37" s="86" t="str">
+        <x:v>15维度×5项目，来源/运行/黑盒分列；P03 VERIFY仍进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="83" t="str">
@@ -25145,7 +25149,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R14842c0d0b5e4ef8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4633377c0ce14db1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27959,9 +27963,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L64" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M64" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M64" s="84" t="str">
+        <x:v>research/cross-project/CrossProjectMatrix.json；research/cross-project/source-catalog.json</x:v>
+      </x:c>
       <x:c r="N64" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -28001,9 +28007,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L65" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M65" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M65" s="84" t="str">
+        <x:v>research/cross-project/validation.json</x:v>
+      </x:c>
       <x:c r="N65" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44050,7 +44058,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re74f25fdfc7f46e6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb019291cd76741b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44344,7 +44352,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41e0b2a81e3941a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1817a0cd24144059"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45760,7 +45768,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5d965353d9184656"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae6e0ce557f5425d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46182,7 +46190,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R251526fee482408e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R491d1cf8b32249db"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49529,7 +49537,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ab5526f849949ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R374a08ae91934091"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc568ee76d90f416d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rc3b562e2adf04e5e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rb4df383442af414d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R408f304dc6d7402c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9e616e98fa5a41bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re2cf61d8cf0e4e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Rc4f4f67d04674e35"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R95fea202852e496c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R92c0db4d103b4b7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbdd861b89af34941"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Red5da874076f4dac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf8b26d1ffe8a45c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R1688881812e14f3f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R41d9ff3bd8804c07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R3ced3bd04cc14b70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R69bf95a2ba914c7c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8cec275bd5b141cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfb3754056f064065"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R917aee43da224650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R8a98bac91f744356"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb15ba72248664330"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R274b568d53bf44dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R87ecf82ee8944c63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4379638adaaa4f42"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7e40883f141d4ef3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfb53ed4d979475d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R31f854d4a2ce49d9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rde7d0e86fbf248ee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra735bf69ea214b4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdbf4ad65cb354c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R4c82a658beec408d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re3576397c7db45b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdae5139ffcba44db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ref3579d36ac74092"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re43ac43d25534a4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R94e74fd90c1e4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb5e3b6ace1494dda"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4445af68ed2b43ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R57a27788e26c4948"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1a4f9129cc3e46bd"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb6bf32892a7a4764"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d131d1611d842f6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1363,11 +1363,11 @@
       </x:c>
       <x:c r="E6" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A6,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F6" s="85" t="n">
         <x:f>IF(B6=0,0,E6/B6)</x:f>
-        <x:v>0.9285714285714286</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R650f3471f2e54104"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf01bda10359a49c9"/>
 </x:worksheet>
 </file>
 
@@ -10124,7 +10124,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfc4d9d07d9444c34"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd30b6c886a74741"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11313,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf1b18d8880804ff3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f963841ca2c4fba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13375,7 +13375,7 @@
         <x:v>15维度×5项目，来源/运行/黑盒分列；P03 VERIFY仍进行中。</x:v>
       </x:c>
     </x:row>
-    <x:row r="38">
+    <x:row r="38" ht="180" customHeight="1">
       <x:c r="A38" s="83" t="str">
         <x:v>RES-032</x:v>
       </x:c>
@@ -13414,12 +13414,16 @@
       </x:c>
       <x:c r="M38" s="84" t="str"/>
       <x:c r="N38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O38" s="84" t="str"/>
-      <x:c r="P38" s="86" t="str"/>
-    </x:row>
-    <x:row r="39">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O38" s="84" t="str">
+        <x:v>research/reuse/ReuseDecisionRegistry.json；research/reuse/source-manifest.json；research/reuse/validation.json</x:v>
+      </x:c>
+      <x:c r="P38" s="86" t="str">
+        <x:v>18项模块分四类；2份MIT文件限定资格，未接入产品；P05许可冲突保留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="180" customHeight="1">
       <x:c r="A39" s="83" t="str">
         <x:v>RES-033</x:v>
       </x:c>
@@ -13458,10 +13462,14 @@
       </x:c>
       <x:c r="M39" s="84" t="str"/>
       <x:c r="N39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O39" s="84" t="str"/>
-      <x:c r="P39" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O39" s="84" t="str">
+        <x:v>research/reuse/ResearchFixtureIndex.json；research/reuse/source-manifest.json；research/reuse/validation.json</x:v>
+      </x:c>
+      <x:c r="P39" s="86" t="str">
+        <x:v>35项资产覆盖五项目；P03无生成PPTX、P04无研究渲染截图，未执行项显式记录。</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -25149,7 +25157,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4633377c0ce14db1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1c3dbaa35c48ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28051,9 +28059,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L66" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M66" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M66" s="84" t="str">
+        <x:v>research/reuse/ReuseDecisionRegistry.json；research/reuse/validation.json</x:v>
+      </x:c>
       <x:c r="N66" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -28093,9 +28103,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L67" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M67" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M67" s="84" t="str">
+        <x:v>research/reuse/ResearchFixtureIndex.json；research/reuse/validation.json</x:v>
+      </x:c>
       <x:c r="N67" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44058,7 +44070,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb019291cd76741b5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea8572c0f58a4f76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44352,7 +44364,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1817a0cd24144059"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d3682fae34a4014"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45768,7 +45780,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae6e0ce557f5425d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2206d8cdd6ba481c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46190,7 +46202,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R491d1cf8b32249db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe4e20bf1364a06"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49537,7 +49549,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R374a08ae91934091"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f612eea251143df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb15ba72248664330"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R274b568d53bf44dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R87ecf82ee8944c63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R4379638adaaa4f42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R7e40883f141d4ef3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rbfb53ed4d979475d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R31f854d4a2ce49d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rde7d0e86fbf248ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ra735bf69ea214b4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdbf4ad65cb354c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R4c82a658beec408d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Re3576397c7db45b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Rdae5139ffcba44db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ref3579d36ac74092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Re43ac43d25534a4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R94e74fd90c1e4c3a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb5e3b6ace1494dda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4445af68ed2b43ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R57a27788e26c4948"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R1a4f9129cc3e46bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf118ce2453664ec2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb27b30f6383b4d39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0647240537b24fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R50508eb027ef41cf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R45cee23dc94d46b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re03d0bcd957344f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5aaf23e92aff4f0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d7053757e36423f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb6ac6c7a5b94472f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rddde8a255b2f4f70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R7688775b4d524fb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf1b85c01c89a448b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R527cad88ae214a9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9b89f6361e394ba2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rec5c27deff7640d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rec2099a50f6d462f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R63cfa6aede3d4434"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfe5bf068d660401b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R68c3035be7e54eb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R7ac4fb97a90942af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7d131d1611d842f6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R39f66ddb95fb4c91"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf01bda10359a49c9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R535ec9a062264578"/>
 </x:worksheet>
 </file>
 
@@ -3643,9 +3643,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I2" s="82" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I2" s="82" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -3778,9 +3780,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -3805,9 +3809,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I8" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -4129,9 +4135,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H20" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I20" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I20" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="83" t="str">
@@ -4156,9 +4164,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H21" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I21" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I21" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="83" t="str">
@@ -4932,7 +4942,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J3" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>contracts/task-spec.schema.json；src/yoloongppt/tasks.py；validation/runtime-core.json；运行时形状/ID校验已接入，E2E仍待执行。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -10124,7 +10134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdd30b6c886a74741"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4875bd7aac1044be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11313,7 +11323,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f963841ca2c4fba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2182929d6d4c2c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19841,7 +19851,7 @@
       <x:c r="O183" s="84" t="str"/>
       <x:c r="P183" s="86" t="str"/>
     </x:row>
-    <x:row r="184">
+    <x:row r="184" ht="180" customHeight="1">
       <x:c r="A184" s="83" t="str">
         <x:v>SYS-001</x:v>
       </x:c>
@@ -19878,10 +19888,14 @@
       </x:c>
       <x:c r="M184" s="84" t="str"/>
       <x:c r="N184" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O184" s="84" t="str"/>
-      <x:c r="P184" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O184" s="84" t="str">
+        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+      </x:c>
+      <x:c r="P184" s="86" t="str">
+        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="185">
       <x:c r="A185" s="83" t="str">
@@ -20051,7 +20065,7 @@
       <x:c r="O188" s="84" t="str"/>
       <x:c r="P188" s="86" t="str"/>
     </x:row>
-    <x:row r="189">
+    <x:row r="189" ht="180" customHeight="1">
       <x:c r="A189" s="83" t="str">
         <x:v>SYS-006</x:v>
       </x:c>
@@ -20088,12 +20102,16 @@
       </x:c>
       <x:c r="M189" s="84" t="str"/>
       <x:c r="N189" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O189" s="84" t="str"/>
-      <x:c r="P189" s="86" t="str"/>
-    </x:row>
-    <x:row r="190">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O189" s="84" t="str">
+        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+      </x:c>
+      <x:c r="P189" s="86" t="str">
+        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" ht="180" customHeight="1">
       <x:c r="A190" s="83" t="str">
         <x:v>SYS-007</x:v>
       </x:c>
@@ -20130,10 +20148,14 @@
       </x:c>
       <x:c r="M190" s="84" t="str"/>
       <x:c r="N190" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O190" s="84" t="str"/>
-      <x:c r="P190" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O190" s="84" t="str">
+        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+      </x:c>
+      <x:c r="P190" s="86" t="str">
+        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="191">
       <x:c r="A191" s="83" t="str">
@@ -20597,7 +20619,7 @@
       <x:c r="O201" s="84" t="str"/>
       <x:c r="P201" s="86" t="str"/>
     </x:row>
-    <x:row r="202">
+    <x:row r="202" ht="180" customHeight="1">
       <x:c r="A202" s="83" t="str">
         <x:v>SYS-019</x:v>
       </x:c>
@@ -20634,12 +20656,16 @@
       </x:c>
       <x:c r="M202" s="84" t="str"/>
       <x:c r="N202" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O202" s="84" t="str"/>
-      <x:c r="P202" s="86" t="str"/>
-    </x:row>
-    <x:row r="203">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O202" s="84" t="str">
+        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+      </x:c>
+      <x:c r="P202" s="86" t="str">
+        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="180" customHeight="1">
       <x:c r="A203" s="83" t="str">
         <x:v>SYS-020</x:v>
       </x:c>
@@ -20676,10 +20702,14 @@
       </x:c>
       <x:c r="M203" s="84" t="str"/>
       <x:c r="N203" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O203" s="84" t="str"/>
-      <x:c r="P203" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O203" s="84" t="str">
+        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+      </x:c>
+      <x:c r="P203" s="86" t="str">
+        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="204">
       <x:c r="A204" s="83" t="str">
@@ -25157,7 +25187,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe1c3dbaa35c48ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb96e7e8048674228"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37535,9 +37565,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L293" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M293" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M293" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+      </x:c>
       <x:c r="N293" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37735,9 +37767,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L298" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M298" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M298" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+      </x:c>
       <x:c r="N298" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37775,9 +37809,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L299" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M299" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M299" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+      </x:c>
       <x:c r="N299" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38255,9 +38291,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L311" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M311" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M311" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+      </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38295,9 +38333,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L312" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M312" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M312" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+      </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44070,7 +44110,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea8572c0f58a4f76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a986f6444a54f5b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44364,7 +44404,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d3682fae34a4014"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8e0d3e98b74b0a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45780,7 +45820,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2206d8cdd6ba481c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cbd15b5c4d048e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46202,7 +46242,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0fe4e20bf1364a06"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95fa15204f274427"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49549,7 +49589,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f612eea251143df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2d8d389ff443eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf118ce2453664ec2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rb27b30f6383b4d39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R0647240537b24fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R50508eb027ef41cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R45cee23dc94d46b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Re03d0bcd957344f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5aaf23e92aff4f0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3d7053757e36423f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rb6ac6c7a5b94472f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rddde8a255b2f4f70"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R7688775b4d524fb9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rf1b85c01c89a448b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R527cad88ae214a9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9b89f6361e394ba2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rec5c27deff7640d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rec2099a50f6d462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R63cfa6aede3d4434"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rfe5bf068d660401b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R68c3035be7e54eb2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R7ac4fb97a90942af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3042fea0bb1d4804"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2f49f137060e4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R78499cafe1e446e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R108f5f3765a249d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd2bf7bc0c7834ffb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7439271332264e2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7f38964f236b465e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7cd78a0d73444133"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R4bba6bea180f4721"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Raeec2b921ad94b7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcf3bde80f0b54a3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R3af0b17357124c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R12ccc914b8074c7f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rdae02dc2fb6240dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R772040bed8b34a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R586def2c998142e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1e76dca3b7b045f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R41cb6ab7756e47ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R731a15a3c2f4446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R80cd0ea736ae490b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R39f66ddb95fb4c91"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfeebc88b23d24d73"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R535ec9a062264578"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf76b81f91b2b49b1"/>
 </x:worksheet>
 </file>
 
@@ -3699,9 +3699,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/source-runtime.json；文本组件可运行，原E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -3726,9 +3728,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>src/yoloongppt/；validation/source-runtime.json；文本组件可运行，原E2E待验证</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -4910,7 +4914,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>契约草案见 contracts/prompt-input.schema.json；解析与落盘待实现。</x:v>
+        <x:v>src/yoloongppt/sources.py；validation/source-runtime.json；原文与上下文已载入，完整原始请求和语义规范化仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -5068,7 +5072,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J7" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>contracts/source-evidence.schema.json；src/yoloongppt/evidence.py；validation/source-runtime.json；文本快照及原生块已存储，confidence为null，其他格式与完整E2E待接入。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -10134,7 +10138,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4875bd7aac1044be"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re54fac85abbb45e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11323,7 +11327,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea2182929d6d4c2c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2821e50011464c0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13481,7 +13485,7 @@
         <x:v>35项资产覆盖五项目；P03无生成PPTX、P04无研究渲染截图，未执行项显式记录。</x:v>
       </x:c>
     </x:row>
-    <x:row r="40">
+    <x:row r="40" ht="180" customHeight="1">
       <x:c r="A40" s="83" t="str">
         <x:v>IN-001</x:v>
       </x:c>
@@ -13521,13 +13525,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O40" s="84" t="str">
-        <x:v>contracts/prompt-input.schema.json；contracts/prompt-input.catalog.json；contracts/prompt-input.fixtures.json；PROJECT_PLAN.md（TASK-IN-001）</x:v>
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
       </x:c>
       <x:c r="P40" s="86" t="str">
-        <x:v>样例跨度静态核对通过；运行时解析器未实现。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41">
+        <x:v>原文/上下文已载入并保留；主题、要求、修改意图语义提取尚未实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="180" customHeight="1">
       <x:c r="A41" s="83" t="str">
         <x:v>IN-002</x:v>
       </x:c>
@@ -13567,10 +13571,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O41" s="84" t="str">
-        <x:v>contracts/text-document.schema.json；contracts/text-document.catalog.json；contracts/text-document.fixtures.json；PROJECT_PLAN.md（TASK-IN-002）</x:v>
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
       </x:c>
       <x:c r="P41" s="86" t="str">
-        <x:v>结构/跨度静态核对通过；解析器未实现。</x:v>
+        <x:v>真实结构解析/原文锚点已运行；行内定位为所属块范围，部分Markdown扩展明确拒绝。</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -14079,7 +14083,7 @@
         <x:v>4 个合成场景与特征/权利边界已静态核验；图像分析与授权流程待运行时验证。</x:v>
       </x:c>
     </x:row>
-    <x:row r="53">
+    <x:row r="53" ht="180" customHeight="1">
       <x:c r="A53" s="83" t="str">
         <x:v>IN-014</x:v>
       </x:c>
@@ -14119,13 +14123,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O53" s="84" t="str">
-        <x:v>contracts/source-bundle.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-014）</x:v>
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
       </x:c>
       <x:c r="P53" s="86" t="str">
-        <x:v>JSON/引用/冲突/去重静态核对通过；DEC-004 未决。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54">
+        <x:v>多源ID/哈希重复候选保留；优先级DEC-004及语义冲突检测未执行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="180" customHeight="1">
       <x:c r="A54" s="83" t="str">
         <x:v>IN-015</x:v>
       </x:c>
@@ -14165,13 +14169,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O54" s="84" t="str">
-        <x:v>contracts/input-issue.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-IN-015）</x:v>
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
       </x:c>
       <x:c r="P54" s="86" t="str">
-        <x:v>JSON/引用/错误码关联静态核对通过；未运行解析器、实例校验器或 AC。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55">
+        <x:v>文本路径、编码、NUL、超限/不支持及解析失败明确返回；其他格式检测待接入。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="180" customHeight="1">
       <x:c r="A55" s="83" t="str">
         <x:v>IN-016</x:v>
       </x:c>
@@ -14211,10 +14215,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O55" s="84" t="str">
-        <x:v>contracts/source-anchor.schema.json、catalog.json、fixtures.json；SourceBundle 已对齐；PROJECT_PLAN.md（TASK-IN-016）</x:v>
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
       </x:c>
       <x:c r="P55" s="86" t="str">
-        <x:v>JSON/引用/锚点身份静态核对通过；未运行解析器、网页抓取或 AC。</x:v>
+        <x:v>文本/Markdown块锚点与原文回读一致；其他格式及最终PPT对象追溯待验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -19939,7 +19943,7 @@
       <x:c r="O185" s="84" t="str"/>
       <x:c r="P185" s="86" t="str"/>
     </x:row>
-    <x:row r="186">
+    <x:row r="186" ht="180" customHeight="1">
       <x:c r="A186" s="83" t="str">
         <x:v>SYS-003</x:v>
       </x:c>
@@ -19976,12 +19980,16 @@
       </x:c>
       <x:c r="M186" s="84" t="str"/>
       <x:c r="N186" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O186" s="84" t="str"/>
-      <x:c r="P186" s="86" t="str"/>
-    </x:row>
-    <x:row r="187">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O186" s="84" t="str">
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+      </x:c>
+      <x:c r="P186" s="86" t="str">
+        <x:v>SourceBundle与文本/Markdown解析已实际运行；IN其他格式及原SYS E2E待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" ht="180" customHeight="1">
       <x:c r="A187" s="83" t="str">
         <x:v>SYS-004</x:v>
       </x:c>
@@ -20018,10 +20026,14 @@
       </x:c>
       <x:c r="M187" s="84" t="str"/>
       <x:c r="N187" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O187" s="84" t="str"/>
-      <x:c r="P187" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O187" s="84" t="str">
+        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+      </x:c>
+      <x:c r="P187" s="86" t="str">
+        <x:v>SQLite原文/结构/锚点/hash/版本与ID查询已运行；原SYS生成QA修订E2E待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="188">
       <x:c r="A188" s="83" t="str">
@@ -25187,7 +25199,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb96e7e8048674228"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576e7bc9c9d6417c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28178,7 +28190,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M68" s="84" t="str">
-        <x:v>contracts/prompt-input.schema.json（草案）；contracts/prompt-input.catalog.json；contracts/prompt-input.fixtures.json；PROJECT_PLAN.md（TASK-IN-001）</x:v>
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
       </x:c>
       <x:c r="N68" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28220,7 +28232,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M69" s="84" t="str">
-        <x:v>contracts/text-document.schema.json（草案）；contracts/text-document.catalog.json；contracts/text-document.fixtures.json；PROJECT_PLAN.md（TASK-IN-002）</x:v>
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
       </x:c>
       <x:c r="N69" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28724,7 +28736,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M81" s="84" t="str">
-        <x:v>contracts/source-bundle.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-014）</x:v>
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
       </x:c>
       <x:c r="N81" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28766,7 +28778,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M82" s="84" t="str">
-        <x:v>contracts/input-issue.schema.json、catalog/fixtures；PROJECT_PLAN.md（TASK-IN-015）</x:v>
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
       </x:c>
       <x:c r="N82" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28808,7 +28820,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M83" s="84" t="str">
-        <x:v>contracts/source-anchor.schema.json、catalog/fixtures；source-bundle 锚点改为结构化对象</x:v>
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
       </x:c>
       <x:c r="N83" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37647,9 +37659,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L295" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M295" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M295" s="84" t="str">
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+      </x:c>
       <x:c r="N295" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37687,9 +37701,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L296" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M296" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M296" s="84" t="str">
+        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+      </x:c>
       <x:c r="N296" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44110,7 +44126,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a986f6444a54f5b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03998d455206486b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44404,7 +44420,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8e0d3e98b74b0a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03a839f9a40b4375"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45820,7 +45836,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cbd15b5c4d048e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de80b49d2504ca4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46242,7 +46258,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95fa15204f274427"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4017813809e142a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49589,7 +49605,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe2d8d389ff443eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd480a37a82954ac6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R3042fea0bb1d4804"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R2f49f137060e4415"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R78499cafe1e446e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R108f5f3765a249d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd2bf7bc0c7834ffb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R7439271332264e2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R7f38964f236b465e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R7cd78a0d73444133"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R4bba6bea180f4721"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Raeec2b921ad94b7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rcf3bde80f0b54a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R3af0b17357124c74"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R12ccc914b8074c7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rdae02dc2fb6240dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R772040bed8b34a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R586def2c998142e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R1e76dca3b7b045f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R41cb6ab7756e47ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R731a15a3c2f4446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R80cd0ea736ae490b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R26e28a534bd642fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R19ff85c15fc64049"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R521510fb1a2c46af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R72339b992d204aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9e2ee9149b3c4f2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R042336ff7bad472d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Re9d7587e7866428e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R573498831ca24619"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R488dcadcda724756"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R94bc392027504f22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf5ad481924d84409"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55fdc8b72ad248c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R35df752063654cde"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R39e61b05aa744ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R480161302d63446f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R220429e7963c43e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R4b914f74adfa4566"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra53482f1d43646f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28616954d253497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb38664f1ba8f402e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rfeebc88b23d24d73"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R914230756f4045df"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf76b81f91b2b49b1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe68665b38c7489a"/>
 </x:worksheet>
 </file>
 
@@ -3757,9 +3757,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I6" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I6" s="86" t="str">
+        <x:v>真实模型规划及模型阶段恢复已接入；完整DEC节点/条件分支/节点重跑未完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -3896,9 +3898,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I11" s="86" t="str">
+        <x:v>新建子集SlideSpec含内容/几何/样式/来源/备注，实际writer消费；其他对象/绑定/模板待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -3923,9 +3927,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I12" s="86" t="str">
+        <x:v>实际DAG与明确PP-05方法实现已执行；正式能力实体登记及完整预执行边界待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -3950,9 +3956,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I13" s="86" t="str">
+        <x:v>原生文本/表格/图表/备注调用与实际ObjectMap已运行；其他原子能力待扩展。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -3977,9 +3985,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I14" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I14" s="86" t="str">
+        <x:v>真实10页原生新建/顺序执行；导入模板/master/layout/theme及已有deck修改待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -4004,9 +4014,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I15" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I15" s="86" t="str">
+        <x:v>实际LibreOffice PDF/10 PNG含hash/version，F盘IPC挂载；live截图/缩略图待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -4031,9 +4043,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I16" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I16" s="86" t="str">
+        <x:v>结构/数值/几何/可编辑性与真实PNG模型审查已运行；可访问性及完整QA未完成，模型可能误判。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -4058,9 +4072,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I17" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I17" s="86" t="str">
+        <x:v>单正文原生对象修订仅改变一个slide XML，ID/其他parts保持，复审/QA恢复；完整RevisionPlan/节点重跑待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -4085,9 +4101,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I18" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I18" s="86" t="str">
+        <x:v>JSON/PPTX/render/trace/QA/manifest实际保存与hash，失败证据保留；完整生命周期清理待完成。 实物：validation/generation-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="83" t="str">
@@ -6004,7 +6022,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J37" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>内容/几何/样式/来源/备注实际消费，其他对象/模板绑定待完成；contracts/deck-execution.schema.json；validation/generation-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -6132,7 +6150,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J41" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>实际调用DAG/方法别名执行，正式AtomicCapability/implementation实体登记待完成；contracts/deck-execution.schema.json；validation/generation-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -6164,7 +6182,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J42" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>32个实际原生对象，逻辑/后端ID、shape/name、来源和call引用，单对象修订ID保持；contracts/deck-execution.schema.json；validation/generation-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -6196,7 +6214,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J43" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>实际PDF/PNG含hash/version/DPI；其他渲染边界未完成；contracts/deck-execution.schema.json；validation/generation-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -8700,7 +8718,7 @@
         <x:v>问题ID</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="165" customHeight="1">
       <x:c r="A2" s="79" t="str">
         <x:v>AC-001</x:v>
       </x:c>
@@ -8720,11 +8738,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G2" s="80" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H2" s="80" t="str"/>
-      <x:c r="I2" s="80" t="str"/>
-      <x:c r="J2" s="82" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H2" s="80" t="str">
+        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+      </x:c>
+      <x:c r="I2" s="80" t="str">
+        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+      </x:c>
+      <x:c r="J2" s="82" t="str">
+        <x:v>10页实物与执行过的QA P0=0；完整DEC轨迹、全部QA及原通过条件未证明。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -9376,7 +9400,7 @@
       <x:c r="I27" s="84" t="str"/>
       <x:c r="J27" s="86" t="str"/>
     </x:row>
-    <x:row r="28">
+    <x:row r="28" ht="165" customHeight="1">
       <x:c r="A28" s="83" t="str">
         <x:v>AC-027</x:v>
       </x:c>
@@ -9396,13 +9420,19 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G28" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H28" s="84" t="str"/>
-      <x:c r="I28" s="84" t="str"/>
-      <x:c r="J28" s="86" t="str"/>
-    </x:row>
-    <x:row r="29">
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H28" s="84" t="str">
+        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+      </x:c>
+      <x:c r="I28" s="84" t="str">
+        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+      </x:c>
+      <x:c r="J28" s="86" t="str">
+        <x:v>原生ObjectMap可回到source/evidence/spec/call/QA；完整decision链及随机最终对象全范围未证明。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="165" customHeight="1">
       <x:c r="A29" s="83" t="str">
         <x:v>AC-028</x:v>
       </x:c>
@@ -9422,11 +9452,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G29" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H29" s="84" t="str"/>
-      <x:c r="I29" s="84" t="str"/>
-      <x:c r="J29" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H29" s="84" t="str">
+        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+      </x:c>
+      <x:c r="I29" s="84" t="str">
+        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+      </x:c>
+      <x:c r="J29" s="86" t="str">
+        <x:v>PowerPoint 16.0 COM实际打开10页32对象无异常；未经UI观察修复提示，不能判通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -10138,7 +10174,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re54fac85abbb45e2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6e725e0d49a4e4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11327,7 +11363,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2821e50011464c0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c5ddd99f2b34dc6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12041,10 +12077,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O9" s="84" t="str">
-        <x:v>contracts/e2e-acceptance.catalog.json；PROJECT_PLAN.md</x:v>
+        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
       </x:c>
       <x:c r="P9" s="86" t="str">
-        <x:v>完成门槛已定义；AC-001–AC-030 均未执行，系统验收未通过。</x:v>
+        <x:v>已有真实10页可编辑PPTX→render→部分QA→单对象修订；完整DEC/全部QA/所有P0 AC未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -20035,7 +20071,7 @@
         <x:v>SQLite原文/结构/锚点/hash/版本与ID查询已运行；原SYS生成QA修订E2E待完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="188">
+    <x:row r="188" ht="172.5" customHeight="1">
       <x:c r="A188" s="83" t="str">
         <x:v>SYS-005</x:v>
       </x:c>
@@ -20072,10 +20108,14 @@
       </x:c>
       <x:c r="M188" s="84" t="str"/>
       <x:c r="N188" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O188" s="84" t="str"/>
-      <x:c r="P188" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O188" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P188" s="86" t="str">
+        <x:v>真实模型规划及模型阶段恢复已接入；完整DEC节点/条件分支/节点重跑未完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="189" ht="180" customHeight="1">
       <x:c r="A189" s="83" t="str">
@@ -20253,7 +20293,7 @@
       <x:c r="O192" s="84" t="str"/>
       <x:c r="P192" s="86" t="str"/>
     </x:row>
-    <x:row r="193">
+    <x:row r="193" ht="172.5" customHeight="1">
       <x:c r="A193" s="83" t="str">
         <x:v>SYS-010</x:v>
       </x:c>
@@ -20290,12 +20330,16 @@
       </x:c>
       <x:c r="M193" s="84" t="str"/>
       <x:c r="N193" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O193" s="84" t="str"/>
-      <x:c r="P193" s="86" t="str"/>
-    </x:row>
-    <x:row r="194">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O193" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P193" s="86" t="str">
+        <x:v>新建子集SlideSpec含内容/几何/样式/来源/备注，实际writer消费；其他对象/绑定/模板待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" ht="172.5" customHeight="1">
       <x:c r="A194" s="83" t="str">
         <x:v>SYS-011</x:v>
       </x:c>
@@ -20332,12 +20376,16 @@
       </x:c>
       <x:c r="M194" s="84" t="str"/>
       <x:c r="N194" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O194" s="84" t="str"/>
-      <x:c r="P194" s="86" t="str"/>
-    </x:row>
-    <x:row r="195">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O194" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P194" s="86" t="str">
+        <x:v>实际DAG与明确PP-05方法实现已执行；正式能力实体登记及完整预执行边界待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" ht="172.5" customHeight="1">
       <x:c r="A195" s="83" t="str">
         <x:v>SYS-012</x:v>
       </x:c>
@@ -20374,12 +20422,16 @@
       </x:c>
       <x:c r="M195" s="84" t="str"/>
       <x:c r="N195" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O195" s="84" t="str"/>
-      <x:c r="P195" s="86" t="str"/>
-    </x:row>
-    <x:row r="196">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O195" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P195" s="86" t="str">
+        <x:v>原生文本/表格/图表/备注调用与实际ObjectMap已运行；其他原子能力待扩展。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" ht="172.5" customHeight="1">
       <x:c r="A196" s="83" t="str">
         <x:v>SYS-013</x:v>
       </x:c>
@@ -20416,12 +20468,16 @@
       </x:c>
       <x:c r="M196" s="84" t="str"/>
       <x:c r="N196" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O196" s="84" t="str"/>
-      <x:c r="P196" s="86" t="str"/>
-    </x:row>
-    <x:row r="197">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O196" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P196" s="86" t="str">
+        <x:v>真实10页原生新建/顺序执行；导入模板/master/layout/theme及已有deck修改待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" ht="172.5" customHeight="1">
       <x:c r="A197" s="83" t="str">
         <x:v>SYS-014</x:v>
       </x:c>
@@ -20458,12 +20514,16 @@
       </x:c>
       <x:c r="M197" s="84" t="str"/>
       <x:c r="N197" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O197" s="84" t="str"/>
-      <x:c r="P197" s="86" t="str"/>
-    </x:row>
-    <x:row r="198">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O197" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P197" s="86" t="str">
+        <x:v>实际LibreOffice PDF/10 PNG含hash/version，F盘IPC挂载；live截图/缩略图待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" ht="172.5" customHeight="1">
       <x:c r="A198" s="83" t="str">
         <x:v>SYS-015</x:v>
       </x:c>
@@ -20500,12 +20560,16 @@
       </x:c>
       <x:c r="M198" s="84" t="str"/>
       <x:c r="N198" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O198" s="84" t="str"/>
-      <x:c r="P198" s="86" t="str"/>
-    </x:row>
-    <x:row r="199">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O198" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P198" s="86" t="str">
+        <x:v>结构/数值/几何/可编辑性与真实PNG模型审查已运行；可访问性及完整QA未完成，模型可能误判。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" ht="172.5" customHeight="1">
       <x:c r="A199" s="83" t="str">
         <x:v>SYS-016</x:v>
       </x:c>
@@ -20542,12 +20606,16 @@
       </x:c>
       <x:c r="M199" s="84" t="str"/>
       <x:c r="N199" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O199" s="84" t="str"/>
-      <x:c r="P199" s="86" t="str"/>
-    </x:row>
-    <x:row r="200">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O199" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P199" s="86" t="str">
+        <x:v>单正文原生对象修订仅改变一个slide XML，ID/其他parts保持，复审/QA恢复；完整RevisionPlan/节点重跑待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" ht="172.5" customHeight="1">
       <x:c r="A200" s="83" t="str">
         <x:v>SYS-017</x:v>
       </x:c>
@@ -20584,10 +20652,14 @@
       </x:c>
       <x:c r="M200" s="84" t="str"/>
       <x:c r="N200" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O200" s="84" t="str"/>
-      <x:c r="P200" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O200" s="84" t="str">
+        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+      </x:c>
+      <x:c r="P200" s="86" t="str">
+        <x:v>JSON/PPTX/render/trace/QA/manifest实际保存与hash，失败证据保留；完整生命周期清理待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="201">
       <x:c r="A201" s="83" t="str">
@@ -20671,10 +20743,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O202" s="84" t="str">
-        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
       </x:c>
       <x:c r="P202" s="86" t="str">
-        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+        <x:v>CLI接入generate/resume/revise/recheck；完整命令/任务生命周期仍待原验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="180" customHeight="1">
@@ -20717,10 +20789,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O203" s="84" t="str">
-        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
       </x:c>
       <x:c r="P203" s="86" t="str">
-        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+        <x:v>HTTP接入/generate、/resume、/revise、/recheck，真实生成已运行；完整jobs/取消/重试等仍待原验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -25199,7 +25271,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R576e7bc9c9d6417c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re54a1fd83d594931"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25682,7 +25754,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M11" s="84" t="str">
-        <x:v>contracts/e2e-acceptance.catalog.json；PROJECT_PLAN.md</x:v>
+        <x:v>已有真实10页可编辑PPTX→render→部分QA→单对象修订；完整DEC/全部QA/所有P0 AC未通过。 证据：validation/generation-artifacts/</x:v>
       </x:c>
       <x:c r="N11" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37743,9 +37815,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L297" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M297" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M297" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N297" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37947,9 +38021,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L302" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M302" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M302" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N302" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37987,9 +38063,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L303" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M303" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M303" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N303" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38027,9 +38105,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L304" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M304" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M304" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N304" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38067,9 +38147,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L305" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M305" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M305" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N305" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38107,9 +38189,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L306" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M306" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M306" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N306" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38147,9 +38231,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L307" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M307" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M307" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38187,9 +38273,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L308" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M308" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M308" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38227,9 +38315,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L309" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M309" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M309" s="84" t="str">
+        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N309" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38310,7 +38400,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M311" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+        <x:v>CLI接入generate/resume/revise/recheck；完整命令/任务生命周期仍待原验收。 证据：validation/generation-artifacts/</x:v>
       </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38352,7 +38442,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M312" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+        <x:v>HTTP接入/generate、/resume、/revise、/recheck，真实生成已运行；完整jobs/取消/重试等仍待原验收。 证据：validation/generation-artifacts/</x:v>
       </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
@@ -44126,7 +44216,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03998d455206486b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e407e9f150d4443"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44420,7 +44510,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03a839f9a40b4375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92ef01943244668"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45836,7 +45926,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6de80b49d2504ca4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fcd90a23e74442e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46080,13 +46170,13 @@
         <x:v>create/read/update；slides/placeholders/text/images/tables/charts/shapes；master/layout/theme 边界；round-trip 保真；高级特性不支持项。</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>待搭建</x:v>
+        <x:v>已运行（新建子集）</x:v>
       </x:c>
       <x:c r="I6" s="84" t="str">
-        <x:v>未执行</x:v>
+        <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="J6" s="84" t="str">
-        <x:v>未冻结（PoC未执行）</x:v>
+        <x:v>python-pptx 1.0.2；实际原生对象/单文本修订，完整后端边界待验证；validation/generation-artifacts/</x:v>
       </x:c>
       <x:c r="K6" s="84" t="str"/>
       <x:c r="L6" s="84" t="str"/>
@@ -46258,7 +46348,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4017813809e142a7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b38ae8fe0e34e5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49605,7 +49695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd480a37a82954ac6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc49d36555cb547ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R26e28a534bd642fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R19ff85c15fc64049"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R521510fb1a2c46af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R72339b992d204aad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9e2ee9149b3c4f2b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R042336ff7bad472d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="Re9d7587e7866428e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R573498831ca24619"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R488dcadcda724756"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R94bc392027504f22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rf5ad481924d84409"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R55fdc8b72ad248c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R35df752063654cde"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R39e61b05aa744ace"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R480161302d63446f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R220429e7963c43e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R4b914f74adfa4566"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra53482f1d43646f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R28616954d253497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rb38664f1ba8f402e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb6de022b209e4512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R14cb248b67714d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R1f3e567dfb444305"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R5e71200de9774085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R35518e5942ca4ea8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rec685b2dadb348d7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8bc12d4e74934d9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R6f8be8cb9f054a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8e9611d02cbc4726"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3ce41f3bad774f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra9eeece214ed4345"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2b2d098d89434960"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Raf90ac2e839941ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rf7cfec752ce44100"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R69a998ecb62841c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8746aeb470144051"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R021b06d3af514496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1965f6e42c0b4b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3473781cfb1a4020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R104feb38cffc4a9b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R914230756f4045df"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02511daf079a4fe1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1468,11 +1468,11 @@
       </x:c>
       <x:c r="E9" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A9,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F9" s="85" t="n">
         <x:f>IF(B9=0,0,E9/B9)</x:f>
-        <x:v>0</x:v>
+        <x:v>0.025</x:v>
       </x:c>
       <x:c r="G9" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfe68665b38c7489a"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c78a2ef21246e1"/>
 </x:worksheet>
 </file>
 
@@ -3672,9 +3672,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I3" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I3" s="86" t="str">
+        <x:v>实际本地平台/精确写入依赖/字体/渲染探测由路由消费；Office/API set/MCP/远端模型完整探测待完成。 validation/route-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -3760,7 +3762,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>真实模型规划及模型阶段恢复已接入；完整DEC节点/条件分支/节点重跑未完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3818,7 +3820,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I8" s="86" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+        <x:v>五项原生能力/实现稳定实体登记，输入输出/平台/依赖/优先级/health；planner/writer真实消费，全部对象×后端待扩展。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3930,7 +3932,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I12" s="86" t="str">
-        <x:v>实际DAG与明确PP-05方法实现已执行；正式能力实体登记及完整预执行边界待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3959,7 +3961,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I13" s="86" t="str">
-        <x:v>原生文本/表格/图表/备注调用与实际ObjectMap已运行；其他原子能力待扩展。 实物：validation/generation-artifacts/</x:v>
+        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4160,7 +4162,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4189,7 +4191,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I21" s="86" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；组件可运行，E2E待验证</x:v>
+        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。 validation/route-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4242,9 +4244,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I23" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I23" s="86" t="str">
+        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。 validation/route-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -4932,7 +4936,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>src/yoloongppt/sources.py；validation/source-runtime.json；原文与上下文已载入，完整原始请求和语义规范化仍待完成。</x:v>
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -4993,9 +4997,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J4" s="86" t="str">
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
       <x:c r="A5" s="83" t="str">
@@ -6054,7 +6060,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J38" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -6086,7 +6092,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J39" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -6246,7 +6252,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J44" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -6278,7 +6284,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J45" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -8462,9 +8468,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H36" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I36" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I36" s="86" t="str">
+        <x:v>DEC-001实际DecisionTrace与最终对象关联；其他39节点仍待完成，validation/route-runtime.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="83" t="str">
@@ -8741,13 +8749,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+        <x:v>真实新请求10页PPTX/渲染/QA P0=0并经过DEC-001；其余39节点及全部原QA/AC条件待完成。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+        <x:v>validation/route-artifacts/；validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>10页实物与执行过的QA P0=0；完整DEC轨迹、全部QA及原通过条件未证明。</x:v>
+        <x:v>完整DEC/QA/全范围未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9423,13 +9431,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+        <x:v>本次所有原生对象关联source/evidence/spec/call/DEC-001；完整决策链及全对象随机抽检未完成。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+        <x:v>validation/route-artifacts/；validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
-        <x:v>原生ObjectMap可回到source/evidence/spec/call/QA；完整decision链及随机最终对象全范围未证明。</x:v>
+        <x:v>完整DEC/QA/全范围未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="165" customHeight="1">
@@ -10174,7 +10182,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6e725e0d49a4e4e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3afbab0059ba44e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11363,7 +11371,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c5ddd99f2b34dc6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500155d32ee94e74"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11761,7 +11769,7 @@
         <x:v>通过：需求ID 308/308；任务ID 453 唯一。</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="72" customHeight="1">
+    <x:row r="3" ht="172.5" customHeight="1">
       <x:c r="A3" s="83" t="str">
         <x:v>GOV-002</x:v>
       </x:c>
@@ -11801,10 +11809,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O3" s="84" t="str">
-        <x:v>contracts/task-route.catalog.json</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P3" s="86" t="str">
-        <x:v>未验证：八种模式契约为草案；运行时路由未实现。</x:v>
+        <x:v>八模式运行时判定/保护策略均有测试；除新建子集外的完整后续流程尚未交付。</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="72" customHeight="1">
@@ -11991,7 +11999,7 @@
         <x:v>Draft 2020-12 schema、catalog 与 pending fixture 标准校验通过；类型、默认值、范围及来源优先级待基线/DEC-004 决定；运行时有效配置 trace 未实现。</x:v>
       </x:c>
     </x:row>
-    <x:row r="8">
+    <x:row r="8" ht="172.5" customHeight="1">
       <x:c r="A8" s="83" t="str">
         <x:v>GOV-007</x:v>
       </x:c>
@@ -12031,10 +12039,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O8" s="84" t="str">
-        <x:v>contracts/object-id.catalog.json；PROJECT_PLAN.md</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P8" s="86" t="str">
-        <x:v>Fixture 追溯链检查通过；真实 PPT 端到端验收待运行时实现。</x:v>
+        <x:v>实际DAG原子能力及实现ID已稳定登记；shape到source/spec/call/DEC-001可追溯，全部对象/决策尚未完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -14901,7 +14909,7 @@
         <x:v>静态核对通过（4 个 fixture）；未运行 JSON Schema 实例验证器、附录 runtime 或 AC。</x:v>
       </x:c>
     </x:row>
-    <x:row r="70">
+    <x:row r="70" ht="172.5" customHeight="1">
       <x:c r="A70" s="83" t="str">
         <x:v>DEC-001</x:v>
       </x:c>
@@ -14940,10 +14948,14 @@
       </x:c>
       <x:c r="M70" s="84" t="str"/>
       <x:c r="N70" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O70" s="84" t="str"/>
-      <x:c r="P70" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O70" s="84" t="str">
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+      </x:c>
+      <x:c r="P70" s="86" t="str">
+        <x:v>八种模式与十个边界实际运行；输入、候选、规则、输出、约束、回退、轨迹及五项目对应齐备。39项核验和真实生成通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="83" t="str">
@@ -19937,7 +19949,7 @@
         <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="185">
+    <x:row r="185" ht="172.5" customHeight="1">
       <x:c r="A185" s="83" t="str">
         <x:v>SYS-002</x:v>
       </x:c>
@@ -19974,10 +19986,14 @@
       </x:c>
       <x:c r="M185" s="84" t="str"/>
       <x:c r="N185" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O185" s="84" t="str"/>
-      <x:c r="P185" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O185" s="84" t="str">
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+      </x:c>
+      <x:c r="P185" s="86" t="str">
+        <x:v>实际本地平台/精确写入依赖/字体/渲染探测由路由消费；Office/API set/MCP/远端模型完整探测待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="186" ht="180" customHeight="1">
       <x:c r="A186" s="83" t="str">
@@ -20111,10 +20127,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O188" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P188" s="86" t="str">
-        <x:v>真实模型规划及模型阶段恢复已接入；完整DEC节点/条件分支/节点重跑未完成。</x:v>
+        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="180" customHeight="1">
@@ -20163,7 +20179,7 @@
         <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="190" ht="180" customHeight="1">
+    <x:row r="190" ht="172.5" customHeight="1">
       <x:c r="A190" s="83" t="str">
         <x:v>SYS-007</x:v>
       </x:c>
@@ -20203,10 +20219,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O190" s="84" t="str">
-        <x:v>ARCHITECTURE.md；src/yoloongppt/；validation/runtime-core.json</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P190" s="86" t="str">
-        <x:v>Docker组件校验/CLI/API已运行；完整生成、QA、修订E2E未执行，不能标完成。</x:v>
+        <x:v>五项原生能力/实现稳定实体登记，输入输出/平台/依赖/优先级/health；planner/writer真实消费，全部对象×后端待扩展。</x:v>
       </x:c>
     </x:row>
     <x:row r="191">
@@ -20379,10 +20395,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O194" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P194" s="86" t="str">
-        <x:v>实际DAG与明确PP-05方法实现已执行；正式能力实体登记及完整预执行边界待完成。</x:v>
+        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="172.5" customHeight="1">
@@ -20425,10 +20441,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O195" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P195" s="86" t="str">
-        <x:v>原生文本/表格/图表/备注调用与实际ObjectMap已运行；其他原子能力待扩展。</x:v>
+        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="172.5" customHeight="1">
@@ -20703,7 +20719,7 @@
       <x:c r="O201" s="84" t="str"/>
       <x:c r="P201" s="86" t="str"/>
     </x:row>
-    <x:row r="202" ht="180" customHeight="1">
+    <x:row r="202" ht="172.5" customHeight="1">
       <x:c r="A202" s="83" t="str">
         <x:v>SYS-019</x:v>
       </x:c>
@@ -20743,13 +20759,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O202" s="84" t="str">
-        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P202" s="86" t="str">
-        <x:v>CLI接入generate/resume/revise/recheck；完整命令/任务生命周期仍待原验收。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="203" ht="180" customHeight="1">
+        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="203" ht="172.5" customHeight="1">
       <x:c r="A203" s="83" t="str">
         <x:v>SYS-020</x:v>
       </x:c>
@@ -20789,10 +20805,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O203" s="84" t="str">
-        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
       </x:c>
       <x:c r="P203" s="86" t="str">
-        <x:v>HTTP接入/generate、/resume、/revise、/recheck，真实生成已运行；完整jobs/取消/重试等仍待原验收。</x:v>
+        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -20837,7 +20853,7 @@
       <x:c r="O204" s="84" t="str"/>
       <x:c r="P204" s="86" t="str"/>
     </x:row>
-    <x:row r="205">
+    <x:row r="205" ht="172.5" customHeight="1">
       <x:c r="A205" s="83" t="str">
         <x:v>SYS-022</x:v>
       </x:c>
@@ -20874,10 +20890,14 @@
       </x:c>
       <x:c r="M205" s="84" t="str"/>
       <x:c r="N205" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O205" s="84" t="str"/>
-      <x:c r="P205" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O205" s="84" t="str">
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+      </x:c>
+      <x:c r="P205" s="86" t="str">
+        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="206">
       <x:c r="A206" s="83" t="str">
@@ -23567,7 +23587,7 @@
       <x:c r="O269" s="84" t="str"/>
       <x:c r="P269" s="86" t="str"/>
     </x:row>
-    <x:row r="270">
+    <x:row r="270" ht="172.5" customHeight="1">
       <x:c r="A270" s="83" t="str">
         <x:v>OBS-003</x:v>
       </x:c>
@@ -23604,10 +23624,14 @@
       </x:c>
       <x:c r="M270" s="84" t="str"/>
       <x:c r="N270" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O270" s="84" t="str"/>
-      <x:c r="P270" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O270" s="84" t="str">
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+      </x:c>
+      <x:c r="P270" s="86" t="str">
+        <x:v>DEC-001保存input/candidates/score/reason/selected/rules/output/duration/error；最终对象关联该节点，其余39节点待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="271">
       <x:c r="A271" s="83" t="str">
@@ -23987,7 +24011,7 @@
       <x:c r="O279" s="84" t="str"/>
       <x:c r="P279" s="86" t="str"/>
     </x:row>
-    <x:row r="280">
+    <x:row r="280" ht="172.5" customHeight="1">
       <x:c r="A280" s="83" t="str">
         <x:v>TST-003</x:v>
       </x:c>
@@ -24024,10 +24048,14 @@
       </x:c>
       <x:c r="M280" s="84" t="str"/>
       <x:c r="N280" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O280" s="84" t="str"/>
-      <x:c r="P280" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O280" s="84" t="str">
+        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+      </x:c>
+      <x:c r="P280" s="86" t="str">
+        <x:v>DEC-001八常规+十边界自动结果和真实链路已保留；DEC-002–040各3+1仍待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="281">
       <x:c r="A281" s="83" t="str">
@@ -25271,7 +25299,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re54a1fd83d594931"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c770606b394fab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25418,7 +25446,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M3" s="84" t="str">
-        <x:v>contracts/task-route.schema.json；contracts/task-route.catalog.json；contracts/task-route.fixtures.json；PROJECT_PLAN.md（TASK-GOV-002；运行时路由未实现）</x:v>
+        <x:v>八模式运行时判定/保护策略均有测试；除新建子集外的完整后续流程尚未交付。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N3" s="86" t="str">
         <x:v>本规划</x:v>
@@ -25712,7 +25740,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M10" s="84" t="str">
-        <x:v>contracts/object-id.catalog.json；PROJECT_PLAN.md</x:v>
+        <x:v>实际DAG原子能力及实现ID已稳定登记；shape到source/spec/call/DEC-001可追溯，全部对象/决策尚未完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N10" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29521,9 +29549,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L98" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M98" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M98" s="84" t="str">
+        <x:v>八种模式与十个边界实际运行；输入、候选、规则、输出、约束、回退、轨迹及五项目对应齐备。39项核验和真实生成通过。 证据：validation/route-runtime.json</x:v>
+      </x:c>
       <x:c r="N98" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -29563,9 +29593,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L99" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M99" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M99" s="84" t="str">
+        <x:v>39项实际检查含八模式/十边界及真实HTTP对象关联，validation/route-runtime.json；失败/澄清轨迹保留。</x:v>
+      </x:c>
       <x:c r="N99" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37691,9 +37723,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L294" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M294" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M294" s="84" t="str">
+        <x:v>实际本地平台/精确写入依赖/字体/渲染探测由路由消费；Office/API set/MCP/远端模型完整探测待完成。 证据：validation/route-runtime.json</x:v>
+      </x:c>
       <x:c r="N294" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37818,7 +37852,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M297" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N297" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37902,7 +37936,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M299" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/runtime-core.json；原E2E验收待执行</x:v>
+        <x:v>五项原生能力/实现稳定实体登记，输入输出/平台/依赖/优先级/health；planner/writer真实消费，全部对象×后端待扩展。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N299" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38066,7 +38100,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M303" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N303" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38108,7 +38142,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M304" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N304" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38400,7 +38434,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M311" s="84" t="str">
-        <x:v>CLI接入generate/resume/revise/recheck；完整命令/任务生命周期仍待原验收。 证据：validation/generation-artifacts/</x:v>
+        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38442,7 +38476,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M312" s="84" t="str">
-        <x:v>HTTP接入/generate、/resume、/revise、/recheck，真实生成已运行；完整jobs/取消/重试等仍待原验收。 证据：validation/generation-artifacts/</x:v>
+        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。 证据：validation/route-runtime.json</x:v>
       </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38521,9 +38555,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L314" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M314" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M314" s="84" t="str">
+        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。 证据：validation/route-runtime.json</x:v>
+      </x:c>
       <x:c r="N314" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -42633,9 +42669,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L415" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M415" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M415" s="84" t="str">
+        <x:v>DEC-001保存input/candidates/score/reason/selected/rules/output/duration/error；最终对象关联该节点，其余39节点待完成。 证据：validation/route-runtime.json</x:v>
+      </x:c>
       <x:c r="N415" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43033,9 +43071,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L425" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M425" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M425" s="84" t="str">
+        <x:v>DEC-001八常规+十边界自动结果和真实链路已保留；DEC-002–040各3+1仍待完成。 证据：validation/route-runtime.json</x:v>
+      </x:c>
       <x:c r="N425" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44216,7 +44256,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e407e9f150d4443"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c3dafb4c824449"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44510,7 +44550,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92ef01943244668"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0b5ba0ae6ef4981"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45926,7 +45966,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fcd90a23e74442e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38b395f31a214535"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46348,7 +46388,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b38ae8fe0e34e5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd49106f231b543fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48040,9 +48080,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M2" s="80" t="str">
-        <x:v>进行中</x:v>
-      </x:c>
-      <x:c r="N2" s="82" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="N2" s="82" t="str">
+        <x:v>src/yoloongppt/routing.py；validation/route-runtime.json；validation/route-project-map.json；validation/route-artifacts/decision-route.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -49695,7 +49737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc49d36555cb547ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d0e676c9ae94f98"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb6de022b209e4512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R14cb248b67714d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R1f3e567dfb444305"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R5e71200de9774085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R35518e5942ca4ea8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rec685b2dadb348d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R8bc12d4e74934d9c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R6f8be8cb9f054a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8e9611d02cbc4726"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3ce41f3bad774f7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra9eeece214ed4345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R2b2d098d89434960"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="Raf90ac2e839941ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rf7cfec752ce44100"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R69a998ecb62841c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R8746aeb470144051"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R021b06d3af514496"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1965f6e42c0b4b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R3473781cfb1a4020"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R104feb38cffc4a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf43ed993661f4c0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R35d76cd4aa6041e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R390213e32017450c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R58bf9799526a4672"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rabc66b1715354117"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R104b6b0131414015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5655e41526864c6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R248ac9c649cb4445"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R08663a713354431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3c4b594f345143d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb025775e514845c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8918d95363a842d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R505073de96c7480d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R601d1802e5924d4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9f12769d80b34865"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd316fe40c62045ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb4ef271387d547fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1b84e6dc7c834b95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0baa09f4baeb4bfb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R46ec98d8c8e7403b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R02511daf079a4fe1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7349cb9fb7fe44e4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1468,11 +1468,11 @@
       </x:c>
       <x:c r="E9" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A9,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F9" s="85" t="n">
         <x:f>IF(B9=0,0,E9/B9)</x:f>
-        <x:v>0.025</x:v>
+        <x:v>0.075</x:v>
       </x:c>
       <x:c r="G9" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4c78a2ef21246e1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ec429254104f5b"/>
 </x:worksheet>
 </file>
 
@@ -3704,7 +3704,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
-        <x:v>src/yoloongppt/；validation/source-runtime.json；文本组件可运行，原E2E待验证</x:v>
+        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3762,7 +3762,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。 validation/route-artifacts/</x:v>
+        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3932,7 +3932,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I12" s="86" t="str">
-        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。 validation/route-artifacts/</x:v>
+        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4048,7 +4048,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
-        <x:v>结构/数值/几何/可编辑性与真实PNG模型审查已运行；可访问性及完整QA未完成，模型可能误判。 实物：validation/generation-artifacts/</x:v>
+        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4077,7 +4077,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I17" s="86" t="str">
-        <x:v>单正文原生对象修订仅改变一个slide XML，ID/其他parts保持，复审/QA恢复；完整RevisionPlan/节点重跑待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4162,7 +4162,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。 validation/route-artifacts/</x:v>
+        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4191,7 +4191,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I21" s="86" t="str">
-        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。 validation/route-artifacts/</x:v>
+        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4247,7 +4247,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I23" s="86" t="str">
-        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。 validation/route-artifacts/</x:v>
+        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5221,9 +5221,11 @@
         <x:v>Schema + fixtures</x:v>
       </x:c>
       <x:c r="I11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="J11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="J11" s="86" t="str">
+        <x:v>当前三节点及来源角色/约束实际消费，完整来源格式与其余节点继续实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -6252,7 +6254,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J44" s="86" t="str">
-        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
+        <x:v>当前三节点及来源角色/约束实际消费，完整来源格式与其余节点继续实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -6284,7 +6286,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J45" s="86" t="str">
-        <x:v>当前DEC-001/五项能力契约已实际消费、落盘；其他节点/能力/完整探测继续，见validation/模式路由与能力登记.md</x:v>
+        <x:v>当前三节点及来源角色/约束实际消费，完整来源格式与其余节点继续实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -8471,7 +8473,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I36" s="86" t="str">
-        <x:v>DEC-001实际DecisionTrace与最终对象关联；其他39节点仍待完成，validation/route-runtime.json</x:v>
+        <x:v>前三节点完整决策轨迹已运行，其余节点及全对象关联待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8749,13 +8751,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>真实新请求10页PPTX/渲染/QA P0=0并经过DEC-001；其余39节点及全部原QA/AC条件待完成。</x:v>
+        <x:v>真实八页原生演示、渲染、已执行质量检查无最高优先级问题，经过前三节点；完整决策与质量验收仍未通过。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/route-artifacts/；validation/route-runtime.json</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>完整DEC/QA/全范围未完成</x:v>
+        <x:v>完整决策、质量与全范围验收未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9431,13 +9433,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>本次所有原生对象关联source/evidence/spec/call/DEC-001；完整决策链及全对象随机抽检未完成。</x:v>
+        <x:v>三节点轨迹与来源角色保留；最终对象已关联来源、证据、规格、调用及模式节点，全部决策对象关联和随机抽检待完成。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>validation/route-artifacts/；validation/route-runtime.json</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
-        <x:v>完整DEC/QA/全范围未完成</x:v>
+        <x:v>完整决策、质量与全范围验收未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="165" customHeight="1">
@@ -10182,7 +10184,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3afbab0059ba44e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dd5cc9aace546a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11371,7 +11373,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R500155d32ee94e74"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R497253afa64246a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11855,10 +11857,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O4" s="84" t="str">
-        <x:v>contracts/constraint-set.catalog.json</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P4" s="86" t="str">
-        <x:v>未验证：约束分类/冲突示例为草案；运行时检测未实现。</x:v>
+        <x:v>硬约束、偏好、默认值已由决策节点实际处理，冲突和输出缺口阻断，降级保留原因；原文规则有界，完整自然语言约束处理仍待实现。</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="72" customHeight="1">
@@ -14957,7 +14959,7 @@
         <x:v>八种模式与十个边界实际运行；输入、候选、规则、输出、约束、回退、轨迹及五项目对应齐备。39项核验和真实生成通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="71">
+    <x:row r="71" ht="195" customHeight="1">
       <x:c r="A71" s="83" t="str">
         <x:v>DEC-002</x:v>
       </x:c>
@@ -14996,12 +14998,16 @@
       </x:c>
       <x:c r="M71" s="84" t="str"/>
       <x:c r="N71" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O71" s="84" t="str"/>
-      <x:c r="P71" s="86" t="str"/>
-    </x:row>
-    <x:row r="72">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O71" s="84" t="str">
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
+      <x:c r="P71" s="86" t="str">
+        <x:v>硬约束、偏好与默认值实际归一化；同级冲突阻断，原输出要求保留。独立入口、候选、规则、轨迹和五项目对应齐备，八页偏好真实消费。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="195" customHeight="1">
       <x:c r="A72" s="83" t="str">
         <x:v>DEC-003</x:v>
       </x:c>
@@ -15040,10 +15046,14 @@
       </x:c>
       <x:c r="M72" s="84" t="str"/>
       <x:c r="N72" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O72" s="84" t="str"/>
-      <x:c r="P72" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O72" s="84" t="str">
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
+      <x:c r="P72" s="86" t="str">
+        <x:v>真实来源身份绑定六类角色，全量快照保留；模型与质量检查只用事实集合，风格测试数字未进入事实输入。正常及冲突样例、独立入口和五项目对应齐备。</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="83" t="str">
@@ -20035,10 +20045,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O186" s="84" t="str">
-        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P186" s="86" t="str">
-        <x:v>SourceBundle与文本/Markdown解析已实际运行；IN其他格式及原SYS E2E待完成。</x:v>
+        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="180" customHeight="1">
@@ -20127,10 +20137,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O188" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P188" s="86" t="str">
-        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。</x:v>
+        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="180" customHeight="1">
@@ -20395,10 +20405,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O194" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P194" s="86" t="str">
-        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。</x:v>
+        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="172.5" customHeight="1">
@@ -20579,10 +20589,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O198" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P198" s="86" t="str">
-        <x:v>结构/数值/几何/可编辑性与真实PNG模型审查已运行；可访问性及完整QA未完成，模型可能误判。</x:v>
+        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="172.5" customHeight="1">
@@ -20625,10 +20635,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O199" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P199" s="86" t="str">
-        <x:v>单正文原生对象修订仅改变一个slide XML，ID/其他parts保持，复审/QA恢复；完整RevisionPlan/节点重跑待完成。</x:v>
+        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="172.5" customHeight="1">
@@ -20759,10 +20769,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O202" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P202" s="86" t="str">
-        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。</x:v>
+        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="172.5" customHeight="1">
@@ -20805,10 +20815,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O203" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P203" s="86" t="str">
-        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。</x:v>
+        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -20893,10 +20903,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O205" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P205" s="86" t="str">
-        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。</x:v>
+        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -23627,10 +23637,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O270" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P270" s="86" t="str">
-        <x:v>DEC-001保存input/candidates/score/reason/selected/rules/output/duration/error；最终对象关联该节点，其余39节点待完成。</x:v>
+        <x:v>前三节点保存输入、候选、选择、规则、输出、时长及错误；完整节点及对象到全部决策关联待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -24051,10 +24061,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O280" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="P280" s="86" t="str">
-        <x:v>DEC-001八常规+十边界自动结果和真实链路已保留；DEC-002–040各3+1仍待完成。</x:v>
+        <x:v>前三节点各至少三个正常及一个边界样例已运行；其余三十七节点和完整回归范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -25299,7 +25309,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53c770606b394fab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc957011df36b4b9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25488,7 +25498,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>contracts/constraint-set.catalog.json（草案；运行时行为未实现）</x:v>
+        <x:v>硬约束、偏好、默认值已由决策节点实际处理，冲突和输出缺口阻断，降级保留原因；原文规则有界，完整自然语言约束处理仍待实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N4" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29637,9 +29647,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L100" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M100" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M100" s="84" t="str">
+        <x:v>硬约束、偏好与默认值实际归一化；同级冲突阻断，原输出要求保留。独立入口、候选、规则、轨迹和五项目对应齐备，八页偏好真实消费。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
       <x:c r="N100" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -29679,9 +29691,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L101" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M101" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M101" s="84" t="str">
+        <x:v>每节点至少三个正常与一个边界样例、独立入口、完整候选轨迹及真实生成通过；40项报告与五项目对应保留。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
       <x:c r="N101" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -29721,9 +29735,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L102" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M102" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M102" s="84" t="str">
+        <x:v>真实来源身份绑定六类角色，全量快照保留；模型与质量检查只用事实集合，风格测试数字未进入事实输入。正常及冲突样例、独立入口和五项目对应齐备。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
       <x:c r="N102" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -29763,9 +29779,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L103" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M103" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M103" s="84" t="str">
+        <x:v>每节点至少三个正常与一个边界样例、独立入口、完整候选轨迹及真实生成通过；40项报告与五项目对应保留。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+      </x:c>
       <x:c r="N103" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37768,7 +37786,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M295" s="84" t="str">
-        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N295" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37852,7 +37870,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M297" s="84" t="str">
-        <x:v>DEC-001已实际执行并保存候选/错误/轨迹；DEC-002–040、条件分支及节点级恢复仍待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N297" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38100,7 +38118,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M303" s="84" t="str">
-        <x:v>DAG绑定登记capability_id/implementation_id，实际检查输入与错配ID；完整后端预执行/缺口判定仍待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N303" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38268,7 +38286,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M307" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38310,7 +38328,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M308" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38434,7 +38452,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M311" s="84" t="str">
-        <x:v>CLI新增route独立节点并保存trace；完整CLI生命周期/bench/debug等范围仍待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38476,7 +38494,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M312" s="84" t="str">
-        <x:v>HTTP /route独立节点与/generate实际消费；完整jobs/取消/重试范围仍待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38558,7 +38576,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M314" s="84" t="str">
-        <x:v>DEC-001独立CLI/API已运行、trace落盘并经真实生成；任意节点/能力/layout/adapter/QARule调试范围待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N314" s="86" t="str">
         <x:v>本规划</x:v>
@@ -42672,7 +42690,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M415" s="84" t="str">
-        <x:v>DEC-001保存input/candidates/score/reason/selected/rules/output/duration/error；最终对象关联该节点，其余39节点待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>前三节点保存输入、候选、选择、规则、输出、时长及错误；完整节点及对象到全部决策关联待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N415" s="86" t="str">
         <x:v>本规划</x:v>
@@ -43074,7 +43092,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M425" s="84" t="str">
-        <x:v>DEC-001八常规+十边界自动结果和真实链路已保留；DEC-002–040各3+1仍待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>前三节点各至少三个正常及一个边界样例已运行；其余三十七节点和完整回归范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
       </x:c>
       <x:c r="N425" s="86" t="str">
         <x:v>本规划</x:v>
@@ -44256,7 +44274,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63c3dafb4c824449"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7624a873e04079"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44550,7 +44568,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0b5ba0ae6ef4981"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49934c361d304c43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45966,7 +45984,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38b395f31a214535"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54e3cd833a98479d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46388,7 +46406,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd49106f231b543fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd1d614fc5049e0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48124,9 +48142,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N3" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="N3" s="86" t="str">
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md；validation/context-project-map.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -48166,9 +48186,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N4" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="N4" s="86" t="str">
+        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md；validation/context-project-map.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -49737,7 +49759,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d0e676c9ae94f98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R578b2760aaee4efd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf43ed993661f4c0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R35d76cd4aa6041e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R390213e32017450c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R58bf9799526a4672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rabc66b1715354117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R104b6b0131414015"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5655e41526864c6e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R248ac9c649cb4445"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R08663a713354431a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R3c4b594f345143d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Rb025775e514845c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R8918d95363a842d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R505073de96c7480d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R601d1802e5924d4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R9f12769d80b34865"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rd316fe40c62045ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="Rb4ef271387d547fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R1b84e6dc7c834b95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R0baa09f4baeb4bfb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R46ec98d8c8e7403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R385e111859ee4e4a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R446a20a451d74076"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R227d9760ad264772"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Ra0d86e16b6df43fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6551a45c2487499a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1d6a36600520427a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R44fc8a3944a54fac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rcc15abfeee2b4240"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd2c61d0c82cf41de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8d658919870649a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R97200bcb113e4d7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra2b3263f0cae41ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R4e25cd8202ed45d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2a644c9ea8eb4a95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf19f48577fcf4c16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R689b2d550828422f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8936269274b34346"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra86b68937a714be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcda08eb46fdf47cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R374e8b8417d8457a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7349cb9fb7fe44e4"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69a9cb07a6db4d4c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R80ec429254104f5b"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22416b0182014e57"/>
 </x:worksheet>
 </file>
 
@@ -3903,7 +3903,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I11" s="86" t="str">
-        <x:v>新建子集SlideSpec含内容/几何/样式/来源/备注，实际writer消费；其他对象/绑定/模板待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3961,7 +3961,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I13" s="86" t="str">
-        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。 validation/route-artifacts/</x:v>
+        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -3990,7 +3990,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I14" s="86" t="str">
-        <x:v>真实10页原生新建/顺序执行；导入模板/master/layout/theme及已有deck修改待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4019,7 +4019,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I15" s="86" t="str">
-        <x:v>实际LibreOffice PDF/10 PNG含hash/version，F盘IPC挂载；live截图/缩略图待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4048,7 +4048,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
-        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -5872,7 +5872,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J32" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；完整 Schema 与运行时集成待后续任务。</x:v>
+        <x:v>七类原生候选、容量和槽位实际消费，完整对象契约范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -6030,7 +6030,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J37" s="86" t="str">
-        <x:v>内容/几何/样式/来源/备注实际消费，其他对象/模板绑定待完成；contracts/deck-execution.schema.json；validation/generation-artifacts/</x:v>
+        <x:v>七类原生候选、容量和槽位实际消费，完整对象契约范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -8751,13 +8751,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>真实八页原生演示、渲染、已执行质量检查无最高优先级问题，经过前三节点；完整决策与质量验收仍未通过。</x:v>
+        <x:v>真实十页原生PPTX、版式编译及模型复审，当前执行检查P0为零；完整决策链与全质量验收未通过。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>完整决策、质量与全范围验收未完成</x:v>
+        <x:v>其余节点、全对象/输入/质量与完整验收继续。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -10184,7 +10184,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7dd5cc9aace546a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2662c1a12094655"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10233,7 +10233,7 @@
         <x:v>备注</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
+    <x:row r="2" ht="195" customHeight="1">
       <x:c r="A2" s="79" t="str">
         <x:v>S00</x:v>
       </x:c>
@@ -10251,12 +10251,16 @@
         <x:v>GOV / SYS-001~002 / SEC</x:v>
       </x:c>
       <x:c r="G2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H2" s="80" t="str"/>
-      <x:c r="I2" s="82" t="str"/>
-    </x:row>
-    <x:row r="3">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H2" s="80" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I2" s="82" t="str">
+        <x:v>CLI/HTTP接收真实任务、原文与来源身份；全输入格式及统一生命周期待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="195" customHeight="1">
       <x:c r="A3" s="83" t="str">
         <x:v>S01</x:v>
       </x:c>
@@ -10276,12 +10280,16 @@
         <x:v>GOV / SYS-001~002 / SEC</x:v>
       </x:c>
       <x:c r="G3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H3" s="84" t="str"/>
-      <x:c r="I3" s="86" t="str"/>
-    </x:row>
-    <x:row r="4">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H3" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I3" s="86" t="str">
+        <x:v>本地平台、锁定依赖、字体、渲染与实际模型列表已探测；Office、MCP及全部后端探测待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="195" customHeight="1">
       <x:c r="A4" s="83" t="str">
         <x:v>S02</x:v>
       </x:c>
@@ -10304,13 +10312,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>contracts/task-route.catalog.json</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
-        <x:v>已形成 DEC-001 路由契约草案；尚无运行时路由实现。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
+        <x:v>八模式判定及冲突保护已运行，完整后续模式执行仍待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="195" customHeight="1">
       <x:c r="A5" s="83" t="str">
         <x:v>S03</x:v>
       </x:c>
@@ -10330,12 +10338,16 @@
         <x:v>GOV / SYS-001~002 / SEC</x:v>
       </x:c>
       <x:c r="G5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H5" s="84" t="str"/>
-      <x:c r="I5" s="86" t="str"/>
-    </x:row>
-    <x:row r="6">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H5" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>实际校验JSON、UTF-8、容量、身份与约束；全部格式、密码、宏及外链风险校验待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="195" customHeight="1">
       <x:c r="A6" s="83" t="str">
         <x:v>S04</x:v>
       </x:c>
@@ -10355,12 +10367,16 @@
         <x:v>IN / CNT / SEC</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H6" s="84" t="str"/>
-      <x:c r="I6" s="86" t="str"/>
-    </x:row>
-    <x:row r="7">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H6" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I6" s="86" t="str">
+        <x:v>文本、Markdown真实来源及角色加载；其他原始格式待实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="195" customHeight="1">
       <x:c r="A7" s="83" t="str">
         <x:v>S05</x:v>
       </x:c>
@@ -10380,12 +10396,16 @@
         <x:v>IN / CNT / SEC</x:v>
       </x:c>
       <x:c r="G7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H7" s="84" t="str"/>
-      <x:c r="I7" s="86" t="str"/>
-    </x:row>
-    <x:row r="8">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H7" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="str">
+        <x:v>实际保存文本块、表格、证据和原文锚点；其他格式图片/图形解析待实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="195" customHeight="1">
       <x:c r="A8" s="83" t="str">
         <x:v>S06</x:v>
       </x:c>
@@ -10405,12 +10425,16 @@
         <x:v>IN / CNT / SEC</x:v>
       </x:c>
       <x:c r="G8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H8" s="84" t="str"/>
-      <x:c r="I8" s="86" t="str"/>
-    </x:row>
-    <x:row r="9">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H8" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I8" s="86" t="str">
+        <x:v>来源哈希、版本、引用与重复候选保留；语义冲突及优先级决策待实现。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="195" customHeight="1">
       <x:c r="A9" s="83" t="str">
         <x:v>S07</x:v>
       </x:c>
@@ -10430,12 +10454,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H9" s="84" t="str"/>
-      <x:c r="I9" s="86" t="str"/>
-    </x:row>
-    <x:row r="10">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H9" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I9" s="86" t="str">
+        <x:v>约束归一化实际运行；完整受众、场景、语气、品牌推断与执行待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="195" customHeight="1">
       <x:c r="A10" s="83" t="str">
         <x:v>S08</x:v>
       </x:c>
@@ -10455,12 +10483,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H10" s="84" t="str"/>
-      <x:c r="I10" s="86" t="str"/>
-    </x:row>
-    <x:row r="11">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H10" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I10" s="86" t="str">
+        <x:v>事实集合及数值成员检查已运行；完整事实、禁止臆造及假设决策待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="195" customHeight="1">
       <x:c r="A11" s="83" t="str">
         <x:v>S09</x:v>
       </x:c>
@@ -10480,10 +10512,14 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H11" s="84" t="str"/>
-      <x:c r="I11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H11" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I11" s="86" t="str">
+        <x:v>真实模型输出整套核心信息及逐页证据引用；独立论点决策及完整证据图待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -10510,7 +10546,7 @@
       <x:c r="H12" s="84" t="str"/>
       <x:c r="I12" s="86" t="str"/>
     </x:row>
-    <x:row r="13">
+    <x:row r="13" ht="195" customHeight="1">
       <x:c r="A13" s="83" t="str">
         <x:v>S11</x:v>
       </x:c>
@@ -10530,12 +10566,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H13" s="84" t="str"/>
-      <x:c r="I13" s="86" t="str"/>
-    </x:row>
-    <x:row r="14">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H13" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I13" s="86" t="str">
+        <x:v>真实模型输出故事线和页面顺序；独立叙事候选与完整章节结构待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="195" customHeight="1">
       <x:c r="A14" s="83" t="str">
         <x:v>S12</x:v>
       </x:c>
@@ -10555,12 +10595,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H14" s="84" t="str"/>
-      <x:c r="I14" s="86" t="str"/>
-    </x:row>
-    <x:row r="15">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H14" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I14" s="86" t="str">
+        <x:v>真实模型输出页面标题序列；章节/子章节及正式大纲对象待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="195" customHeight="1">
       <x:c r="A15" s="83" t="str">
         <x:v>S13</x:v>
       </x:c>
@@ -10580,12 +10624,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H15" s="84" t="str"/>
-      <x:c r="I15" s="86" t="str"/>
-    </x:row>
-    <x:row r="16">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H15" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I15" s="86" t="str">
+        <x:v>十页硬预算、八页偏好实际消费；时长与章节分配预算待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="195" customHeight="1">
       <x:c r="A16" s="83" t="str">
         <x:v>S14</x:v>
       </x:c>
@@ -10605,12 +10653,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H16" s="84" t="str"/>
-      <x:c r="I16" s="86" t="str"/>
-    </x:row>
-    <x:row r="17">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H16" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I16" s="86" t="str">
+        <x:v>真实模型按页组织内容并检查总页数；完整语义拆合及跨页衔接待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="195" customHeight="1">
       <x:c r="A17" s="83" t="str">
         <x:v>S15</x:v>
       </x:c>
@@ -10630,12 +10682,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H17" s="84" t="str"/>
-      <x:c r="I17" s="86" t="str"/>
-    </x:row>
-    <x:row r="18">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H17" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I17" s="86" t="str">
+        <x:v>每页实际保存目标及核心信息；独立页面目标决策与完整受众推导待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="195" customHeight="1">
       <x:c r="A18" s="83" t="str">
         <x:v>S16</x:v>
       </x:c>
@@ -10655,12 +10711,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H18" s="84" t="str"/>
-      <x:c r="I18" s="86" t="str"/>
-    </x:row>
-    <x:row r="19">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H18" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I18" s="86" t="str">
+        <x:v>当前文本、表格、图表及开场/结尾版式实际运行；完整类型决策待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="195" customHeight="1">
       <x:c r="A19" s="83" t="str">
         <x:v>S17</x:v>
       </x:c>
@@ -10680,12 +10740,16 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G19" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H19" s="84" t="str"/>
-      <x:c r="I19" s="86" t="str"/>
-    </x:row>
-    <x:row r="20">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H19" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I19" s="86" t="str">
+        <x:v>实际测量文本/表格槽位，容量不足明确失败；语义改写、拆合及图片预算待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="195" customHeight="1">
       <x:c r="A20" s="83" t="str">
         <x:v>S18</x:v>
       </x:c>
@@ -10705,10 +10769,14 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G20" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H20" s="84" t="str"/>
-      <x:c r="I20" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H20" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I20" s="86" t="str">
+        <x:v>原生文本面板、表格、分类图表实际写入；完整图文、流程、时间线与关系表达待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="83" t="str">
@@ -10735,7 +10803,7 @@
       <x:c r="H21" s="84" t="str"/>
       <x:c r="I21" s="86" t="str"/>
     </x:row>
-    <x:row r="22">
+    <x:row r="22" ht="195" customHeight="1">
       <x:c r="A22" s="83" t="str">
         <x:v>S20</x:v>
       </x:c>
@@ -10755,10 +10823,14 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G22" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H22" s="84" t="str"/>
-      <x:c r="I22" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H22" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I22" s="86" t="str">
+        <x:v>显式颜色与已安装字体配置已消费；模板、母版、主题和参考图解析待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -10785,7 +10857,7 @@
       <x:c r="H23" s="84" t="str"/>
       <x:c r="I23" s="86" t="str"/>
     </x:row>
-    <x:row r="24">
+    <x:row r="24" ht="195" customHeight="1">
       <x:c r="A24" s="83" t="str">
         <x:v>S22</x:v>
       </x:c>
@@ -10805,12 +10877,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G24" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H24" s="84" t="str"/>
-      <x:c r="I24" s="86" t="str"/>
-    </x:row>
-    <x:row r="25">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H24" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I24" s="86" t="str">
+        <x:v>七类原生候选按槽位与实测容量检索；完整素材及模板条件待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="195" customHeight="1">
       <x:c r="A25" s="83" t="str">
         <x:v>S23</x:v>
       </x:c>
@@ -10830,12 +10906,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G25" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H25" s="84" t="str"/>
-      <x:c r="I25" s="86" t="str"/>
-    </x:row>
-    <x:row r="26">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H25" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I25" s="86" t="str">
+        <x:v>当前容量、页面层级与相邻变化实际评分；完整语义、品牌、素材比例及多后端待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="195" customHeight="1">
       <x:c r="A26" s="83" t="str">
         <x:v>S24</x:v>
       </x:c>
@@ -10855,12 +10935,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G26" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H26" s="84" t="str"/>
-      <x:c r="I26" s="86" t="str"/>
-    </x:row>
-    <x:row r="27">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H26" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I26" s="86" t="str">
+        <x:v>当前标题、正文、数据及备注映射稳定槽位；图片和完整模板占位符待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="195" customHeight="1">
       <x:c r="A27" s="83" t="str">
         <x:v>S25</x:v>
       </x:c>
@@ -10880,12 +10964,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G27" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H27" s="84" t="str"/>
-      <x:c r="I27" s="86" t="str"/>
-    </x:row>
-    <x:row r="28">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H27" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I27" s="86" t="str">
+        <x:v>实际几何槽位、边距和非重叠检查；连接线、旋转、裁切等待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="195" customHeight="1">
       <x:c r="A28" s="83" t="str">
         <x:v>S26</x:v>
       </x:c>
@@ -10905,12 +10993,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G28" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H28" s="84" t="str"/>
-      <x:c r="I28" s="86" t="str"/>
-    </x:row>
-    <x:row r="29">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H28" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I28" s="86" t="str">
+        <x:v>实际中文字体、字号、颜色、填充和描边；阴影、圆角、图片处理等待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="195" customHeight="1">
       <x:c r="A29" s="83" t="str">
         <x:v>S27</x:v>
       </x:c>
@@ -10930,12 +11022,16 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G29" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H29" s="84" t="str"/>
-      <x:c r="I29" s="86" t="str"/>
-    </x:row>
-    <x:row r="30">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H29" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I29" s="86" t="str">
+        <x:v>原生备注与证据已写入；动画、过渡、媒体和动作待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="195" customHeight="1">
       <x:c r="A30" s="83" t="str">
         <x:v>S28</x:v>
       </x:c>
@@ -10955,12 +11051,16 @@
         <x:v>DEC-038 / PPT / ADP / SYS</x:v>
       </x:c>
       <x:c r="G30" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H30" s="84" t="str"/>
-      <x:c r="I30" s="86" t="str"/>
-    </x:row>
-    <x:row r="31">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H30" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I30" s="86" t="str">
+        <x:v>统一页面规格经真实编译/写入消费；完整素材、模板及绑定待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="195" customHeight="1">
       <x:c r="A31" s="83" t="str">
         <x:v>S29</x:v>
       </x:c>
@@ -10980,12 +11080,16 @@
         <x:v>DEC-038 / PPT / ADP / SYS</x:v>
       </x:c>
       <x:c r="G31" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H31" s="84" t="str"/>
-      <x:c r="I31" s="86" t="str"/>
-    </x:row>
-    <x:row r="32">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H31" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I31" s="86" t="str">
+        <x:v>实际schema、能力绑定、字体、数据和容量检查；完整路径/权限/模板与后端缺口待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="195" customHeight="1">
       <x:c r="A32" s="83" t="str">
         <x:v>S30</x:v>
       </x:c>
@@ -11005,12 +11109,16 @@
         <x:v>DEC-038 / PPT / ADP / SYS</x:v>
       </x:c>
       <x:c r="G32" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H32" s="84" t="str"/>
-      <x:c r="I32" s="86" t="str"/>
-    </x:row>
-    <x:row r="33">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H32" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I32" s="86" t="str">
+        <x:v>当前PP-05登记实现实际选择；全九路线按保真/任务能力动态选择待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="195" customHeight="1">
       <x:c r="A33" s="83" t="str">
         <x:v>S31</x:v>
       </x:c>
@@ -11030,12 +11138,16 @@
         <x:v>DEC-038 / PPT / ADP / SYS</x:v>
       </x:c>
       <x:c r="G33" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H33" s="84" t="str"/>
-      <x:c r="I33" s="86" t="str"/>
-    </x:row>
-    <x:row r="34">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H33" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I33" s="86" t="str">
+        <x:v>实际能力调用DAG与稳定对象/实现ID；完整对象及复杂依赖待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="195" customHeight="1">
       <x:c r="A34" s="83" t="str">
         <x:v>S32</x:v>
       </x:c>
@@ -11055,12 +11167,16 @@
         <x:v>DEC-038 / PPT / ADP / SYS</x:v>
       </x:c>
       <x:c r="G34" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H34" s="84" t="str"/>
-      <x:c r="I34" s="86" t="str"/>
-    </x:row>
-    <x:row r="35">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H34" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I34" s="86" t="str">
+        <x:v>真实原生PPTX与单文本修订已运行；已有文件保真编辑和全部对象待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="195" customHeight="1">
       <x:c r="A35" s="83" t="str">
         <x:v>S33</x:v>
       </x:c>
@@ -11080,12 +11196,16 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H35" s="84" t="str"/>
-      <x:c r="I35" s="86" t="str"/>
-    </x:row>
-    <x:row r="36">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H35" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I35" s="86" t="str">
+        <x:v>真实PDF与逐页PNG，版本/hash已保存；live截图和完整缩略图范围待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="195" customHeight="1">
       <x:c r="A36" s="83" t="str">
         <x:v>S34</x:v>
       </x:c>
@@ -11105,12 +11225,16 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G36" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H36" s="84" t="str"/>
-      <x:c r="I36" s="86" t="str"/>
-    </x:row>
-    <x:row r="37">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H36" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I36" s="86" t="str">
+        <x:v>实际ZIP/XML、边界、对象映射与PDF字词检查；完整关系与结构规则待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="195" customHeight="1">
       <x:c r="A37" s="83" t="str">
         <x:v>S35</x:v>
       </x:c>
@@ -11130,12 +11254,16 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H37" s="84" t="str"/>
-      <x:c r="I37" s="86" t="str"/>
-    </x:row>
-    <x:row r="38">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H37" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I37" s="86" t="str">
+        <x:v>真实渲染页经模型视觉审查；全部确定性视觉规则和验收阈值待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="195" customHeight="1">
       <x:c r="A38" s="83" t="str">
         <x:v>S36</x:v>
       </x:c>
@@ -11155,12 +11283,16 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H38" s="84" t="str"/>
-      <x:c r="I38" s="86" t="str"/>
-    </x:row>
-    <x:row r="39">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H38" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I38" s="86" t="str">
+        <x:v>实际数值/引用检查与模型事实审查；完整语义真值及图像对应待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="195" customHeight="1">
       <x:c r="A39" s="83" t="str">
         <x:v>S37</x:v>
       </x:c>
@@ -11180,10 +11312,14 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H39" s="84" t="str"/>
-      <x:c r="I39" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H39" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I39" s="86" t="str">
+        <x:v>原生文本/表格/图表和嵌入数据已检查；导入往返、母版/主题保真待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -11210,7 +11346,7 @@
       <x:c r="H40" s="84" t="str"/>
       <x:c r="I40" s="86" t="str"/>
     </x:row>
-    <x:row r="41">
+    <x:row r="41" ht="195" customHeight="1">
       <x:c r="A41" s="83" t="str">
         <x:v>S39</x:v>
       </x:c>
@@ -11230,12 +11366,16 @@
         <x:v>DEC-039~040 / REV / QA</x:v>
       </x:c>
       <x:c r="G41" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H41" s="84" t="str"/>
-      <x:c r="I41" s="86" t="str"/>
-    </x:row>
-    <x:row r="42">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H41" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I41" s="86" t="str">
+        <x:v>数值引用问题可触发受限修正；完整质量问题到任意节点修订计划待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="195" customHeight="1">
       <x:c r="A42" s="83" t="str">
         <x:v>S40</x:v>
       </x:c>
@@ -11255,12 +11395,16 @@
         <x:v>DEC-039~040 / REV / QA</x:v>
       </x:c>
       <x:c r="G42" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H42" s="84" t="str"/>
-      <x:c r="I42" s="86" t="str"/>
-    </x:row>
-    <x:row r="43">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H42" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I42" s="86" t="str">
+        <x:v>既有单文本修订保留其他parts及实体ID，恢复复用模型；任意节点/对象范围待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="195" customHeight="1">
       <x:c r="A43" s="83" t="str">
         <x:v>S41</x:v>
       </x:c>
@@ -11280,12 +11424,16 @@
         <x:v>DEC-039~040 / REV / QA</x:v>
       </x:c>
       <x:c r="G43" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H43" s="84" t="str"/>
-      <x:c r="I43" s="86" t="str"/>
-    </x:row>
-    <x:row r="44">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H43" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I43" s="86" t="str">
+        <x:v>实际报告草稿及未通过验收状态；完整终止/重试策略待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="195" customHeight="1">
       <x:c r="A44" s="83" t="str">
         <x:v>S42</x:v>
       </x:c>
@@ -11305,12 +11453,16 @@
         <x:v>SYS / OBS / OPS / TST</x:v>
       </x:c>
       <x:c r="G44" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H44" s="84" t="str"/>
-      <x:c r="I44" s="86" t="str"/>
-    </x:row>
-    <x:row r="45">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H44" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I44" s="86" t="str">
+        <x:v>实际导出PPTX/PDF/PNG与trace/QA；完整导出配置和最终验收门控待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="195" customHeight="1">
       <x:c r="A45" s="83" t="str">
         <x:v>S43</x:v>
       </x:c>
@@ -11330,12 +11482,16 @@
         <x:v>SYS / OBS / OPS / TST</x:v>
       </x:c>
       <x:c r="G45" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H45" s="84" t="str"/>
-      <x:c r="I45" s="86" t="str"/>
-    </x:row>
-    <x:row r="46">
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H45" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I45" s="86" t="str">
+        <x:v>来源、模型、依赖版本和既有版权记录已保留；全部资产/模板许可及转换合并清单待完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="195" customHeight="1">
       <x:c r="A46" s="87" t="str">
         <x:v>S44</x:v>
       </x:c>
@@ -11355,10 +11511,14 @@
         <x:v>SYS / OBS / OPS / TST</x:v>
       </x:c>
       <x:c r="G46" s="88" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H46" s="88" t="str"/>
-      <x:c r="I46" s="90" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H46" s="88" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+      </x:c>
+      <x:c r="I46" s="90" t="str">
+        <x:v>既有原稿曾经PowerPoint实际打开；本版、修复提示和全部可编辑交付验收待完成。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G2:G46">
@@ -11373,7 +11533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R497253afa64246a1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65f9e2c105b8462e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16238,10 +16398,14 @@
       </x:c>
       <x:c r="M99" s="84" t="str"/>
       <x:c r="N99" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O99" s="84" t="str"/>
-      <x:c r="P99" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O99" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
+      <x:c r="P99" s="86" t="str">
+        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="83" t="str">
@@ -16282,10 +16446,14 @@
       </x:c>
       <x:c r="M100" s="84" t="str"/>
       <x:c r="N100" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O100" s="84" t="str"/>
-      <x:c r="P100" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O100" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
+      <x:c r="P100" s="86" t="str">
+        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="83" t="str">
@@ -16370,10 +16538,14 @@
       </x:c>
       <x:c r="M102" s="84" t="str"/>
       <x:c r="N102" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O102" s="84" t="str"/>
-      <x:c r="P102" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O102" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
+      <x:c r="P102" s="86" t="str">
+        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="83" t="str">
@@ -16414,10 +16586,14 @@
       </x:c>
       <x:c r="M103" s="84" t="str"/>
       <x:c r="N103" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O103" s="84" t="str"/>
-      <x:c r="P103" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O103" s="84" t="str">
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
+      <x:c r="P103" s="86" t="str">
+        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="83" t="str">
@@ -20359,10 +20535,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O193" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="P193" s="86" t="str">
-        <x:v>新建子集SlideSpec含内容/几何/样式/来源/备注，实际writer消费；其他对象/绑定/模板待完成。</x:v>
+        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="172.5" customHeight="1">
@@ -20451,10 +20627,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O195" s="84" t="str">
-        <x:v>validation/route-runtime.json；validation/route-artifacts/；validation/模式路由与能力登记.md</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="P195" s="86" t="str">
-        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。</x:v>
+        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="172.5" customHeight="1">
@@ -20497,10 +20673,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O196" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="P196" s="86" t="str">
-        <x:v>真实10页原生新建/顺序执行；导入模板/master/layout/theme及已有deck修改待完成。</x:v>
+        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="172.5" customHeight="1">
@@ -20543,10 +20719,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O197" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="P197" s="86" t="str">
-        <x:v>实际LibreOffice PDF/10 PNG含hash/version，F盘IPC挂载；live截图/缩略图待完成。</x:v>
+        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="172.5" customHeight="1">
@@ -20589,10 +20765,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O198" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="P198" s="86" t="str">
-        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。</x:v>
+        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="172.5" customHeight="1">
@@ -25309,7 +25485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc957011df36b4b9c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53b11fd1dae84f89"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32007,9 +32183,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L156" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M156" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M156" s="84" t="str">
+        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N156" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32049,9 +32227,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L157" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M157" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M157" s="84" t="str">
+        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N157" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32091,9 +32271,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L158" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M158" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M158" s="84" t="str">
+        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N158" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32133,9 +32315,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L159" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M159" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M159" s="84" t="str">
+        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N159" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32259,9 +32443,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L162" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M162" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M162" s="84" t="str">
+        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N162" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32301,9 +32487,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L163" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M163" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M163" s="84" t="str">
+        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N163" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32343,9 +32531,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L164" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M164" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M164" s="84" t="str">
+        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N164" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32385,9 +32575,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L165" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M165" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M165" s="84" t="str">
+        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
       <x:c r="N165" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38076,7 +38268,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M302" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="N302" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38160,7 +38352,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M304" s="84" t="str">
-        <x:v>五项登记能力实际写入并核对输入/输出，真实ObjectMap/调用；完整对象及失败恢复范围待完成。 证据：validation/route-runtime.json</x:v>
+        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="N304" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38202,7 +38394,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M305" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="N305" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38244,7 +38436,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M306" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="N306" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38286,7 +38478,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M307" s="84" t="str">
-        <x:v>模型事实输入和质量检查使用已判定事实集合，实际八页渲染复审；完整视觉、事实、结构规则仍待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
       </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
@@ -44274,7 +44466,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e7624a873e04079"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700ddc6b9c444ee3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44568,7 +44760,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49934c361d304c43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64137ef55bf14965"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45984,7 +46176,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54e3cd833a98479d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d11160023704024"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46406,7 +46598,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fd1d614fc5049e0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfedf53cf7bb444ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49322,9 +49514,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M31" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N31" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N31" s="86" t="str">
+        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="83" t="str">
@@ -49364,9 +49558,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M32" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N32" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N32" s="86" t="str">
+        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="83" t="str">
@@ -49448,9 +49644,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M34" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N34" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N34" s="86" t="str">
+        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="83" t="str">
@@ -49490,9 +49688,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N35" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N35" s="86" t="str">
+        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="83" t="str">
@@ -49759,7 +49959,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R578b2760aaee4efd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f8a8772180442d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R385e111859ee4e4a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R446a20a451d74076"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R227d9760ad264772"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Ra0d86e16b6df43fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R6551a45c2487499a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R1d6a36600520427a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R44fc8a3944a54fac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rcc15abfeee2b4240"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rd2c61d0c82cf41de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R8d658919870649a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R97200bcb113e4d7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Ra2b3263f0cae41ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R4e25cd8202ed45d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R2a644c9ea8eb4a95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rf19f48577fcf4c16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R689b2d550828422f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8936269274b34346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Ra86b68937a714be1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rcda08eb46fdf47cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R374e8b8417d8457a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc8e66eec37ef4805"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4b21d75ec5154dcf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra20f952c99a34ded"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9a19bf8c33264fa1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R748eb9e114854d84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc3944ef35d904094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5bf1837496c547eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R56eb07a507ef46c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5f5d42bdabb74f90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1a8941cb50774693"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re6f32de22c1948b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd491b2a563e0476c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R52b16306e6c8421c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rab04d5b0f2be4539"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R08e85b9ec67241d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ree473a81ac0c4919"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R147feee1888d4f57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R452e0903e6e644bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd376adbec0a64070"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rae959a1925ff4d18"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69a9cb07a6db4d4c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R63e99e5c80c84e6d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1468,11 +1468,11 @@
       </x:c>
       <x:c r="E9" s="84" t="n">
         <x:f>COUNTIFS('需求主表'!$B$2:$B$1000,A9,'需求主表'!$N$2:$N$1000,"已完成")</x:f>
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F9" s="85" t="n">
         <x:f>IF(B9=0,0,E9/B9)</x:f>
-        <x:v>0.075</x:v>
+        <x:v>0.125</x:v>
       </x:c>
       <x:c r="G9" s="84" t="str">
         <x:v>域内所有 requirement 均需有输入/规则/输出/验收。</x:v>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22416b0182014e57"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f160e2bd144801"/>
 </x:worksheet>
 </file>
 
@@ -3762,7 +3762,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4048,7 +4048,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
-        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4077,7 +4077,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I17" s="86" t="str">
-        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4162,7 +4162,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4191,7 +4191,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I21" s="86" t="str">
-        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4247,7 +4247,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I23" s="86" t="str">
-        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5096,7 +5096,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J7" s="86" t="str">
-        <x:v>contracts/source-evidence.schema.json；src/yoloongppt/evidence.py；validation/source-runtime.json；文本快照及原生块已存储，confidence为null，其他格式与完整E2E待接入。</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -5128,7 +5128,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J8" s="86" t="str">
-        <x:v>contracts/evidence-conflict.*.json；DEC-004/检测运行时未完成。</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -5160,7 +5160,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J9" s="86" t="str">
-        <x:v>TASK-CNT-001 草案见 contracts/fact-constraint-set.schema.json、catalog.json、fixtures.json；事实抽取/改写校验器待实现。</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -5192,7 +5192,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J10" s="86" t="str">
-        <x:v>GOV-007 ID/引用约定见 contracts/object-id.catalog.json；TASK-CNT-004 草案与六个 fixture 见 contracts/assumption.*.json；运行时集成/DEC-005 待后续任务。</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -6254,7 +6254,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J44" s="86" t="str">
-        <x:v>当前三节点及来源角色/约束实际消费，完整来源格式与其余节点继续实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -6286,7 +6286,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="J45" s="86" t="str">
-        <x:v>当前三节点及来源角色/约束实际消费，完整来源格式与其余节点继续实现。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点实际消费原对象及来源锚点；冲突、已选值、稳定假设与边界保留，完整格式/节点/语义范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -8473,7 +8473,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I36" s="86" t="str">
-        <x:v>前三节点完整决策轨迹已运行，其余节点及全对象关联待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点完整轨迹已消费，全节点和全部对象关联待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -8751,13 +8751,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>真实十页原生PPTX、版式编译及模型复审，当前执行检查P0为零；完整决策链与全质量验收未通过。</x:v>
+        <x:v>前五节点真实生成/已选事实单对象修订，已执行P0=0；完整DEC/对象/QA/系统验收未满足。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>其余节点、全对象/输入/质量与完整验收继续。</x:v>
+        <x:v>系统原验收全部条件未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9433,13 +9433,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>三节点轨迹与来源角色保留；最终对象已关联来源、证据、规格、调用及模式节点，全部决策对象关联和随机抽检待完成。</x:v>
+        <x:v>前五节点真实生成/已选事实单对象修订，已执行P0=0；完整DEC/对象/QA/系统验收未满足。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
-        <x:v>完整决策、质量与全范围验收未完成</x:v>
+        <x:v>系统原验收全部条件未完成</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="165" customHeight="1">
@@ -10184,7 +10184,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2662c1a12094655"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65a24eb44ca4477c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10428,7 +10428,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>来源ID/哈希、用户优先级及冲突候选真实执行，未决阻断；全格式及完整语义冲突待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="I8" s="86" t="str">
         <x:v>来源哈希、版本、引用与重复候选保留；语义冲突及优先级决策待实现。</x:v>
@@ -10486,7 +10486,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>真实FactConstraintSet、显式假设/精确推算/占位/询问及可引用边界运行；自动事实抽取完整性及全格式待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="I10" s="86" t="str">
         <x:v>事实集合及数值成员检查已运行；完整事实、禁止臆造及假设决策待完成。</x:v>
@@ -11286,7 +11286,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H38" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>实际已选值/假设可见性/否决值/数值与备注检查，独立真实视觉事实复审；完整语义真值及全图像对应待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="I38" s="86" t="str">
         <x:v>实际数值/引用检查与模型事实审查；完整语义真值及图像对应待完成。</x:v>
@@ -11369,7 +11369,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H41" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>真实失败断点恢复事实解释及内容规划，新主模型/复审；单文本修改保持已选事实和单part范围，完整修订计划待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="I41" s="86" t="str">
         <x:v>数值引用问题可触发受限修正；完整质量问题到任意节点修订计划待完成。</x:v>
@@ -11533,7 +11533,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65f9e2c105b8462e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d38340e57994a24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11832,7 +11832,7 @@
     <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="12" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="12" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="52.5" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -14329,10 +14329,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O53" s="84" t="str">
-        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P53" s="86" t="str">
-        <x:v>多源ID/哈希重复候选保留；优先级DEC-004及语义冲突检测未执行。</x:v>
+        <x:v>真实多源ID/哈希去重候选及来源优先级/冲突规则实际执行，完整原文保留。全输入格式及完整语义冲突范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="180" customHeight="1">
@@ -14467,10 +14467,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O56" s="84" t="str">
-        <x:v>contracts/fact-constraint-set.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-001）</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P56" s="86" t="str">
-        <x:v>JSON/refs/evidence 锚点关联静态核对通过；未运行引擎或 AC。</x:v>
+        <x:v>真实模型解释逐字锚定数值/范围，原事实约束实际消费；保留主体/动词上下文，拒绝臆造范围。全部格式、语义抽取完整性及全部事实改写验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -14559,10 +14559,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O58" s="84" t="str">
-        <x:v>contracts/evidence-conflict.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-003）</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P58" s="86" t="str">
-        <x:v>静态核对通过；运行时与AC未执行。</x:v>
+        <x:v>8%/9%真实冲突全部保留；明确优先级选8%，无策略阻断，生成与修订不采用9%。全格式语义冲突/合并与系统验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -14605,10 +14605,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O59" s="84" t="str">
-        <x:v>contracts/assumption.schema.json、catalog.json、fixtures.json；contracts/evidence-conflict.fixtures.json；PROJECT_PLAN.md（TASK-CNT-004）</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P59" s="86" t="str">
-        <x:v>静态核对通过（6 个 fixture）；未运行 JSON Schema 实例验证器、运行时或 AC。</x:v>
+        <x:v>假设/精确推算/占位/询问/失败实际执行并注册；生成及QA消费假设引用和可见标记。完整自动缺失识别及全链路验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -15215,7 +15215,7 @@
         <x:v>真实来源身份绑定六类角色，全量快照保留；模型与质量检查只用事实集合，风格测试数字未进入事实输入。正常及冲突样例、独立入口和五项目对应齐备。</x:v>
       </x:c>
     </x:row>
-    <x:row r="73">
+    <x:row r="73" ht="247.5" customHeight="1">
       <x:c r="A73" s="83" t="str">
         <x:v>DEC-004</x:v>
       </x:c>
@@ -15254,12 +15254,16 @@
       </x:c>
       <x:c r="M73" s="84" t="str"/>
       <x:c r="N73" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O73" s="84" t="str"/>
-      <x:c r="P73" s="86" t="str"/>
-    </x:row>
-    <x:row r="74">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O73" s="84" t="str">
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
+      <x:c r="P73" s="86" t="str">
+        <x:v>实际SourceEvidence逐来源校验后生成候选；用户选定或来源优先级决定冲突，无唯一选择时unresolved并阻断。独立CLI/API、规则/轨迹、三正常及边界、五项目固定源码对应齐备；真实生成和修订消费已选值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="247.5" customHeight="1">
       <x:c r="A74" s="83" t="str">
         <x:v>DEC-005</x:v>
       </x:c>
@@ -15298,10 +15302,14 @@
       </x:c>
       <x:c r="M74" s="84" t="str"/>
       <x:c r="N74" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O74" s="84" t="str"/>
-      <x:c r="P74" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="O74" s="84" t="str">
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
+      <x:c r="P74" s="86" t="str">
+        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="83" t="str">
@@ -20313,10 +20321,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O188" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P188" s="86" t="str">
-        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。</x:v>
+        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="180" customHeight="1">
@@ -20765,10 +20773,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O198" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P198" s="86" t="str">
-        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。</x:v>
+        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="172.5" customHeight="1">
@@ -20811,10 +20819,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O199" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P199" s="86" t="str">
-        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。</x:v>
+        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="172.5" customHeight="1">
@@ -20945,10 +20953,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O202" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P202" s="86" t="str">
-        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。</x:v>
+        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="172.5" customHeight="1">
@@ -20991,10 +20999,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O203" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P203" s="86" t="str">
-        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。</x:v>
+        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -21079,10 +21087,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O205" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P205" s="86" t="str">
-        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。</x:v>
+        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -23813,10 +23821,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O270" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P270" s="86" t="str">
-        <x:v>前三节点保存输入、候选、选择、规则、输出、时长及错误；完整节点及对象到全部决策关联待完成。</x:v>
+        <x:v>前五节点保存候选/选择/原来源/约束/hash/输出/时长/错误；完整节点与全部对象关联待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="271">
@@ -24237,10 +24245,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O280" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="P280" s="86" t="str">
-        <x:v>前三节点各至少三个正常及一个边界样例已运行；其余三十七节点和完整回归范围待完成。</x:v>
+        <x:v>前五节点正常/边界及真实链路已执行，事实工作包35节点检查+16实物检查；其余35节点及完整回归范围待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="281">
@@ -25485,7 +25493,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R53b11fd1dae84f89"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19d4af5497aa4a43"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29022,7 +29030,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M81" s="84" t="str">
-        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+        <x:v>真实多源ID/哈希去重候选及来源优先级/冲突规则实际执行，完整原文保留。全输入格式及完整语义冲突范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N81" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29148,7 +29156,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M84" s="84" t="str">
-        <x:v>contracts/fact-constraint-set.schema.json、catalog/fixtures；PROJECT_PLAN.md（TASK-CNT-001）</x:v>
+        <x:v>真实模型解释逐字锚定数值/范围，原事实约束实际消费；保留主体/动词上下文，拒绝臆造范围。全部格式、语义抽取完整性及全部事实改写验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N84" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29232,7 +29240,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M86" s="84" t="str">
-        <x:v>contracts/evidence-conflict.*.json</x:v>
+        <x:v>8%/9%真实冲突全部保留；明确优先级选8%，无策略阻断，生成与修订不采用9%。全格式语义冲突/合并与系统验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N86" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29274,7 +29282,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M87" s="84" t="str">
-        <x:v>contracts/assumption.*.json；contracts/evidence-conflict.fixtures.json；PROJECT_PLAN.md（TASK-CNT-004）</x:v>
+        <x:v>假设/精确推算/占位/询问/失败实际执行并注册；生成及QA消费假设引用和可见标记。完整自动缺失识别及全链路验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N87" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29999,9 +30007,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L104" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M104" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M104" s="84" t="str">
+        <x:v>实际SourceEvidence逐来源校验后生成候选；用户选定或来源优先级决定冲突，无唯一选择时unresolved并阻断。独立CLI/API、规则/轨迹、三正常及边界、五项目固定源码对应齐备；真实生成和修订消费已选值。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
       <x:c r="N104" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30041,9 +30051,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L105" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M105" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M105" s="84" t="str">
+        <x:v>三正常以上、边界/冲突、独立入口及完整候选轨迹通过；实际生成/修订及初次失败保留，五项目partial/not_found明确。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
       <x:c r="N105" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30083,9 +30095,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L106" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M106" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M106" s="84" t="str">
+        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
       <x:c r="N106" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30125,9 +30139,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L107" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M107" s="84" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="M107" s="84" t="str">
+        <x:v>三正常以上、边界/冲突、独立入口及完整候选轨迹通过；实际生成/修订及初次失败保留，五项目partial/not_found明确。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
       <x:c r="N107" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38062,7 +38078,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M297" s="84" t="str">
-        <x:v>前三决策节点独立及真实生成运行，候选与错误轨迹落盘；其余三十七节点、条件分支和节点恢复待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N297" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38478,7 +38494,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M307" s="84" t="str">
-        <x:v>多栏文字按真实PDF对象坐标检查，删除PDF词反例仍检出；实际模型复审通过当前检查，完整质量规则待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38520,7 +38536,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M308" s="84" t="str">
-        <x:v>修订与复查沿用事实快照，缺失或污染阻断；既有单文本修订回归通过，完整修订计划及对象范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38644,7 +38660,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M311" s="84" t="str">
-        <x:v>新增约束与来源角色独立命令并保存轨迹；完整命令生命周期、基准与调试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38686,7 +38702,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M312" s="84" t="str">
-        <x:v>新增约束与来源角色独立接口，生成入口实际消费；完整作业、取消与重试范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38768,7 +38784,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M314" s="84" t="str">
-        <x:v>前三节点独立入口、失败轨迹及真实链路齐备；任意节点、能力、布局、后端和质量规则调试待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N314" s="86" t="str">
         <x:v>本规划</x:v>
@@ -42882,7 +42898,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M415" s="84" t="str">
-        <x:v>前三节点保存输入、候选、选择、规则、输出、时长及错误；完整节点及对象到全部决策关联待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点保存候选/选择/原来源/约束/hash/输出/时长/错误；完整节点与全部对象关联待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N415" s="86" t="str">
         <x:v>本规划</x:v>
@@ -43284,7 +43300,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M425" s="84" t="str">
-        <x:v>前三节点各至少三个正常及一个边界样例已运行；其余三十七节点和完整回归范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>前五节点正常/边界及真实链路已执行，事实工作包35节点检查+16实物检查；其余35节点及完整回归范围待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
       </x:c>
       <x:c r="N425" s="86" t="str">
         <x:v>本规划</x:v>
@@ -44466,7 +44482,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R700ddc6b9c444ee3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9e231c1dcb94aef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44760,7 +44776,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64137ef55bf14965"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289f5a8718dd48c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46176,7 +46192,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d11160023704024"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b85eb861b7406b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46598,7 +46614,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfedf53cf7bb444ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ca2c576a724386"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48422,9 +48438,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N5" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="N5" s="86" t="str">
+        <x:v>实际SourceEvidence逐来源校验后生成候选；用户选定或来源优先级决定冲突，无唯一选择时unresolved并阻断。独立CLI/API、规则/轨迹、三正常及边界、五项目固定源码对应齐备；真实生成和修订消费已选值。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -48464,9 +48482,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N6" s="86" t="str"/>
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="N6" s="86" t="str">
+        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -49959,7 +49979,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f8a8772180442d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea21f866c72b4fc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rc8e66eec37ef4805"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4b21d75ec5154dcf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ra20f952c99a34ded"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R9a19bf8c33264fa1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R748eb9e114854d84"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Rc3944ef35d904094"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R5bf1837496c547eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R56eb07a507ef46c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R5f5d42bdabb74f90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R1a8941cb50774693"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Re6f32de22c1948b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rd491b2a563e0476c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R52b16306e6c8421c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rab04d5b0f2be4539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R08e85b9ec67241d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Ree473a81ac0c4919"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R147feee1888d4f57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R452e0903e6e644bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rd376adbec0a64070"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Rae959a1925ff4d18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8b358ba0ef9b48ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R8c11c0a8f94846f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R25f224899d1f4918"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R2a623d19a98f40de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4e0e64ea8b524d1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3bf3552a5c97407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1974f20d32c848a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1ae21d69567c4f3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ree4e8cf0c4ee41b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R02a5751927ec4d04"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5dee281793664b0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R70001a41ad6a4440"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2a8e0c098f424a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc7824bb4a21c4d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd97954bb32724504"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R49ab81363f2c4aaa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3e33e7f94b4b49ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8aaea77e29d54bd6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R36bc9b941ad640ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R463e8387be8a4a5e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R63e99e5c80c84e6d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d4e70a024ce4b41"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9f160e2bd144801"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41f23fadd27f4caf"/>
 </x:worksheet>
 </file>
 
@@ -2035,9 +2035,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -2062,9 +2064,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -2116,9 +2120,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -2143,9 +2149,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I8" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -2170,9 +2178,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I9" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -2224,9 +2234,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I11" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -2251,9 +2263,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I12" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -2278,9 +2292,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I13" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -2359,9 +2375,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I16" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I16" s="86" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="87" t="str">
@@ -2386,9 +2404,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H17" s="88" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I17" s="90" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I17" s="90" t="str">
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="H2:H17">
@@ -2472,9 +2492,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I2" s="82" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I2" s="82" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -2499,9 +2521,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I3" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I3" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -2526,9 +2550,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -2553,9 +2579,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -2580,9 +2608,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I6" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I6" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -2688,9 +2718,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I10" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I10" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -2823,9 +2855,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I15" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I15" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -2963,9 +2997,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I2" s="82" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I2" s="82" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -3044,9 +3080,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -3233,9 +3271,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I12" s="86" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -3704,7 +3744,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
-        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -3733,7 +3773,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I5" s="86" t="str">
-        <x:v>src/yoloongppt/；validation/source-runtime.json；文本组件可运行，原E2E待验证</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3762,7 +3802,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -4106,7 +4146,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I18" s="86" t="str">
-        <x:v>JSON/PPTX/render/trace/QA/manifest实际保存与hash，失败证据保留；完整生命周期清理待完成。 实物：validation/generation-artifacts/</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -4162,7 +4202,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4191,7 +4231,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I21" s="86" t="str">
-        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -4217,9 +4257,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H22" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I22" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I22" s="86" t="str">
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -4247,7 +4289,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I23" s="86" t="str">
-        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -7633,9 +7675,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I5" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I5" s="86" t="str">
+        <x:v>实际长解析作业独立进程组，运行中取消终止PID；队列取消、显式新ID重试、服务重启标interrupted而不重复模型请求已运行。模型/下载/渲染全部故障与性能/跨平台矩阵待完成。 validation/job-lifecycle.json</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -8443,9 +8487,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H35" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I35" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I35" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="83" t="str">
@@ -8499,9 +8545,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I37" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I37" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="83" t="str">
@@ -8526,9 +8574,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I38" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I38" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="83" t="str">
@@ -8553,9 +8603,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I39" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I39" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -8580,9 +8632,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I40" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I40" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="83" t="str">
@@ -8634,9 +8688,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H42" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I42" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I42" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="87" t="str">
@@ -8751,13 +8807,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>前五节点真实生成/已选事实单对象修订，已执行P0=0；完整DEC/对象/QA/系统验收未满足。</x:v>
+        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
-        <x:v>系统原验收全部条件未完成</x:v>
+        <x:v>完整原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -9433,13 +9489,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>前五节点真实生成/已选事实单对象修订，已执行P0=0；完整DEC/对象/QA/系统验收未满足。</x:v>
+        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
-        <x:v>系统原验收全部条件未完成</x:v>
+        <x:v>完整原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="165" customHeight="1">
@@ -9520,11 +9576,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G31" s="88" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H31" s="88" t="str"/>
-      <x:c r="I31" s="88" t="str"/>
-      <x:c r="J31" s="90" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H31" s="88" t="str">
+        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
+      </x:c>
+      <x:c r="I31" s="88" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="J31" s="90" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="G2:G31">
@@ -10184,7 +10246,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R65a24eb44ca4477c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6801d803aa34965"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10312,7 +10374,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
         <x:v>八模式判定及冲突保护已运行，完整后续模式执行仍待完成。</x:v>
@@ -10341,7 +10403,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I5" s="86" t="str">
         <x:v>实际校验JSON、UTF-8、容量、身份与约束；全部格式、密码、宏及外链风险校验待完成。</x:v>
@@ -10370,7 +10432,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
         <x:v>文本、Markdown真实来源及角色加载；其他原始格式待实现。</x:v>
@@ -10399,7 +10461,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I7" s="86" t="str">
         <x:v>实际保存文本块、表格、证据和原文锚点；其他格式图片/图形解析待实现。</x:v>
@@ -10428,7 +10490,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>来源ID/哈希、用户优先级及冲突候选真实执行，未决阻断；全格式及完整语义冲突待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I8" s="86" t="str">
         <x:v>来源哈希、版本、引用与重复候选保留；语义冲突及优先级决策待实现。</x:v>
@@ -10486,7 +10548,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>真实FactConstraintSet、显式假设/精确推算/占位/询问及可引用边界运行；自动事实抽取完整性及全格式待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I10" s="86" t="str">
         <x:v>事实集合及数值成员检查已运行；完整事实、禁止臆造及假设决策待完成。</x:v>
@@ -10515,7 +10577,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H11" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I11" s="86" t="str">
         <x:v>真实模型输出整套核心信息及逐页证据引用；独立论点决策及完整证据图待完成。</x:v>
@@ -10541,9 +10603,11 @@
         <x:v>CNT / DEC-001~020</x:v>
       </x:c>
       <x:c r="G12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H12" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H12" s="84" t="str">
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+      </x:c>
       <x:c r="I12" s="86" t="str"/>
     </x:row>
     <x:row r="13" ht="195" customHeight="1">
@@ -10569,7 +10633,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H13" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I13" s="86" t="str">
         <x:v>真实模型输出故事线和页面顺序；独立叙事候选与完整章节结构待完成。</x:v>
@@ -10598,7 +10662,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H14" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I14" s="86" t="str">
         <x:v>真实模型输出页面标题序列；章节/子章节及正式大纲对象待完成。</x:v>
@@ -10627,7 +10691,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H15" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I15" s="86" t="str">
         <x:v>十页硬预算、八页偏好实际消费；时长与章节分配预算待完成。</x:v>
@@ -10656,7 +10720,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H16" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
         <x:v>真实模型按页组织内容并检查总页数；完整语义拆合及跨页衔接待完成。</x:v>
@@ -10685,7 +10749,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H17" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I17" s="86" t="str">
         <x:v>每页实际保存目标及核心信息；独立页面目标决策与完整受众推导待完成。</x:v>
@@ -10714,7 +10778,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H18" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I18" s="86" t="str">
         <x:v>当前文本、表格、图表及开场/结尾版式实际运行；完整类型决策待完成。</x:v>
@@ -10743,7 +10807,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H19" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I19" s="86" t="str">
         <x:v>实际测量文本/表格槽位，容量不足明确失败；语义改写、拆合及图片预算待完成。</x:v>
@@ -10772,7 +10836,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H20" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
         <x:v>原生文本面板、表格、分类图表实际写入；完整图文、流程、时间线与关系表达待完成。</x:v>
@@ -10798,9 +10862,11 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G21" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H21" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H21" s="84" t="str">
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+      </x:c>
       <x:c r="I21" s="86" t="str"/>
     </x:row>
     <x:row r="22" ht="195" customHeight="1">
@@ -10826,7 +10892,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H22" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I22" s="86" t="str">
         <x:v>显式颜色与已安装字体配置已消费；模板、母版、主题和参考图解析待完成。</x:v>
@@ -10852,9 +10918,11 @@
         <x:v>DEC-021~037 / TPL / AST</x:v>
       </x:c>
       <x:c r="G23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H23" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H23" s="84" t="str">
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+      </x:c>
       <x:c r="I23" s="86" t="str"/>
     </x:row>
     <x:row r="24" ht="195" customHeight="1">
@@ -10996,7 +11064,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I28" s="86" t="str">
         <x:v>实际中文字体、字号、颜色、填充和描边；阴影、圆角、图片处理等待完成。</x:v>
@@ -11025,7 +11093,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H29" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I29" s="86" t="str">
         <x:v>原生备注与证据已写入；动画、过渡、媒体和动作待完成。</x:v>
@@ -11054,7 +11122,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H30" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I30" s="86" t="str">
         <x:v>统一页面规格经真实编译/写入消费；完整素材、模板及绑定待完成。</x:v>
@@ -11083,7 +11151,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H31" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I31" s="86" t="str">
         <x:v>实际schema、能力绑定、字体、数据和容量检查；完整路径/权限/模板与后端缺口待完成。</x:v>
@@ -11369,7 +11437,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H41" s="84" t="str">
-        <x:v>真实失败断点恢复事实解释及内容规划，新主模型/复审；单文本修改保持已选事实和单part范围，完整修订计划待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I41" s="86" t="str">
         <x:v>数值引用问题可触发受限修正；完整质量问题到任意节点修订计划待完成。</x:v>
@@ -11398,7 +11466,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H42" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I42" s="86" t="str">
         <x:v>既有单文本修订保留其他parts及实体ID，恢复复用模型；任意节点/对象范围待完成。</x:v>
@@ -11427,7 +11495,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H43" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I43" s="86" t="str">
         <x:v>实际报告草稿及未通过验收状态；完整终止/重试策略待完成。</x:v>
@@ -11456,7 +11524,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H44" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I44" s="86" t="str">
         <x:v>实际导出PPTX/PDF/PNG与trace/QA；完整导出配置和最终验收门控待完成。</x:v>
@@ -11485,7 +11553,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H45" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I45" s="86" t="str">
         <x:v>来源、模型、依赖版本和既有版权记录已保留；全部资产/模板许可及转换合并清单待完成。</x:v>
@@ -11514,7 +11582,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H46" s="88" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="I46" s="90" t="str">
         <x:v>既有原稿曾经PowerPoint实际打开；本版、修复提示和全部可编辑交付验收待完成。</x:v>
@@ -11533,7 +11601,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d38340e57994a24"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb96647955e4856"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13823,10 +13891,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O42" s="84" t="str">
-        <x:v>contracts/docx-evidence.schema.json；contracts/docx-evidence.catalog.json；contracts/docx-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-003）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P42" s="86" t="str">
-        <x:v>结构/资产静态核对通过；页码未实测，解析器未实现。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -13869,10 +13937,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O43" s="84" t="str">
-        <x:v>contracts/pdf-evidence.schema.json；contracts/pdf-evidence.catalog.json；contracts/pdf-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-004）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P43" s="86" t="str">
-        <x:v>结构/坐标静态核对通过；解析器与真实坐标未验收。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -13961,10 +14029,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O45" s="84" t="str">
-        <x:v>contracts/imported-deck.schema.json；contracts/imported-deck.catalog.json；contracts/imported-deck.fixtures.json；PROJECT_PLAN.md（TASK-IN-006）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P45" s="86" t="str">
-        <x:v>静态核对通过；真实PPTX解析未验收。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -14007,10 +14075,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O46" s="84" t="str">
-        <x:v>contracts/template-pack.schema.json；contracts/template-pack.catalog.json；contracts/template-pack.fixtures.json；PROJECT_PLAN.md（TASK-IN-007）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P46" s="86" t="str">
-        <x:v>静态核对通过；PPTX解析未验收。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -14053,10 +14121,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O47" s="84" t="str">
-        <x:v>contracts/tabular-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-008）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P47" s="86" t="str">
-        <x:v>静态核对通过；真实解析器与验收待实现。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -14145,10 +14213,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O49" s="84" t="str">
-        <x:v>contracts/structured-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-010）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P49" s="86" t="str">
-        <x:v>JSON/引用/fixture静态核对通过；真实解析器与验收待实现。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -14191,10 +14259,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O50" s="84" t="str">
-        <x:v>contracts/image-evidence.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-011）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P50" s="86" t="str">
-        <x:v>静态结构/引用核对通过；真实图像分析与验收待实现。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -14237,10 +14305,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O51" s="84" t="str">
-        <x:v>contracts/asset-inventory.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-IN-012）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P51" s="86" t="str">
-        <x:v>路径/引用/fixture静态核对通过；真实目录扫描待实现。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -14375,10 +14443,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O54" s="84" t="str">
-        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P54" s="86" t="str">
-        <x:v>文本路径、编码、NUL、超限/不支持及解析失败明确返回；其他格式检测待接入。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="180" customHeight="1">
@@ -14421,10 +14489,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O55" s="84" t="str">
-        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="P55" s="86" t="str">
-        <x:v>文本/Markdown块锚点与原文回读一致；其他格式及最终PPT对象追溯待验收。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -14651,10 +14719,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O60" s="84" t="str">
-        <x:v>contracts/audience-profile.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-005）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P60" s="86" t="str">
-        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -14697,10 +14765,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O61" s="84" t="str">
-        <x:v>contracts/presentation-scenario.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-006）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P61" s="86" t="str">
-        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -14743,10 +14811,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O62" s="84" t="str">
-        <x:v>contracts/language-style-spec.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-007）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P62" s="86" t="str">
-        <x:v>静态核对通过（4 个 fixture，覆盖中文/英文/混合）；JSON Schema 实例验证器、运行时和 AC 未运行。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -14789,10 +14857,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O63" s="84" t="str">
-        <x:v>contracts/deck-thesis.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-008）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P63" s="86" t="str">
-        <x:v>静态核对通过（3 个 fixture）；JSON Schema 实例验证器、DEC-009、运行时和 AC 未运行。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -14835,10 +14903,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O64" s="84" t="str">
-        <x:v>contracts/content-graph.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-009）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P64" s="86" t="str">
-        <x:v>静态核对通过（3 个 fixture）；关系抽取、图语义校验、运行时与 AC 未运行。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -14927,10 +14995,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O66" s="84" t="str">
-        <x:v>contracts/content-rewrite-trace.schema.json、catalog.json、fixtures.json；PROJECT_PLAN.md（TASK-CNT-011）</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P66" s="86" t="str">
-        <x:v>静态核对通过（4 个 fixture）；未运行 JSON Schema 实例验证器、摘要运行时/语义检查和 AC。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -15019,10 +15087,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O68" s="84" t="str">
-        <x:v>contracts/notes-spec.schema.json；catalog.json；fixtures.json</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P68" s="86" t="str">
-        <x:v>静态核对通过（3 个 fixture）；未运行 JSON Schema 实例验证器、PPT notes writer、PPT-023 或 AC。</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -15350,10 +15418,14 @@
       </x:c>
       <x:c r="M75" s="84" t="str"/>
       <x:c r="N75" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O75" s="84" t="str"/>
-      <x:c r="P75" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O75" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P75" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="83" t="str">
@@ -15394,10 +15466,14 @@
       </x:c>
       <x:c r="M76" s="84" t="str"/>
       <x:c r="N76" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O76" s="84" t="str"/>
-      <x:c r="P76" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O76" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P76" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="83" t="str">
@@ -15438,10 +15514,14 @@
       </x:c>
       <x:c r="M77" s="84" t="str"/>
       <x:c r="N77" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O77" s="84" t="str"/>
-      <x:c r="P77" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O77" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P77" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="83" t="str">
@@ -15482,10 +15562,14 @@
       </x:c>
       <x:c r="M78" s="84" t="str"/>
       <x:c r="N78" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O78" s="84" t="str"/>
-      <x:c r="P78" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O78" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P78" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="83" t="str">
@@ -15526,10 +15610,14 @@
       </x:c>
       <x:c r="M79" s="84" t="str"/>
       <x:c r="N79" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O79" s="84" t="str"/>
-      <x:c r="P79" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O79" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P79" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="83" t="str">
@@ -15570,10 +15658,14 @@
       </x:c>
       <x:c r="M80" s="84" t="str"/>
       <x:c r="N80" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O80" s="84" t="str"/>
-      <x:c r="P80" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O80" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P80" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="83" t="str">
@@ -15614,10 +15706,14 @@
       </x:c>
       <x:c r="M81" s="84" t="str"/>
       <x:c r="N81" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O81" s="84" t="str"/>
-      <x:c r="P81" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O81" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P81" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="83" t="str">
@@ -15658,10 +15754,14 @@
       </x:c>
       <x:c r="M82" s="84" t="str"/>
       <x:c r="N82" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O82" s="84" t="str"/>
-      <x:c r="P82" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O82" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P82" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="83" t="str">
@@ -15702,10 +15802,14 @@
       </x:c>
       <x:c r="M83" s="84" t="str"/>
       <x:c r="N83" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O83" s="84" t="str"/>
-      <x:c r="P83" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O83" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P83" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="83" t="str">
@@ -15746,10 +15850,14 @@
       </x:c>
       <x:c r="M84" s="84" t="str"/>
       <x:c r="N84" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O84" s="84" t="str"/>
-      <x:c r="P84" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O84" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P84" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="83" t="str">
@@ -15790,10 +15898,14 @@
       </x:c>
       <x:c r="M85" s="84" t="str"/>
       <x:c r="N85" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O85" s="84" t="str"/>
-      <x:c r="P85" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O85" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P85" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="83" t="str">
@@ -15834,10 +15946,14 @@
       </x:c>
       <x:c r="M86" s="84" t="str"/>
       <x:c r="N86" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O86" s="84" t="str"/>
-      <x:c r="P86" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O86" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P86" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="83" t="str">
@@ -15878,10 +15994,14 @@
       </x:c>
       <x:c r="M87" s="84" t="str"/>
       <x:c r="N87" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O87" s="84" t="str"/>
-      <x:c r="P87" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O87" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P87" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="83" t="str">
@@ -15922,10 +16042,14 @@
       </x:c>
       <x:c r="M88" s="84" t="str"/>
       <x:c r="N88" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O88" s="84" t="str"/>
-      <x:c r="P88" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O88" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P88" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="83" t="str">
@@ -15966,10 +16090,14 @@
       </x:c>
       <x:c r="M89" s="84" t="str"/>
       <x:c r="N89" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O89" s="84" t="str"/>
-      <x:c r="P89" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O89" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P89" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="83" t="str">
@@ -16010,10 +16138,14 @@
       </x:c>
       <x:c r="M90" s="84" t="str"/>
       <x:c r="N90" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O90" s="84" t="str"/>
-      <x:c r="P90" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O90" s="84" t="str">
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
+      <x:c r="P90" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="83" t="str">
@@ -16907,10 +17039,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O110" s="84" t="str">
-        <x:v>contracts/template-source-record.*.json；PROJECT_PLAN.md</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P110" s="86" t="str">
-        <x:v>静态对照 3 个上游项目及真实 PPTX；运行时、渲染与 AC 未验证。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -16953,10 +17085,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O111" s="84" t="str">
-        <x:v>contracts/master-spec.schema.json；catalog.json；fixtures.json；PROJECT_PLAN.md（TASK-TPL-002）</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P111" s="86" t="str">
-        <x:v>静态核对；继承未解析。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -16999,10 +17131,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O112" s="84" t="str">
-        <x:v>contracts/layout-template.schema.json; contracts/layout-template.catalog.json; contracts/layout-template.fixtures.json; PROJECT_PLAN.md</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P112" s="86" t="str">
-        <x:v>已完成静态源码对照及真实 PPTX 结构盘点；产品解析器、继承结果和应用级验证待完成。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -17045,10 +17177,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O113" s="84" t="str">
-        <x:v>contracts/layout-slot.*.json; contracts/layout-template.*.json; PROJECT_PLAN.md</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P113" s="86" t="str">
-        <x:v>产品运行时验证待完成</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -17091,10 +17223,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O114" s="84" t="str">
-        <x:v>contracts/design-tokens.schema.json、design-tokens.catalog.json、design-tokens.fixtures.json、PROJECT_PLAN.md</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P114" s="86" t="str">
-        <x:v>上游源码与真实 PPTX 样例静态对照已建立；产品 parser/runtime、渲染和 AC 验证待完成</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -17275,10 +17407,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O118" s="84" t="str">
-        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; scripts/project.ps1; compose.yaml; Dockerfile; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P118" s="86" t="str">
-        <x:v>样例为 1 master/11 layouts/1 theme/0 slides；项目 Docker workspace 已运行（Engine 27.4.0 环境观测，通用容器不含产品 runtime）；模板导入/重建、输出 master/layout/theme 比对、round-trip/render 未运行，任务继续进行中。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
       </x:c>
     </x:row>
     <x:row r="119">
@@ -17486,10 +17618,14 @@
       </x:c>
       <x:c r="M123" s="84" t="str"/>
       <x:c r="N123" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O123" s="84" t="str"/>
-      <x:c r="P123" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O123" s="84" t="str">
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P123" s="86" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="83" t="str">
@@ -17612,10 +17748,14 @@
       </x:c>
       <x:c r="M126" s="84" t="str"/>
       <x:c r="N126" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O126" s="84" t="str"/>
-      <x:c r="P126" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O126" s="84" t="str">
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
+      <x:c r="P126" s="86" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="127">
       <x:c r="A127" s="83" t="str">
@@ -17738,10 +17878,14 @@
       </x:c>
       <x:c r="M129" s="84" t="str"/>
       <x:c r="N129" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O129" s="84" t="str"/>
-      <x:c r="P129" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O129" s="84" t="str">
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
+      <x:c r="P129" s="86" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="130">
       <x:c r="A130" s="83" t="str">
@@ -18032,10 +18176,14 @@
       </x:c>
       <x:c r="M136" s="84" t="str"/>
       <x:c r="N136" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O136" s="84" t="str"/>
-      <x:c r="P136" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O136" s="84" t="str">
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
+      <x:c r="P136" s="86" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="137">
       <x:c r="A137" s="83" t="str">
@@ -18286,10 +18434,14 @@
       </x:c>
       <x:c r="M142" s="84" t="str"/>
       <x:c r="N142" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O142" s="84" t="str"/>
-      <x:c r="P142" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O142" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P142" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="143">
       <x:c r="A143" s="83" t="str">
@@ -18330,10 +18482,14 @@
       </x:c>
       <x:c r="M143" s="84" t="str"/>
       <x:c r="N143" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O143" s="84" t="str"/>
-      <x:c r="P143" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O143" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P143" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="144">
       <x:c r="A144" s="83" t="str">
@@ -18550,10 +18706,14 @@
       </x:c>
       <x:c r="M148" s="84" t="str"/>
       <x:c r="N148" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O148" s="84" t="str"/>
-      <x:c r="P148" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O148" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P148" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="149">
       <x:c r="A149" s="83" t="str">
@@ -18594,10 +18754,14 @@
       </x:c>
       <x:c r="M149" s="84" t="str"/>
       <x:c r="N149" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O149" s="84" t="str"/>
-      <x:c r="P149" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O149" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P149" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="150">
       <x:c r="A150" s="83" t="str">
@@ -18638,10 +18802,14 @@
       </x:c>
       <x:c r="M150" s="84" t="str"/>
       <x:c r="N150" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O150" s="84" t="str"/>
-      <x:c r="P150" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O150" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P150" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="151">
       <x:c r="A151" s="83" t="str">
@@ -18729,10 +18897,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O152" s="84" t="str">
-        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P152" s="84" t="str">
-        <x:v>部分：PP-04 已验证矩形 AutoShape 与文本修改、fill/stroke、EMU；圆/箭头/callout/banner、adjustments、rotation、完整读改保留渲染仍未覆盖，暂无路线证明完整 P0。</x:v>
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -18774,10 +18942,14 @@
       </x:c>
       <x:c r="M153" s="84" t="str"/>
       <x:c r="N153" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O153" s="84" t="str"/>
-      <x:c r="P153" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O153" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P153" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="154">
       <x:c r="A154" s="83" t="str">
@@ -18818,10 +18990,14 @@
       </x:c>
       <x:c r="M154" s="84" t="str"/>
       <x:c r="N154" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O154" s="84" t="str"/>
-      <x:c r="P154" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O154" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P154" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="155">
       <x:c r="A155" s="83" t="str">
@@ -18865,10 +19041,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O155" s="84" t="str">
-        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P155" s="86" t="str">
-        <x:v>部分：PP-04 已验证本 PoC 嵌入 PNG 的 add/replace/read；关系、alt text、对象身份、EMU bounds 保持，SHA-256 改变，Validator 0 错误。裁切、布局、其他图片操作与渲染未覆盖。</x:v>
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -18957,10 +19133,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O157" s="84" t="str">
-        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P157" s="86" t="str">
-        <x:v>Partial：表格文本往返通过。</x:v>
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="158">
@@ -19005,10 +19181,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O158" s="84" t="str">
-        <x:v>contracts/capability-status.catalog.json；research/poc/PP-04/artifacts/report.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="P158" s="86" t="str">
-        <x:v>Partial：图表数据往返通过。</x:v>
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="159">
@@ -19226,10 +19402,14 @@
       </x:c>
       <x:c r="M163" s="84" t="str"/>
       <x:c r="N163" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O163" s="84" t="str"/>
-      <x:c r="P163" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O163" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P163" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="164">
       <x:c r="A164" s="83" t="str">
@@ -19270,10 +19450,14 @@
       </x:c>
       <x:c r="M164" s="84" t="str"/>
       <x:c r="N164" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O164" s="84" t="str"/>
-      <x:c r="P164" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O164" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P164" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="165">
       <x:c r="A165" s="83" t="str">
@@ -19534,10 +19718,14 @@
       </x:c>
       <x:c r="M170" s="84" t="str"/>
       <x:c r="N170" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O170" s="84" t="str"/>
-      <x:c r="P170" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O170" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P170" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="171">
       <x:c r="A171" s="83" t="str">
@@ -19578,10 +19766,14 @@
       </x:c>
       <x:c r="M171" s="84" t="str"/>
       <x:c r="N171" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O171" s="84" t="str"/>
-      <x:c r="P171" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O171" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P171" s="86" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="172">
       <x:c r="A172" s="83" t="str">
@@ -20229,10 +20421,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O186" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P186" s="86" t="str">
-        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="180" customHeight="1">
@@ -20275,10 +20467,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O187" s="84" t="str">
-        <x:v>src/yoloongppt/sources.py；evidence.py；markdown.py；validation/source-runtime.json</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P187" s="86" t="str">
-        <x:v>SQLite原文/结构/锚点/hash/版本与ID查询已运行；原SYS生成QA修订E2E待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="188" ht="172.5" customHeight="1">
@@ -20321,10 +20513,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O188" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P188" s="86" t="str">
-        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="189" ht="180" customHeight="1">
@@ -20865,10 +21057,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O200" s="84" t="str">
-        <x:v>src/yoloongppt/；validation/generation-runtime.json；validation/generation-artifacts/</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P200" s="86" t="str">
-        <x:v>JSON/PPTX/render/trace/QA/manifest实际保存与hash，失败证据保留；完整生命周期清理待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="201">
@@ -20953,10 +21145,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O202" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P202" s="86" t="str">
-        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="203" ht="172.5" customHeight="1">
@@ -20999,10 +21191,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O203" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P203" s="86" t="str">
-        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="204">
@@ -21042,10 +21234,14 @@
       </x:c>
       <x:c r="M204" s="84" t="str"/>
       <x:c r="N204" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O204" s="84" t="str"/>
-      <x:c r="P204" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O204" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+      </x:c>
+      <x:c r="P204" s="86" t="str">
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="205" ht="172.5" customHeight="1">
       <x:c r="A205" s="83" t="str">
@@ -21087,10 +21283,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O205" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="P205" s="86" t="str">
-        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="206">
@@ -21130,10 +21326,14 @@
       </x:c>
       <x:c r="M206" s="84" t="str"/>
       <x:c r="N206" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O206" s="84" t="str"/>
-      <x:c r="P206" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O206" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P206" s="86" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="207">
       <x:c r="A207" s="83" t="str">
@@ -21172,10 +21372,14 @@
       </x:c>
       <x:c r="M207" s="84" t="str"/>
       <x:c r="N207" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O207" s="84" t="str"/>
-      <x:c r="P207" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O207" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P207" s="86" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="208">
       <x:c r="A208" s="83" t="str">
@@ -21256,10 +21460,14 @@
       </x:c>
       <x:c r="M209" s="84" t="str"/>
       <x:c r="N209" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O209" s="84" t="str"/>
-      <x:c r="P209" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O209" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P209" s="86" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="210">
       <x:c r="A210" s="83" t="str">
@@ -21298,10 +21506,14 @@
       </x:c>
       <x:c r="M210" s="84" t="str"/>
       <x:c r="N210" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O210" s="84" t="str"/>
-      <x:c r="P210" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O210" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P210" s="86" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="211">
       <x:c r="A211" s="83" t="str">
@@ -21508,10 +21720,14 @@
       </x:c>
       <x:c r="M215" s="84" t="str"/>
       <x:c r="N215" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O215" s="84" t="str"/>
-      <x:c r="P215" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O215" s="84" t="str">
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
+      <x:c r="P215" s="86" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="216">
       <x:c r="A216" s="83" t="str">
@@ -22516,10 +22732,14 @@
       </x:c>
       <x:c r="M239" s="84" t="str"/>
       <x:c r="N239" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O239" s="84" t="str"/>
-      <x:c r="P239" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O239" s="84" t="str">
+        <x:v>validation/job-lifecycle.json</x:v>
+      </x:c>
+      <x:c r="P239" s="86" t="str">
+        <x:v>实际长解析作业独立进程组，运行中取消终止PID；队列取消、显式新ID重试、服务重启标interrupted而不重复模型请求已运行。模型/下载/渲染全部故障与性能/跨平台矩阵待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="240">
       <x:c r="A240" s="83" t="str">
@@ -23776,10 +23996,14 @@
       </x:c>
       <x:c r="M269" s="84" t="str"/>
       <x:c r="N269" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O269" s="84" t="str"/>
-      <x:c r="P269" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O269" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P269" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="270" ht="172.5" customHeight="1">
       <x:c r="A270" s="83" t="str">
@@ -23864,10 +24088,14 @@
       </x:c>
       <x:c r="M271" s="84" t="str"/>
       <x:c r="N271" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O271" s="84" t="str"/>
-      <x:c r="P271" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O271" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P271" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="272">
       <x:c r="A272" s="83" t="str">
@@ -23906,10 +24134,14 @@
       </x:c>
       <x:c r="M272" s="84" t="str"/>
       <x:c r="N272" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O272" s="84" t="str"/>
-      <x:c r="P272" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O272" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P272" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="273">
       <x:c r="A273" s="83" t="str">
@@ -23948,10 +24180,14 @@
       </x:c>
       <x:c r="M273" s="84" t="str"/>
       <x:c r="N273" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O273" s="84" t="str"/>
-      <x:c r="P273" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O273" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P273" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="274">
       <x:c r="A274" s="83" t="str">
@@ -23990,10 +24226,14 @@
       </x:c>
       <x:c r="M274" s="84" t="str"/>
       <x:c r="N274" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O274" s="84" t="str"/>
-      <x:c r="P274" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O274" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P274" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="275">
       <x:c r="A275" s="83" t="str">
@@ -24074,10 +24314,14 @@
       </x:c>
       <x:c r="M276" s="84" t="str"/>
       <x:c r="N276" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O276" s="84" t="str"/>
-      <x:c r="P276" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O276" s="84" t="str">
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
+      <x:c r="P276" s="86" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="277">
       <x:c r="A277" s="83" t="str">
@@ -25493,7 +25737,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19d4af5497aa4a43"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9375555822a24c0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28568,7 +28812,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M70" s="84" t="str">
-        <x:v>contracts/docx-evidence.schema.json（草案）；contracts/docx-evidence.catalog.json；contracts/docx-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-003）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N70" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28610,7 +28854,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M71" s="84" t="str">
-        <x:v>contracts/pdf-evidence.schema.json（草案）；contracts/pdf-evidence.catalog.json；contracts/pdf-evidence.fixtures.json；PROJECT_PLAN.md（TASK-IN-004）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N71" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28694,7 +28938,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M73" s="84" t="str">
-        <x:v>contracts/imported-deck.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-006）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N73" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28736,7 +28980,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M74" s="84" t="str">
-        <x:v>contracts/template-pack.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-007）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N74" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28778,7 +29022,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M75" s="84" t="str">
-        <x:v>contracts/tabular-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-008）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N75" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28862,7 +29106,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M77" s="84" t="str">
-        <x:v>contracts/structured-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-010）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N77" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28904,7 +29148,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M78" s="84" t="str">
-        <x:v>contracts/image-evidence.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-011）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N78" s="86" t="str">
         <x:v>本规划</x:v>
@@ -28946,7 +29190,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M79" s="84" t="str">
-        <x:v>contracts/asset-inventory.schema.json；catalog/fixtures；PROJECT_PLAN.md（TASK-IN-012）</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N79" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29072,7 +29316,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M82" s="84" t="str">
-        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N82" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29114,7 +29358,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M83" s="84" t="str">
-        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
       </x:c>
       <x:c r="N83" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29324,7 +29568,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M88" s="84" t="str">
-        <x:v>contracts/audience-profile.*.json；PROJECT_PLAN.md（TASK-CNT-005）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N88" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29366,7 +29610,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M89" s="84" t="str">
-        <x:v>contracts/presentation-scenario.*.json；PROJECT_PLAN.md（TASK-CNT-006）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N89" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29408,7 +29652,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M90" s="84" t="str">
-        <x:v>contracts/language-style-spec.*.json；PROJECT_PLAN.md（TASK-CNT-007）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N90" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29450,7 +29694,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M91" s="84" t="str">
-        <x:v>contracts/deck-thesis.*.json；PROJECT_PLAN.md（TASK-CNT-008）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N91" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29492,7 +29736,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M92" s="84" t="str">
-        <x:v>contracts/content-graph.*.json；PROJECT_PLAN.md（TASK-CNT-009）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N92" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29576,7 +29820,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M94" s="84" t="str">
-        <x:v>contracts/content-rewrite-trace.*.json；PROJECT_PLAN.md（TASK-CNT-011）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N94" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29660,7 +29904,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M96" s="84" t="str">
-        <x:v>contracts/notes-spec.*.json；PROJECT_PLAN.md（TASK-CNT-013）</x:v>
+        <x:v>调用方受众/场景/风格进入真实模型，按候选故事线和页预算生成，整段容量移动保留原文及可见假设/来源/占位标记。自动语义推断、全部故事线/多级章节/改写原验收待完成。 validation/narrative-runtime.json；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N96" s="86" t="str">
         <x:v>本规划</x:v>
@@ -30183,9 +30427,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L108" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M108" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M108" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N108" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30225,9 +30471,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L109" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M109" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M109" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N109" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30267,9 +30515,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L110" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M110" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M110" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N110" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30309,9 +30559,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L111" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M111" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M111" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N111" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30351,9 +30603,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L112" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M112" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M112" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N112" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30393,9 +30647,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L113" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M113" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M113" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N113" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30435,9 +30691,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L114" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M114" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M114" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N114" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30477,9 +30735,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L115" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M115" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M115" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N115" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30519,9 +30779,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L116" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M116" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M116" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N116" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30561,9 +30823,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L117" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M117" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M117" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N117" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30603,9 +30867,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L118" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M118" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M118" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N118" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30645,9 +30911,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L119" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M119" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M119" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N119" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30687,9 +30955,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L120" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M120" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M120" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N120" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30729,9 +30999,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L121" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M121" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M121" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N121" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30771,9 +31043,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L122" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M122" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M122" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N122" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30813,9 +31087,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L123" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M123" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M123" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N123" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30855,9 +31131,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L124" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M124" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M124" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N124" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30897,9 +31175,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L125" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M125" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M125" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N125" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30939,9 +31219,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L126" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M126" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M126" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N126" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -30981,9 +31263,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L127" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M127" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M127" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N127" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31023,9 +31307,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L128" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M128" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M128" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N128" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31065,9 +31351,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L129" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M129" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M129" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N129" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31107,9 +31395,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L130" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M130" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M130" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N130" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31149,9 +31439,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L131" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M131" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M131" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N131" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31191,9 +31483,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L132" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M132" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M132" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N132" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31233,9 +31527,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L133" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M133" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M133" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N133" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31275,9 +31571,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L134" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M134" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M134" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N134" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31317,9 +31615,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L135" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M135" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M135" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N135" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31359,9 +31659,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L136" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M136" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M136" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N136" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31401,9 +31703,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L137" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M137" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M137" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N137" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31443,9 +31747,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L138" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M138" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M138" s="84" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N138" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31485,9 +31791,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L139" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M139" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M139" s="84" t="str">
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
       <x:c r="N139" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33140,7 +33448,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M178" s="84" t="str">
-        <x:v>contracts/template-source-record.*.json；PROJECT_PLAN.md（TASK-TPL-001）</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N178" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33182,7 +33490,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M179" s="84" t="str">
-        <x:v>contracts/master-spec.*.json；PROJECT_PLAN.md（TASK-TPL-002）</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N179" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33224,7 +33532,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M180" s="84" t="str">
-        <x:v>contracts/layout-template.schema.json; contracts/layout-template.catalog.json; contracts/layout-template.fixtures.json; PROJECT_PLAN.md</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N180" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33266,7 +33574,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M181" s="84" t="str">
-        <x:v>contracts/layout-slot.*.json; contracts/layout-template.*.json; PROJECT_PLAN.md</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N181" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33308,7 +33616,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M182" s="84" t="str">
-        <x:v>contracts/design-tokens.schema.json、design-tokens.catalog.json、design-tokens.fixtures.json、PROJECT_PLAN.md</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N182" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33476,7 +33784,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M186" s="84" t="str">
-        <x:v>contracts/template-import-report.schema.json; contracts/template-import-report.catalog.json; contracts/template-import-report.fixtures.json; PROJECT_PLAN.md#TASK-TPL-009; scripts/project.ps1; compose.yaml; Dockerfile; research/P01/README.md; research/P03/README.md; research/P04/README.md</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
       </x:c>
       <x:c r="N186" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33675,9 +33983,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L191" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M191" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M191" s="84" t="str">
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N191" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33795,9 +34105,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L194" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M194" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M194" s="84" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
       <x:c r="N194" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33915,9 +34227,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L197" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M197" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M197" s="84" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
       <x:c r="N197" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34195,9 +34509,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L204" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M204" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M204" s="84" t="str">
+        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+      </x:c>
       <x:c r="N204" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34437,9 +34753,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L210" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M210" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M210" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N210" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34521,9 +34839,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L212" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M212" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M212" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N212" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34941,9 +35261,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L222" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M222" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M222" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N222" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35025,9 +35347,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L224" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M224" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M224" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N224" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35109,9 +35433,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L226" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M226" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M226" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N226" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35277,9 +35603,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L230" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M230" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M230" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N230" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35361,9 +35689,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L232" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M232" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M232" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N232" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35445,9 +35775,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L234" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M234" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M234" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N234" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35529,9 +35861,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L236" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M236" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M236" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N236" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35697,9 +36031,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L240" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M240" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M240" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N240" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35781,9 +36117,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L242" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M242" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M242" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N242" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -36201,9 +36539,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L252" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M252" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M252" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N252" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -36285,9 +36625,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L254" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M254" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M254" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N254" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -36789,9 +37131,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L266" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M266" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M266" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N266" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -36873,9 +37217,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L268" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M268" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M268" s="84" t="str">
+        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N268" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37994,7 +38340,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M295" s="84" t="str">
-        <x:v>实际解析来源后绑定角色与资产身份，保留完整原文和独立事实快照；完整输入格式与统一加载范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N295" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38036,7 +38382,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M296" s="84" t="str">
-        <x:v>validation/source-runtime.json；src/yoloongppt/；原完整范围/E2E仍待执行</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N296" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38078,7 +38424,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M297" s="84" t="str">
-        <x:v>前五决策节点及事实解释阶段恢复实际运行；真实失败断点复用解释，源身份/hash变化阻断，主模型和复审新调用。其余35节点/条件分支及完整恢复待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N297" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38578,7 +38924,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M309" s="84" t="str">
-        <x:v>真实草稿链路及31项组件检查见validation/generation-runtime.json；完整原验收仍未通过。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N309" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38660,7 +39006,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M311" s="84" t="str">
-        <x:v>增加resolve-evidence与fact-boundaries独立命令，输入/候选/规则/输出落盘；完整CLI生命周期/基准待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N311" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38702,7 +39048,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M312" s="84" t="str">
-        <x:v>增加两事实决策API并由生成/修订消费；原HTTP错误/trace一致，完整作业/取消/重试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N312" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38741,9 +39087,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L313" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M313" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M313" s="84" t="str">
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+      </x:c>
       <x:c r="N313" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38784,7 +39132,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M314" s="84" t="str">
-        <x:v>前五节点独立入口和实际失败/恢复轨迹齐备；全部节点、能力、布局、后端与规则调试待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
       </x:c>
       <x:c r="N314" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38823,9 +39171,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L315" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M315" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M315" s="84" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N315" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38863,9 +39213,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L316" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M316" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M316" s="84" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N316" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38943,9 +39295,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L318" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M318" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M318" s="84" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N318" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38983,9 +39337,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L319" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M319" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M319" s="84" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N319" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39183,9 +39539,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L324" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M324" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M324" s="84" t="str">
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+      </x:c>
       <x:c r="N324" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40983,9 +41341,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L368" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M368" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M368" s="84" t="str">
+        <x:v>实际长解析作业独立进程组，运行中取消终止PID；队列取消、显式新ID重试、服务重启标interrupted而不重复模型请求已运行。模型/下载/渲染全部故障与性能/跨平台矩阵待完成。 validation/job-lifecycle.json</x:v>
+      </x:c>
       <x:c r="N368" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -42855,9 +43215,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L414" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M414" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M414" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N414" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -42937,9 +43299,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L416" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M416" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M416" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N416" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -42977,9 +43341,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L417" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M417" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M417" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N417" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43017,9 +43383,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L418" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M418" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M418" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N418" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43057,9 +43425,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L419" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M419" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M419" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N419" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -43137,9 +43507,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L421" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M421" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M421" s="84" t="str">
+        <x:v>真实任务结构化事件、原子执行轨迹、供应商token/latency/request ID、产物hash清单及version manifest、保存运行结构差异入口已接入；已生成/修订实物保留。全类型/全链路关联、兼容重放、全部版本和比较原验收待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+      </x:c>
       <x:c r="N421" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44482,7 +44854,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9e231c1dcb94aef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R348bf6f4b77d48fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44776,7 +45148,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R289f5a8718dd48c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c4c29143d34558"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46192,7 +46564,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73b85eb861b7406b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R748d51432e354eb3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46614,7 +46986,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ca2c576a724386"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd702583dd6004b41"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46717,7 +47089,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: create/open/save-as; properties and dimensions; merge not implemented</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
         <x:v>Untested</x:v>
@@ -46734,7 +47106,7 @@
       <x:c r="N2" s="80" t="str"/>
       <x:c r="O2" s="80" t="str"/>
       <x:c r="P2" s="82" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -46763,7 +47135,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I3" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: add/read slides; hide/duplicate/move/delete not implemented</x:v>
       </x:c>
       <x:c r="J3" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46780,7 +47152,7 @@
       <x:c r="N3" s="84" t="str"/>
       <x:c r="O3" s="84" t="str"/>
       <x:c r="P3" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -46809,7 +47181,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I4" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J4" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46826,7 +47198,7 @@
       <x:c r="N4" s="84" t="str"/>
       <x:c r="O4" s="84" t="str"/>
       <x:c r="P4" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -46855,7 +47227,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I5" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J5" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46872,7 +47244,7 @@
       <x:c r="N5" s="84" t="str"/>
       <x:c r="O5" s="84" t="str"/>
       <x:c r="P5" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -46901,7 +47273,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I6" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J6" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46918,7 +47290,7 @@
       <x:c r="N6" s="84" t="str"/>
       <x:c r="O6" s="84" t="str"/>
       <x:c r="P6" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -46947,7 +47319,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I7" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J7" s="84" t="str">
         <x:v>Untested</x:v>
@@ -46964,7 +47336,7 @@
       <x:c r="N7" s="84" t="str"/>
       <x:c r="O7" s="84" t="str"/>
       <x:c r="P7" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -46993,7 +47365,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I8" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: read placeholder type/idx/bounds; fill existing text placeholders</x:v>
       </x:c>
       <x:c r="J8" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47010,7 +47382,7 @@
       <x:c r="N8" s="84" t="str"/>
       <x:c r="O8" s="84" t="str"/>
       <x:c r="P8" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -47039,7 +47411,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I9" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: create/read/update text frames; preserve unrelated XML</x:v>
       </x:c>
       <x:c r="J9" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47056,7 +47428,7 @@
       <x:c r="N9" s="84" t="str"/>
       <x:c r="O9" s="84" t="str"/>
       <x:c r="P9" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -47085,7 +47457,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I10" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: font/size/bold/italic/underline/color/alignment; advanced bullets/tabs not implemented</x:v>
       </x:c>
       <x:c r="J10" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47102,7 +47474,7 @@
       <x:c r="N10" s="84" t="str"/>
       <x:c r="O10" s="84" t="str"/>
       <x:c r="P10" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -47131,7 +47503,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I11" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J11" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47148,7 +47520,7 @@
       <x:c r="N11" s="84" t="str"/>
       <x:c r="O11" s="84" t="str"/>
       <x:c r="P11" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -47177,7 +47549,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I12" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: rectangle/ellipse/rounded rectangle/arrows; fill/stroke/rotation</x:v>
       </x:c>
       <x:c r="J12" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47194,7 +47566,7 @@
       <x:c r="N12" s="84" t="str"/>
       <x:c r="O12" s="84" t="str"/>
       <x:c r="P12" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -47223,7 +47595,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I13" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: straight/elbow/curved connectors; connection points/reroute/freeform not implemented</x:v>
       </x:c>
       <x:c r="J13" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47240,7 +47612,7 @@
       <x:c r="N13" s="84" t="str"/>
       <x:c r="O13" s="84" t="str"/>
       <x:c r="P13" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -47269,7 +47641,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I14" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: native group creation and child indexing; ungroup/locks not implemented</x:v>
       </x:c>
       <x:c r="J14" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47286,7 +47658,7 @@
       <x:c r="N14" s="84" t="str"/>
       <x:c r="O14" s="84" t="str"/>
       <x:c r="P14" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -47315,7 +47687,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I15" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: embedded PNG/JPEG create/read/replace; crop/effects not implemented; shared image replacement rejected</x:v>
       </x:c>
       <x:c r="J15" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47332,7 +47704,7 @@
       <x:c r="N15" s="84" t="str"/>
       <x:c r="O15" s="84" t="str"/>
       <x:c r="P15" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -47361,7 +47733,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I16" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J16" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47378,7 +47750,7 @@
       <x:c r="N16" s="84" t="str"/>
       <x:c r="O16" s="84" t="str"/>
       <x:c r="P16" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -47407,7 +47779,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I17" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: native rows/columns/cells and cell text edit; pagination not implemented</x:v>
       </x:c>
       <x:c r="J17" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47424,7 +47796,7 @@
       <x:c r="N17" s="84" t="str"/>
       <x:c r="O17" s="84" t="str"/>
       <x:c r="P17" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -47453,7 +47825,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I18" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: category charts and replace data with embedded workbook; combo/error bars not implemented</x:v>
       </x:c>
       <x:c r="J18" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47470,7 +47842,7 @@
       <x:c r="N18" s="84" t="str"/>
       <x:c r="O18" s="84" t="str"/>
       <x:c r="P18" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -47499,7 +47871,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I19" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J19" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47516,7 +47888,7 @@
       <x:c r="N19" s="84" t="str"/>
       <x:c r="O19" s="84" t="str"/>
       <x:c r="P19" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -47545,7 +47917,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I20" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J20" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47562,7 +47934,7 @@
       <x:c r="N20" s="84" t="str"/>
       <x:c r="O20" s="84" t="str"/>
       <x:c r="P20" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -47591,7 +47963,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I21" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J21" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47608,7 +47980,7 @@
       <x:c r="N21" s="84" t="str"/>
       <x:c r="O21" s="84" t="str"/>
       <x:c r="P21" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -47637,7 +48009,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I22" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J22" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47654,7 +48026,7 @@
       <x:c r="N22" s="84" t="str"/>
       <x:c r="O22" s="84" t="str"/>
       <x:c r="P22" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -47683,7 +48055,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I23" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: safe https/http/mailto text hyperlink; executable file/action links rejected</x:v>
       </x:c>
       <x:c r="J23" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47700,7 +48072,7 @@
       <x:c r="N23" s="84" t="str"/>
       <x:c r="O23" s="84" t="str"/>
       <x:c r="P23" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -47729,7 +48101,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I24" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: read/update existing notes; notes master preserved</x:v>
       </x:c>
       <x:c r="J24" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47746,7 +48118,7 @@
       <x:c r="N24" s="84" t="str"/>
       <x:c r="O24" s="84" t="str"/>
       <x:c r="P24" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -47775,7 +48147,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I25" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J25" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47792,7 +48164,7 @@
       <x:c r="N25" s="84" t="str"/>
       <x:c r="O25" s="84" t="str"/>
       <x:c r="P25" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -47821,7 +48193,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I26" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J26" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47838,7 +48210,7 @@
       <x:c r="N26" s="84" t="str"/>
       <x:c r="O26" s="84" t="str"/>
       <x:c r="P26" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -47867,7 +48239,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I27" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J27" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47884,7 +48256,7 @@
       <x:c r="N27" s="84" t="str"/>
       <x:c r="O27" s="84" t="str"/>
       <x:c r="P27" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -47913,7 +48285,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J28" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47930,7 +48302,7 @@
       <x:c r="N28" s="84" t="str"/>
       <x:c r="O28" s="84" t="str"/>
       <x:c r="P28" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -47959,7 +48331,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I29" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>unsupported: Existing OOXML parts are inventoried and preserved; native editing is unavailable.</x:v>
       </x:c>
       <x:c r="J29" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47976,7 +48348,7 @@
       <x:c r="N29" s="84" t="str"/>
       <x:c r="O29" s="84" t="str"/>
       <x:c r="P29" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -48005,7 +48377,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I30" s="84" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: alt text and shape order indexing; complete accessibility audit not implemented</x:v>
       </x:c>
       <x:c r="J30" s="84" t="str">
         <x:v>Untested</x:v>
@@ -48022,7 +48394,7 @@
       <x:c r="N30" s="84" t="str"/>
       <x:c r="O30" s="84" t="str"/>
       <x:c r="P30" s="86" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -48051,7 +48423,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I31" s="88" t="str">
-        <x:v>Untested</x:v>
+        <x:v>partial: slide-id + shape-id stable mapping; extension/custom XML preserved</x:v>
       </x:c>
       <x:c r="J31" s="88" t="str">
         <x:v>Untested</x:v>
@@ -48068,7 +48440,7 @@
       <x:c r="N31" s="88" t="str"/>
       <x:c r="O31" s="88" t="str"/>
       <x:c r="P31" s="90" t="str">
-        <x:v>contracts/capability-status.catalog.json；按 CapabilityStatus 草案记录</x:v>
+        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -48526,9 +48898,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N7" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -48568,9 +48942,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N8" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -48610,9 +48986,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N9" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -48652,9 +49030,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N10" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N10" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -48694,9 +49074,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M11" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N11" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N11" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -48736,9 +49118,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N12" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -48778,9 +49162,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N13" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -48820,9 +49206,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N14" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N14" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -48862,9 +49250,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N15" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N15" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -48904,9 +49294,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N16" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N16" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -48946,9 +49338,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M17" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N17" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N17" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -48988,9 +49382,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N18" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N18" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="83" t="str">
@@ -49030,9 +49426,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M19" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N19" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N19" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="83" t="str">
@@ -49072,9 +49470,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M20" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N20" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N20" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="83" t="str">
@@ -49114,9 +49514,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M21" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N21" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N21" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="83" t="str">
@@ -49156,9 +49558,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M22" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N22" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N22" s="86" t="str">
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -49979,7 +50383,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea21f866c72b4fc1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cef7e73256f42e5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R8b358ba0ef9b48ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R8c11c0a8f94846f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R25f224899d1f4918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R2a623d19a98f40de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R4e0e64ea8b524d1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R3bf3552a5c97407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R1974f20d32c848a0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R1ae21d69567c4f3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Ree4e8cf0c4ee41b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R02a5751927ec4d04"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R5dee281793664b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R70001a41ad6a4440"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R2a8e0c098f424a6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Rc7824bb4a21c4d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rd97954bb32724504"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R49ab81363f2c4aaa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R3e33e7f94b4b49ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R8aaea77e29d54bd6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R36bc9b941ad640ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R463e8387be8a4a5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb3dd0649d4ee48c5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4239cb07b6fd4f34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rffa94b4636df4212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R173bc81da42c4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R0b272917fcda4fcb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R46df0c05fb77444a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0165750b9a3047ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R23293dd03c304beb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2e79a9405f38481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbc70329469a343e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R43e80a73c55c4b7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb9daab412954473a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R760c7e7fdea7499e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R4d012af11f524a4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R78d1ed1ab8254021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rbed12595064647af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8205ab65f8494813"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb980d080c495409f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R48b4c75f37ef491a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R9f38c90bffd6445e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1d4e70a024ce4b41"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905452fb79d34c4b"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41f23fadd27f4caf"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85268bea81e8472e"/>
 </x:worksheet>
 </file>
 
@@ -2495,7 +2495,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I2" s="82" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2611,7 +2611,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2664,9 +2664,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I8" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -2774,9 +2776,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I12" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -2801,9 +2805,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I13" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -2828,9 +2834,11 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H14" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I14" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I14" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -3000,7 +3008,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I2" s="82" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -3053,9 +3061,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H4" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I4" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I4" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -3083,7 +3093,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I5" s="86" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -3109,9 +3119,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I6" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I6" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -3136,9 +3148,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -3163,9 +3177,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H8" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I8" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I8" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -3274,7 +3290,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I12" s="86" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -3300,9 +3316,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H13" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I13" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I13" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本地实际字节/hash/MIME核验和原子缓存运行；远程HTTPS/public-IP/redirect限制已编码但公开下载/重试原验收未执行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -3354,9 +3372,11 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H15" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I15" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I15" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已批准节点/明示关系变为可编辑原生shape/connector，并保留evidence_quote；全图类型/布局/语义验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -3886,9 +3906,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I9" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -3913,9 +3935,11 @@
         <x:v>至少一个 E2E 用例实际经过该组件；组件可单独测试。</x:v>
       </x:c>
       <x:c r="H10" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I10" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I10" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已解析真实图片/hash/像素/MIME/许可与显式授权，真实生成消费；敏感文件/越界链接拒绝。全部来源/质量语义待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -3943,7 +3967,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I11" s="86" t="str">
-        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3972,7 +3996,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I12" s="86" t="str">
-        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -4001,7 +4025,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I13" s="86" t="str">
-        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -4030,7 +4054,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I14" s="86" t="str">
-        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实六页包含原生图片和可编辑流程，消费模板继承与跨页DAG。全部母版/布局/既有文件修改路线待验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -4059,7 +4083,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I15" s="86" t="str">
-        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 六页PPTX实际LibreOffice PDF/PNG/hash渲染，QA-only恢复保持文件/渲染字节。live截图/全部renderer待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -4088,7 +4112,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
-        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4117,7 +4141,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I17" s="86" t="str">
-        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8028,9 +8052,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="H18" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I18" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I18" s="86" t="str">
+        <x:v>validation/visual-path-guards.json；validation/视觉决策与真实素材.md 素材/模板读取前拒绝secrets/.git/.ssh/.env及实际链接越界，23项真实路径guard通过；全部用户/输出/执行路径安全原验收仍待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="83" t="str">
@@ -8807,10 +8833,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
+        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -9489,10 +9515,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
+        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -9579,10 +9605,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H31" s="88" t="str">
-        <x:v>真实八页多源生成+DEC1–21有界消费+作业/取消/MCP入口/已有PPT精确修改，P0=0；全决策/QA/模式/系统原条件未满足。</x:v>
+        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
       </x:c>
       <x:c r="I31" s="88" t="str">
-        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/parallel-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="J31" s="90" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -10246,7 +10272,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6801d803aa34965"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19b0e6741f1497b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10403,10 +10429,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H5" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I5" s="86" t="str">
-        <x:v>实际校验JSON、UTF-8、容量、身份与约束；全部格式、密码、宏及外链风险校验待完成。</x:v>
+        <x:v>新增素材/模板敏感路径和真实链接越界guard。全类型/密码/宏/输出权限原验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="195" customHeight="1">
@@ -10606,9 +10632,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H12" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
-      </x:c>
-      <x:c r="I12" s="86" t="str"/>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="I12" s="86" t="str">
+        <x:v>只消费已批准原文明示节点与箭头，原生流程可编辑。完整内容关系抽取/因果证明及全图类型待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="195" customHeight="1">
       <x:c r="A13" s="83" t="str">
@@ -10836,10 +10864,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H20" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>原生文本面板、表格、分类图表实际写入；完整图文、流程、时间线与关系表达待完成。</x:v>
+        <x:v>DEC022–029实际选择文本/图/表/图表/流程，语义价值全验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10865,9 +10893,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H21" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
-      </x:c>
-      <x:c r="I21" s="86" t="str"/>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="I21" s="86" t="str">
+        <x:v>真实图片asset_id/文件/hash/许可与授权进入主生成；在线检索/生成服务未验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="22" ht="195" customHeight="1">
       <x:c r="A22" s="83" t="str">
@@ -10892,10 +10922,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H22" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I22" s="86" t="str">
-        <x:v>显式颜色与已安装字体配置已消费；模板、母版、主题和参考图解析待完成。</x:v>
+        <x:v>真实模板文件及母版/布局/主题/styles解析进入生成；全部tokens/品牌锁待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -10921,9 +10951,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H23" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
-      </x:c>
-      <x:c r="I23" s="86" t="str"/>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="I23" s="86" t="str">
+        <x:v>模板注册与候选查询已消费，尺寸冲突失败，未静默默认替换；完整容量/跨模板评分待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24" ht="195" customHeight="1">
       <x:c r="A24" s="83" t="str">
@@ -10948,10 +10980,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H24" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I24" s="86" t="str">
-        <x:v>七类原生候选按槽位与实测容量检索；完整素材及模板条件待完成。</x:v>
+        <x:v>文本、数据、图片和流程实际候选/后端能力/容量检查；全类型/多后端待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="195" customHeight="1">
@@ -10977,10 +11009,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H25" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I25" s="86" t="str">
-        <x:v>当前容量、页面层级与相邻变化实际评分；完整语义、品牌、素材比例及多后端待完成。</x:v>
+        <x:v>实际容量/层级/变化评分与trace；完整语义/品牌评分待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="195" customHeight="1">
@@ -11006,10 +11038,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H26" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I26" s="86" t="str">
-        <x:v>当前标题、正文、数据及备注映射稳定槽位；图片和完整模板占位符待完成。</x:v>
+        <x:v>稳定原生槽位绑定图片/节点/边；任意模板字段和全槽位待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="195" customHeight="1">
@@ -11035,10 +11067,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H27" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I27" s="86" t="str">
-        <x:v>实际几何槽位、边距和非重叠检查；连接线、旋转、裁切等待完成。</x:v>
+        <x:v>原生几何/节点/连接端点计算，真实写入渲染；freeform及所有关系布局待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="195" customHeight="1">
@@ -11064,10 +11096,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I28" s="86" t="str">
-        <x:v>实际中文字体、字号、颜色、填充和描边；阴影、圆角、图片处理等待完成。</x:v>
+        <x:v>字体/填充/描边/背景与声明设计变化进入实际执行；全效果待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="195" customHeight="1">
@@ -11093,10 +11125,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H29" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I29" s="86" t="str">
-        <x:v>原生备注与证据已写入；动画、过渡、媒体和动作待完成。</x:v>
+        <x:v>实际notes执行；动画/切换未支持显式报告，完整增强待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="195" customHeight="1">
@@ -11122,10 +11154,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H30" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I30" s="86" t="str">
-        <x:v>统一页面规格经真实编译/写入消费；完整素材、模板及绑定待完成。</x:v>
+        <x:v>图片与流程的统一spec实际消费；全对象/模板/绑定验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="195" customHeight="1">
@@ -11151,10 +11183,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H31" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I31" s="86" t="str">
-        <x:v>实际schema、能力绑定、字体、数据和容量检查；完整路径/权限/模板与后端缺口待完成。</x:v>
+        <x:v>素材hash/权限、字体、schema、容量和原子能力检查；所有路径与后端缺口待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="195" customHeight="1">
@@ -11180,10 +11212,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H32" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I32" s="86" t="str">
-        <x:v>当前PP-05登记实现实际选择；全九路线按保真/任务能力动态选择待完成。</x:v>
+        <x:v>当前PP-05原子实现已选择，九路线动态选择原验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="195" customHeight="1">
@@ -11209,10 +11241,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H33" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I33" s="86" t="str">
-        <x:v>实际能力调用DAG与稳定对象/实现ID；完整对象及复杂依赖待完成。</x:v>
+        <x:v>图片/shape/connector进入真实DAG及ObjectMap；全部对象复杂依赖待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="195" customHeight="1">
@@ -11238,10 +11270,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H34" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I34" s="86" t="str">
-        <x:v>真实原生PPTX与单文本修订已运行；已有文件保真编辑和全部对象待完成。</x:v>
+        <x:v>真实六页原生图片/流程PPTX与局部RevisionPlan已保存；全部模式和保真待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="195" customHeight="1">
@@ -11267,10 +11299,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H35" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I35" s="86" t="str">
-        <x:v>真实PDF与逐页PNG，版本/hash已保存；live截图和完整缩略图范围待完成。</x:v>
+        <x:v>实际PDF/逐页PNG/hash版本保存，QA-only复用字节；live/全部缩略图待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="195" customHeight="1">
@@ -11296,10 +11328,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H36" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I36" s="86" t="str">
-        <x:v>实际ZIP/XML、边界、对象映射与PDF字词检查；完整关系与结构规则待完成。</x:v>
+        <x:v>部分原生结构/边界/空对象/碰撞/溢出检查运行；完整结构验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="195" customHeight="1">
@@ -11325,10 +11357,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H37" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I37" s="86" t="str">
-        <x:v>真实渲染页经模型视觉审查；全部确定性视觉规则和验收阈值待完成。</x:v>
+        <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="195" customHeight="1">
@@ -11354,10 +11386,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H38" s="84" t="str">
-        <x:v>实际已选值/假设可见性/否决值/数值与备注检查，独立真实视觉事实复审；完整语义真值及全图像对应待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I38" s="86" t="str">
-        <x:v>实际数值/引用检查与模型事实审查；完整语义真值及图像对应待完成。</x:v>
+        <x:v>数值引用与真实模型事实复审，图片尺寸仅对同页实际hash/像素验证后排除元数据；完整语义真值待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="195" customHeight="1">
@@ -11383,10 +11415,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H39" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I39" s="86" t="str">
-        <x:v>原生文本/表格/图表和嵌入数据已检查；导入往返、母版/主题保真待完成。</x:v>
+        <x:v>原生图片/节点/边可编辑，局部非目标parts保持；全对象round-trip待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11409,10 +11441,14 @@
         <x:v>QA / PPT / OBS</x:v>
       </x:c>
       <x:c r="G40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="H40" s="84" t="str"/>
-      <x:c r="I40" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="H40" s="84" t="str">
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="I40" s="86" t="str">
+        <x:v>已检查原生alt-text/阅读顺序/字号/对比/表头部分字段，语言/RTL与完整可访问性待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41" ht="195" customHeight="1">
       <x:c r="A41" s="83" t="str">
@@ -11437,10 +11473,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H41" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I41" s="86" t="str">
-        <x:v>数值引用问题可触发受限修正；完整质量问题到任意节点修订计划待完成。</x:v>
+        <x:v>DEC039将实际issue映射局部RevisionPlan/fail/needs_input；全部节点修订待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="195" customHeight="1">
@@ -11466,10 +11502,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H42" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I42" s="86" t="str">
-        <x:v>既有单文本修订保留其他parts及实体ID，恢复复用模型；任意节点/对象范围待完成。</x:v>
+        <x:v>24项RevisionPlan消费者检查，真实布局/颜色局部修改和QA/history；任意节点/对象待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="195" customHeight="1">
@@ -11495,10 +11531,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H43" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I43" s="86" t="str">
-        <x:v>实际报告草稿及未通过验收状态；完整终止/重试策略待完成。</x:v>
+        <x:v>六页QA-only P0=0但保留4警告，终止warning/not_passed；没有把DEC轨迹齐全当作完整验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="195" customHeight="1">
@@ -11524,10 +11560,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H44" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I44" s="86" t="str">
-        <x:v>实际导出PPTX/PDF/PNG与trace/QA；完整导出配置和最终验收门控待完成。</x:v>
+        <x:v>PPTX/PDF/PNG/manifest/trace/QA实物导出；最终系统验收门控尚未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="195" customHeight="1">
@@ -11553,10 +11589,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H45" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I45" s="86" t="str">
-        <x:v>来源、模型、依赖版本和既有版权记录已保留；全部资产/模板许可及转换合并清单待完成。</x:v>
+        <x:v>素材/模板来源/hash/许可/unknown状态及模型版本保存；全来源合并许可清单待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="195" customHeight="1">
@@ -11582,10 +11618,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H46" s="88" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I46" s="90" t="str">
-        <x:v>既有原稿曾经PowerPoint实际打开；本版、修复提示和全部可编辑交付验收待完成。</x:v>
+        <x:v>六页可编辑原生对象与真实渲染已检查，本版PowerPoint实际打开/全部交付原验收未完成。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11601,7 +11637,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb96647955e4856"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17684678187b4088"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12315,10 +12351,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O9" s="84" t="str">
-        <x:v>validation/generation-artifacts/；validation/generation-runtime.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P9" s="86" t="str">
-        <x:v>已有真实10页可编辑PPTX→render→部分QA→单对象修订；完整DEC/全部QA/所有P0 AC未通过。</x:v>
+        <x:v>真实六页可编辑PPTX/渲染/QA-only恢复P0=0，原生RevisionPlan局部修订实物运行。4警告及完整QA/所有P0 AC仍未通过，系统非完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -16186,10 +16222,14 @@
       </x:c>
       <x:c r="M91" s="84" t="str"/>
       <x:c r="N91" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O91" s="84" t="str"/>
-      <x:c r="P91" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O91" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P91" s="86" t="str">
+        <x:v>真实模型消费文本/图文/表/图表/流程选择，原生执行并保留依据。完整矩阵/信息图等范围未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="83" t="str">
@@ -16230,10 +16270,14 @@
       </x:c>
       <x:c r="M92" s="84" t="str"/>
       <x:c r="N92" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O92" s="84" t="str"/>
-      <x:c r="P92" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O92" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P92" s="86" t="str">
+        <x:v>图片数量及信息/装饰角色进入实际规划，缺失图显式失败。信息价值/全语义相关性待验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="83" t="str">
@@ -16274,10 +16318,14 @@
       </x:c>
       <x:c r="M93" s="84" t="str"/>
       <x:c r="N93" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O93" s="84" t="str"/>
-      <x:c r="P93" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O93" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P93" s="86" t="str">
+        <x:v>模型仅选登记asset_id，解析真实文件/hash/许可授权，保留原模型声明。在线检索/生成服务未验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="83" t="str">
@@ -16318,10 +16366,14 @@
       </x:c>
       <x:c r="M94" s="84" t="str"/>
       <x:c r="N94" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O94" s="84" t="str"/>
-      <x:c r="P94" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O94" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P94" s="86" t="str">
+        <x:v>真实结构化表格行列检查及原生写入，未补齐/裁剪数据。强调字段/分页/必要性完整验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="83" t="str">
@@ -16362,10 +16414,14 @@
       </x:c>
       <x:c r="M95" s="84" t="str"/>
       <x:c r="N95" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O95" s="84" t="str"/>
-      <x:c r="P95" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O95" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P95" s="86" t="str">
+        <x:v>bar/column/line原生数据消费并检查维度。area/pie/scatter及完整分析目的策略未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="83" t="str">
@@ -16406,10 +16462,14 @@
       </x:c>
       <x:c r="M96" s="84" t="str"/>
       <x:c r="N96" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O96" s="84" t="str"/>
-      <x:c r="P96" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O96" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P96" s="86" t="str">
+        <x:v>已批准原文节点和明示顺序箭头进入原生形状/连接线。拒绝词法猜测因果，完整七类关系图语义待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="83" t="str">
@@ -16450,10 +16510,14 @@
       </x:c>
       <x:c r="M97" s="84" t="str"/>
       <x:c r="N97" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O97" s="84" t="str"/>
-      <x:c r="P97" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O97" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P97" s="86" t="str">
+        <x:v>实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="83" t="str">
@@ -16494,10 +16558,14 @@
       </x:c>
       <x:c r="M98" s="84" t="str"/>
       <x:c r="N98" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O98" s="84" t="str"/>
-      <x:c r="P98" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O98" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P98" s="86" t="str">
+        <x:v>真实模型及writer消费字体/色板/背景/形状语言，保留来源与默认值。完整效果/设计tokens未验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="83" t="str">
@@ -16541,10 +16609,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O99" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P99" s="86" t="str">
-        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。</x:v>
+        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -16589,10 +16657,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O100" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P100" s="86" t="str">
-        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。</x:v>
+        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -16634,10 +16702,14 @@
       </x:c>
       <x:c r="M101" s="84" t="str"/>
       <x:c r="N101" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O101" s="84" t="str"/>
-      <x:c r="P101" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O101" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P101" s="86" t="str">
+        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="83" t="str">
@@ -16681,10 +16753,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O102" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P102" s="86" t="str">
-        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。</x:v>
+        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -16729,10 +16801,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O103" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P103" s="86" t="str">
-        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。</x:v>
+        <x:v>CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -16774,10 +16846,14 @@
       </x:c>
       <x:c r="M104" s="84" t="str"/>
       <x:c r="N104" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O104" s="84" t="str"/>
-      <x:c r="P104" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O104" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P104" s="86" t="str">
+        <x:v>填充/描边/背景/对比及声明设计变化实际消费。渐变/阴影/透明度等完整效果待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="83" t="str">
@@ -16818,10 +16894,14 @@
       </x:c>
       <x:c r="M105" s="84" t="str"/>
       <x:c r="N105" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O105" s="84" t="str"/>
-      <x:c r="P105" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O105" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P105" s="86" t="str">
+        <x:v>原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="83" t="str">
@@ -16862,10 +16942,14 @@
       </x:c>
       <x:c r="M106" s="84" t="str"/>
       <x:c r="N106" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O106" s="84" t="str"/>
-      <x:c r="P106" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O106" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P106" s="86" t="str">
+        <x:v>实际备注进入原生notes；动画/切换不支持时显式报告，未当作交付。完整演示增强待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="83" t="str">
@@ -16906,10 +16990,14 @@
       </x:c>
       <x:c r="M107" s="84" t="str"/>
       <x:c r="N107" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O107" s="84" t="str"/>
-      <x:c r="P107" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O107" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P107" s="86" t="str">
+        <x:v>已消费能力登记与PP-05实际原子DAG预执行，缺口结构化失败。九路线动态选择/模板round-trip全验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="83" t="str">
@@ -16950,10 +17038,14 @@
       </x:c>
       <x:c r="M108" s="84" t="str"/>
       <x:c r="N108" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O108" s="84" t="str"/>
-      <x:c r="P108" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O108" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P108" s="86" t="str">
+        <x:v>质量问题映射RevisionPlan及fail/输入需求，原生局部布局/样式修订真实执行，未修改part保持。全部节点重跑未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="83" t="str">
@@ -16994,10 +17086,14 @@
       </x:c>
       <x:c r="M109" s="84" t="str"/>
       <x:c r="N109" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O109" s="84" t="str"/>
-      <x:c r="P109" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O109" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P109" s="86" t="str">
+        <x:v>真实六页QA-only恢复P0=0保留4警告，19项接口/恢复与10项重复恢复各自记录；轨迹齐全仍warning/not_passed，不是40节点原验收完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="83" t="str">
@@ -17039,10 +17135,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O110" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P110" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+        <x:v>真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="111">
@@ -17223,10 +17319,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O114" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P114" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+        <x:v>真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="115">
@@ -17315,10 +17411,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O116" s="84" t="str">
-        <x:v>contracts/capacity-rules.schema.json/catalog.json/fixtures.json；contracts/layout-template.*.json；contracts/layout-slot.*.json；PROJECT_PLAN.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P116" s="86" t="str">
-        <x:v>已建立容量规则并接入 LayoutTemplate/Slot。覆盖字符、行、列表、图片、表格、图表和最小字号；真实样例无 slide 部件，未测阈值保留 unknown。</x:v>
+        <x:v>原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="117">
@@ -17492,10 +17588,14 @@
       </x:c>
       <x:c r="M120" s="84" t="str"/>
       <x:c r="N120" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O120" s="84" t="str"/>
-      <x:c r="P120" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O120" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P120" s="86" t="str">
+        <x:v>原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="83" t="str">
@@ -17534,10 +17634,14 @@
       </x:c>
       <x:c r="M121" s="84" t="str"/>
       <x:c r="N121" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O121" s="84" t="str"/>
-      <x:c r="P121" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O121" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P121" s="86" t="str">
+        <x:v>原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="83" t="str">
@@ -17576,10 +17680,14 @@
       </x:c>
       <x:c r="M122" s="84" t="str"/>
       <x:c r="N122" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O122" s="84" t="str"/>
-      <x:c r="P122" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O122" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P122" s="86" t="str">
+        <x:v>原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="83" t="str">
@@ -17751,10 +17859,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O126" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P126" s="86" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+        <x:v>实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="127">
@@ -17836,10 +17944,14 @@
       </x:c>
       <x:c r="M128" s="84" t="str"/>
       <x:c r="N128" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O128" s="84" t="str"/>
-      <x:c r="P128" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O128" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P128" s="86" t="str">
+        <x:v>实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="129">
       <x:c r="A129" s="83" t="str">
@@ -17881,10 +17993,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O129" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P129" s="86" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+        <x:v>实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="130">
@@ -17924,10 +18036,14 @@
       </x:c>
       <x:c r="M130" s="84" t="str"/>
       <x:c r="N130" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O130" s="84" t="str"/>
-      <x:c r="P130" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O130" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P130" s="86" t="str">
+        <x:v>真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="131">
       <x:c r="A131" s="83" t="str">
@@ -17966,10 +18082,14 @@
       </x:c>
       <x:c r="M131" s="84" t="str"/>
       <x:c r="N131" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O131" s="84" t="str"/>
-      <x:c r="P131" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O131" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P131" s="86" t="str">
+        <x:v>真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="132">
       <x:c r="A132" s="83" t="str">
@@ -18008,10 +18128,14 @@
       </x:c>
       <x:c r="M132" s="84" t="str"/>
       <x:c r="N132" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O132" s="84" t="str"/>
-      <x:c r="P132" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O132" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P132" s="86" t="str">
+        <x:v>真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="133">
       <x:c r="A133" s="83" t="str">
@@ -18179,10 +18303,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O136" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P136" s="86" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。</x:v>
+        <x:v>实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="137">
@@ -18222,10 +18346,14 @@
       </x:c>
       <x:c r="M137" s="84" t="str"/>
       <x:c r="N137" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O137" s="84" t="str"/>
-      <x:c r="P137" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O137" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P137" s="86" t="str">
+        <x:v>本地实际字节/hash/MIME核验和原子缓存运行；远程HTTPS/public-IP/redirect限制已编码但公开下载/重试原验收未执行。</x:v>
+      </x:c>
     </x:row>
     <x:row r="138">
       <x:c r="A138" s="83" t="str">
@@ -18306,10 +18434,14 @@
       </x:c>
       <x:c r="M139" s="84" t="str"/>
       <x:c r="N139" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O139" s="84" t="str"/>
-      <x:c r="P139" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O139" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P139" s="86" t="str">
+        <x:v>已批准节点/明示关系变为可编辑原生shape/connector，并保留evidence_quote；全图类型/布局/语义验收待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="140">
       <x:c r="A140" s="83" t="str">
@@ -18897,10 +19029,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O152" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P152" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+        <x:v>主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="153">
@@ -18945,10 +19077,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O153" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P153" s="86" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+        <x:v>主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="154">
@@ -19041,10 +19173,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O155" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P155" s="86" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+        <x:v>主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="156">
@@ -19721,10 +19853,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O170" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P170" s="86" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+        <x:v>主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="171">
@@ -19769,10 +19901,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O171" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P171" s="86" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。</x:v>
+        <x:v>主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="172">
@@ -20648,10 +20780,14 @@
       </x:c>
       <x:c r="M191" s="84" t="str"/>
       <x:c r="N191" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O191" s="84" t="str"/>
-      <x:c r="P191" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O191" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P191" s="86" t="str">
+        <x:v>持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+      </x:c>
     </x:row>
     <x:row r="192">
       <x:c r="A192" s="83" t="str">
@@ -20690,10 +20826,14 @@
       </x:c>
       <x:c r="M192" s="84" t="str"/>
       <x:c r="N192" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O192" s="84" t="str"/>
-      <x:c r="P192" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O192" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P192" s="86" t="str">
+        <x:v>已解析真实图片/hash/像素/MIME/许可与显式授权，真实生成消费；敏感文件/越界链接拒绝。全部来源/质量语义待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="193" ht="172.5" customHeight="1">
       <x:c r="A193" s="83" t="str">
@@ -20735,10 +20875,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O193" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P193" s="86" t="str">
-        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。</x:v>
+        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="172.5" customHeight="1">
@@ -20781,10 +20921,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O194" s="84" t="str">
-        <x:v>validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P194" s="86" t="str">
-        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。</x:v>
+        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="195" ht="172.5" customHeight="1">
@@ -20827,10 +20967,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O195" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P195" s="86" t="str">
-        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。</x:v>
+        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="172.5" customHeight="1">
@@ -20873,10 +21013,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O196" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P196" s="86" t="str">
-        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。</x:v>
+        <x:v>真实六页包含原生图片和可编辑流程，消费模板继承与跨页DAG。全部母版/布局/既有文件修改路线待验收。</x:v>
       </x:c>
     </x:row>
     <x:row r="197" ht="172.5" customHeight="1">
@@ -20919,10 +21059,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O197" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P197" s="86" t="str">
-        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。</x:v>
+        <x:v>六页PPTX实际LibreOffice PDF/PNG/hash渲染，QA-only恢复保持文件/渲染字节。live截图/全部renderer待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="198" ht="172.5" customHeight="1">
@@ -20965,10 +21105,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O198" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P198" s="86" t="str">
-        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。</x:v>
+        <x:v>结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="172.5" customHeight="1">
@@ -21011,10 +21151,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O199" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P199" s="86" t="str">
-        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。</x:v>
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="172.5" customHeight="1">
@@ -21552,10 +21692,14 @@
       </x:c>
       <x:c r="M211" s="84" t="str"/>
       <x:c r="N211" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O211" s="84" t="str"/>
-      <x:c r="P211" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O211" s="84" t="str">
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P211" s="86" t="str">
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="212">
       <x:c r="A212" s="83" t="str">
@@ -21723,10 +21867,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O215" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="P215" s="86" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -21766,10 +21910,14 @@
       </x:c>
       <x:c r="M216" s="84" t="str"/>
       <x:c r="N216" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O216" s="84" t="str"/>
-      <x:c r="P216" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O216" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P216" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="217">
       <x:c r="A217" s="83" t="str">
@@ -21850,10 +21998,14 @@
       </x:c>
       <x:c r="M218" s="84" t="str"/>
       <x:c r="N218" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O218" s="84" t="str"/>
-      <x:c r="P218" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O218" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P218" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="219">
       <x:c r="A219" s="83" t="str">
@@ -21892,10 +22044,14 @@
       </x:c>
       <x:c r="M219" s="84" t="str"/>
       <x:c r="N219" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O219" s="84" t="str"/>
-      <x:c r="P219" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O219" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P219" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="220">
       <x:c r="A220" s="83" t="str">
@@ -21934,10 +22090,14 @@
       </x:c>
       <x:c r="M220" s="84" t="str"/>
       <x:c r="N220" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O220" s="84" t="str"/>
-      <x:c r="P220" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O220" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P220" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="221">
       <x:c r="A221" s="83" t="str">
@@ -21976,10 +22136,14 @@
       </x:c>
       <x:c r="M221" s="84" t="str"/>
       <x:c r="N221" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O221" s="84" t="str"/>
-      <x:c r="P221" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O221" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P221" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="222">
       <x:c r="A222" s="83" t="str">
@@ -22060,10 +22224,14 @@
       </x:c>
       <x:c r="M223" s="84" t="str"/>
       <x:c r="N223" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O223" s="84" t="str"/>
-      <x:c r="P223" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O223" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P223" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="224">
       <x:c r="A224" s="83" t="str">
@@ -22102,10 +22270,14 @@
       </x:c>
       <x:c r="M224" s="84" t="str"/>
       <x:c r="N224" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O224" s="84" t="str"/>
-      <x:c r="P224" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O224" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P224" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="225">
       <x:c r="A225" s="83" t="str">
@@ -22144,10 +22316,14 @@
       </x:c>
       <x:c r="M225" s="84" t="str"/>
       <x:c r="N225" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O225" s="84" t="str"/>
-      <x:c r="P225" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O225" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P225" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="226">
       <x:c r="A226" s="83" t="str">
@@ -22186,10 +22362,14 @@
       </x:c>
       <x:c r="M226" s="84" t="str"/>
       <x:c r="N226" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O226" s="84" t="str"/>
-      <x:c r="P226" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O226" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P226" s="86" t="str">
+        <x:v>实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="227">
       <x:c r="A227" s="83" t="str">
@@ -22228,10 +22408,14 @@
       </x:c>
       <x:c r="M227" s="84" t="str"/>
       <x:c r="N227" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O227" s="84" t="str"/>
-      <x:c r="P227" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O227" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P227" s="86" t="str">
+        <x:v>实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="228">
       <x:c r="A228" s="83" t="str">
@@ -22270,10 +22454,14 @@
       </x:c>
       <x:c r="M228" s="84" t="str"/>
       <x:c r="N228" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O228" s="84" t="str"/>
-      <x:c r="P228" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O228" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P228" s="86" t="str">
+        <x:v>实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="229">
       <x:c r="A229" s="83" t="str">
@@ -22312,10 +22500,14 @@
       </x:c>
       <x:c r="M229" s="84" t="str"/>
       <x:c r="N229" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O229" s="84" t="str"/>
-      <x:c r="P229" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O229" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P229" s="86" t="str">
+        <x:v>实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="230">
       <x:c r="A230" s="83" t="str">
@@ -22354,10 +22546,14 @@
       </x:c>
       <x:c r="M230" s="84" t="str"/>
       <x:c r="N230" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O230" s="84" t="str"/>
-      <x:c r="P230" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O230" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P230" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="231">
       <x:c r="A231" s="83" t="str">
@@ -22396,10 +22592,14 @@
       </x:c>
       <x:c r="M231" s="84" t="str"/>
       <x:c r="N231" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O231" s="84" t="str"/>
-      <x:c r="P231" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O231" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P231" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="232">
       <x:c r="A232" s="83" t="str">
@@ -22438,10 +22638,14 @@
       </x:c>
       <x:c r="M232" s="84" t="str"/>
       <x:c r="N232" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O232" s="84" t="str"/>
-      <x:c r="P232" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O232" s="84" t="str">
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P232" s="86" t="str">
+        <x:v>实际局部RevisionPlan保留非目标ZIP成员/对象，before/after specs、hash及QA保存；全部未知部件/模式round-trip原验收未完成。</x:v>
+      </x:c>
     </x:row>
     <x:row r="233">
       <x:c r="A233" s="83" t="str">
@@ -22480,10 +22684,14 @@
       </x:c>
       <x:c r="M233" s="84" t="str"/>
       <x:c r="N233" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O233" s="84" t="str"/>
-      <x:c r="P233" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O233" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P233" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="234">
       <x:c r="A234" s="83" t="str">
@@ -22522,10 +22730,14 @@
       </x:c>
       <x:c r="M234" s="84" t="str"/>
       <x:c r="N234" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O234" s="84" t="str"/>
-      <x:c r="P234" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O234" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P234" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="235">
       <x:c r="A235" s="83" t="str">
@@ -22564,10 +22776,14 @@
       </x:c>
       <x:c r="M235" s="84" t="str"/>
       <x:c r="N235" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O235" s="84" t="str"/>
-      <x:c r="P235" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O235" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+      </x:c>
+      <x:c r="P235" s="86" t="str">
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="236">
       <x:c r="A236" s="83" t="str">
@@ -23282,10 +23498,14 @@
       </x:c>
       <x:c r="M252" s="84" t="str"/>
       <x:c r="N252" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O252" s="84" t="str"/>
-      <x:c r="P252" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O252" s="84" t="str">
+        <x:v>validation/visual-path-guards.json；validation/视觉决策与真实素材.md</x:v>
+      </x:c>
+      <x:c r="P252" s="86" t="str">
+        <x:v>素材/模板读取前拒绝secrets/.git/.ssh/.env及实际链接越界，23项真实路径guard通过；全部用户/输出/执行路径安全原验收仍待补。</x:v>
+      </x:c>
     </x:row>
     <x:row r="253">
       <x:c r="A253" s="83" t="str">
@@ -25737,7 +25957,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9375555822a24c0e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9932a1ca45304735"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26220,7 +26440,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M11" s="84" t="str">
-        <x:v>已有真实10页可编辑PPTX→render→部分QA→单对象修订；完整DEC/全部QA/所有P0 AC未通过。 证据：validation/generation-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 真实六页可编辑PPTX/渲染/QA-only恢复P0=0，原生RevisionPlan局部修订实物运行。4警告及完整QA/所有P0 AC仍未通过，系统非完成。</x:v>
       </x:c>
       <x:c r="N11" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31835,9 +32055,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L140" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M140" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M140" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模型消费文本/图文/表/图表/流程选择，原生执行并保留依据。完整矩阵/信息图等范围未完成。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N140" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31877,9 +32099,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L141" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M141" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M141" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N141" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31919,9 +32143,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L142" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M142" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M142" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 图片数量及信息/装饰角色进入实际规划，缺失图显式失败。信息价值/全语义相关性待验收。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N142" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -31961,9 +32187,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L143" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M143" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M143" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N143" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32003,9 +32231,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L144" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M144" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M144" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 模型仅选登记asset_id，解析真实文件/hash/许可授权，保留原模型声明。在线检索/生成服务未验收。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N144" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32045,9 +32275,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L145" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M145" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M145" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N145" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32087,9 +32319,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L146" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M146" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M146" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实结构化表格行列检查及原生写入，未补齐/裁剪数据。强调字段/分页/必要性完整验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N146" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32129,9 +32363,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L147" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M147" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M147" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N147" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32171,9 +32407,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L148" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M148" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M148" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ bar/column/line原生数据消费并检查维度。area/pie/scatter及完整分析目的策略未完成。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N148" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32213,9 +32451,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L149" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M149" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M149" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N149" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32255,9 +32495,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L150" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M150" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M150" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已批准原文节点和明示顺序箭头进入原生形状/连接线。拒绝词法猜测因果，完整七类关系图语义待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N150" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32297,9 +32539,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L151" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M151" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M151" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N151" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32339,9 +32583,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L152" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M152" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M152" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N152" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32381,9 +32627,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L153" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M153" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M153" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N153" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32423,9 +32671,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L154" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M154" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M154" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模型及writer消费字体/色板/背景/形状语言，保留来源与默认值。完整效果/设计tokens未验收。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N154" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32465,9 +32715,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L155" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M155" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M155" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N155" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32510,7 +32762,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M156" s="84" t="str">
-        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
       <x:c r="N156" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32554,7 +32806,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M157" s="84" t="str">
-        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
       </x:c>
       <x:c r="N157" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32598,7 +32850,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M158" s="84" t="str">
-        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
       <x:c r="N158" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32642,7 +32894,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M159" s="84" t="str">
-        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
       </x:c>
       <x:c r="N159" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32683,9 +32935,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L160" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M160" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M160" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N160" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32725,9 +32979,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L161" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M161" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M161" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N161" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32770,7 +33026,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M162" s="84" t="str">
-        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
       </x:c>
       <x:c r="N162" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32814,7 +33070,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M163" s="84" t="str">
-        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
       </x:c>
       <x:c r="N163" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32858,7 +33114,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M164" s="84" t="str">
-        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
       </x:c>
       <x:c r="N164" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32902,7 +33158,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M165" s="84" t="str">
-        <x:v>当前子集23项核验及真实产物；完整节点输入输出、五项目对应和全部原验收继续。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
       </x:c>
       <x:c r="N165" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32943,9 +33199,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L166" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M166" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M166" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 填充/描边/背景/对比及声明设计变化实际消费。渐变/阴影/透明度等完整效果待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N166" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -32985,9 +33243,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L167" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M167" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M167" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N167" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33027,9 +33287,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L168" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M168" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M168" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N168" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33069,9 +33331,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L169" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M169" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M169" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N169" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33111,9 +33375,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L170" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M170" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M170" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 实际备注进入原生notes；动画/切换不支持时显式报告，未当作交付。完整演示增强待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N170" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33153,9 +33419,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L171" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M171" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M171" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N171" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33195,9 +33463,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L172" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M172" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M172" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 已消费能力登记与PP-05实际原子DAG预执行，缺口结构化失败。九路线动态选择/模板round-trip全验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N172" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33237,9 +33507,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L173" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M173" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M173" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N173" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33279,9 +33551,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L174" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M174" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M174" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 质量问题映射RevisionPlan及fail/输入需求，原生局部布局/样式修订真实执行，未修改part保持。全部节点重跑未完成。完整原验收仍未通过。</x:v>
+      </x:c>
       <x:c r="N174" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33321,9 +33595,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L175" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M175" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M175" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N175" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33363,9 +33639,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L176" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M176" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M176" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 真实六页QA-only恢复P0=0保留4警告，19项接口/恢复与10项重复恢复各自记录；轨迹齐全仍warning/not_passed，不是40节点原验收完成。</x:v>
+      </x:c>
       <x:c r="N176" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33405,9 +33683,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L177" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M177" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M177" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N177" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33448,7 +33728,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M178" s="84" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
       <x:c r="N178" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33616,7 +33896,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M182" s="84" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模板注册、源文件/hash/license、母版/布局/主题tokens进入生成；未知容量/字体许可保留未知，完整tokens与三上游验收待补。</x:v>
       </x:c>
       <x:c r="N182" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33700,7 +33980,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M184" s="84" t="str">
-        <x:v>contracts/capacity-rules.schema.json/catalog.json/fixtures.json；contracts/layout-template.*.json；contracts/layout-slot.*.json；PROJECT_PLAN.md；以 source_review_only fixture 记录无实测容量，产品阈值待验证。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
       </x:c>
       <x:c r="N184" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33863,9 +34143,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L188" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M188" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M188" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
       <x:c r="N188" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33903,9 +34185,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L189" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M189" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M189" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
       <x:c r="N189" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -33943,9 +34227,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L190" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M190" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M190" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生布局语法/容量/分配/多样性实际编译图片及关系图，不裁正文。全部槽位类型、自适应拆合及三上游模板验收待补。</x:v>
+      </x:c>
       <x:c r="N190" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34108,7 +34394,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M194" s="84" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
       <x:c r="N194" s="86" t="str">
         <x:v>本规划</x:v>
@@ -34187,9 +34473,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L196" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M196" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M196" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
+      </x:c>
       <x:c r="N196" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34230,7 +34518,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M197" s="84" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
       <x:c r="N197" s="86" t="str">
         <x:v>本规划</x:v>
@@ -34269,9 +34557,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L198" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M198" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M198" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
       <x:c r="N198" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34309,9 +34599,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L199" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M199" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M199" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 真实图片DPI/像素和角色区分、低质量警告保留；模型图片/文案复审已执行。水印/压缩/主体和完整语义相关性待补。</x:v>
+      </x:c>
       <x:c r="N199" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34349,9 +34641,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L200" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M200" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M200" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+      </x:c>
       <x:c r="N200" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34512,7 +34806,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M204" s="84" t="str">
-        <x:v>资产目录/图片像素、DPI、aspect、格式、alpha、ICC、主色与dHash已运行；完全哈希与感知重复仅候选，许可unknown显式保留。全部来源/类型、生成下载、语义相关性、重复授权/裁切及原验收待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记素材来源、hash/像素/MIME/授权/unknownlicense及重复候选，画像选择进入PPTX。未知许可不当作已授权版权；全类型/语义重复待补。</x:v>
       </x:c>
       <x:c r="N204" s="86" t="str">
         <x:v>本规划</x:v>
@@ -34551,9 +34845,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L205" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M205" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M205" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本地实际字节/hash/MIME核验和原子缓存运行；远程HTTPS/public-IP/redirect限制已编码但公开下载/重试原验收未执行。</x:v>
+      </x:c>
       <x:c r="N205" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34631,9 +34927,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L207" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M207" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M207" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已批准节点/明示关系变为可编辑原生shape/connector，并保留evidence_quote；全图类型/布局/语义验收待补。</x:v>
+      </x:c>
       <x:c r="N207" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35606,7 +35904,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M230" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
       <x:c r="N230" s="86" t="str">
         <x:v>本规划</x:v>
@@ -35647,9 +35945,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L231" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M231" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M231" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N231" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35692,7 +35992,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M232" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
       <x:c r="N232" s="86" t="str">
         <x:v>本规划</x:v>
@@ -35733,9 +36033,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L233" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M233" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M233" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N233" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -35864,7 +36166,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M236" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
       <x:c r="N236" s="86" t="str">
         <x:v>本规划</x:v>
@@ -35905,9 +36207,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L237" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M237" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M237" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N237" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37134,7 +37438,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M266" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
       <x:c r="N266" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37175,9 +37479,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L267" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M267" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M267" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N267" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -37220,7 +37526,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M268" s="84" t="str">
-        <x:v>PP-05原生文字/形状/线/组/图片/表/图表实际创建，已有PPT可定向修改并保留未知部件/非目标形状；32项实物检查及CLI/API/MCP入口。能力清单逐CRUD/保真/渲染标partial/unsupported，不表示全部对象子能力或Office专属功能完成。 validation/native-object-artifacts/；validation/原生对象与既有PPT修订.md；validation/parallel-integration.json</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 主生成DAG实际创建shape/connector/图片，stable ObjectMap/元数据/alt-text与渲染证据保存；PP-05部分能力，不代替全部CRUD/路线验收。</x:v>
       </x:c>
       <x:c r="N268" s="86" t="str">
         <x:v>本规划</x:v>
@@ -37261,9 +37567,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L269" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M269" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M269" s="84" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N269" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38547,9 +38855,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L300" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M300" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M300" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+      </x:c>
       <x:c r="N300" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38587,9 +38897,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L301" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M301" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M301" s="84" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已解析真实图片/hash/像素/MIME/许可与显式授权，真实生成消费；敏感文件/越界链接拒绝。全部来源/质量语义待补。</x:v>
+      </x:c>
       <x:c r="N301" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -38630,7 +38942,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M302" s="84" t="str">
-        <x:v>统一规格实际消费内容驱动候选、槽位、每页样式并写入真实十页；完整素材、模板和绑定待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
       <x:c r="N302" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38672,7 +38984,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M303" s="84" t="str">
-        <x:v>预执行消费归一化约束及输出要求，能力登记仍实际绑定；完整后端预执行和能力缺口范围待完成。 validation/context-runtime.json；validation/context-artifacts/；validation/约束归一化与来源分流.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
       <x:c r="N303" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38714,7 +39026,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M304" s="84" t="str">
-        <x:v>原生文本面板、字号、边距、描边与逐页样式经登记输入校验和实际写入；全部对象及失败恢复待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
       <x:c r="N304" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38756,7 +39068,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M305" s="84" t="str">
-        <x:v>十页实际顺序构建并保存布局评分，恢复时维持槽位对象身份；完整模板、母版与导入修改待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实六页包含原生图片和可编辑流程，消费模板继承与跨页DAG。全部母版/布局/既有文件修改路线待验收。</x:v>
       </x:c>
       <x:c r="N305" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38798,7 +39110,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M306" s="84" t="str">
-        <x:v>实际渲染PDF、PNG及坐标文字；主产物哈希与版本保留，live与完整缩略图范围待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 六页PPTX实际LibreOffice PDF/PNG/hash渲染，QA-only恢复保持文件/渲染字节。live截图/全部renderer待补。</x:v>
       </x:c>
       <x:c r="N306" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38840,7 +39152,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M307" s="84" t="str">
-        <x:v>生成/QA用已选事实投影；UUID元数据与明确否决值备注分开检查，事实/假设/占位边界参与检查。真实四页P0=0，完整质量及AC待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
       </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38882,7 +39194,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M308" s="84" t="str">
-        <x:v>单文本修订沿用已选事实及冲突轨迹，快照缺失/hash变化或被否决数值在写入前阻断；实际单part修订和复审已运行。完整修订计划/对象/原验收待完成。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
       </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39379,9 +39691,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L320" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M320" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M320" s="84" t="str">
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+      </x:c>
       <x:c r="N320" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39542,7 +39856,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M324" s="84" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
       </x:c>
       <x:c r="N324" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39581,9 +39895,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L325" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M325" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M325" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N325" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39623,9 +39939,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L326" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M326" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M326" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N326" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39745,9 +40063,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L329" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M329" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M329" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N329" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39787,9 +40107,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L330" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M330" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M330" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N330" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39827,9 +40149,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L331" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M331" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M331" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N331" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39869,9 +40193,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L332" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M332" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M332" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N332" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39909,9 +40235,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L333" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M333" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M333" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N333" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39951,9 +40279,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L334" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M334" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M334" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N334" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39991,9 +40321,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L335" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M335" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M335" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N335" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40033,9 +40365,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L336" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M336" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M336" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N336" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40155,9 +40489,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L339" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M339" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M339" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N339" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40197,9 +40533,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L340" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M340" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M340" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N340" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40237,9 +40575,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L341" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M341" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M341" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N341" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40279,9 +40619,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L342" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M342" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M342" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N342" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40319,9 +40661,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L343" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M343" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M343" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N343" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40361,9 +40705,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L344" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M344" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M344" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N344" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40401,9 +40747,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L345" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M345" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M345" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
       <x:c r="N345" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40443,9 +40791,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L346" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M346" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M346" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N346" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40483,9 +40833,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L347" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M347" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M347" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
       <x:c r="N347" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40525,9 +40877,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L348" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M348" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M348" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N348" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40565,9 +40919,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L349" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M349" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M349" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
       <x:c r="N349" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40607,9 +40963,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L350" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M350" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M350" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N350" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40647,9 +41005,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L351" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M351" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M351" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 实际表/图数据数值引用核验及真实模型视觉/事实复审，六页QA-only保留审查警告。语义真值、全部图表/表格与完整正负样例待补。</x:v>
+      </x:c>
       <x:c r="N351" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40689,9 +41049,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L352" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M352" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M352" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N352" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40729,9 +41091,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L353" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M353" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M353" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N353" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40771,9 +41135,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L354" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M354" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M354" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N354" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40811,9 +41177,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L355" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M355" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M355" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N355" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40853,9 +41221,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L356" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M356" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M356" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N356" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40893,9 +41263,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L357" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M357" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M357" s="84" t="str">
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 实际局部RevisionPlan保留非目标ZIP成员/对象，before/after specs、hash及QA保存；全部未知部件/模式round-trip原验收未完成。</x:v>
+      </x:c>
       <x:c r="N357" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40935,9 +41307,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L358" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M358" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M358" s="84" t="str">
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N358" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40975,9 +41349,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L359" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M359" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M359" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N359" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41017,9 +41393,11 @@
         <x:v>P1</x:v>
       </x:c>
       <x:c r="L360" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M360" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M360" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N360" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41057,9 +41435,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L361" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M361" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M361" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N361" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41099,9 +41479,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L362" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M362" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M362" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N362" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41139,9 +41521,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L363" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M363" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M363" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+      </x:c>
       <x:c r="N363" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41181,9 +41565,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L364" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M364" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M364" s="84" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N364" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41863,9 +42249,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L381" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M381" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M381" s="84" t="str">
+        <x:v>validation/visual-path-guards.json；validation/视觉决策与真实素材.md 素材/模板读取前拒绝secrets/.git/.ssh/.env及实际链接越界，23项真实路径guard通过；全部用户/输出/执行路径安全原验收仍待补。</x:v>
+      </x:c>
       <x:c r="N381" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -41905,9 +42293,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L382" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M382" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M382" s="84" t="str">
+        <x:v>validation/visual-path-guards.json；validation/视觉决策与真实素材.md 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+      </x:c>
       <x:c r="N382" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44854,7 +45244,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R348bf6f4b77d48fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda5842e35384a2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45148,7 +45538,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40c4c29143d34558"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67117c179ec94610"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46564,7 +46954,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R748d51432e354eb3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ea23a51a084a31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46986,7 +47376,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd702583dd6004b41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra80c0f96735a4889"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47549,7 +47939,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I12" s="84" t="str">
-        <x:v>partial: rectangle/ellipse/rounded rectangle/arrows; fill/stroke/rotation</x:v>
+        <x:v>Partial：主生成与RevisionPlan实际消费原生图片/shape/connector/ObjectMap；全部CRUD及该能力全范围未通过。</x:v>
       </x:c>
       <x:c r="J12" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47566,7 +47956,7 @@
       <x:c r="N12" s="84" t="str"/>
       <x:c r="O12" s="84" t="str"/>
       <x:c r="P12" s="86" t="str">
-        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -47595,7 +47985,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I13" s="84" t="str">
-        <x:v>partial: straight/elbow/curved connectors; connection points/reroute/freeform not implemented</x:v>
+        <x:v>Partial：主生成与RevisionPlan实际消费原生图片/shape/connector/ObjectMap；全部CRUD及该能力全范围未通过。</x:v>
       </x:c>
       <x:c r="J13" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47612,7 +48002,7 @@
       <x:c r="N13" s="84" t="str"/>
       <x:c r="O13" s="84" t="str"/>
       <x:c r="P13" s="86" t="str">
-        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -47687,7 +48077,7 @@
         <x:v>Partial</x:v>
       </x:c>
       <x:c r="I15" s="84" t="str">
-        <x:v>partial: embedded PNG/JPEG create/read/replace; crop/effects not implemented; shared image replacement rejected</x:v>
+        <x:v>Partial：主生成与RevisionPlan实际消费原生图片/shape/connector/ObjectMap；全部CRUD及该能力全范围未通过。</x:v>
       </x:c>
       <x:c r="J15" s="84" t="str">
         <x:v>Untested</x:v>
@@ -47704,7 +48094,7 @@
       <x:c r="N15" s="84" t="str"/>
       <x:c r="O15" s="84" t="str"/>
       <x:c r="P15" s="86" t="str">
-        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -48377,7 +48767,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I30" s="84" t="str">
-        <x:v>partial: alt text and shape order indexing; complete accessibility audit not implemented</x:v>
+        <x:v>Partial：主生成与RevisionPlan实际消费原生图片/shape/connector/ObjectMap；全部CRUD及该能力全范围未通过。</x:v>
       </x:c>
       <x:c r="J30" s="84" t="str">
         <x:v>Untested</x:v>
@@ -48394,7 +48784,7 @@
       <x:c r="N30" s="84" t="str"/>
       <x:c r="O30" s="84" t="str"/>
       <x:c r="P30" s="86" t="str">
-        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -48423,7 +48813,7 @@
         <x:v>Untested</x:v>
       </x:c>
       <x:c r="I31" s="88" t="str">
-        <x:v>partial: slide-id + shape-id stable mapping; extension/custom XML preserved</x:v>
+        <x:v>Partial：主生成与RevisionPlan实际消费原生图片/shape/connector/ObjectMap；全部CRUD及该能力全范围未通过。</x:v>
       </x:c>
       <x:c r="J31" s="88" t="str">
         <x:v>Untested</x:v>
@@ -48440,7 +48830,7 @@
       <x:c r="N31" s="88" t="str"/>
       <x:c r="O31" s="88" t="str"/>
       <x:c r="P31" s="90" t="str">
-        <x:v>validation/native-object-artifacts/native-object-runtime.json；validation/native-object-artifacts/preservation-report.json；仅PP-05组件范围，全对象原验收未通过</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -49602,9 +49992,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M23" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N23" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N23" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模型消费文本/图文/表/图表/流程选择，原生执行并保留依据。完整矩阵/信息图等范围未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -49644,9 +50036,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M24" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N24" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N24" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 图片数量及信息/装饰角色进入实际规划，缺失图显式失败。信息价值/全语义相关性待验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="83" t="str">
@@ -49686,9 +50080,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M25" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N25" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N25" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 模型仅选登记asset_id，解析真实文件/hash/许可授权，保留原模型声明。在线检索/生成服务未验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="83" t="str">
@@ -49728,9 +50124,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M26" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N26" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N26" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实结构化表格行列检查及原生写入，未补齐/裁剪数据。强调字段/分页/必要性完整验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="83" t="str">
@@ -49770,9 +50168,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M27" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N27" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N27" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ bar/column/line原生数据消费并检查维度。area/pie/scatter及完整分析目的策略未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="83" t="str">
@@ -49812,9 +50212,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M28" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N28" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N28" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 已批准原文节点和明示顺序箭头进入原生形状/连接线。拒绝词法猜测因果，完整七类关系图语义待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="83" t="str">
@@ -49854,9 +50256,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M29" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N29" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N29" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -49896,9 +50300,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M30" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N30" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N30" s="86" t="str">
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 真实模型及writer消费字体/色板/背景/形状语言，保留来源与默认值。完整效果/设计tokens未验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="83" t="str">
@@ -49941,7 +50347,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N31" s="86" t="str">
-        <x:v>七类原生文本、表格、图表版式按内容槽位及实际容量生成候选；素材比例、完整类型及独立正式节点契约待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -49985,7 +50391,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N32" s="86" t="str">
-        <x:v>实际容量、开场结尾层级与相邻变化参与评分，失败候选保留理由；完整语义、品牌、素材、多后端与正式节点验收待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -50026,9 +50432,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M33" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N33" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N33" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="83" t="str">
@@ -50071,7 +50479,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N34" s="86" t="str">
-        <x:v>已实际执行文本、表格、图表几何槽位与非重叠检查；连接线、裁切、旋转及完整类型待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -50115,7 +50523,7 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N35" s="86" t="str">
-        <x:v>已实测中文字形、字号、段距、边距与容量，超出全部候选时失败；RTL、字体替代和完整文本适配待完成。 validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -50156,9 +50564,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M36" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N36" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N36" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/ 填充/描边/背景/对比及声明设计变化实际消费。渐变/阴影/透明度等完整效果待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="83" t="str">
@@ -50198,9 +50608,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M37" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N37" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N37" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="83" t="str">
@@ -50240,9 +50652,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M38" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N38" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N38" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 实际备注进入原生notes；动画/切换不支持时显式报告，未当作交付。完整演示增强待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="83" t="str">
@@ -50282,9 +50696,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M39" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N39" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N39" s="86" t="str">
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 已消费能力登记与PP-05实际原子DAG预执行，缺口结构化失败。九路线动态选择/模板round-trip全验收待补。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -50324,9 +50740,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M40" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N40" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N40" s="86" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/ 质量问题映射RevisionPlan及fail/输入需求，原生局部布局/样式修订真实执行，未修改part保持。全部节点重跑未完成。完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="87" t="str">
@@ -50366,9 +50784,11 @@
         <x:v>planning/schema/theme/layout/render/QA/revise/MCP</x:v>
       </x:c>
       <x:c r="M41" s="88" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="N41" s="90" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="N41" s="90" t="str">
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 真实六页QA-only恢复P0=0保留4警告，19项接口/恢复与10项重复恢复各自记录；轨迹齐全仍warning/not_passed，不是40节点原验收完成。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="M2:M41">
@@ -50383,7 +50803,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0cef7e73256f42e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12ba011168564f60"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rb3dd0649d4ee48c5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R4239cb07b6fd4f34"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rffa94b4636df4212"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R173bc81da42c4f0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R0b272917fcda4fcb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R46df0c05fb77444a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R0165750b9a3047ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R23293dd03c304beb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R2e79a9405f38481e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rbc70329469a343e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R43e80a73c55c4b7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rb9daab412954473a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R760c7e7fdea7499e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R4d012af11f524a4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R78d1ed1ab8254021"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="Rbed12595064647af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R8205ab65f8494813"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rb980d080c495409f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R48b4c75f37ef491a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R9f38c90bffd6445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd0f8aa1e140c43d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rbd62915834c24c01"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R13bdebb329174f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Re3ddb367399d4137"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9c08a9817e48433a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6d09165b5cd94f2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4f8c976a5cea4639"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rdc0a194ab31e4ba0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8dfaf6ae67844ab2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R11fabb9c31854b36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R548a3ec11a934ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rdaa3a3274e914ad1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R067151f2eba944e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9143c60e3295426e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R890c678e562848a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6e4aede425404ee9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R345d5b848c5c4e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc1ea2e09c54e41fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9608174f2b024d06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R183622d5024f4c20"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R905452fb79d34c4b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R314a57d3b1c0455d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85268bea81e8472e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra950f2f9d6264110"/>
 </x:worksheet>
 </file>
 
@@ -2524,7 +2524,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I3" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -2553,7 +2554,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -2582,7 +2584,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I5" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -2637,9 +2640,12 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I7" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I7" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -2693,9 +2699,12 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I9" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I9" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -2892,9 +2901,12 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H16" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I16" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I16" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="87" t="str">
@@ -2919,9 +2931,12 @@
         <x:v>通过至少 PPT Master、Presenton、ai-agent-ppt 与真实 PPTX master/layout 样例验证。</x:v>
       </x:c>
       <x:c r="H17" s="88" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I17" s="90" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I17" s="90" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="H2:H17">
@@ -3034,9 +3049,12 @@
         <x:v>本规划</x:v>
       </x:c>
       <x:c r="H3" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="I3" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="I3" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -3180,7 +3198,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I8" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3909,7 +3928,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I9" s="86" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -3967,7 +3987,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I11" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -4025,7 +4046,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I13" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -8966,11 +8988,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G7" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H7" s="84" t="str"/>
-      <x:c r="I7" s="84" t="str"/>
-      <x:c r="J7" s="86" t="str"/>
+        <x:v>部分执行</x:v>
+      </x:c>
+      <x:c r="H7" s="84" t="str">
+        <x:v>组件汇总时记录：原生模板68项及后续2项边界已执行，4套真实PPTX/PDF/PNG、品牌对象保持、正式编译/断点实物存在。原要求为真实PPTX master/layout/logo/footer、保持结构/品牌锁/内容可编辑的全链SYS/QA。三上游模板族、全部复杂品牌/页面模式/PowerPoint桌面及当前真实AI任务独立复审未完成；模板多图槽与focal-only cover显式未支持。 集成后新增：当前真实四页恢复及独立模型复审已执行（人工素材输入），P0=0、5警告保留；详见fresh_api。完整原条件仍未通过。</x:v>
+      </x:c>
+      <x:c r="I7" s="84" t="str">
+        <x:v>validation/template-slot-artifacts/template-slots.json；validation/template-slot-artifacts/template-gallery-guard.json；validation/template-slot-artifacts/export-manifest.json；validation/native-capacity-live-artifacts/current-resumed/quality-report.json；validation/native-capacity-integration.json</x:v>
+      </x:c>
+      <x:c r="J7" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -9122,11 +9150,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G13" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H13" s="84" t="str"/>
-      <x:c r="I13" s="84" t="str"/>
-      <x:c r="J13" s="86" t="str"/>
+        <x:v>部分执行</x:v>
+      </x:c>
+      <x:c r="H13" s="84" t="str">
+        <x:v>组件汇总时记录：8张不同宽高比人工素材的选定/显式裁切/布局/无拉伸/DPI和图注已在32项及长标题5项增量中形成原生实物；原验收要求用户8张图的自动选图/裁切/布局全链SYS/QA。真实用户图像AI独立相关性/图质复审及完整全链尚未通过，当前fresh API结果待ROOT追加，不把人工光栅夹具称作用户图验收。 集成后新增：当前真实四页恢复及独立模型复审已执行（人工素材输入），P0=0、5警告保留；详见fresh_api。完整原条件仍未通过。</x:v>
+      </x:c>
+      <x:c r="I13" s="84" t="str">
+        <x:v>validation/gallery-artifacts/b81e5a47-0d59-4963-87a5-daa257d654ef/gallery-runtime.json；validation/gallery-artifacts/long-title-ae033e62/gallery-long-title-runtime.json；validation/gallery-artifacts/source-evidence.json；validation/native-capacity-live-artifacts/current-resumed/quality-report.json；validation/native-capacity-integration.json</x:v>
+      </x:c>
+      <x:c r="J13" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -9174,11 +9208,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G15" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H15" s="84" t="str"/>
-      <x:c r="I15" s="84" t="str"/>
-      <x:c r="J15" s="86" t="str"/>
+        <x:v>部分执行</x:v>
+      </x:c>
+      <x:c r="H15" s="84" t="str">
+        <x:v>组件汇总时记录：26行及25列表格实际自适应分页形成10页可编辑原生表格并真实渲染，161项组件套件内核对完整值/单位；已有PDF228项单元格只读核对另列。原验收为大表/多列容量超限处理且不缩至不可读的全链SYS/QA。复杂合并表格、全部模板约束、独立语义/视觉模型审查与新API全链结果仍未完成。 集成后新增：当前真实四页恢复及独立模型复审已执行（人工素材输入），P0=0、5警告保留；详见fresh_api。完整原条件仍未通过。</x:v>
+      </x:c>
+      <x:c r="I15" s="84" t="str">
+        <x:v>validation/adaptive-content-artifacts/current-font-metrics-success/adaptive-content-verification.json；validation/adaptive-content-artifacts/current-font-metrics-success/table-render-bbox-audit.json；validation/adaptive-content-artifacts/export-manifest.json；validation/native-capacity-live-artifacts/current-resumed/quality-report.json；validation/native-capacity-integration.json</x:v>
+      </x:c>
+      <x:c r="J15" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -9200,11 +9240,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G16" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H16" s="84" t="str"/>
-      <x:c r="I16" s="84" t="str"/>
-      <x:c r="J16" s="86" t="str"/>
+        <x:v>部分执行</x:v>
+      </x:c>
+      <x:c r="H16" s="84" t="str">
+        <x:v>组件汇总时记录：混合长标题/完整列表分页已在161项组件套件执行；八图长标题另外5项增量实物扩标题框而不缩字，渲染/确定性QA无问题。原验收为超长中英混合标题与列表实际触发ContentBudget/AdaptiveLayout且无overflow的全链SYS/QA。全部页面/锁定模板/极端文本组合、独立模型复审和当前fresh API最终结果尚未完成。 集成后新增：当前真实四页恢复及独立模型复审已执行（人工素材输入），P0=0、5警告保留；详见fresh_api。完整原条件仍未通过。</x:v>
+      </x:c>
+      <x:c r="I16" s="84" t="str">
+        <x:v>validation/adaptive-content-artifacts/current-font-metrics-success/adaptive-content-verification.json；validation/gallery-artifacts/long-title-ae033e62/gallery-long-title-runtime.json；validation/adaptive-content-artifacts/export-manifest.json；validation/native-capacity-live-artifacts/current-resumed/quality-report.json；validation/native-capacity-integration.json</x:v>
+      </x:c>
+      <x:c r="J16" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -10272,7 +10318,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd19b0e6741f1497b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbac281eee7384348"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10835,10 +10881,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H19" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I19" s="86" t="str">
-        <x:v>实际测量文本/表格槽位，容量不足明确失败；语义改写、拆合及图片预算待完成。</x:v>
+        <x:v>实际测量文本/表格槽位，容量不足明确失败；语义改写、拆合及图片预算待完成。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="195" customHeight="1">
@@ -10864,10 +10911,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H20" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I20" s="86" t="str">
-        <x:v>DEC022–029实际选择文本/图/表/图表/流程，语义价值全验收待补。</x:v>
+        <x:v>DEC022–029实际选择文本/图/表/图表/流程，语义价值全验收待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -10893,10 +10941,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H21" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I21" s="86" t="str">
-        <x:v>真实图片asset_id/文件/hash/许可与授权进入主生成；在线检索/生成服务未验收。</x:v>
+        <x:v>真实图片asset_id/文件/hash/许可与授权进入主生成；在线检索/生成服务未验收。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="195" customHeight="1">
@@ -10922,10 +10971,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H22" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I22" s="86" t="str">
-        <x:v>真实模板文件及母版/布局/主题/styles解析进入生成；全部tokens/品牌锁待补。</x:v>
+        <x:v>真实模板文件及母版/布局/主题/styles解析进入生成；全部tokens/品牌锁待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -11067,10 +11117,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H27" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I27" s="86" t="str">
-        <x:v>原生几何/节点/连接端点计算，真实写入渲染；freeform及所有关系布局待补。</x:v>
+        <x:v>原生几何/节点/连接端点计算，真实写入渲染；freeform及所有关系布局待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="195" customHeight="1">
@@ -11096,10 +11147,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I28" s="86" t="str">
-        <x:v>字体/填充/描边/背景与声明设计变化进入实际执行；全效果待补。</x:v>
+        <x:v>字体/填充/描边/背景与声明设计变化进入实际执行；全效果待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="195" customHeight="1">
@@ -11125,10 +11177,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H29" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I29" s="86" t="str">
-        <x:v>实际notes执行；动画/切换未支持显式报告，完整增强待补。</x:v>
+        <x:v>实际notes执行；动画/切换未支持显式报告，完整增强待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="195" customHeight="1">
@@ -11154,10 +11207,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H30" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I30" s="86" t="str">
-        <x:v>图片与流程的统一spec实际消费；全对象/模板/绑定验收待补。</x:v>
+        <x:v>图片与流程的统一spec实际消费；全对象/模板/绑定验收待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="195" customHeight="1">
@@ -11183,10 +11237,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H31" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I31" s="86" t="str">
-        <x:v>素材hash/权限、字体、schema、容量和原子能力检查；所有路径与后端缺口待补。</x:v>
+        <x:v>素材hash/权限、字体、schema、容量和原子能力检查；所有路径与后端缺口待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="195" customHeight="1">
@@ -11212,10 +11267,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H32" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I32" s="86" t="str">
-        <x:v>当前PP-05原子实现已选择，九路线动态选择原验收待补。</x:v>
+        <x:v>当前PP-05原子实现已选择，九路线动态选择原验收待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="195" customHeight="1">
@@ -11241,10 +11297,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H33" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I33" s="86" t="str">
-        <x:v>图片/shape/connector进入真实DAG及ObjectMap；全部对象复杂依赖待补。</x:v>
+        <x:v>图片/shape/connector进入真实DAG及ObjectMap；全部对象复杂依赖待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="195" customHeight="1">
@@ -11270,10 +11327,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H34" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I34" s="86" t="str">
-        <x:v>真实六页原生图片/流程PPTX与局部RevisionPlan已保存；全部模式和保真待补。</x:v>
+        <x:v>真实六页原生图片/流程PPTX与局部RevisionPlan已保存；全部模式和保真待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="195" customHeight="1">
@@ -11299,10 +11357,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H35" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I35" s="86" t="str">
-        <x:v>实际PDF/逐页PNG/hash版本保存，QA-only复用字节；live/全部缩略图待补。</x:v>
+        <x:v>实际PDF/逐页PNG/hash版本保存，QA-only复用字节；live/全部缩略图待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="195" customHeight="1">
@@ -11328,10 +11387,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H36" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I36" s="86" t="str">
-        <x:v>部分原生结构/边界/空对象/碰撞/溢出检查运行；完整结构验收待补。</x:v>
+        <x:v>部分原生结构/边界/空对象/碰撞/溢出检查运行；完整结构验收待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="195" customHeight="1">
@@ -11357,10 +11417,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H37" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I37" s="86" t="str">
-        <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。</x:v>
+        <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="195" customHeight="1">
@@ -11386,10 +11447,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H38" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
       </x:c>
       <x:c r="I38" s="86" t="str">
-        <x:v>数值引用与真实模型事实复审，图片尺寸仅对同页实际hash/像素验证后排除元数据；完整语义真值待补。</x:v>
+        <x:v>数值引用与真实模型事实复审，图片尺寸仅对同页实际hash/像素验证后排除元数据；完整语义真值待补。
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="195" customHeight="1">
@@ -11637,7 +11699,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17684678187b4088"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c7064ae8c2b43ef"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15841,10 +15903,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O83" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P83" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
@@ -15889,10 +15952,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O84" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P84" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="85">
@@ -15937,10 +16001,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O85" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P85" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="86">
@@ -15985,10 +16050,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O86" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P86" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="87">
@@ -16033,10 +16099,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O87" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P87" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="88">
@@ -16081,10 +16148,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O88" s="84" t="str">
-        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P88" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="89">
@@ -16513,10 +16581,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O97" s="84" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P97" s="86" t="str">
-        <x:v>实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+        <x:v>实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="98">
@@ -16609,10 +16678,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O99" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/</x:v>
       </x:c>
       <x:c r="P99" s="86" t="str">
-        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="100">
@@ -16657,10 +16727,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O100" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/</x:v>
       </x:c>
       <x:c r="P100" s="86" t="str">
-        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="101">
@@ -16705,10 +16776,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O101" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P101" s="86" t="str">
-        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="102">
@@ -16753,10 +16825,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O102" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/</x:v>
       </x:c>
       <x:c r="P102" s="86" t="str">
-        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="103">
@@ -16801,10 +16874,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O103" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/</x:v>
       </x:c>
       <x:c r="P103" s="86" t="str">
-        <x:v>CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
+        <x:v>CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="104">
@@ -16897,10 +16971,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O105" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/</x:v>
       </x:c>
       <x:c r="P105" s="86" t="str">
-        <x:v>原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+        <x:v>原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="106">
@@ -17181,10 +17256,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O111" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P111" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="112">
@@ -17227,10 +17303,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O112" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P112" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="113">
@@ -17273,10 +17350,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O113" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/parallel-integration.json；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P113" s="86" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="114">
@@ -17365,10 +17443,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O115" s="84" t="str">
-        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md</x:v>
+        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P115" s="86" t="str">
-        <x:v>已建立带证据的候选/未知关系；产品 parser/runtime、决策评分、渲染和 AC 验证待完成</x:v>
+        <x:v>已建立带证据的候选/未知关系；产品 parser/runtime、决策评分、渲染和 AC 验证待完成
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="116">
@@ -17457,10 +17536,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O117" s="84" t="str">
-        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008</x:v>
+        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P117" s="86" t="str">
-        <x:v>静态 crosswalk 覆盖 4 类来源；P03=unknown、subTitle=unmapped；runtime 待验。</x:v>
+        <x:v>静态 crosswalk 覆盖 4 类来源；P03=unknown、subTitle=unmapped；runtime 待验。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="118">
@@ -17772,10 +17852,15 @@
       </x:c>
       <x:c r="M124" s="84" t="str"/>
       <x:c r="N124" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O124" s="84" t="str"/>
-      <x:c r="P124" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O124" s="84" t="str">
+        <x:v>；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
+      </x:c>
+      <x:c r="P124" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="125">
       <x:c r="A125" s="83" t="str">
@@ -17814,10 +17899,15 @@
       </x:c>
       <x:c r="M125" s="84" t="str"/>
       <x:c r="N125" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O125" s="84" t="str"/>
-      <x:c r="P125" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O125" s="84" t="str">
+        <x:v>；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
+      </x:c>
+      <x:c r="P125" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="126">
       <x:c r="A126" s="83" t="str">
@@ -17902,10 +17992,15 @@
       </x:c>
       <x:c r="M127" s="84" t="str"/>
       <x:c r="N127" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O127" s="84" t="str"/>
-      <x:c r="P127" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O127" s="84" t="str">
+        <x:v>；validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/</x:v>
+      </x:c>
+      <x:c r="P127" s="86" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 完整原验收仍未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="128">
       <x:c r="A128" s="83" t="str">
@@ -18131,10 +18226,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O132" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/</x:v>
       </x:c>
       <x:c r="P132" s="86" t="str">
-        <x:v>真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+        <x:v>真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="133">
@@ -20783,10 +20879,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O191" s="84" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/；validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/</x:v>
       </x:c>
       <x:c r="P191" s="86" t="str">
-        <x:v>持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+        <x:v>持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="192">
@@ -20875,10 +20972,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O193" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/</x:v>
       </x:c>
       <x:c r="P193" s="86" t="str">
-        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="194" ht="172.5" customHeight="1">
@@ -20967,10 +21065,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O195" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/</x:v>
       </x:c>
       <x:c r="P195" s="86" t="str">
-        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="196" ht="172.5" customHeight="1">
@@ -22139,10 +22238,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O221" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/</x:v>
       </x:c>
       <x:c r="P221" s="86" t="str">
-        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="222">
@@ -25957,7 +26057,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9932a1ca45304735"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a212eb3a078461f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31354,7 +31454,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M124" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N124" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31398,7 +31499,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M125" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N125" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31442,7 +31544,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M126" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N126" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31486,7 +31589,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M127" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N127" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31530,7 +31634,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M128" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N128" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31574,7 +31679,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M129" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N129" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31618,7 +31724,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M130" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N130" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31662,7 +31769,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M131" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N131" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31706,7 +31814,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M132" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N132" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31750,7 +31859,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M133" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N133" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31794,7 +31904,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M134" s="84" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N134" s="86" t="str">
         <x:v>本规划</x:v>
@@ -31838,7 +31949,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M135" s="84" t="str">
-        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>模块正常/边界与真实模型消费已有证据；节点全部原验收尚未完成。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N135" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32586,7 +32698,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M152" s="84" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N152" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32630,7 +32743,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M153" s="84" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N153" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32762,7 +32876,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M156" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N156" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32806,7 +32921,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M157" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N157" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32850,7 +32966,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M158" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N158" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32894,7 +33011,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M159" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N159" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32938,7 +33056,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M160" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N160" s="86" t="str">
         <x:v>本规划</x:v>
@@ -32982,7 +33101,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M161" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N161" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33026,7 +33146,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M162" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N162" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33070,7 +33191,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M163" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N163" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33114,7 +33236,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M164" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N164" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33158,7 +33281,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M165" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N165" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33290,7 +33414,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M168" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N168" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33334,7 +33459,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M169" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N169" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33770,7 +33896,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M179" s="84" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N179" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33812,7 +33939,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M180" s="84" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N180" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33854,7 +33982,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M181" s="84" t="str">
-        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>真实解析母版/布局/主题/占位符/继承/尺寸，CLI/API/MCP入口可调用；真实原生文本槽位实例化且母版/布局/主题保持。容量/全部tokens/品牌锁/全部比例转换和三上游模板验收待完成，普通generate尚不替换自定义模板。 validation/input-format-artifacts/；validation/parallel-integration.json
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N181" s="86" t="str">
         <x:v>本规划</x:v>
@@ -33938,7 +34067,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M183" s="84" t="str">
-        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md</x:v>
+        <x:v>contracts/layout-applicability.schema.json、catalog.json、fixtures.json；contracts/layout-template.schema.json/catalog.json/fixtures.json；PROJECT_PLAN.md
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N183" s="86" t="str">
         <x:v>本规划</x:v>
@@ -34022,7 +34152,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M185" s="84" t="str">
-        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008</x:v>
+        <x:v>contracts/template-field-map.*.json; PROJECT_PLAN.md#TASK-TPL-008
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N185" s="86" t="str">
         <x:v>本规划</x:v>
@@ -34311,9 +34442,12 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L192" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M192" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M192" s="84" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N192" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34351,9 +34485,12 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L193" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M193" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M193" s="84" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N193" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34433,9 +34570,12 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L195" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M195" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M195" s="84" t="str">
+        <x:v>
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N195" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -34644,7 +34784,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M200" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实图片contain/显式焦点适配已接布局、裁切结果进入原生写入/渲染。人脸/对象感知裁切及全原验收待补。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N200" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38858,7 +38999,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M300" s="84" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 持久登记真实模板文件、来源/license/hash、母版/布局/主题、tokens和结构预览；生成已实际消费。渲染预览/全模板规则待验收。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N300" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38942,7 +39084,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M302" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N302" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39026,7 +39169,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M304" s="84" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N304" s="86" t="str">
         <x:v>本规划</x:v>
@@ -40324,7 +40468,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M335" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N335" s="86" t="str">
         <x:v>本规划</x:v>
@@ -40368,7 +40513,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M336" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N336" s="86" t="str">
         <x:v>本规划</x:v>
@@ -45244,7 +45390,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reda5842e35384a2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra95971c0f98d4a3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45538,7 +45684,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67117c179ec94610"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81e5f99483e4ffe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46954,7 +47100,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ea23a51a084a31"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa3b6235e4d442ba"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47376,7 +47522,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra80c0f96735a4889"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2d675e7f7844313"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49643,7 +49789,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N15" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -49687,7 +49834,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N16" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -49731,7 +49879,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N17" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -49775,7 +49924,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N18" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -49819,7 +49969,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N19" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -49863,7 +50014,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N20" s="86" t="str">
-        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md</x:v>
+        <x:v>prepare/real model/finalize实际消费16节点：受众、场景、叙事候选、页/章预算、页意图、容量、正文/备注和引用位置；75项模块检查与真实8页生成通过。自动推断、语义关系、多级章节、时长换算、语义拆合及全部引用模式仍未完成，节点原完整验收保持进行中。 validation/narrative-runtime.json；validation/parallel-integration.json；validation/叙事决策并行实现.md
+2026-10-11增量：已在Docker实际执行161项组件检查：完整正文soft 1→8页、混合长标题default 1→1页、26行纵表/25列横表soft 2→10页、hard短正文1→1页，共20页可编辑PPTX/4PDF/20PNG，确定性QA均P0=0且无警告。全部正文/表格值/单位/原引用可追溯，横向重复显式关键列；hard超容量/硬变软/缺失关键列/不可拆句/锁定模板等明确失败。另只读已有表格PDF执行228项按原生单元格几何核对，不生成/渲染/调用模型，不合并为389项同版本套件。保留标记容量与旧字体行高两次失败，成功161项绑定实际新字体版本；后续共享源码变化不冒称全套已重跑。独立语义复审、复杂合并表格、锁定模板全部适配、三上游模板与全链AC-014/015仍待完成。 后续10项分页说明定向检查及当前真实恢复的14行表格，原161项并未重跑。 validation/完整正文和大表格自适应分页.md；validation/adaptive-content-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -50259,7 +50411,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N29" s="86" t="str">
-        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。</x:v>
+        <x:v>validation/visual-runtime.json；validation/visual-path-guards.json；validation/visual-live-artifacts/ 实际登记/检索模板族，生成继承真实母版/布局/主题，尺寸不符显式拒绝。品牌锁和全部模板验收待补。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -50347,7 +50500,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N31" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -50391,7 +50545,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N32" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生文本/图/关系图候选、实际容量、后端支持与多样性评分已接生成，46项直接版式检查。完整语义/品牌/多后端待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -50435,7 +50590,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N33" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行68项原生模板槽位/品牌锁/字段映射/容量与显式fallback检查，4个可编辑PPTX各真实PDF/PNG渲染，另有Schema→compile→原子写入→ObjectMap→checkpoint实物。后续只增量执行2项模板多图结构化拒绝与单图cover缺crop拒绝边界，不重跑68项/渲染，分别保留源码哈希；当前模板多原生图槽及focal-only cover未支持，不以拒绝算功能通过。三上游模板族、全部页面模式、复杂品牌/OOXML语义及PowerPoint桌面与独立模型复审仍待完成。 validation/模板原生槽位与品牌锁.md；validation/template-slot-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -50479,7 +50635,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N34" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 真实内容/图片/关系节点绑定稳定槽位，原生几何与连接端点进入对象DAG。任意模板绑定/freeform等仍未完整。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -50523,7 +50680,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N35" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ CJK字形/字号/边距/容量实测；不靠截字或不可读缩字过关。RTL与全部字体替代链待补。完整原验收仍未通过。
+2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 validation/native-capacity-integration.json；validation/native-capacity-live-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -50611,7 +50769,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="N37" s="86" t="str">
-        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。</x:v>
+        <x:v>validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/ 原生图片contain/显式适配策略、尺寸/hash进入执行与QA。人脸/主体感知裁切/mask等全范围待验收。完整原验收仍未通过。
+2026-10-11增量：已在Docker实际执行32项检查：8张不同宽高比contain、3张显式焦点cover、2张显式crop，共3页13个原生图片对象及原据可见图注，真实PDF/逐页PNG与原生QA无问题；低DPI、缺失、重复、hash/像素/来源错配等明确失败。首次PDF抽字插入空白比较失败保留原报告，在原PPTX/render字节不变下仅修比较并核对原生图注逐字一致。后续只执行5项长标题8图增量，用实际字体扩标题框而不缩字，复用8原输入，shared compile/writer、一页真实渲染/QA通过；原32项未重跑，两个版本分别保留源码hash。输入为人工光栅夹具，独立语义/图质模型复审、真实用户8图AI全链AC-012、人脸/对象感知和感知重复仍待完成。 validation/实现八图原生布局与焦点裁切.md；validation/gallery-artifacts/；完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -50803,7 +50962,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12ba011168564f60"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28d26a614b624604"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rd0f8aa1e140c43d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="Rbd62915834c24c01"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="R13bdebb329174f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Re3ddb367399d4137"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R9c08a9817e48433a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R6d09165b5cd94f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R4f8c976a5cea4639"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="Rdc0a194ab31e4ba0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="R8dfaf6ae67844ab2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R11fabb9c31854b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R548a3ec11a934ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rdaa3a3274e914ad1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R067151f2eba944e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R9143c60e3295426e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R890c678e562848a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R6e4aede425404ee9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R345d5b848c5c4e10"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rc1ea2e09c54e41fc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R9608174f2b024d06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R183622d5024f4c20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re0ffc6b8fa144db7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3311ae5caace4638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ree76c51dd1104fb8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6973f663cf7a4888"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd1654e6366fe4ea3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R73f39920c2984de9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R311f3f2f0c1f4135"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3eec6b5aca4b4e9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf4870f91f1ba48d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdfcf985daff144f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ef3b8280ba14511"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rfc693cc8df5d44ac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R60c78fd603624232"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5d0fca1ecb294a5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R96ecb3caebf84b24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R15882047e4ad4e95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R17f8c3e451404d3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4c70c8a0bbbc4785"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R4042246b72ff41f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R957ce92c4cb04e66"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R314a57d3b1c0455d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a2e719d91c74a6c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra950f2f9d6264110"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477479ab7f6b409e"/>
 </x:worksheet>
 </file>
 
@@ -4163,7 +4163,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I17" s="86" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -9046,11 +9047,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G9" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H9" s="84" t="str"/>
-      <x:c r="I9" s="84" t="str"/>
-      <x:c r="J9" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H9" s="84" t="str">
+        <x:v>真实自然语言只修改第1/6页标题；16项API检查，未修改页/对象字节保留，PowerPoint原生文字框读取匹配。P0=0/6警告；修订稿目标对象实际选中改存复开及完整质量原验收未完成。</x:v>
+      </x:c>
+      <x:c r="I9" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="J9" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -9072,11 +9079,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G10" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H10" s="84" t="str"/>
-      <x:c r="I10" s="84" t="str"/>
-      <x:c r="J10" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H10" s="84" t="str">
+        <x:v>真实API系列重排15项、换图14项及再次换图14项，内嵌工作簿/图表缓存与系列一致；COM图片hash/图表值匹配。未验证有来源的新数值改写、所有图表/图片/裁切及完整事实语义。</x:v>
+      </x:c>
+      <x:c r="I10" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="J10" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -9098,11 +9111,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G11" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H11" s="84" t="str"/>
-      <x:c r="I11" s="84" t="str"/>
-      <x:c r="J11" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H11" s="84" t="str">
+        <x:v>复用明确人工故障注入父稿，真实恢复标题色与正文几何、锁定其余对象，15项检查；事实/数据不变，重渲染及新模型审查P0=0/7警告。旧父缺DEC022–038，完整视觉改善/品牌/事实原验收仍待满足。</x:v>
+      </x:c>
+      <x:c r="I11" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="J11" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -9593,13 +9612,13 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H29" s="84" t="str">
-        <x:v>validation/generation-artifacts/；validation/powerpoint-generation-open.json</x:v>
+        <x:v>PowerPoint16.0实际打开四个新修订稿，489项文字/图片/图表/几何对照；原稿hash不变。初次4条水平连接线比较失败保留，按显式端点纠正比较器后通过；COM无异常不证明UI无修复提示。</x:v>
       </x:c>
       <x:c r="I29" s="84" t="str">
-        <x:v>已执行部分：真实生成/修订/报告与平台观测</x:v>
+        <x:v>validation/powerpoint-open-artifacts/</x:v>
       </x:c>
       <x:c r="J29" s="86" t="str">
-        <x:v>PowerPoint 16.0 COM实际打开10页32对象无异常；未经UI观察修复提示，不能判通过。</x:v>
+        <x:v>完整原验收未通过</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -10318,7 +10337,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbac281eee7384348"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13bd4676e9ff4dcb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11417,11 +11436,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H37" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I37" s="86" t="str">
         <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。
-2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
+2026-10-11：五次真实render/独立选页模型复审；美化局部几何/颜色恢复，全部视觉规则仍待覆盖。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="195" customHeight="1">
@@ -11477,10 +11497,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H39" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I39" s="86" t="str">
-        <x:v>原生图片/节点/边可编辑，局部非目标parts保持；全对象round-trip待补。</x:v>
+        <x:v>原生图片/节点/边可编辑，局部非目标parts保持；全对象round-trip待补。
+2026-10-11：五次原生修订和52项夹具检查保留未选parts/XML；COM读取证明有界原生对象，所有对象编辑性/客户端语义待验收。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11506,10 +11527,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H40" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I40" s="86" t="str">
-        <x:v>已检查原生alt-text/阅读顺序/字号/对比/表头部分字段，语言/RTL与完整可访问性待补。</x:v>
+        <x:v>已检查原生alt-text/阅读顺序/字号/对比/表头部分字段，语言/RTL与完整可访问性待补。
+2026-10-11：换图的alt_text与图注证据同步，连接线descr承载关系时明确拒绝alt修改；完整可访问性待验收。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="195" customHeight="1">
@@ -11535,10 +11557,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H41" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I41" s="86" t="str">
-        <x:v>DEC039将实际issue映射局部RevisionPlan/fail/needs_input；全部节点修订待补。</x:v>
+        <x:v>DEC039将实际issue映射局部RevisionPlan/fail/needs_input；全部节点修订待补。
+2026-10-11：继承已有RevisionPlan路径；新增用户批次指令与真实模型目标解释保留trace，不等同全QA自动动作已支持。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="195" customHeight="1">
@@ -11564,10 +11587,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H42" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I42" s="86" t="str">
-        <x:v>24项RevisionPlan消费者检查，真实布局/颜色局部修改和QA/history；任意节点/对象待补。</x:v>
+        <x:v>24项RevisionPlan消费者检查，真实布局/颜色局部修改和QA/history；任意节点/对象待补。
+2026-10-11：多页多对象批次修改→实际render→独立选页复审→QA/history；未选页/对象字节保留，重复换图可继续修订。任意节点/对象/已有deck语义仍待补。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="195" customHeight="1">
@@ -11593,10 +11617,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H43" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I43" s="86" t="str">
-        <x:v>六页QA-only P0=0但保留4警告，终止warning/not_passed；没有把DEC轨迹齐全当作完整验收。</x:v>
+        <x:v>六页QA-only P0=0但保留4警告，终止warning/not_passed；没有把DEC轨迹齐全当作完整验收。
+2026-10-11：五次P0=0但警告及覆盖缺口保留，均warning/final_allowed=false；不替旧父补缺失DEC。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="195" customHeight="1">
@@ -11680,10 +11705,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H46" s="88" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="I46" s="90" t="str">
-        <x:v>六页可编辑原生对象与真实渲染已检查，本版PowerPoint实际打开/全部交付原验收未完成。</x:v>
+        <x:v>六页可编辑原生对象与真实渲染已检查，本版PowerPoint实际打开/全部交付原验收未完成。
+2026-10-11：四份新修订稿实际PowerPoint只读打开及489项对照；更早父稿副本编辑另存复开成立。UI无修复提示及修订稿目标对象实际改存复开仍未验证。 完整步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11699,7 +11725,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c7064ae8c2b43ef"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1157b4baa05494b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20040,10 +20066,14 @@
       </x:c>
       <x:c r="M172" s="84" t="str"/>
       <x:c r="N172" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O172" s="84" t="str"/>
-      <x:c r="P172" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O172" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="P172" s="86" t="str">
+        <x:v>2026-10-11增量：本机PowerPoint16.0.20430.20092实际COM打开父稿/副本改文案另存复开与四份新修订只读检查489项；原稿hash不变。另存重写非目标XML/关系及部分printerSettings，非字节保真；新建/高级对象/并发/弹窗/UI修复提示未完整验证。 完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="173">
       <x:c r="A173" s="83" t="str">
@@ -21250,10 +21280,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O199" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P199" s="86" t="str">
-        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11增量：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="172.5" customHeight="1">
@@ -21568,10 +21599,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O206" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P206" s="86" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。
+2026-10-11增量：现有原生导入与批次写入相接；含母版/布局/图表/图片/备注/未知扩展的组件夹具52项检查。任意已有PPT内容与语义导入仍未完整。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="207">
@@ -21614,10 +21646,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O207" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P207" s="86" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。
+2026-10-11增量：批次前置验证及原子另存保留未选ZIP负载/实体ID；共享媒体/工作簿/备注拒绝跨范围修改，未支持对象不重新保存。所有未知对象客户端语义保真仍待覆盖。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="208">
@@ -21657,10 +21690,14 @@
       </x:c>
       <x:c r="M208" s="84" t="str"/>
       <x:c r="N208" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O208" s="84" t="str"/>
-      <x:c r="P208" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O208" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="P208" s="86" t="str">
+        <x:v>2026-10-11增量：真实DeepSeek解析限定两页自然语言指令，范围/原文证据/候选唯一性校验；明确scope越界拒绝。完整deck/section语义范围和任意既有deck仍待实现。 完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="209">
       <x:c r="A209" s="83" t="str">
@@ -21702,10 +21739,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O209" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P209" s="86" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。
+2026-10-11增量：ID/shape/name/text/placeholder/页号选择器在授权范围内唯一定位；真实模型选择保留原文匹配与目标证据。范围组件39项是合成响应测试，非真实AI验收。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="210">
@@ -21748,10 +21786,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O210" s="84" t="str">
-        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>validation/native-object-artifacts/；validation/parallel-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P210" s="86" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。
+2026-10-11增量：批次文字/图表系列/登记图片/单元格/几何/有界格式/替代文字/备注接入；实际API两页改标题、原图表系列重排、换图及重复换图，未选对象与页字节不变。完整图表新数值、裁切及复杂对象原验收未完成。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="211">
@@ -21794,10 +21833,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O211" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P211" s="86" t="str">
-        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11增量：指令或原RevisionPlan才修改几何；锁/品牌范围前置核对；真实故障注入父稿局部恢复正文布局和标题颜色，真实重渲染/复审。任意layout/节点重排仍待补。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="212">
@@ -21921,10 +21961,14 @@
       </x:c>
       <x:c r="M214" s="84" t="str"/>
       <x:c r="N214" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O214" s="84" t="str"/>
-      <x:c r="P214" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O214" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="P214" s="86" t="str">
+        <x:v>2026-10-11增量：实际beautify锁定其余对象，正文几何与标题对比修复，事实/数据不变；8页P0=0但7警告且旧父缺DEC022–038，不伪造继承节点。完整视觉与品牌验收未通过。 完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="215">
       <x:c r="A215" s="83" t="str">
@@ -21966,10 +22010,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O215" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P215" s="86" t="str">
-        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11增量：每次成功保存instruction/scope/locks、逐操作中间与最终spec、原生part差异、QA前后、父子run与版本hash；结构化失败另留manifest。完整所有修订路径仍待覆盖。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="216">
@@ -22833,10 +22878,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O234" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P234" s="86" t="str">
-        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11增量：五次实际API修订均P0=0，警告6/4/5/7/6，final_allowed=false；原失败与旧父覆盖缺口保留。全问题类型/自动修订与原AC未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="235">
@@ -22879,10 +22925,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O235" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
       </x:c>
       <x:c r="P235" s="86" t="str">
-        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11增量：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -24978,10 +25025,14 @@
       </x:c>
       <x:c r="M284" s="84" t="str"/>
       <x:c r="N284" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O284" s="84" t="str"/>
-      <x:c r="P284" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O284" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="P284" s="86" t="str">
+        <x:v>2026-10-11增量：原生52项组件含共享引用、组锁、双图表/内嵌工作簿、图像/表格/备注以及未知扩展保留；真实修订比较未改页/对象/包成员。全部对象/客户端round-trip仍待覆盖。 完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="285">
       <x:c r="A285" s="83" t="str">
@@ -25440,10 +25491,14 @@
       </x:c>
       <x:c r="M295" s="84" t="str"/>
       <x:c r="N295" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="O295" s="84" t="str"/>
-      <x:c r="P295" s="86" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="O295" s="84" t="str">
+        <x:v>validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+      </x:c>
+      <x:c r="P295" s="86" t="str">
+        <x:v>2026-10-11增量：两页文案、图表、换图及再次换图、故障注入美化五次实际修订74项检查；不混同不同版本39/52/10组件检查。修订后PowerPoint实际改存复开尚未执行。 完整原验收未通过。</x:v>
+      </x:c>
     </x:row>
     <x:row r="296">
       <x:c r="A296" s="83" t="str">
@@ -26057,7 +26112,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a212eb3a078461f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c9d20a90164cfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37750,9 +37805,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L270" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M270" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M270" s="84" t="str">
+        <x:v>2026-10-11：本机PowerPoint16.0.20430.20092实际COM打开父稿/副本改文案另存复开与四份新修订只读检查489项；原稿hash不变。另存重写非目标XML/关系及部分printerSettings，非字节保真；新建/高级对象/并发/弹窗/UI修复提示未完整验证。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N270" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/vba/api/overview/powerpoint/object-model</x:v>
       </x:c>
@@ -37792,9 +37849,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L271" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M271" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M271" s="84" t="str">
+        <x:v>2026-10-11：本机PowerPoint16.0.20430.20092实际COM打开父稿/副本改文案另存复开与四份新修订只读检查489项；原稿hash不变。另存重写非目标XML/关系及部分printerSettings，非字节保真；新建/高级对象/并发/弹窗/UI修复提示未完整验证。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N271" s="86" t="str">
         <x:v>https://learn.microsoft.com/en-us/office/vba/api/overview/powerpoint/object-model</x:v>
       </x:c>
@@ -39338,7 +39397,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M308" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39630,7 +39690,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M315" s="84" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json
+2026-10-11：现有原生导入与批次写入相接；含母版/布局/图表/图片/备注/未知扩展的组件夹具52项检查。任意已有PPT内容与语义导入仍未完整。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N315" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39672,7 +39733,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M316" s="84" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json
+2026-10-11：批次前置验证及原子另存保留未选ZIP负载/实体ID；共享媒体/工作簿/备注拒绝跨范围修改，未支持对象不重新保存。所有未知对象客户端语义保真仍待覆盖。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N316" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39711,9 +39773,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L317" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M317" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M317" s="84" t="str">
+        <x:v>2026-10-11：真实DeepSeek解析限定两页自然语言指令，范围/原文证据/候选唯一性校验；明确scope越界拒绝。完整deck/section语义范围和任意既有deck仍待实现。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N317" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -39754,7 +39818,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M318" s="84" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json
+2026-10-11：ID/shape/name/text/placeholder/页号选择器在授权范围内唯一定位；真实模型选择保留原文匹配与目标证据。范围组件39项是合成响应测试，非真实AI验收。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N318" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39796,7 +39861,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M319" s="84" t="str">
-        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json</x:v>
+        <x:v>stable slide-id+shape-id索引、精确选择器、expected_sha256及save-as，修改文字/格式/位置/单元格/图表+内嵌工作簿/图片/替代文字/备注；未涉及ZIP成员byte相同、非目标形状XML相同。真实API修改已执行；完整自然语言范围、语义定位、所有部件语义、质量/历史原验收待完成。 validation/native-object-artifacts/；validation/parallel-integration.json
+2026-10-11：批次文字/图表系列/登记图片/单元格/几何/有界格式/替代文字/备注接入；实际API两页改标题、原图表系列重排、换图及重复换图，未选对象与页字节不变。完整图表新数值、裁切及复杂对象原验收未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N319" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39838,7 +39904,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M320" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11：指令或原RevisionPlan才修改几何；锁/品牌范围前置核对；真实故障注入父稿局部恢复正文布局和标题颜色，真实重渲染/复审。任意layout/节点重排仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N320" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39957,9 +40024,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L323" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M323" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M323" s="84" t="str">
+        <x:v>2026-10-11：实际beautify锁定其余对象，正文几何与标题对比修复，事实/数据不变；8页P0=0但7警告且旧父缺DEC022–038，不伪造继承节点。完整视觉与品牌验收未通过。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N323" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -40000,7 +40069,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M324" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
+2026-10-11：每次成功保存instruction/scope/locks、逐操作中间与最终spec、原生part差异、QA前后、父子run与版本hash；结构化失败另留manifest。完整所有修订路径仍待覆盖。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N324" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41584,7 +41654,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M361" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11：五次实际API修订均P0=0，警告6/4/5/7/6，final_allowed=false；原失败与旧父覆盖缺口保留。全问题类型/自动修订与原AC未通过。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N361" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41628,7 +41699,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M362" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11：五次实际API修订均P0=0，警告6/4/5/7/6，final_allowed=false；原失败与旧父覆盖缺口保留。全问题类型/自动修订与原AC未通过。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N362" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41670,7 +41742,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M363" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
+2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N363" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41714,7 +41787,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M364" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
+2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N364" s="86" t="str">
         <x:v>本规划</x:v>
@@ -44367,9 +44441,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L429" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M429" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M429" s="84" t="str">
+        <x:v>2026-10-11：原生52项组件含共享引用、组锁、双图表/内嵌工作簿、图像/表格/备注以及未知扩展保留；真实修订比较未改页/对象/包成员。全部对象/客户端round-trip仍待覆盖。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N429" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -44807,9 +44883,11 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="L440" s="84" t="str">
-        <x:v>未开始</x:v>
-      </x:c>
-      <x:c r="M440" s="84" t="str"/>
+        <x:v>进行中</x:v>
+      </x:c>
+      <x:c r="M440" s="84" t="str">
+        <x:v>2026-10-11：两页文案、图表、换图及再次换图、故障注入美化五次实际修订74项检查；不混同不同版本39/52/10组件检查。修订后PowerPoint实际改存复开尚未执行。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+      </x:c>
       <x:c r="N440" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
@@ -45390,7 +45468,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra95971c0f98d4a3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fc7909d95004407"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45684,7 +45762,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re81e5f99483e4ffe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0387acef51ca484e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47100,7 +47178,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa3b6235e4d442ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f6c9839fca473b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47192,18 +47270,26 @@
         <x:v>新建/打开/另存/关闭；slides；shapes；text；images；tables；charts；masters/layouts/themes；notes/comments；transitions/animations；对象 ID/geometry；读取/修改现有 PPT；事件/选择；渲染/导出能力；并发/进程/弹窗/权限。</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>待搭建</x:v>
+        <x:v>本机已安装，COM部分实际执行</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>未执行</x:v>
+        <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="J2" s="80" t="str">
-        <x:v>未冻结（PoC未执行）</x:v>
-      </x:c>
-      <x:c r="K2" s="80" t="str"/>
-      <x:c r="L2" s="80" t="str"/>
-      <x:c r="M2" s="80" t="str"/>
-      <x:c r="N2" s="82" t="str"/>
+        <x:v>PowerPoint16.0.20430.20092</x:v>
+      </x:c>
+      <x:c r="K2" s="80" t="str">
+        <x:v>新建未执行；现有稿打开/只读检查已执行</x:v>
+      </x:c>
+      <x:c r="L2" s="80" t="str">
+        <x:v>validation/powerpoint-open-artifacts/；父稿副本文字修改另存复开，Office重写非目标parts，未证明字节保真</x:v>
+      </x:c>
+      <x:c r="M2" s="80" t="str">
+        <x:v>高级能力/事件/并发/UI弹窗未完整执行</x:v>
+      </x:c>
+      <x:c r="N2" s="82" t="str">
+        <x:v>COM为独立平台PoC；不是Docker运行依赖或已选产品后端，AC028仍缺UI修复提示观察。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -47522,7 +47608,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2d675e7f7844313"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d879d74ea3240e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50962,7 +51048,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R28d26a614b624604"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279db42536214643"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Re0ffc6b8fa144db7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R3311ae5caace4638"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Ree76c51dd1104fb8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="R6973f663cf7a4888"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="Rd1654e6366fe4ea3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="R73f39920c2984de9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R311f3f2f0c1f4135"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R3eec6b5aca4b4e9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf4870f91f1ba48d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="Rdfcf985daff144f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="R6ef3b8280ba14511"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="Rfc693cc8df5d44ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R60c78fd603624232"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="R5d0fca1ecb294a5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="R96ecb3caebf84b24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R15882047e4ad4e95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R17f8c3e451404d3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="R4c70c8a0bbbc4785"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="R4042246b72ff41f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="R957ce92c4cb04e66"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rf07d0c629ab74f6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0-1全链路" sheetId="2" r:id="R81f2749fd36b4ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="需求主表" sheetId="3" r:id="Rccdbea9ff5a441be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="可执行任务" sheetId="4" r:id="Ra8870320409c430d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="开源项目研究对象" sheetId="5" r:id="R51f7c7a652aa4696"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目源码拆解点" sheetId="6" r:id="Raebd9b3133d343f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint后端" sheetId="7" r:id="R3f0c91427d1e4d48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PowerPoint对象矩阵" sheetId="8" r:id="R79fb50cf364c40c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="决策链" sheetId="9" r:id="Rf9f52534621d4b37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="输入源矩阵" sheetId="10" r:id="R21f33a6f61474142"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模板版式要求" sheetId="11" r:id="Ra22682bb32794889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="素材与可视化" sheetId="12" r:id="R944f428c2bc14be3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="系统组件接口" sheetId="13" r:id="R8f7cf96d7ab344bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据对象" sheetId="14" r:id="Ra10362394b684b68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="错误Fallback" sheetId="15" r:id="Rfdcc87523428441e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="非功能与安全" sheetId="16" r:id="R1d3b67645a8c431a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="验收矩阵" sheetId="17" r:id="R2e7050b5e9ac447c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codex交接" sheetId="18" r:id="Rcfc07ae87e0e4000"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源索引" sheetId="19" r:id="Rc160e7286f8f452a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="覆盖校验" sheetId="20" r:id="Ra9b77e0017474149"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9a2e719d91c74a6c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0f7820b20cc2478e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1910,7 +1910,7 @@
     <x:mergeCell ref="A1:J1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R477479ab7f6b409e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32938d9adc004ed3"/>
 </x:worksheet>
 </file>
 
@@ -3783,7 +3783,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I4" s="86" t="str">
-        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md
+2026-10-12：三格式助手已由parse_input实际调用并纳入parser_version；真实XLSX生成和单段prompt链路经过SourceLoader。原始快照/角色/选定事实保留，HTML/YAML/OCR等原范围未完成。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -4134,7 +4135,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="I16" s="86" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。
+2026-10-12：单段描述六页24对象→原生PPTX/真实render/独立review，P0=0/3警告；局部修订后P0=0/2警告。人工视觉发现封面操作指令泄漏，自动QA未拦截；完整事实/内容适用性/可编辑性等原QA仍未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -4164,7 +4166,8 @@
       </x:c>
       <x:c r="I17" s="86" t="str">
         <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
-2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/
+2026-10-12：复用前一批次消费者，明确局部改封面标题/正文清除操作指令；真实复审15项流程检查，另8项Native数据/字节检查，只有slide1.xml改变，其他页/数据/选定事实保留。未称全节点自动修订完成。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -8856,10 +8859,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
+        <x:v>单段prompt实际6页/24原生对象（22文字+1表+1图表），真实事实/内容/复审；生成3警告、局部修订2警告，均P0=0/final=false。15流程+8原生实物检查，不替代原约10页及完整原验收。</x:v>
       </x:c>
       <x:c r="I2" s="80" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="J2" s="82" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -8885,11 +8888,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G3" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H3" s="84" t="str"/>
-      <x:c r="I3" s="84" t="str"/>
-      <x:c r="J3" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H3" s="84" t="str">
+        <x:v>DOCX增强34项组件；旧夹具引用未逐字落证据时拒绝，当前有效夹具实际模型日期无依据变换再拒绝。没有PPTX成功制品，完整原AC未通过。</x:v>
+      </x:c>
+      <x:c r="I3" s="84" t="str">
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
+      </x:c>
+      <x:c r="J3" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -8911,11 +8920,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G4" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H4" s="84" t="str"/>
-      <x:c r="I4" s="84" t="str"/>
-      <x:c r="J4" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H4" s="84" t="str">
+        <x:v>PDF四页含文本/网格/图片夹具38项；实际六页输入事实解释模型输出截断，MODEL_OUTPUT_INCOMPLETE保留，未降级生成，完整AC未通过。</x:v>
+      </x:c>
+      <x:c r="I4" s="84" t="str">
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
+      </x:c>
+      <x:c r="J4" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -8963,11 +8978,17 @@
         <x:v>P0</x:v>
       </x:c>
       <x:c r="G6" s="84" t="str">
-        <x:v>未执行</x:v>
-      </x:c>
-      <x:c r="H6" s="84" t="str"/>
-      <x:c r="I6" s="84" t="str"/>
-      <x:c r="J6" s="86" t="str"/>
+        <x:v>部分执行/未通过</x:v>
+      </x:c>
+      <x:c r="H6" s="84" t="str">
+        <x:v>真实两sheet/日期/时序/分类/缓存和百分比显示→六页原生表格与分单位图表，12项链路/P0=0/4警告；缓存新鲜/所有格式/完整语义仍未验收，图表合计与月份混排需独立语义评估。</x:v>
+      </x:c>
+      <x:c r="I6" s="84" t="str">
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
+      </x:c>
+      <x:c r="J6" s="86" t="str">
+        <x:v>完整原验收未通过</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -9580,10 +9601,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H28" s="84" t="str">
-        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
+        <x:v>本轮保留原始来源/hash、选定事实、DEC001–040有界trace、DeckSpec/ObjectMap/native执行/QA/revision/版本；人工指令泄漏另存问题与修订记录，完整随机对象抽检未完成。</x:v>
       </x:c>
       <x:c r="I28" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="J28" s="86" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -9670,10 +9691,10 @@
         <x:v>部分执行/未通过</x:v>
       </x:c>
       <x:c r="H31" s="88" t="str">
-        <x:v>真实六页主模型/PPTX/图片/流程/渲染与QA-only恢复。P0=0保留4警告，原生局部RevisionPlan执行；完整原验收未满足。</x:v>
+        <x:v>当前从单段描述到生成/实际render/QA/局部修订/再QA可运行；硬4页不足、DOCX事实/日期、PDF输出截断保留显式fail。S00–44有界消费不等于全部模式/覆盖及final原验收，当前final仍false。</x:v>
       </x:c>
       <x:c r="I31" s="88" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="J31" s="90" t="str">
         <x:v>完整原验收未通过</x:v>
@@ -10337,7 +10358,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13bd4676e9ff4dcb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae62e003ee1a485b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10407,10 +10428,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H2" s="80" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I2" s="82" t="str">
-        <x:v>CLI/HTTP接收真实任务、原文与来源身份；全输入格式及统一生命周期待完成。</x:v>
+        <x:v>CLI/HTTP接收真实任务、原文与来源身份；全输入格式及统一生命周期待完成。
+2026-10-12：单段prompt的真实TaskSpec进入HTTP/CLI/MCP共享核心，输出六页并可局部再修订；完整所有输入与任务模式待验收。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="195" customHeight="1">
@@ -10523,10 +10545,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H6" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>文本、Markdown真实来源及角色加载；其他原始格式待实现。</x:v>
+        <x:v>2026-10-12当前：当前SourceLoader实际读取prompt/text/Markdown、DOCX/XLSX/CSV/PPTX/POTX/PDF/image/JSON/XML的有界原文件；本轮三格式增强接入。HTML/URL/YAML/OCR及全部资产类型仍待完成。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="195" customHeight="1">
@@ -10552,10 +10574,10 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H7" s="84" t="str">
-        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md</x:v>
+        <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I7" s="86" t="str">
-        <x:v>实际保存文本块、表格、证据和原文锚点；其他格式图片/图形解析待实现。</x:v>
+        <x:v>2026-10-12当前：三格式原文/结构/原生段格页与图片部件证据已保存，候选结构进入模型但不视为语义真值；物理Word页/OCR/复杂PDF表格/全部格式语义待补。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="195" customHeight="1">
@@ -10610,10 +10632,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H9" s="84" t="str">
-        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json</x:v>
+        <x:v>validation/layout-runtime.json；validation/layout-artifacts/；validation/版式编译与链路进度修复.md；validation/context-runtime.json；validation/generation-runtime.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I9" s="86" t="str">
-        <x:v>约束归一化实际运行；完整受众、场景、语气、品牌推断与执行待完成。</x:v>
+        <x:v>约束归一化实际运行；完整受众、场景、语气、品牌推断与执行待完成。
+2026-10-12：硬四页不足明确失败；显式软六页描述生成六页，约束沿用。完整受众/场景/品牌与任意自然语言约束仍待验收。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="195" customHeight="1">
@@ -11406,11 +11429,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H36" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I36" s="86" t="str">
         <x:v>部分原生结构/边界/空对象/碰撞/溢出检查运行；完整结构验收待补。
-2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
+2026-10-12：新描述与XLSX实物真实结构/渲染检查P0=0，原生数值与字节另验；全结构规则仍未完成。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="195" customHeight="1">
@@ -11436,12 +11460,13 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H37" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I37" s="86" t="str">
         <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。
 2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
-2026-10-11：五次真实render/独立选页模型复审；美化局部几何/颜色恢复，全部视觉规则仍待覆盖。 完整步骤与原验收未通过。</x:v>
+2026-10-11：五次真实render/独立选页模型复审；美化局部几何/颜色恢复，全部视觉规则仍待覆盖。 完整步骤与原验收未通过。
+2026-10-12：实际render经人工查看，发现封面操作指令外泄并仅修封面。自动QA未发现该内容问题，不能以P0=0判全部视觉/内容通过。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="195" customHeight="1">
@@ -11467,11 +11492,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H38" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/native-capacity-integration.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I38" s="86" t="str">
         <x:v>数值引用与真实模型事实复审，图片尺寸仅对同页实际hash/像素验证后排除元数据；完整语义真值待补。
-2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
+2026-10-12：事实/数值与实际模型审查执行，DOCX日期错误/PDF截断拒绝，XLSX数字单位实际保留。完整事实语义/内容适用性仍未通过。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="195" customHeight="1">
@@ -11497,11 +11523,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H39" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I39" s="86" t="str">
         <x:v>原生图片/节点/边可编辑，局部非目标parts保持；全对象round-trip待补。
-2026-10-11：五次原生修订和52项夹具检查保留未选parts/XML；COM读取证明有界原生对象，所有对象编辑性/客户端语义待验收。 完整步骤与原验收未通过。</x:v>
+2026-10-11：五次原生修订和52项夹具检查保留未选parts/XML；COM读取证明有界原生对象，所有对象编辑性/客户端语义待验收。 完整步骤与原验收未通过。
+2026-10-12：当前六页24原生对象含可编辑表/图；8项实物核对源数值和未改parts，所有对象与PowerPointUI兼容待验收。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -11587,11 +11614,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H42" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I42" s="86" t="str">
         <x:v>24项RevisionPlan消费者检查，真实布局/颜色局部修改和QA/history；任意节点/对象待补。
-2026-10-11：多页多对象批次修改→实际render→独立选页复审→QA/history；未选页/对象字节保留，重复换图可继续修订。任意节点/对象/已有deck语义仍待补。 完整步骤与原验收未通过。</x:v>
+2026-10-11：多页多对象批次修改→实际render→独立选页复审→QA/history；未选页/对象字节保留，重复换图可继续修订。任意节点/对象/已有deck语义仍待补。 完整步骤与原验收未通过。
+2026-10-12：当前明确局部改首页两个对象，其他五页/数据/选定事实保留，仅slide1.xml改变，实际选页重审；全部节点自动修订未完成。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="195" customHeight="1">
@@ -11617,11 +11645,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H43" s="84" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I43" s="86" t="str">
         <x:v>六页QA-only P0=0但保留4警告，终止warning/not_passed；没有把DEC轨迹齐全当作完整验收。
-2026-10-11：五次P0=0但警告及覆盖缺口保留，均warning/final_allowed=false；不替旧父补缺失DEC。 完整步骤与原验收未通过。</x:v>
+2026-10-11：五次P0=0但警告及覆盖缺口保留，均warning/final_allowed=false；不替旧父补缺失DEC。 完整步骤与原验收未通过。
+2026-10-12：当前生成/修订均warning/final_allowed=false；自动0P0不能覆盖人工发现内容问题或完整覆盖缺口。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="195" customHeight="1">
@@ -11705,11 +11734,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="H46" s="88" t="str">
-        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I46" s="90" t="str">
         <x:v>六页可编辑原生对象与真实渲染已检查，本版PowerPoint实际打开/全部交付原验收未完成。
-2026-10-11：四份新修订稿实际PowerPoint只读打开及489项对照；更早父稿副本编辑另存复开成立。UI无修复提示及修订稿目标对象实际改存复开仍未验证。 完整步骤与原验收未通过。</x:v>
+2026-10-11：四份新修订稿实际PowerPoint只读打开及489项对照；更早父稿副本编辑另存复开成立。UI无修复提示及修订稿目标对象实际改存复开仍未验证。 完整步骤与原验收未通过。
+2026-10-12：当前可下载六页原生PPTX/PDF/PNG，报告及剩余范围已交付；本版未重跑PowerPointUI，AC028与全部原AC仍未通过。 完整步骤原验收未通过。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -11725,7 +11755,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1157b4baa05494b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd947b102874c4925"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14015,10 +14045,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O42" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P42" s="86" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。
+2026-10-12阶段收尾：原DOCX解析已接native evidence增强：heading/table逻辑grid/合并/图片部件hash尺寸alt、hyperlink/脚注/引用、物理页pending；34项组件通过。有效外链URI另登记原生关系字面证据，未下载。旧夹具引用关系异常与当前实际模型日期变换均拒绝；本轮完整DOCX生成未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -14061,10 +14092,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O43" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P43" s="86" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。
+2026-10-12阶段收尾：固定Poppler真实4页夹具38项通过，页/块/逐字坐标、网格/标题候选与真实图片清单进入source_context；跨页表/并列正文/OCR/图片几何不猜，超限明确失败。六页PDF实际模型输出截断阻断生成，完整AC003未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -14245,10 +14277,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O47" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P47" s="86" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。
+2026-10-12阶段收尾：XLSX显示投影接入：日期1900/1904、固定格式/百分比/引用单位、已有公式缓存、原cell/range与候选，57项组件通过。未知/地域/条件格式/缺缓存原数据保留但不冒作数值事实。两sheet实际API六页PPTX/render/真实审查12项通过，P0=0/4警告；全Excel显示/语义AC005仍未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -14613,10 +14646,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O55" s="84" t="str">
-        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P55" s="86" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。
+2026-10-12阶段收尾：三格式原生定位与source_context进入真正SourceLoader/初始事实解释，原始字节/hash保留；DOCX新增URI有独立关系锚点，PDF重复数字保留不同字锚点。物理Word页、OCR与全格式来源绑定仍待完成。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -15497,10 +15531,11 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="O74" s="84" t="str">
-        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P74" s="86" t="str">
-        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。</x:v>
+        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。
+2026-10-12阶段收尾：本轮新增source_context实际消费，候选不宣称事实真值；XLSX显示值区分底层存储/缓存。DOCX无依据引用/日期与PDF模型截断在写PPT前失败，原独立节点已完成状态保留，不等于来源语义与AC全通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -20679,10 +20714,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O186" s="84" t="str">
-        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+        <x:v>validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P186" s="86" t="str">
-        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。
+2026-10-12阶段收尾：三格式助手已由parse_input实际调用并纳入parser_version；真实XLSX生成和单段prompt链路经过SourceLoader。原始快照/角色/选定事实保留，HTML/YAML/OCR等原范围未完成。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="187" ht="180" customHeight="1">
@@ -21234,10 +21270,11 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O198" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P198" s="86" t="str">
-        <x:v>结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
+        <x:v>结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。
+2026-10-12阶段收尾：单段描述六页24对象→原生PPTX/真实render/独立review，P0=0/3警告；局部修订后P0=0/2警告。人工视觉发现封面操作指令泄漏，自动QA未拦截；完整事实/内容适用性/可编辑性等原QA仍未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="199" ht="172.5" customHeight="1">
@@ -21280,11 +21317,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O199" s="84" t="str">
-        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P199" s="86" t="str">
         <x:v>RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
-2026-10-11增量：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 完整原验收未通过。</x:v>
+2026-10-11增量：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 完整原验收未通过。
+2026-10-12阶段收尾：复用前一批次消费者，明确局部改封面标题/正文清除操作指令；真实复审15项流程检查，另8项Native数据/字节检查，只有slide1.xml改变，其他页/数据/选定事实保留。未称全节点自动修订完成。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="200" ht="172.5" customHeight="1">
@@ -22925,11 +22963,12 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="O235" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/；validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="P235" s="86" t="str">
         <x:v>部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
-2026-10-11增量：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 完整原验收未通过。</x:v>
+2026-10-11增量：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 完整原验收未通过。
+2026-10-12阶段收尾：人工发现的task_instruction_leak另记slide/object/type/P1/measurement/threshold/action/render hash及改后状态，原自动QA不覆盖；自动规则尚未支持该问题，完整issue/修订原验收仍未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
     <x:row r="236">
@@ -26112,7 +26151,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c9d20a90164cfc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49494dde5f504b47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29187,7 +29226,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M70" s="84" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json
+2026-10-12：原DOCX解析已接native evidence增强：heading/table逻辑grid/合并/图片部件hash尺寸alt、hyperlink/脚注/引用、物理页pending；34项组件通过。有效外链URI另登记原生关系字面证据，未下载。旧夹具引用关系异常与当前实际模型日期变换均拒绝；本轮完整DOCX生成未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N70" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29229,7 +29269,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M71" s="84" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json
+2026-10-12：固定Poppler真实4页夹具38项通过，页/块/逐字坐标、网格/标题候选与真实图片清单进入source_context；跨页表/并列正文/OCR/图片几何不猜，超限明确失败。六页PDF实际模型输出截断阻断生成，完整AC003未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N71" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29397,7 +29438,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M75" s="84" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json
+2026-10-12：XLSX显示投影接入：日期1900/1904、固定格式/百分比/引用单位、已有公式缓存、原cell/range与候选，57项组件通过。未知/地域/条件格式/缺缓存原数据保留但不冒作数值事实。两sheet实际API六页PPTX/render/真实审查12项通过，P0=0/4警告；全Excel显示/语义AC005仍未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N75" s="86" t="str">
         <x:v>本规划</x:v>
@@ -29733,7 +29775,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M83" s="84" t="str">
-        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json</x:v>
+        <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。 validation/input-format-artifacts/；validation/输入格式与原生模板实装.md；validation/parallel-integration.json；validation/job-lifecycle.json
+2026-10-12：三格式原生定位与source_context进入真正SourceLoader/初始事实解释，原始字节/hash保留；DOCX新增URI有独立关系锚点，PDF重复数字保留不同字锚点。物理Word页、OCR与全格式来源绑定仍待完成。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N83" s="86" t="str">
         <x:v>本规划</x:v>
@@ -30717,7 +30760,8 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="M106" s="84" t="str">
-        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>事实直接使用、显式假设、精确推算、placeholder及询问/失败已运行；假设稳定ID及可见标记，未决阻断。独立入口、原FactConstraintSet/Assumption校验、候选/轨迹、正常边界和五项目对应齐备。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md
+2026-10-12：本轮新增source_context实际消费，候选不宣称事实真值；XLSX显示值区分底层存储/缓存。DOCX无依据引用/日期与PDF模型截断在写PPT前失败，原独立节点已完成状态保留，不等于来源语义与AC全通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="N106" s="86" t="str">
         <x:v>本规划</x:v>
@@ -30761,7 +30805,8 @@
         <x:v>已完成</x:v>
       </x:c>
       <x:c r="M107" s="84" t="str">
-        <x:v>三正常以上、边界/冲突、独立入口及完整候选轨迹通过；实际生成/修订及初次失败保留，五项目partial/not_found明确。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md</x:v>
+        <x:v>三正常以上、边界/冲突、独立入口及完整候选轨迹通过；实际生成/修订及初次失败保留，五项目partial/not_found明确。 validation/fact-runtime.json；validation/fact-integration.json；validation/fact-project-map.json；validation/fact-artifacts/；validation/来源冲突与事实边界.md
+2026-10-12：本轮新增source_context实际消费，候选不宣称事实真值；XLSX显示值区分底层存储/缓存。DOCX无依据引用/日期与PDF模型截断在写PPT前失败，原独立节点已完成状态保留，不等于来源语义与AC全通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="N107" s="86" t="str">
         <x:v>本规划</x:v>
@@ -38848,7 +38893,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M295" s="84" t="str">
-        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md</x:v>
+        <x:v>四模块已接统一CLI/API/MCP或生成主链路；持久化作业、create/status/artifacts/cancel/retry、独立节点调试与精确已有PPT编辑已执行。真实八页AI生成/渲染/QA P0=0；全部生命周期、任意节点/能力/布局调试、全部MCP链路和系统AC待完成。 validation/parallel-integration.json；validation/job-lifecycle.json；validation/并行核心功能集成.md
+2026-10-12：三格式助手已由parse_input实际调用并纳入parser_version；真实XLSX生成和单段prompt链路经过SourceLoader。原始快照/角色/选定事实保留，HTML/YAML/OCR等原范围未完成。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N295" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39355,7 +39401,8 @@
         <x:v>进行中</x:v>
       </x:c>
       <x:c r="M307" s="84" t="str">
-        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。</x:v>
+        <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 结构/视觉几何/图片DPI/可访问性/一致性与真实模型复审运行。50/23/46/23/38及增量3/4各有版本，未汇称全套重跑。完整QA待补。
+2026-10-12：单段描述六页24对象→原生PPTX/真实render/独立review，P0=0/3警告；局部修订后P0=0/2警告。人工视觉发现封面操作指令泄漏，自动QA未拦截；完整事实/内容适用性/可编辑性等原QA仍未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N307" s="86" t="str">
         <x:v>本规划</x:v>
@@ -39398,7 +39445,8 @@
       </x:c>
       <x:c r="M308" s="84" t="str">
         <x:v>validation/revision-plan-artifacts/；validation/visual-live-artifacts/ RevisionPlan几何/样式消费者24项实际检查，局部修改保留非目标part、锁与before/after/QA/history；完整任意节点/对象修订未完成。
-2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+2026-10-11：共享revise入口连接批次识别→前置规格/锁校验→原生修改→真实render→独立选页模型复审→QA/history；CLI/MCP锁拒绝实跑。全部节点局部重跑仍未完成。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。
+2026-10-12：复用前一批次消费者，明确局部改封面标题/正文清除操作指令；真实复审15项流程检查，另8项Native数据/字节检查，只有slide1.xml改变，其他页/数据/选定事实保留。未称全节点自动修订完成。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N308" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41743,7 +41791,8 @@
       </x:c>
       <x:c r="M363" s="84" t="str">
         <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 部分原生结构、边界/碰撞/溢出、层级/对比/DPI、一致性/可访问性规则与DEC039/040实跑。历史38项和设计变化3/尺寸4分别保留；完整原QA验收未通过。
-2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。
+2026-10-12：人工发现的task_instruction_leak另记slide/object/type/P1/measurement/threshold/action/render hash及改后状态，原自动QA不覆盖；自动规则尚未支持该问题，完整issue/修订原验收仍未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N363" s="86" t="str">
         <x:v>本规划</x:v>
@@ -41788,7 +41837,8 @@
       </x:c>
       <x:c r="M364" s="84" t="str">
         <x:v>validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/visual-live-artifacts/ 本版直接/历史证据范围分别记录，完整原验收待补。
-2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。</x:v>
+2026-10-11：复审只更新所选页并保留其他页issue；DEC040消费真实祖先节点，未把P0=0当final。所有issue完整字段/阈值/action原验收仍待补。 validation/批量局部修订与原生保真.md；validation/batch-revision-artifacts/；完整原验收未通过。
+2026-10-12：人工发现的task_instruction_leak另记slide/object/type/P1/measurement/threshold/action/render hash及改后状态，原自动QA不覆盖；自动规则尚未支持该问题，完整issue/修订原验收仍未通过。 当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json；完整原验收未通过。</x:v>
       </x:c>
       <x:c r="N364" s="86" t="str">
         <x:v>本规划</x:v>
@@ -45468,7 +45518,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fc7909d95004407"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a0a669be8cb4ff0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45762,7 +45812,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0387acef51ca484e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40fbc9a33dfa477a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47178,7 +47228,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3f6c9839fca473b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93f0754e609e4c09"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47608,7 +47658,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d879d74ea3240e3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48a9756cca1e4a57"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51048,7 +51098,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R279db42536214643"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e0f96447e3e478d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
+++ b/AI_PPT_完整需求与任务矩阵_V0.3.xlsx
@@ -1257,7 +1257,7 @@
         <x:v>日期</x:v>
       </x:c>
       <x:c r="D2" s="15" t="str">
-        <x:v>2026-10-01</x:v>
+        <x:v>2026-10-12</x:v>
       </x:c>
       <x:c r="E2" s="15" t="str">
         <x:v>主需求</x:v>
@@ -1276,6 +1276,11 @@
       </x:c>
       <x:c r="J2" s="16" t="n">
         <x:v>45</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="35" customHeight="1">
+      <x:c r="A3" s="14" t="str">
+        <x:v>EXEC-20261012-01：GPT-6.1 sol 自主开发；Docling 与已选开源模块优先复用；禁止开发工期预算；全部原验收一次整体交付。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1908,6 +1913,7 @@
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A3:J3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32938d9adc004ed3"/>
@@ -9761,7 +9767,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E2" s="80" t="str"/>
-      <x:c r="F2" s="82" t="str"/>
+      <x:c r="F2" s="82" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="83" t="str">
@@ -9777,7 +9785,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E3" s="84" t="str"/>
-      <x:c r="F3" s="86" t="str"/>
+      <x:c r="F3" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="83" t="str">
@@ -9793,7 +9803,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E4" s="84" t="str"/>
-      <x:c r="F4" s="86" t="str"/>
+      <x:c r="F4" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="83" t="str">
@@ -9809,7 +9821,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E5" s="84" t="str"/>
-      <x:c r="F5" s="86" t="str"/>
+      <x:c r="F5" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -9825,7 +9839,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E6" s="84" t="str"/>
-      <x:c r="F6" s="86" t="str"/>
+      <x:c r="F6" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -9841,7 +9857,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E7" s="84" t="str"/>
-      <x:c r="F7" s="86" t="str"/>
+      <x:c r="F7" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -9857,7 +9875,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E8" s="84" t="str"/>
-      <x:c r="F8" s="86" t="str"/>
+      <x:c r="F8" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -9873,7 +9893,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E9" s="84" t="str"/>
-      <x:c r="F9" s="86" t="str"/>
+      <x:c r="F9" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -9889,7 +9911,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E10" s="84" t="str"/>
-      <x:c r="F10" s="86" t="str"/>
+      <x:c r="F10" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -9905,7 +9929,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E11" s="84" t="str"/>
-      <x:c r="F11" s="86" t="str"/>
+      <x:c r="F11" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -9921,7 +9947,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E12" s="84" t="str"/>
-      <x:c r="F12" s="86" t="str"/>
+      <x:c r="F12" s="86" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="87" t="str">
@@ -9937,7 +9965,9 @@
         <x:v>未开始</x:v>
       </x:c>
       <x:c r="E13" s="88" t="str"/>
-      <x:c r="F13" s="90" t="str"/>
+      <x:c r="F13" s="90" t="str">
+        <x:v>EXEC-20261012-01：由GPT-6.1 sol完成接入/实现/验证；复用有效证据，保持原交接要求。</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="87" t="str">
@@ -9959,7 +9989,147 @@
         <x:v>与 GOV-009 需求行、任务行保持一致。</x:v>
       </x:c>
     </x:row>
+    <x:row r="16" ht="30" customHeight="1">
+      <x:c r="A16" s="80" t="str">
+        <x:v>用户授权执行要求 EXEC-20261012-01</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="63" customHeight="1">
+      <x:c r="A17" s="80" t="str">
+        <x:v>开发主体</x:v>
+      </x:c>
+      <x:c r="B17" s="80" t="str">
+        <x:v>后续开发完全由 GPT-6.1 sol 负责，包含源码接入、融合改造、环境处理、联调、测试、宿主操作、缺陷修复、原矩阵回填、文档、日志、提交和推送。不得将编程、测试、排障或集成任务交给人完成，不按人力团队排期。产品运行中的用户输入、确认和调试能力仍按原需求保留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="63" customHeight="1">
+      <x:c r="A18" s="80" t="str">
+        <x:v>整体交付</x:v>
+      </x:c>
+      <x:c r="B18" s="80" t="str">
+        <x:v>一次性完成指以全部原需求及验收完成后的整体系统为最终交付。持续执行必要工作，不将演示稿、主链路子集、研究报告、契约草案或阶段收尾当作全部完成，不要求用户逐包发送继续指令。内部并行、检查点、测试和版本提交仅用于保证实现、验证与恢复。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="63" customHeight="1">
+      <x:c r="A19" s="80" t="str">
+        <x:v>禁止工期预算</x:v>
+      </x:c>
+      <x:c r="B19" s="80" t="str">
+        <x:v>目标、任务安排与交付说明只记录需要实现的行为、原 ID、依赖、具体接入、验收条件和证据。不输出开发小时数、工作日、周月预算、人日人周、排期或预计交付日期。产品页数预算、模型成本、超时和性能阈值属于原功能与验收，完整保留。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="63" customHeight="1">
+      <x:c r="A20" s="80" t="str">
+        <x:v>开源复用顺序</x:v>
+      </x:c>
+      <x:c r="B20" s="80" t="str">
+        <x:v>优先直接调用已固定版本的开源库、CLI、API或服务；需要时连同必要依赖复用可合法采用的模块并保留许可与修改记录；接口差异通过薄适配层连接；只有上游未覆盖、实际缺陷或原验收不满足的部分才补充实现。不得因语言偏好、目录不同或旧仅参考决定而重写现成功能。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="80" customHeight="1">
+      <x:c r="A21" s="80" t="str">
+        <x:v>文档与来源</x:v>
+      </x:c>
+      <x:c r="B21" s="80" t="str">
+        <x:v>DOCX、PDF、扫描件及适用输入优先接入 Docling 的成熟解析、表格、OCR和结构化输出。融合层绑定原文件/hash、page/paragraph/cell/source anchor、资产与事实 ID，映射到既有 SourceBundle/Evidence。保留已有有效解析证据；只有 Docling 未覆盖的原能力补充适配。解析候选不自动等于事实真值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="63" customHeight="1">
+      <x:c r="A22" s="80" t="str">
+        <x:v>模板与原生执行</x:v>
+      </x:c>
+      <x:c r="B22" s="80" t="str">
+        <x:v>优先接入 PPT Master 已有模板/导出/检查/编辑模块与 Presenton 的模板、布局、元素和内容 schema。复用已验证的原生对象库及本项目现有写入能力，不重新实现完整导出引擎。融合代码负责统一对象映射、模板与品牌锁、容量、资产许可、能力路由和保留边界。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="80" customHeight="1">
+      <x:c r="A23" s="80" t="str">
+        <x:v>质量与修订</x:v>
+      </x:c>
+      <x:c r="B23" s="80" t="str">
+        <x:v>优先复用 PPTAgent/DeepPresenter 的渲染、视觉审查契约及 freshness 检查和 PPT Master 的结构/导出检查，连接现有局部修订模块。融合层统一 slide/object、severity、measurement、threshold、action 和 RevisionPlan，修订后实际重渲染与独立复查。事实真值、内容适用性及任意原稿保真等上游缺口按原验收补齐。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="63" customHeight="1">
+      <x:c r="A24" s="80" t="str">
+        <x:v>后端与兼容</x:v>
+      </x:c>
+      <x:c r="B24" s="80" t="str">
+        <x:v>PP-01–09 按原行完成真实 PoC、能力状态及证据，不人为扩成九套全功能引擎自研。PPT-001–030 按原条件至少由适用后端满足必需能力，并如实登记其他路线。AC-028 验证 PowerPoint 无修复提示，其他客户端差异按原可选要求处理。原允许的保留或降级必须显式记录，不能冲销必须支持的能力。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="63" customHeight="1">
+      <x:c r="A25" s="80" t="str">
+        <x:v>既有研究与决定</x:v>
+      </x:c>
+      <x:c r="B25" s="80" t="str">
+        <x:v>复用现有 P01–P05 固定快照、源码定位、契约、产物、测试和运行证据，不重复全量 clone、安装或研究。RES-032 中仅参考/抽象复用属于可调整的历史工程决定：在来源、依赖、许可与实际接口核对后更新为直接调用或模块复用。未接入模块不得写为已实现，未知许可和实际缺陷不得隐去。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="63" customHeight="1">
+      <x:c r="A26" s="80" t="str">
+        <x:v>融合与并行</x:v>
+      </x:c>
+      <x:c r="B26" s="80" t="str">
+        <x:v>主智能体独占共享入口、主链路、原矩阵、文档、日志和 Git；至多三个子智能体按不重叠模块推进。先约定输入输出和文件归属，再完成模块行为并集中集成。保留原 Task ID 与依赖，将同一运行能力涉及的原任务成组完成，禁止把一个节点或函数拆成多次串行交付。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="80" customHeight="1">
+      <x:c r="A27" s="80" t="str">
+        <x:v>验收与真实状态</x:v>
+      </x:c>
+      <x:c r="B27" s="80" t="str">
+        <x:v>全部 308 条主需求、453 个任务、S00–S44、DEC-001–040、PPT-001–030、PP-01–09 和 AC-001–030 按原条件核对。上游有代码、安装成功、组件通过、P0=0或生成一份 PPTX 均不自动等于完整验收。Partial、Unsupported、Untested、Blocked 和未执行继续保留真实状态、剩余条件与证据。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="63" customHeight="1">
+      <x:c r="A28" s="80" t="str">
+        <x:v>恢复与阻塞</x:v>
+      </x:c>
+      <x:c r="B28" s="80" t="str">
+        <x:v>中断后从当前分支、工作区、上次提交、远端和未完成项恢复，复用有效证据，直接继续可执行动作。实质失败保留错误、版本、原 ID、证据及下一动作；对同一假设两次实验无新证据时更换排查路径。外部条件确实缺失时准确记录，不伪造完成，也不将可自主处理的工作交给用户。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="63" customHeight="1">
+      <x:c r="A29" s="80" t="str">
+        <x:v>范围与环境</x:v>
+      </x:c>
+      <x:c r="B29" s="80" t="str">
+        <x:v>GOV-009 排除账号、计费、多租户、协同编辑和模板商城；模板生成/解析/使用及 CLI/API/MCP/调试仍在范围。项目数据、依赖、临时目录、日志、Docker 可写层/卷/缓存均保持 F 盘约束。固定版本、来源归属、密钥保护、安全、许可、取消和失败恢复按原要求执行。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="80" customHeight="1">
+      <x:c r="A30" s="80" t="str">
+        <x:v>授权变更记录</x:v>
+      </x:c>
+      <x:c r="B30" s="80" t="str">
+        <x:v>EXEC-20261012-01：用户明确授权将执行方式改为 GPT-6.1 sol 独立开发、开源复用优先、禁止开发工期预算及全部原验收一次整体交付。同步 GOAL.md、原 V0.3 DOCX 和 XLSX。变更关联原治理、复用、来源、模板、对象、QA、修订、后端和工程交付 ID，不新增主需求或可执行任务；已有状态与失败证据保持。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="35" customHeight="1">
+      <x:c r="A32" s="80" t="str">
+        <x:v>变更记录：2026-10-12 用户授权；原需求/任务/依赖/验收/状态不变；三份文件同步。</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A16:C16"/>
+    <x:mergeCell ref="B17:C17"/>
+    <x:mergeCell ref="B18:C18"/>
+    <x:mergeCell ref="B19:C19"/>
+    <x:mergeCell ref="B20:C20"/>
+    <x:mergeCell ref="B21:C21"/>
+    <x:mergeCell ref="B22:C22"/>
+    <x:mergeCell ref="B23:C23"/>
+    <x:mergeCell ref="B24:C24"/>
+    <x:mergeCell ref="B25:C25"/>
+    <x:mergeCell ref="B26:C26"/>
+    <x:mergeCell ref="B27:C27"/>
+    <x:mergeCell ref="B28:C28"/>
+    <x:mergeCell ref="B29:C29"/>
+    <x:mergeCell ref="B30:C30"/>
+    <x:mergeCell ref="A32:C32"/>
+  </x:mergeCells>
   <x:conditionalFormatting sqref="D2:D13">
     <x:cfRule type="expression" dxfId="44" priority="1">
       <x:formula>D2="已完成"</x:formula>
@@ -10355,6 +10525,29 @@
         <x:v>Office.js Add-in + Node bridge；支持 inspect/screenshot/raw OOXML/verify 等；安全边界需单独验证。</x:v>
       </x:c>
     </x:row>
+    <x:row r="17" ht="66" customHeight="1">
+      <x:c r="A17" s="79" t="str">
+        <x:v>SRC-016</x:v>
+      </x:c>
+      <x:c r="B17" s="80" t="str">
+        <x:v>开源组件</x:v>
+      </x:c>
+      <x:c r="C17" s="80" t="str">
+        <x:v>Docling</x:v>
+      </x:c>
+      <x:c r="D17" s="80" t="str">
+        <x:v>https://github.com/docling-project/docling</x:v>
+      </x:c>
+      <x:c r="E17" s="80" t="str">
+        <x:v>IN-003/004/005/008/016；SYS-003；RES-032；GOV-010</x:v>
+      </x:c>
+      <x:c r="F17" s="80" t="str">
+        <x:v>2026-10-12</x:v>
+      </x:c>
+      <x:c r="G17" s="82" t="str">
+        <x:v>代码 MIT；模型与依赖分别核对；本轮登记执行来源，产品集成时冻结实际版本/hash；尚未接入产品</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -10522,7 +10715,7 @@
         <x:v>新增素材/模板敏感路径和真实链接越界guard。全类型/密码/宏/输出权限原验收待补。</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="195" customHeight="1">
+    <x:row r="6" ht="151" customHeight="1">
       <x:c r="A6" s="83" t="str">
         <x:v>S04</x:v>
       </x:c>
@@ -10548,10 +10741,11 @@
         <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I6" s="86" t="str">
-        <x:v>2026-10-12当前：当前SourceLoader实际读取prompt/text/Markdown、DOCX/XLSX/CSV/PPTX/POTX/PDF/image/JSON/XML的有界原文件；本轮三格式增强接入。HTML/URL/YAML/OCR及全部资产类型仍待完成。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="195" customHeight="1">
+        <x:v>2026-10-12当前：当前SourceLoader实际读取prompt/text/Markdown、DOCX/XLSX/CSV/PPTX/POTX/PDF/image/JSON/XML的有界原文件；本轮三格式增强接入。HTML/URL/YAML/OCR及全部资产类型仍待完成。
+EXEC-20261012-01：优先调用Docling及成熟SourceLoader，映射现有SourceBundle与文件/hash。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="151" customHeight="1">
       <x:c r="A7" s="83" t="str">
         <x:v>S05</x:v>
       </x:c>
@@ -10577,7 +10771,8 @@
         <x:v>并行核心模块已增加输入、叙事、模板、原生对象、精确编辑、任务及MCP入口；仅已执行子能力。剩余完整条件以原需求行和原验收为准，未通过不可标完成。 validation/并行核心功能集成.md；当前实现与阶段收尾报告_20261012.md；validation/stage-closure-artifacts/；validation/stage-closure-summary.json</x:v>
       </x:c>
       <x:c r="I7" s="86" t="str">
-        <x:v>2026-10-12当前：三格式原文/结构/原生段格页与图片部件证据已保存，候选结构进入模型但不视为语义真值；物理Word页/OCR/复杂PDF表格/全部格式语义待补。</x:v>
+        <x:v>2026-10-12当前：三格式原文/结构/原生段格页与图片部件证据已保存，候选结构进入模型但不视为语义真值；物理Word页/OCR/复杂PDF表格/全部格式语义待补。
+EXEC-20261012-01：复用结构/OCR/表格能力，融合page/paragraph/cell锚点、资产和事实ID。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="195" customHeight="1">
@@ -11376,7 +11571,7 @@
 2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="195" customHeight="1">
+    <x:row r="35" ht="372" customHeight="1">
       <x:c r="A35" s="83" t="str">
         <x:v>S33</x:v>
       </x:c>
@@ -11403,10 +11598,11 @@
       </x:c>
       <x:c r="I35" s="86" t="str">
         <x:v>实际PDF/逐页PNG/hash版本保存，QA-only复用字节；live/全部缩略图待补。
-2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="195" customHeight="1">
+2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
+EXEC-20261012-01：优先接已有渲染器；统一产物与版本/hash，不另造渲染引擎。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="424" customHeight="1">
       <x:c r="A36" s="83" t="str">
         <x:v>S34</x:v>
       </x:c>
@@ -11434,10 +11630,11 @@
       <x:c r="I36" s="86" t="str">
         <x:v>部分原生结构/边界/空对象/碰撞/溢出检查运行；完整结构验收待补。
 2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
-2026-10-12：新描述与XLSX实物真实结构/渲染检查P0=0，原生数值与字节另验；全结构规则仍未完成。 完整步骤原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" ht="195" customHeight="1">
+2026-10-12：新描述与XLSX实物真实结构/渲染检查P0=0，原生数值与字节另验；全结构规则仍未完成。 完整步骤原验收未通过。
+EXEC-20261012-01：复用PPT Master结构/导出检查并统一原Issue契约。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="489" customHeight="1">
       <x:c r="A37" s="83" t="str">
         <x:v>S35</x:v>
       </x:c>
@@ -11466,10 +11663,11 @@
         <x:v>实际模型视觉复审与层级/对比/DPI/一致性规则，警告保留；全规则待补。
 2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
 2026-10-11：五次真实render/独立选页模型复审；美化局部几何/颜色恢复，全部视觉规则仍待覆盖。 完整步骤与原验收未通过。
-2026-10-12：实际render经人工查看，发现封面操作指令外泄并仅修封面。自动QA未发现该内容问题，不能以P0=0判全部视觉/内容通过。 完整步骤原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" ht="195" customHeight="1">
+2026-10-12：实际render经人工查看，发现封面操作指令外泄并仅修封面。自动QA未发现该内容问题，不能以P0=0判全部视觉/内容通过。 完整步骤原验收未通过。
+EXEC-20261012-01：复用PPTAgent视觉审查模块，保留真实图像、阈值和问题定位。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="476" customHeight="1">
       <x:c r="A38" s="83" t="str">
         <x:v>S36</x:v>
       </x:c>
@@ -11497,10 +11695,11 @@
       <x:c r="I38" s="86" t="str">
         <x:v>数值引用与真实模型事实复审，图片尺寸仅对同页实际hash/像素验证后排除元数据；完整语义真值待补。
 2026-10-11：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整S步骤与原验收未通过。
-2026-10-12：事实/数值与实际模型审查执行，DOCX日期错误/PDF截断拒绝，XLSX数字单位实际保留。完整事实语义/内容适用性仍未通过。 完整步骤原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" ht="195" customHeight="1">
+2026-10-12：事实/数值与实际模型审查执行，DOCX日期错误/PDF截断拒绝，XLSX数字单位实际保留。完整事实语义/内容适用性仍未通过。 完整步骤原验收未通过。
+EXEC-20261012-01：沿用既有事实证据核对，补上游未覆盖的语义条件，不能以视觉审查代替事实验收。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="268" customHeight="1">
       <x:c r="A39" s="83" t="str">
         <x:v>S37</x:v>
       </x:c>
@@ -11528,10 +11727,11 @@
       <x:c r="I39" s="86" t="str">
         <x:v>原生图片/节点/边可编辑，局部非目标parts保持；全对象round-trip待补。
 2026-10-11：五次原生修订和52项夹具检查保留未选parts/XML；COM读取证明有界原生对象，所有对象编辑性/客户端语义待验收。 完整步骤与原验收未通过。
-2026-10-12：当前六页24原生对象含可编辑表/图；8项实物核对源数值和未改parts，所有对象与PowerPointUI兼容待验收。 完整步骤原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
+2026-10-12：当前六页24原生对象含可编辑表/图；8项实物核对源数值和未改parts，所有对象与PowerPointUI兼容待验收。 完整步骤原验收未通过。
+EXEC-20261012-01：复用原生对象库/上游编辑测试，按原对象与backend条件验证可编辑性。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="216" customHeight="1">
       <x:c r="A40" s="83" t="str">
         <x:v>S38</x:v>
       </x:c>
@@ -11558,10 +11758,11 @@
       </x:c>
       <x:c r="I40" s="86" t="str">
         <x:v>已检查原生alt-text/阅读顺序/字号/对比/表头部分字段，语言/RTL与完整可访问性待补。
-2026-10-11：换图的alt_text与图注证据同步，连接线descr承载关系时明确拒绝alt修改；完整可访问性待验收。 完整步骤与原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" ht="195" customHeight="1">
+2026-10-11：换图的alt_text与图注证据同步，连接线descr承载关系时明确拒绝alt修改；完整可访问性待验收。 完整步骤与原验收未通过。
+EXEC-20261012-01：统一上游问题到原slide/object/action，保留严重度、测量值与阈值。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="216" customHeight="1">
       <x:c r="A41" s="83" t="str">
         <x:v>S39</x:v>
       </x:c>
@@ -11588,10 +11789,11 @@
       </x:c>
       <x:c r="I41" s="86" t="str">
         <x:v>DEC039将实际issue映射局部RevisionPlan/fail/needs_input；全部节点修订待补。
-2026-10-11：继承已有RevisionPlan路径；新增用户批次指令与真实模型目标解释保留trace，不等同全QA自动动作已支持。 完整步骤与原验收未通过。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" ht="195" customHeight="1">
+2026-10-11：继承已有RevisionPlan路径；新增用户批次指令与真实模型目标解释保留trace，不等同全QA自动动作已支持。 完整步骤与原验收未通过。
+EXEC-20261012-01：统一RevisionPlan与范围/锁/版本，不重写完整修订引擎。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="268" customHeight="1">
       <x:c r="A42" s="83" t="str">
         <x:v>S40</x:v>
       </x:c>
@@ -11619,7 +11821,8 @@
       <x:c r="I42" s="86" t="str">
         <x:v>24项RevisionPlan消费者检查，真实布局/颜色局部修改和QA/history；任意节点/对象待补。
 2026-10-11：多页多对象批次修改→实际render→独立选页复审→QA/history；未选页/对象字节保留，重复换图可继续修订。任意节点/对象/已有deck语义仍待补。 完整步骤与原验收未通过。
-2026-10-12：当前明确局部改首页两个对象，其他五页/数据/选定事实保留，仅slide1.xml改变，实际选页重审；全部节点自动修订未完成。 完整步骤原验收未通过。</x:v>
+2026-10-12：当前明确局部改首页两个对象，其他五页/数据/选定事实保留，仅slide1.xml改变，实际选页重审；全部节点自动修订未完成。 完整步骤原验收未通过。
+EXEC-20261012-01：调用既有局部修改及上游适用能力，实际渲染和独立复查。</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="195" customHeight="1">
@@ -11682,7 +11885,7 @@
         <x:v>PPTX/PDF/PNG/manifest/trace/QA实物导出；最终系统验收门控尚未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="195" customHeight="1">
+    <x:row r="45" ht="190" customHeight="1">
       <x:c r="A45" s="83" t="str">
         <x:v>S43</x:v>
       </x:c>
@@ -11708,10 +11911,11 @@
         <x:v>validation/visual-live-artifacts/；validation/layout-stage-artifacts/；validation/visual-execution-artifacts/；validation/visual-live-artifacts/；validation/quality-stage-artifacts/；validation/revision-plan-artifacts/quality-design-variation.json；validation/visual-live-artifacts/；validation/revision-plan-artifacts/；validation/visual-live-artifacts/</x:v>
       </x:c>
       <x:c r="I45" s="86" t="str">
-        <x:v>素材/模板来源/hash/许可/unknown状态及模型版本保存；全来源合并许可清单待补。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" ht="195" customHeight="1">
+        <x:v>素材/模板来源/hash/许可/unknown状态及模型版本保存；全来源合并许可清单待补。
+EXEC-20261012-01：固定模块/依赖版本和许可，未知边界明确记录；开发由GPT完成。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="268" customHeight="1">
       <x:c r="A46" s="87" t="str">
         <x:v>S44</x:v>
       </x:c>
@@ -11739,7 +11943,8 @@
       <x:c r="I46" s="90" t="str">
         <x:v>六页可编辑原生对象与真实渲染已检查，本版PowerPoint实际打开/全部交付原验收未完成。
 2026-10-11：四份新修订稿实际PowerPoint只读打开及489项对照；更早父稿副本编辑另存复开成立。UI无修复提示及修订稿目标对象实际改存复开仍未验证。 完整步骤与原验收未通过。
-2026-10-12：当前可下载六页原生PPTX/PDF/PNG，报告及剩余范围已交付；本版未重跑PowerPointUI，AC028与全部原AC仍未通过。 完整步骤原验收未通过。</x:v>
+2026-10-12：当前可下载六页原生PPTX/PDF/PNG，报告及剩余范围已交付；本版未重跑PowerPointUI，AC028与全部原AC仍未通过。 完整步骤原验收未通过。
+EXEC-20261012-01：全部原验收后整体交付；不以阶段稿替代，不安排人工开发或工期预算。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -12107,7 +12312,7 @@
         <x:v>验收结果</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="72" customHeight="1">
+    <x:row r="2" ht="47" customHeight="1">
       <x:c r="A2" s="79" t="str">
         <x:v>GOV-001</x:v>
       </x:c>
@@ -12142,7 +12347,9 @@
       <x:c r="L2" s="80" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M2" s="80" t="str"/>
+      <x:c r="M2" s="80" t="str">
+        <x:v>EXEC-20261012-01：用户授权执行修订同步三份文件；原ID、需求、依赖、验收及状态保持。</x:v>
+      </x:c>
       <x:c r="N2" s="80" t="str">
         <x:v>已完成</x:v>
       </x:c>
@@ -12429,7 +12636,7 @@
         <x:v>实际DAG原子能力及实现ID已稳定登记；shape到source/spec/call/DEC-001可追溯，全部对象/决策尚未完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="9">
+    <x:row r="9" ht="60" customHeight="1">
       <x:c r="A9" s="83" t="str">
         <x:v>GOV-008</x:v>
       </x:c>
@@ -12464,7 +12671,9 @@
       <x:c r="L9" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M9" s="84" t="str"/>
+      <x:c r="M9" s="84" t="str">
+        <x:v>EXEC-20261012-01：全部原验收一次整体交付；中间产物、P0=0和阶段收尾不代替最终完成。</x:v>
+      </x:c>
       <x:c r="N9" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -12521,7 +12730,7 @@
         <x:v>GOV-009 范围声明已与 AGENTS.md 和 Codex交接 CH-013 对齐。</x:v>
       </x:c>
     </x:row>
-    <x:row r="11">
+    <x:row r="11" ht="60" customHeight="1">
       <x:c r="A11" s="83" t="str">
         <x:v>GOV-010</x:v>
       </x:c>
@@ -12556,7 +12765,9 @@
       <x:c r="L11" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M11" s="84" t="str"/>
+      <x:c r="M11" s="84" t="str">
+        <x:v>EXEC-20261012-01：复用固定上游快照与证据；Docling和新接模块在实际集成时登记版本/hash。</x:v>
+      </x:c>
       <x:c r="N11" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -13817,7 +14028,7 @@
         <x:v>15维度×5项目，来源/运行/黑盒分列；P03 VERIFY仍进行中。</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="180" customHeight="1">
+    <x:row r="38" ht="73" customHeight="1">
       <x:c r="A38" s="83" t="str">
         <x:v>RES-032</x:v>
       </x:c>
@@ -13854,7 +14065,9 @@
       <x:c r="L38" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M38" s="84" t="str"/>
+      <x:c r="M38" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先直接调用/模块复用；核对来源、依赖、许可和接口后调整旧仅参考/抽象复用决定，不以工程偏好重写现成功能。</x:v>
+      </x:c>
       <x:c r="N38" s="84" t="str">
         <x:v>已完成</x:v>
       </x:c>
@@ -14005,7 +14218,7 @@
         <x:v>真实结构解析/原文锚点已运行；行内定位为所属块范围，部分Markdown扩展明确拒绝。</x:v>
       </x:c>
     </x:row>
-    <x:row r="42">
+    <x:row r="42" ht="164" customHeight="1">
       <x:c r="A42" s="83" t="str">
         <x:v>IN-003</x:v>
       </x:c>
@@ -14040,7 +14253,9 @@
       <x:c r="L42" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M42" s="84" t="str"/>
+      <x:c r="M42" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先接Docling DOCX结构输出到现有SourceBundle/Evidence及原锚点；保留原解析证据，缺口才补适配。</x:v>
+      </x:c>
       <x:c r="N42" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -14052,7 +14267,7 @@
 2026-10-12阶段收尾：原DOCX解析已接native evidence增强：heading/table逻辑grid/合并/图片部件hash尺寸alt、hyperlink/脚注/引用、物理页pending；34项组件通过。有效外链URI另登记原生关系字面证据，未下载。旧夹具引用关系异常与当前实际模型日期变换均拒绝；本轮完整DOCX生成未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="43">
+    <x:row r="43" ht="151" customHeight="1">
       <x:c r="A43" s="83" t="str">
         <x:v>IN-004</x:v>
       </x:c>
@@ -14087,7 +14302,9 @@
       <x:c r="L43" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M43" s="84" t="str"/>
+      <x:c r="M43" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先接Docling PDF布局、表格和结构输出，保留page/坐标/source anchor与完整证据。</x:v>
+      </x:c>
       <x:c r="N43" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -14099,7 +14316,7 @@
 2026-10-12阶段收尾：固定Poppler真实4页夹具38项通过，页/块/逐字坐标、网格/标题候选与真实图片清单进入source_context；跨页表/并列正文/OCR/图片几何不猜，超限明确失败。六页PDF实际模型输出截断阻断生成，完整AC003未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="44">
+    <x:row r="44" ht="73" customHeight="1">
       <x:c r="A44" s="83" t="str">
         <x:v>IN-005</x:v>
       </x:c>
@@ -14134,7 +14351,9 @@
       <x:c r="L44" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M44" s="84" t="str"/>
+      <x:c r="M44" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先复用Docling OCR与成熟OCR引擎；模型/语言/置信度/页面定位按原验收记录。</x:v>
+      </x:c>
       <x:c r="N44" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -14237,7 +14456,7 @@
         <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="47">
+    <x:row r="47" ht="164" customHeight="1">
       <x:c r="A47" s="83" t="str">
         <x:v>IN-008</x:v>
       </x:c>
@@ -14272,7 +14491,9 @@
       <x:c r="L47" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M47" s="84" t="str"/>
+      <x:c r="M47" s="84" t="str">
+        <x:v>EXEC-20261012-01：评估Docling适用输出，保留现有公式缓存、显示值、单位与cell/range能力；不丢原字段。</x:v>
+      </x:c>
       <x:c r="N47" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -14606,7 +14827,7 @@
         <x:v>原生结构适配器已接SourceLoader/证据事务：DOCX/XLSX/CSV/PPTX/PDF/图像/JSON/XML，原字节、格式锚点、结构/警告保存，31项正常/边界通过；DOCX与文本实际生成。空结构/图片保留在nontext_evidence，不伪造OCR事实。DOCX物理页、PDF表格/扫描OCR、完整显示语义、YAML/路径选择/全资产类型待完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="180" customHeight="1">
+    <x:row r="55" ht="151" customHeight="1">
       <x:c r="A55" s="83" t="str">
         <x:v>IN-016</x:v>
       </x:c>
@@ -14641,7 +14862,9 @@
       <x:c r="L55" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M55" s="84" t="str"/>
+      <x:c r="M55" s="84" t="str">
+        <x:v>EXEC-20261012-01：融合层保留原文件/hash、page/paragraph/cell锚点、资产与事实ID，不把候选冒作事实真值。</x:v>
+      </x:c>
       <x:c r="N55" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -20674,7 +20897,7 @@
         <x:v>实际本地平台/精确写入依赖/字体/渲染探测由路由消费；Office/API set/MCP/远端模型完整探测待完成。</x:v>
       </x:c>
     </x:row>
-    <x:row r="186" ht="180" customHeight="1">
+    <x:row r="186" ht="125" customHeight="1">
       <x:c r="A186" s="83" t="str">
         <x:v>SYS-003</x:v>
       </x:c>
@@ -20709,7 +20932,9 @@
       <x:c r="L186" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M186" s="84" t="str"/>
+      <x:c r="M186" s="84" t="str">
+        <x:v>EXEC-20261012-01：SourceLoader实际调用成熟解析器，统一SourceBundle、结构化错误及trace。</x:v>
+      </x:c>
       <x:c r="N186" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -21091,7 +21316,7 @@
         <x:v>生成将实际图片及流程节点/边转统一规格、槽位、原子DAG/ObjectMap，23项组件直接执行。全部对象/后端/能力门控待补。</x:v>
       </x:c>
     </x:row>
-    <x:row r="195" ht="172.5" customHeight="1">
+    <x:row r="195" ht="203" customHeight="1">
       <x:c r="A195" s="83" t="str">
         <x:v>SYS-012</x:v>
       </x:c>
@@ -21126,7 +21351,9 @@
       <x:c r="L195" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M195" s="84" t="str"/>
+      <x:c r="M195" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先调用成熟原生对象库与开源执行模块，按现有AtomicCapability/对象映射消费；只补必需适配。</x:v>
+      </x:c>
       <x:c r="N195" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -21138,7 +21365,7 @@
 2026-10-11增量：三个组件已接visual→narrative/adaptive→layout/compile→原生写入→实际render/QA。实际API新生成ad03ceec复用人工原始输入，真实事实/内容/图像审查调用，产出4页但标题分页产生2项P0；增加可见原表分页说明并预留容量后，恢复468ac35a逐字复用该真实事实/内容种子，重新写入/渲染/实际模型复审，9项集成检查通过：8个原生图片、完整混合长标题、14行表格、3→4页、模型种子来源复用与真实新审查。当前P0=0、5项警告保留，DEC040=warning/final_allowed=false，完整原验收未通过。模板68/图库32/自适应161各历史版本，模板2/图库5/上下文15/分页说明10增量及同PDF228只读检查分别记录；不冒称当前全套重跑。 完整原验收仍未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="196" ht="172.5" customHeight="1">
+    <x:row r="196" ht="60" customHeight="1">
       <x:c r="A196" s="83" t="str">
         <x:v>SYS-013</x:v>
       </x:c>
@@ -21173,7 +21400,9 @@
       <x:c r="L196" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M196" s="84" t="str"/>
+      <x:c r="M196" s="84" t="str">
+        <x:v>EXEC-20261012-01：优先接PPT Master导出/编辑与Presenton适用对象模型，结合已验证原生库；保留模板/主题/未知部件。</x:v>
+      </x:c>
       <x:c r="N196" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -21184,7 +21413,7 @@
         <x:v>真实六页包含原生图片和可编辑流程，消费模板继承与跨页DAG。全部母版/布局/既有文件修改路线待验收。</x:v>
       </x:c>
     </x:row>
-    <x:row r="197" ht="172.5" customHeight="1">
+    <x:row r="197" ht="73" customHeight="1">
       <x:c r="A197" s="83" t="str">
         <x:v>SYS-014</x:v>
       </x:c>
@@ -21219,7 +21448,9 @@
       <x:c r="L197" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M197" s="84" t="str"/>
+      <x:c r="M197" s="84" t="str">
+        <x:v>EXEC-20261012-01：复用现有LibreOffice/Poppler与PPTAgent适用渲染模块；统一PNG/PDF/thumbnail、hash及renderer版本。</x:v>
+      </x:c>
       <x:c r="N197" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -21230,7 +21461,7 @@
         <x:v>六页PPTX实际LibreOffice PDF/PNG/hash渲染，QA-only恢复保持文件/渲染字节。live截图/全部renderer待补。</x:v>
       </x:c>
     </x:row>
-    <x:row r="198" ht="172.5" customHeight="1">
+    <x:row r="198" ht="138" customHeight="1">
       <x:c r="A198" s="83" t="str">
         <x:v>SYS-015</x:v>
       </x:c>
@@ -21265,7 +21496,9 @@
       <x:c r="L198" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M198" s="84" t="str"/>
+      <x:c r="M198" s="84" t="str">
+        <x:v>EXEC-20261012-01：接PPTAgent视觉审查/freshness及PPT Master检查器，统一原QA问题契约，补上游事实/语义缺口。</x:v>
+      </x:c>
       <x:c r="N198" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -21277,7 +21510,7 @@
 2026-10-12阶段收尾：单段描述六页24对象→原生PPTX/真实render/独立review，P0=0/3警告；局部修订后P0=0/2警告。人工视觉发现封面操作指令泄漏，自动QA未拦截；完整事实/内容适用性/可编辑性等原QA仍未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="199" ht="172.5" customHeight="1">
+    <x:row r="199" ht="151" customHeight="1">
       <x:c r="A199" s="83" t="str">
         <x:v>SYS-016</x:v>
       </x:c>
@@ -21312,7 +21545,9 @@
       <x:c r="L199" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M199" s="84" t="str"/>
+      <x:c r="M199" s="84" t="str">
+        <x:v>EXEC-20261012-01：连接上游与现有局部修改能力，统一范围/锁/版本/RevisionPlan及修订后的真实复查。</x:v>
+      </x:c>
       <x:c r="N199" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -22008,7 +22243,7 @@
         <x:v>2026-10-11增量：实际beautify锁定其余对象，正文几何与标题对比修复，事实/数据不变；8页P0=0但7警告且旧父缺DEC022–038，不伪造继承节点。完整视觉与品牌验收未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="215">
+    <x:row r="215" ht="99" customHeight="1">
       <x:c r="A215" s="83" t="str">
         <x:v>REV-010</x:v>
       </x:c>
@@ -22043,7 +22278,9 @@
       <x:c r="L215" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M215" s="84" t="str"/>
+      <x:c r="M215" s="84" t="str">
+        <x:v>EXEC-20261012-01：保留真实修订前后实物、对象差异与独立复查；已存在的修订模块优先复用。</x:v>
+      </x:c>
       <x:c r="N215" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -22923,7 +23160,7 @@
 2026-10-11增量：五次实际API修订均P0=0，警告6/4/5/7/6，final_allowed=false；原失败与旧父覆盖缺口保留。全问题类型/自动修订与原AC未通过。 完整原验收未通过。</x:v>
       </x:c>
     </x:row>
-    <x:row r="235">
+    <x:row r="235" ht="164" customHeight="1">
       <x:c r="A235" s="83" t="str">
         <x:v>QA-020</x:v>
       </x:c>
@@ -22958,7 +23195,9 @@
       <x:c r="L235" s="84" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M235" s="84" t="str"/>
+      <x:c r="M235" s="84" t="str">
+        <x:v>EXEC-20261012-01：复用检查与审查模块，按原slide/object/severity/measurement/threshold/action消费；有代码不等于原验收通过。</x:v>
+      </x:c>
       <x:c r="N235" s="84" t="str">
         <x:v>进行中</x:v>
       </x:c>
@@ -26085,7 +26324,7 @@
       <x:c r="O308" s="84" t="str"/>
       <x:c r="P308" s="86" t="str"/>
     </x:row>
-    <x:row r="309">
+    <x:row r="309" ht="60" customHeight="1">
       <x:c r="A309" s="87" t="str">
         <x:v>OPS-012</x:v>
       </x:c>
@@ -26120,7 +26359,9 @@
       <x:c r="L309" s="88" t="str">
         <x:v>本规划</x:v>
       </x:c>
-      <x:c r="M309" s="88" t="str"/>
+      <x:c r="M309" s="88" t="str">
+        <x:v>EXEC-20261012-01：GPT-6.1 sol独立完成实现/测试/排障/交付，不要求人工开发，不估算工期，不以阶段结果结束整体目标。</x:v>
+      </x:c>
       <x:c r="N309" s="88" t="str">
         <x:v>未开始</x:v>
       </x:c>
@@ -26174,6 +26415,10 @@
     <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="30" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="44" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" customWidth="1"/>
+    <x:col min="16" max="16" width="39" customWidth="1"/>
+    <x:col min="17" max="17" width="45" customWidth="1"/>
+    <x:col min="18" max="18" width="24" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -26219,6 +26464,18 @@
       <x:c r="N1" s="39" t="str">
         <x:v>来源</x:v>
       </x:c>
+      <x:c r="O1" s="39" t="str">
+        <x:v>执行主体</x:v>
+      </x:c>
+      <x:c r="P1" s="39" t="str">
+        <x:v>实现原则</x:v>
+      </x:c>
+      <x:c r="Q1" s="39" t="str">
+        <x:v>优先复用来源</x:v>
+      </x:c>
+      <x:c r="R1" s="39" t="str">
+        <x:v>执行修订</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="79" t="str">
@@ -26261,6 +26518,18 @@
       <x:c r="N2" s="82" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O2" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P2" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q2" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R2" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="83" t="str">
@@ -26303,6 +26572,18 @@
       <x:c r="N3" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O3" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P3" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q3" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R3" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="83" t="str">
@@ -26345,6 +26626,18 @@
       <x:c r="N4" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O4" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P4" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q4" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R4" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="83" t="str">
@@ -26387,6 +26680,18 @@
       <x:c r="N5" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O5" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P5" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q5" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R5" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="83" t="str">
@@ -26429,6 +26734,18 @@
       <x:c r="N6" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O6" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P6" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q6" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R6" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="83" t="str">
@@ -26471,6 +26788,18 @@
       <x:c r="N7" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O7" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P7" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q7" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R7" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="83" t="str">
@@ -26513,6 +26842,18 @@
       <x:c r="N8" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O8" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P8" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q8" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R8" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="83" t="str">
@@ -26555,6 +26896,18 @@
       <x:c r="N9" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O9" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P9" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q9" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R9" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="83" t="str">
@@ -26597,6 +26950,18 @@
       <x:c r="N10" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O10" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P10" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q10" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R10" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="83" t="str">
@@ -26639,6 +27004,18 @@
       <x:c r="N11" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O11" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P11" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q11" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R11" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="83" t="str">
@@ -26681,6 +27058,18 @@
       <x:c r="N12" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O12" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P12" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q12" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R12" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="83" t="str">
@@ -26723,6 +27112,18 @@
       <x:c r="N13" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O13" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P13" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q13" s="82" t="str">
+        <x:v>原schema/ID/能力/来源/变更记录</x:v>
+      </x:c>
+      <x:c r="R13" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="83" t="str">
@@ -26765,6 +27166,18 @@
       <x:c r="N14" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O14" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P14" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q14" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R14" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="83" t="str">
@@ -26809,6 +27222,18 @@
       <x:c r="N15" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O15" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P15" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q15" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R15" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="83" t="str">
@@ -26853,6 +27278,18 @@
       <x:c r="N16" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O16" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P16" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q16" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R16" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="83" t="str">
@@ -26897,6 +27334,18 @@
       <x:c r="N17" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O17" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P17" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q17" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R17" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="83" t="str">
@@ -26941,6 +27390,18 @@
       <x:c r="N18" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O18" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P18" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q18" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R18" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="83" t="str">
@@ -26985,6 +27446,18 @@
       <x:c r="N19" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O19" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P19" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q19" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R19" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="83" t="str">
@@ -27029,6 +27502,18 @@
       <x:c r="N20" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O20" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P20" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q20" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R20" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="83" t="str">
@@ -27073,6 +27558,18 @@
       <x:c r="N21" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O21" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P21" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q21" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R21" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="83" t="str">
@@ -27117,6 +27614,18 @@
       <x:c r="N22" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O22" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P22" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q22" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R22" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="83" t="str">
@@ -27161,6 +27670,18 @@
       <x:c r="N23" s="86" t="str">
         <x:v>https://github.com/hugohe3/ppt-master</x:v>
       </x:c>
+      <x:c r="O23" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P23" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q23" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R23" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="83" t="str">
@@ -27203,6 +27724,18 @@
       <x:c r="N24" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O24" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P24" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q24" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R24" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="83" t="str">
@@ -27247,6 +27780,18 @@
       <x:c r="N25" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O25" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P25" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q25" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R25" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="83" t="str">
@@ -27291,6 +27836,18 @@
       <x:c r="N26" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O26" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P26" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q26" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R26" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="83" t="str">
@@ -27335,6 +27892,18 @@
       <x:c r="N27" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O27" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P27" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q27" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R27" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="83" t="str">
@@ -27379,6 +27948,18 @@
       <x:c r="N28" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O28" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P28" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q28" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R28" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="83" t="str">
@@ -27423,6 +28004,18 @@
       <x:c r="N29" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O29" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P29" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q29" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R29" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="83" t="str">
@@ -27467,6 +28060,18 @@
       <x:c r="N30" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O30" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P30" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q30" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R30" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="83" t="str">
@@ -27511,6 +28116,18 @@
       <x:c r="N31" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O31" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P31" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q31" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R31" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="83" t="str">
@@ -27555,6 +28172,18 @@
       <x:c r="N32" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O32" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P32" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q32" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R32" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="83" t="str">
@@ -27599,6 +28228,18 @@
       <x:c r="N33" s="86" t="str">
         <x:v>https://github.com/icip-cas/PPTAgent</x:v>
       </x:c>
+      <x:c r="O33" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P33" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q33" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R33" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="83" t="str">
@@ -27641,6 +28282,18 @@
       <x:c r="N34" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O34" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P34" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q34" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R34" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="83" t="str">
@@ -27685,6 +28338,18 @@
       <x:c r="N35" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O35" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P35" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q35" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R35" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="83" t="str">
@@ -27729,6 +28394,18 @@
       <x:c r="N36" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O36" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P36" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q36" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R36" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="83" t="str">
@@ -27773,6 +28450,18 @@
       <x:c r="N37" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O37" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P37" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q37" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R37" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="83" t="str">
@@ -27817,6 +28506,18 @@
       <x:c r="N38" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O38" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P38" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q38" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R38" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="83" t="str">
@@ -27861,6 +28562,18 @@
       <x:c r="N39" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O39" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P39" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q39" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R39" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="83" t="str">
@@ -27905,6 +28618,18 @@
       <x:c r="N40" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O40" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P40" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q40" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R40" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="83" t="str">
@@ -27949,6 +28674,18 @@
       <x:c r="N41" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O41" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P41" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q41" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R41" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="83" t="str">
@@ -27993,6 +28730,18 @@
       <x:c r="N42" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
       </x:c>
+      <x:c r="O42" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P42" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q42" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R42" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="83" t="str">
@@ -28036,6 +28785,18 @@
       </x:c>
       <x:c r="N43" s="86" t="str">
         <x:v>https://github.com/presenton/presenton</x:v>
+      </x:c>
+      <x:c r="O43" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P43" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q43" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R43" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -28083,6 +28844,18 @@
       <x:c r="N44" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O44" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P44" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q44" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R44" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="83" t="str">
@@ -28131,6 +28904,18 @@
       <x:c r="N45" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O45" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P45" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q45" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R45" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="83" t="str">
@@ -28179,6 +28964,18 @@
       <x:c r="N46" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O46" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P46" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q46" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R46" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="83" t="str">
@@ -28227,6 +29024,18 @@
       <x:c r="N47" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O47" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P47" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q47" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R47" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="83" t="str">
@@ -28271,6 +29080,18 @@
       <x:c r="N48" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O48" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P48" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q48" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R48" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="83" t="str">
@@ -28315,6 +29136,18 @@
       <x:c r="N49" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O49" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P49" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q49" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R49" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="83" t="str">
@@ -28359,6 +29192,18 @@
       <x:c r="N50" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O50" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P50" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q50" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R50" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="83" t="str">
@@ -28403,6 +29248,18 @@
       <x:c r="N51" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O51" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P51" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q51" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R51" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="83" t="str">
@@ -28447,6 +29304,18 @@
       <x:c r="N52" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O52" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P52" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q52" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R52" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="83" t="str">
@@ -28491,6 +29360,18 @@
       <x:c r="N53" s="86" t="str">
         <x:v>https://github.com/peterfei/ai-agent-ppt</x:v>
       </x:c>
+      <x:c r="O53" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P53" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q53" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R53" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="83" t="str">
@@ -28533,6 +29414,18 @@
       <x:c r="N54" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O54" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P54" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q54" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R54" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="83" t="str">
@@ -28577,6 +29470,18 @@
       <x:c r="N55" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O55" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P55" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q55" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R55" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="83" t="str">
@@ -28621,6 +29526,18 @@
       <x:c r="N56" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O56" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P56" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q56" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R56" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="83" t="str">
@@ -28665,6 +29582,18 @@
       <x:c r="N57" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O57" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P57" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q57" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R57" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="83" t="str">
@@ -28709,6 +29638,18 @@
       <x:c r="N58" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O58" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P58" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q58" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R58" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="83" t="str">
@@ -28753,6 +29694,18 @@
       <x:c r="N59" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O59" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P59" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q59" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R59" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="83" t="str">
@@ -28797,6 +29750,18 @@
       <x:c r="N60" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O60" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P60" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q60" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R60" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="83" t="str">
@@ -28841,6 +29806,18 @@
       <x:c r="N61" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O61" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P61" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q61" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R61" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="83" t="str">
@@ -28885,6 +29862,18 @@
       <x:c r="N62" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O62" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P62" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q62" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R62" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="83" t="str">
@@ -28929,6 +29918,18 @@
       <x:c r="N63" s="86" t="str">
         <x:v>https://github.com/lijunliu-gh/auto-ppt-engine</x:v>
       </x:c>
+      <x:c r="O63" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P63" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q63" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R63" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="83" t="str">
@@ -28973,6 +29974,18 @@
       <x:c r="N64" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O64" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P64" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q64" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R64" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="83" t="str">
@@ -29017,6 +30030,18 @@
       <x:c r="N65" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O65" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P65" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q65" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R65" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="83" t="str">
@@ -29061,6 +30086,18 @@
       <x:c r="N66" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O66" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P66" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q66" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R66" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="83" t="str">
@@ -29105,6 +30142,18 @@
       <x:c r="N67" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O67" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P67" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q67" s="82" t="str">
+        <x:v>复用P01–P05固定快照、已完成研究与证据</x:v>
+      </x:c>
+      <x:c r="R67" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="83" t="str">
@@ -29147,6 +30196,18 @@
       <x:c r="N68" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O68" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P68" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q68" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R68" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="83" t="str">
@@ -29189,6 +30250,18 @@
       <x:c r="N69" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O69" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P69" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q69" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R69" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="83" t="str">
@@ -29232,6 +30305,18 @@
       <x:c r="N70" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O70" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P70" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q70" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R70" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="83" t="str">
@@ -29275,6 +30360,18 @@
       <x:c r="N71" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O71" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P71" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q71" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R71" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="83" t="str">
@@ -29317,6 +30414,18 @@
       <x:c r="N72" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O72" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P72" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q72" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R72" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="83" t="str">
@@ -29359,6 +30468,18 @@
       <x:c r="N73" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O73" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P73" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q73" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R73" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="83" t="str">
@@ -29401,6 +30522,18 @@
       <x:c r="N74" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O74" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P74" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q74" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R74" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="83" t="str">
@@ -29444,6 +30577,18 @@
       <x:c r="N75" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O75" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P75" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q75" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R75" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="83" t="str">
@@ -29486,6 +30631,18 @@
       <x:c r="N76" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O76" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P76" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q76" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R76" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="83" t="str">
@@ -29528,6 +30685,18 @@
       <x:c r="N77" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O77" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P77" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q77" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R77" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="83" t="str">
@@ -29570,6 +30739,18 @@
       <x:c r="N78" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O78" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P78" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q78" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R78" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="83" t="str">
@@ -29612,6 +30793,18 @@
       <x:c r="N79" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O79" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P79" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q79" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R79" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="83" t="str">
@@ -29654,6 +30847,18 @@
       <x:c r="N80" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O80" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P80" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q80" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R80" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="83" t="str">
@@ -29696,6 +30901,18 @@
       <x:c r="N81" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O81" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P81" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q81" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R81" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="83" t="str">
@@ -29738,6 +30955,18 @@
       <x:c r="N82" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O82" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P82" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q82" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R82" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="83" t="str">
@@ -29781,6 +31010,18 @@
       <x:c r="N83" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O83" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P83" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q83" s="82" t="str">
+        <x:v>Docling；既有SourceLoader/解析库；仅补原能力缺口</x:v>
+      </x:c>
+      <x:c r="R83" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="84">
       <x:c r="A84" s="83" t="str">
@@ -29823,6 +31064,18 @@
       <x:c r="N84" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O84" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P84" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q84" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R84" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="85">
       <x:c r="A85" s="83" t="str">
@@ -29865,6 +31118,18 @@
       <x:c r="N85" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O85" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P85" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q85" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R85" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="86">
       <x:c r="A86" s="83" t="str">
@@ -29907,6 +31172,18 @@
       <x:c r="N86" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O86" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P86" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q86" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R86" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="87">
       <x:c r="A87" s="83" t="str">
@@ -29949,6 +31226,18 @@
       <x:c r="N87" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O87" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P87" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q87" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R87" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="88">
       <x:c r="A88" s="83" t="str">
@@ -29991,6 +31280,18 @@
       <x:c r="N88" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O88" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P88" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q88" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R88" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="89">
       <x:c r="A89" s="83" t="str">
@@ -30033,6 +31334,18 @@
       <x:c r="N89" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O89" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P89" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q89" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R89" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="90">
       <x:c r="A90" s="83" t="str">
@@ -30075,6 +31388,18 @@
       <x:c r="N90" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O90" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P90" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q90" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R90" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="91">
       <x:c r="A91" s="83" t="str">
@@ -30117,6 +31442,18 @@
       <x:c r="N91" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O91" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P91" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q91" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R91" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="92">
       <x:c r="A92" s="83" t="str">
@@ -30159,6 +31496,18 @@
       <x:c r="N92" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O92" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P92" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q92" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R92" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="93">
       <x:c r="A93" s="83" t="str">
@@ -30201,6 +31550,18 @@
       <x:c r="N93" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O93" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P93" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q93" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R93" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="94">
       <x:c r="A94" s="83" t="str">
@@ -30243,6 +31604,18 @@
       <x:c r="N94" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O94" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P94" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q94" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R94" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="95">
       <x:c r="A95" s="83" t="str">
@@ -30285,6 +31658,18 @@
       <x:c r="N95" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O95" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P95" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q95" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R95" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="96">
       <x:c r="A96" s="83" t="str">
@@ -30327,6 +31712,18 @@
       <x:c r="N96" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O96" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P96" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q96" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R96" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="97">
       <x:c r="A97" s="83" t="str">
@@ -30369,6 +31766,18 @@
       <x:c r="N97" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O97" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P97" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q97" s="82" t="str">
+        <x:v>已选项目内容处理模块；既有事实/来源/冲突模块</x:v>
+      </x:c>
+      <x:c r="R97" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="98">
       <x:c r="A98" s="83" t="str">
@@ -30413,6 +31822,18 @@
       <x:c r="N98" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O98" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P98" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q98" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R98" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="99">
       <x:c r="A99" s="83" t="str">
@@ -30457,6 +31878,18 @@
       <x:c r="N99" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O99" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P99" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q99" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R99" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="100">
       <x:c r="A100" s="83" t="str">
@@ -30501,6 +31934,18 @@
       <x:c r="N100" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O100" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P100" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q100" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R100" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="101">
       <x:c r="A101" s="83" t="str">
@@ -30545,6 +31990,18 @@
       <x:c r="N101" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O101" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P101" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q101" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R101" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="102">
       <x:c r="A102" s="83" t="str">
@@ -30589,6 +32046,18 @@
       <x:c r="N102" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O102" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P102" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q102" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R102" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="103">
       <x:c r="A103" s="83" t="str">
@@ -30633,6 +32102,18 @@
       <x:c r="N103" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O103" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P103" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q103" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R103" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="104">
       <x:c r="A104" s="83" t="str">
@@ -30677,6 +32158,18 @@
       <x:c r="N104" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O104" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P104" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q104" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R104" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="105">
       <x:c r="A105" s="83" t="str">
@@ -30721,6 +32214,18 @@
       <x:c r="N105" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O105" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P105" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q105" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R105" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="106">
       <x:c r="A106" s="83" t="str">
@@ -30766,6 +32271,18 @@
       <x:c r="N106" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O106" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P106" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q106" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R106" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="107">
       <x:c r="A107" s="83" t="str">
@@ -30811,6 +32328,18 @@
       <x:c r="N107" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O107" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P107" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q107" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R107" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="108">
       <x:c r="A108" s="83" t="str">
@@ -30855,6 +32384,18 @@
       <x:c r="N108" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O108" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P108" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q108" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R108" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="109">
       <x:c r="A109" s="83" t="str">
@@ -30899,6 +32440,18 @@
       <x:c r="N109" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O109" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P109" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q109" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R109" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="110">
       <x:c r="A110" s="83" t="str">
@@ -30943,6 +32496,18 @@
       <x:c r="N110" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O110" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P110" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q110" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R110" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="111">
       <x:c r="A111" s="83" t="str">
@@ -30987,6 +32552,18 @@
       <x:c r="N111" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O111" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P111" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q111" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R111" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="112">
       <x:c r="A112" s="83" t="str">
@@ -31031,6 +32608,18 @@
       <x:c r="N112" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O112" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P112" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q112" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R112" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="113">
       <x:c r="A113" s="83" t="str">
@@ -31075,6 +32664,18 @@
       <x:c r="N113" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O113" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P113" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q113" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R113" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="114">
       <x:c r="A114" s="83" t="str">
@@ -31119,6 +32720,18 @@
       <x:c r="N114" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O114" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P114" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q114" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R114" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="115">
       <x:c r="A115" s="83" t="str">
@@ -31163,6 +32776,18 @@
       <x:c r="N115" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O115" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P115" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q115" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R115" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="116">
       <x:c r="A116" s="83" t="str">
@@ -31207,6 +32832,18 @@
       <x:c r="N116" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O116" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P116" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q116" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R116" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="117">
       <x:c r="A117" s="83" t="str">
@@ -31251,6 +32888,18 @@
       <x:c r="N117" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O117" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P117" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q117" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R117" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="118">
       <x:c r="A118" s="83" t="str">
@@ -31295,6 +32944,18 @@
       <x:c r="N118" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O118" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P118" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q118" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R118" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="119">
       <x:c r="A119" s="83" t="str">
@@ -31339,6 +33000,18 @@
       <x:c r="N119" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O119" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P119" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q119" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R119" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="120">
       <x:c r="A120" s="83" t="str">
@@ -31383,6 +33056,18 @@
       <x:c r="N120" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O120" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P120" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q120" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R120" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="121">
       <x:c r="A121" s="83" t="str">
@@ -31427,6 +33112,18 @@
       <x:c r="N121" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O121" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P121" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q121" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R121" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="122">
       <x:c r="A122" s="83" t="str">
@@ -31471,6 +33168,18 @@
       <x:c r="N122" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O122" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P122" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q122" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R122" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="123">
       <x:c r="A123" s="83" t="str">
@@ -31515,6 +33224,18 @@
       <x:c r="N123" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O123" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P123" s="82" t="str">
+        <x:v>先调用/复用，再薄适配；有证据缺口才补实现</x:v>
+      </x:c>
+      <x:c r="Q123" s="82" t="str">
+        <x:v>PPT Master/PPTAgent/Presenton决策模块；既有DEC消费者</x:v>
+      </x:c>
+      <x:c r="R123" s="82" t="str">
+        <x:v>EXEC-20261012-01</x:v>
+      </x:c>
     </x:row>
     <x:row r="124">
       <x:c r="A124" s="83" t="str">
@@ -31560,6 +33281,18 @@
       <x:c r="N124" s="86" t="str">
         <x:v>本规划</x:v>
       </x:c>
+      <x:c r="O124" s="82" t="str">
+        <x:v>GPT-6.1 sol</x:v>
+      </x:c>
+      <x:c r="P124" s="82" t="str">
+        <x:v>